--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="228" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,64 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>72.0 → 65.2</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>72.0</t>
-  </si>
-  <si>
-    <t>65.2</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.6% → -3.8%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.6%</t>
-  </si>
-  <si>
-    <t>-3.8%</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>53.7 → 42.1</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>53.7</t>
-  </si>
-  <si>
-    <t>42.1</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -275,7 +218,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -309,13 +252,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -329,7 +265,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -351,12 +287,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -438,23 +368,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -463,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -822,8 +750,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
     <col min="18" max="18" width="8.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
@@ -964,10 +891,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>174</v>
+        <v>174.83</v>
       </c>
       <c r="D2">
-        <v>-1.97</v>
+        <v>0.48</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -976,46 +903,46 @@
         <v>112.72</v>
       </c>
       <c r="G2">
-        <v>-16.49</v>
+        <v>-16.1</v>
       </c>
       <c r="H2">
-        <v>54.36</v>
+        <v>55.1</v>
       </c>
       <c r="I2">
-        <v>-0.32</v>
+        <v>1.6</v>
       </c>
       <c r="J2">
-        <v>10.48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K2">
-        <v>13.48</v>
+        <v>16.06</v>
       </c>
       <c r="L2">
-        <v>45.33</v>
+        <v>46.77</v>
       </c>
       <c r="M2">
-        <v>24.13</v>
+        <v>23.85</v>
       </c>
       <c r="N2">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="P2">
-        <v>175.62</v>
+        <v>176.17</v>
       </c>
       <c r="Q2">
-        <v>161.61</v>
+        <v>162.59</v>
       </c>
       <c r="R2">
-        <v>157.18</v>
+        <v>157.73</v>
       </c>
       <c r="S2">
-        <v>165.87</v>
+        <v>166.08</v>
       </c>
       <c r="T2">
-        <v>4.9</v>
+        <v>5.27</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -1030,34 +957,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>65.25</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="Z2">
-        <v>5.23</v>
+        <v>5.32</v>
       </c>
       <c r="AA2">
-        <v>3.17</v>
+        <v>3.6</v>
       </c>
       <c r="AB2">
-        <v>2.06</v>
+        <v>1.72</v>
       </c>
       <c r="AC2">
-        <v>91.66</v>
+        <v>85.34999999999999</v>
       </c>
       <c r="AD2">
-        <v>94.72</v>
+        <v>91.81999999999999</v>
       </c>
       <c r="AE2">
-        <v>4.49</v>
+        <v>4.48</v>
       </c>
       <c r="AF2">
-        <v>-16.84</v>
+        <v>-5.08</v>
       </c>
       <c r="AG2">
-        <v>181.35</v>
+        <v>182.94</v>
       </c>
       <c r="AH2">
-        <v>141.87</v>
+        <v>142.25</v>
       </c>
       <c r="AI2">
         <v>163.43</v>
@@ -1066,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>47.03</v>
+        <v>45.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1077,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>428.2</v>
+        <v>429.55</v>
       </c>
       <c r="D3">
-        <v>-2.29</v>
+        <v>0.32</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1089,46 +1016,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-3.84</v>
+        <v>-3.54</v>
       </c>
       <c r="H3">
-        <v>90.31</v>
+        <v>90.91</v>
       </c>
       <c r="I3">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="J3">
-        <v>5.39</v>
+        <v>6.6</v>
       </c>
       <c r="K3">
-        <v>39.77</v>
+        <v>40.61</v>
       </c>
       <c r="L3">
-        <v>21.65</v>
+        <v>21.93</v>
       </c>
       <c r="M3">
-        <v>11.2</v>
+        <v>9.869999999999999</v>
       </c>
       <c r="N3">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O3">
         <v>85</v>
       </c>
       <c r="P3">
-        <v>420.2</v>
+        <v>423.78</v>
       </c>
       <c r="Q3">
-        <v>403.43</v>
+        <v>404.74</v>
       </c>
       <c r="R3">
-        <v>405.85</v>
+        <v>406.63</v>
       </c>
       <c r="S3">
-        <v>322.56</v>
+        <v>322.94</v>
       </c>
       <c r="T3">
-        <v>32.75</v>
+        <v>33.01</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1143,34 +1070,34 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>62.25</v>
+        <v>62.79</v>
       </c>
       <c r="Z3">
-        <v>6.43</v>
+        <v>7.36</v>
       </c>
       <c r="AA3">
-        <v>2.87</v>
+        <v>3.77</v>
       </c>
       <c r="AB3">
-        <v>3.56</v>
+        <v>3.59</v>
       </c>
       <c r="AC3">
-        <v>85.84999999999999</v>
+        <v>85.23</v>
       </c>
       <c r="AD3">
-        <v>86.43000000000001</v>
+        <v>86.75</v>
       </c>
       <c r="AE3">
-        <v>14.4</v>
+        <v>14.37</v>
       </c>
       <c r="AF3">
-        <v>-24.31</v>
+        <v>-49.06</v>
       </c>
       <c r="AG3">
-        <v>430.49</v>
+        <v>434.21</v>
       </c>
       <c r="AH3">
-        <v>376.37</v>
+        <v>375.27</v>
       </c>
       <c r="AI3">
         <v>387.9</v>
@@ -1179,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>36.56</v>
+        <v>39.54</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1190,10 +1117,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>412.5</v>
+        <v>411.3</v>
       </c>
       <c r="D4">
-        <v>-3.71</v>
+        <v>-0.29</v>
       </c>
       <c r="E4">
         <v>577.7</v>
@@ -1202,46 +1129,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-28.6</v>
+        <v>-28.8</v>
       </c>
       <c r="H4">
-        <v>19.67</v>
+        <v>19.32</v>
       </c>
       <c r="I4">
-        <v>-4.19</v>
+        <v>-2.41</v>
       </c>
       <c r="J4">
-        <v>-0.18</v>
+        <v>-1.46</v>
       </c>
       <c r="K4">
-        <v>-0.36</v>
+        <v>-0.66</v>
       </c>
       <c r="L4">
-        <v>-29.38</v>
+        <v>-28.43</v>
       </c>
       <c r="M4">
-        <v>-22.21</v>
+        <v>-23.01</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="P4">
-        <v>421.78</v>
+        <v>419.75</v>
       </c>
       <c r="Q4">
-        <v>428</v>
+        <v>425.88</v>
       </c>
       <c r="R4">
-        <v>421.47</v>
+        <v>421.57</v>
       </c>
       <c r="S4">
-        <v>426.05</v>
+        <v>425.65</v>
       </c>
       <c r="T4">
-        <v>-3.18</v>
+        <v>-3.37</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1256,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>42.15</v>
+        <v>41.42</v>
       </c>
       <c r="Z4">
-        <v>-0.16</v>
+        <v>-1.1</v>
       </c>
       <c r="AA4">
-        <v>1.04</v>
+        <v>0.62</v>
       </c>
       <c r="AB4">
-        <v>-1.2</v>
+        <v>-1.71</v>
       </c>
       <c r="AC4">
-        <v>31.25</v>
+        <v>25.41</v>
       </c>
       <c r="AD4">
-        <v>27.81</v>
+        <v>31.8</v>
       </c>
       <c r="AE4">
-        <v>13.15</v>
+        <v>12.79</v>
       </c>
       <c r="AF4">
-        <v>-51.02</v>
+        <v>-86.72</v>
       </c>
       <c r="AG4">
-        <v>446.22</v>
+        <v>441.18</v>
       </c>
       <c r="AH4">
-        <v>409.78</v>
+        <v>410.59</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1292,7 +1219,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>28.57</v>
+        <v>25.65</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1303,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1027.3</v>
+        <v>1008.9</v>
       </c>
       <c r="D5">
-        <v>0.52</v>
+        <v>-1.79</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1315,46 +1242,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-3.93</v>
+        <v>-5.65</v>
       </c>
       <c r="H5">
-        <v>44.13</v>
+        <v>41.55</v>
       </c>
       <c r="I5">
-        <v>-0.16</v>
+        <v>-1.67</v>
       </c>
       <c r="J5">
-        <v>1.13</v>
+        <v>-0.39</v>
       </c>
       <c r="K5">
-        <v>15.06</v>
+        <v>13.04</v>
       </c>
       <c r="L5">
-        <v>27.77</v>
+        <v>23.16</v>
       </c>
       <c r="M5">
-        <v>0.58</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>1022.1</v>
+        <v>1018.68</v>
       </c>
       <c r="Q5">
-        <v>1019.46</v>
+        <v>1020.03</v>
       </c>
       <c r="R5">
-        <v>970.86</v>
+        <v>973.02</v>
       </c>
       <c r="S5">
-        <v>895.55</v>
+        <v>896.8</v>
       </c>
       <c r="T5">
-        <v>14.71</v>
+        <v>12.5</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1369,34 +1296,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>57.56</v>
+        <v>51.21</v>
       </c>
       <c r="Z5">
-        <v>12.77</v>
+        <v>11.04</v>
       </c>
       <c r="AA5">
-        <v>15.52</v>
+        <v>14.63</v>
       </c>
       <c r="AB5">
-        <v>-2.76</v>
+        <v>-3.59</v>
       </c>
       <c r="AC5">
-        <v>24.61</v>
+        <v>21.98</v>
       </c>
       <c r="AD5">
-        <v>23.27</v>
+        <v>22.7</v>
       </c>
       <c r="AE5">
-        <v>22.96</v>
+        <v>22.91</v>
       </c>
       <c r="AF5">
-        <v>-49.13</v>
+        <v>-31.57</v>
       </c>
       <c r="AG5">
-        <v>1058.7</v>
+        <v>1058.24</v>
       </c>
       <c r="AH5">
-        <v>980.21</v>
+        <v>981.83</v>
       </c>
       <c r="AI5">
         <v>1076.68</v>
@@ -1405,7 +1332,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>18.95</v>
+        <v>16.61</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1437,37 +1364,37 @@
         <v>-2.11</v>
       </c>
       <c r="J6">
-        <v>-3.33</v>
+        <v>-2.93</v>
       </c>
       <c r="K6">
-        <v>-13.11</v>
+        <v>-13.43</v>
       </c>
       <c r="L6">
         <v>-33.52</v>
       </c>
       <c r="M6">
-        <v>-3.62</v>
+        <v>-2.63</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="P6">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="Q6">
         <v>2.34</v>
       </c>
       <c r="R6">
-        <v>2.44</v>
+        <v>2.43</v>
       </c>
       <c r="S6">
         <v>2.74</v>
       </c>
       <c r="T6">
-        <v>-15.39</v>
+        <v>-15.24</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1491,19 +1418,19 @@
         <v>-0.03</v>
       </c>
       <c r="AB6">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>55.78</v>
+        <v>59.57</v>
       </c>
       <c r="AD6">
-        <v>69.26000000000001</v>
+        <v>61.54</v>
       </c>
       <c r="AE6">
         <v>0.07000000000000001</v>
       </c>
       <c r="AF6">
-        <v>53.68</v>
+        <v>116.74</v>
       </c>
       <c r="AG6">
         <v>2.41</v>
@@ -1512,13 +1439,13 @@
         <v>2.28</v>
       </c>
       <c r="AI6">
-        <v>2.54</v>
+        <v>2.53</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>24.74</v>
+        <v>26.99</v>
       </c>
     </row>
   </sheetData>
@@ -1659,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1679,777 +1606,668 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
+      <c r="E6" s="4" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>60</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>64</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>10.48</v>
+      </c>
+      <c r="D7" s="5">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.68</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>70</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>72</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>5.39</v>
+      </c>
+      <c r="D8" s="5">
+        <v>6.6</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.21</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-0.18</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-1.46</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.13</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-0.39</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.52</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.33</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-2.93</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>14.38</v>
-      </c>
-      <c r="D9" s="7">
-        <v>10.48</v>
-      </c>
-      <c r="E9" s="8">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-0.32</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.6</v>
+      </c>
+      <c r="E12" s="7">
+        <v>1.92</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>6.89</v>
-      </c>
-      <c r="D10" s="7">
-        <v>5.39</v>
-      </c>
-      <c r="E10" s="8">
-        <v>-1.5</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>2.9</v>
+      </c>
+      <c r="D13" s="5">
+        <v>4.35</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>4.51</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-0.18</v>
-      </c>
-      <c r="E11" s="8">
-        <v>-4.69</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-4.19</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.41</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.78</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>0.67</v>
-      </c>
-      <c r="D12" s="7">
-        <v>1.13</v>
-      </c>
-      <c r="E12" s="9">
-        <v>0.46</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-0.16</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-1.67</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5">
+        <v>45.33</v>
+      </c>
+      <c r="D16" s="5">
+        <v>46.77</v>
+      </c>
+      <c r="E16" s="7">
+        <v>1.44</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>21.65</v>
+      </c>
+      <c r="D17" s="5">
+        <v>21.93</v>
+      </c>
+      <c r="E17" s="7">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-29.38</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-28.43</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>27.77</v>
+      </c>
+      <c r="D19" s="5">
+        <v>23.16</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-4.61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5">
+        <v>13.48</v>
+      </c>
+      <c r="D20" s="5">
+        <v>16.06</v>
+      </c>
+      <c r="E20" s="7">
+        <v>2.58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5">
+        <v>39.77</v>
+      </c>
+      <c r="D21" s="5">
+        <v>40.61</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.84</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-0.36</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-0.66</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>15.06</v>
+      </c>
+      <c r="D23" s="5">
+        <v>13.04</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>-2.93</v>
-      </c>
-      <c r="D13" s="7">
-        <v>-3.33</v>
-      </c>
-      <c r="E13" s="8">
-        <v>-0.4</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-13.11</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-13.43</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.32</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>6.81</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-0.32</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-7.13</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-16.49</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-16.1</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.39</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="D15" s="7">
-        <v>2.9</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-5.97</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-3.84</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-3.54</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.3</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>1.3</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-4.19</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-5.49</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-28.6</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-28.8</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>0.9399999999999999</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-0.16</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-3.93</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-5.65</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-1.72</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5">
+        <v>174</v>
+      </c>
+      <c r="D29" s="5">
+        <v>174.83</v>
+      </c>
+      <c r="E29" s="7">
+        <v>0.83</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5">
+        <v>428.2</v>
+      </c>
+      <c r="D30" s="5">
+        <v>429.55</v>
+      </c>
+      <c r="E30" s="7">
+        <v>1.35</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5">
+        <v>412.5</v>
+      </c>
+      <c r="D31" s="5">
+        <v>411.3</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.2</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>1027.3</v>
+      </c>
+      <c r="D32" s="5">
+        <v>1008.9</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-18.4</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C33" s="5">
+        <v>79</v>
+      </c>
+      <c r="D33" s="5">
+        <v>99</v>
+      </c>
+      <c r="E33" s="7">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="C34" s="5">
+        <v>99</v>
+      </c>
+      <c r="D34" s="5">
+        <v>79</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="5">
+        <v>65.25</v>
+      </c>
+      <c r="D35" s="5">
+        <v>66.06999999999999</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.82</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C36" s="5">
+        <v>62.25</v>
+      </c>
+      <c r="D36" s="5">
+        <v>62.79</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.54</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>42.15</v>
+      </c>
+      <c r="D37" s="5">
+        <v>41.42</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-0.73</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>57.56</v>
+      </c>
+      <c r="D38" s="5">
+        <v>51.21</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-6.35</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="5">
+        <v>-16.84</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-5.08</v>
+      </c>
+      <c r="E39" s="7">
+        <v>11.76</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C40" s="5">
+        <v>-24.31</v>
+      </c>
+      <c r="D40" s="5">
+        <v>-49.06</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-24.75</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C41" s="5">
+        <v>-51.02</v>
+      </c>
+      <c r="D41" s="5">
+        <v>-86.72</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-35.7</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-49.13</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-31.57</v>
+      </c>
+      <c r="E42" s="7">
+        <v>17.56</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>-1.69</v>
-      </c>
-      <c r="D18" s="7">
-        <v>-2.11</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.42</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7">
-        <v>51.03</v>
-      </c>
-      <c r="D19" s="7">
-        <v>45.33</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-5.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>25.14</v>
-      </c>
-      <c r="D20" s="7">
-        <v>21.65</v>
-      </c>
-      <c r="E20" s="8">
-        <v>-3.49</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-24.93</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-29.38</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-4.45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>30.41</v>
-      </c>
-      <c r="D22" s="7">
-        <v>27.77</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-2.64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-34.83</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-33.52</v>
-      </c>
-      <c r="E23" s="9">
-        <v>1.31</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
-        <v>11.77</v>
-      </c>
-      <c r="D24" s="7">
-        <v>13.48</v>
-      </c>
-      <c r="E24" s="9">
-        <v>1.71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>38.23</v>
-      </c>
-      <c r="D25" s="7">
-        <v>39.77</v>
-      </c>
-      <c r="E25" s="9">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>0.59</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-0.36</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-0.95</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>10.81</v>
-      </c>
-      <c r="D27" s="7">
-        <v>15.06</v>
-      </c>
-      <c r="E27" s="9">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-16.85</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-13.11</v>
-      </c>
-      <c r="E28" s="9">
-        <v>3.74</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-14.81</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-16.49</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-1.68</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-1.58</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-3.84</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-2.26</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-26.66</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-28.6</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.94</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-4.42</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-3.93</v>
-      </c>
-      <c r="E32" s="9">
-        <v>0.49</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="7">
-        <v>177.5</v>
-      </c>
-      <c r="D33" s="7">
-        <v>174</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-3.5</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="7">
-        <v>438.25</v>
-      </c>
-      <c r="D34" s="7">
-        <v>428.2</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-10.05</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="7">
-        <v>428.4</v>
-      </c>
-      <c r="D35" s="7">
-        <v>412.5</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-15.9</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="7">
-        <v>1022</v>
-      </c>
-      <c r="D36" s="7">
-        <v>1027.3</v>
-      </c>
-      <c r="E36" s="9">
-        <v>5.3</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="7">
-        <v>99</v>
-      </c>
-      <c r="D37" s="7">
-        <v>79</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-20</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="7">
-        <v>79</v>
-      </c>
-      <c r="D38" s="7">
-        <v>99</v>
-      </c>
-      <c r="E38" s="9">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="7">
-        <v>72.03</v>
-      </c>
-      <c r="D39" s="7">
-        <v>65.25</v>
-      </c>
-      <c r="E39" s="8">
-        <v>-6.78</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="7">
-        <v>69.08</v>
-      </c>
-      <c r="D40" s="7">
-        <v>62.25</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-6.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="7">
-        <v>53.67</v>
-      </c>
-      <c r="D41" s="7">
-        <v>42.15</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-11.52</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="7">
-        <v>56.11</v>
-      </c>
-      <c r="D42" s="7">
-        <v>57.56</v>
-      </c>
-      <c r="E42" s="9">
-        <v>1.45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="B43" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="7">
-        <v>-36.52</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-16.84</v>
-      </c>
-      <c r="E43" s="9">
-        <v>19.68</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="7">
-        <v>3685.58</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-24.31</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-3709.89</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-52.56</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-51.02</v>
-      </c>
-      <c r="E45" s="9">
-        <v>1.54</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-16.14</v>
-      </c>
-      <c r="D46" s="7">
-        <v>-49.13</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-32.99</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-21.17</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C43" s="5">
         <v>53.68</v>
       </c>
-      <c r="E47" s="9">
-        <v>74.84999999999999</v>
+      <c r="D43" s="5">
+        <v>116.74</v>
+      </c>
+      <c r="E43" s="7">
+        <v>63.06</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2469,60 +2287,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>73</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>75</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>76</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>77</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>78</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>79</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>80</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
-        <v>53.8</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>52.7</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>2.7</v>
-      </c>
-      <c r="G2" s="12">
-        <v>11</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>2.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>11.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2624,37 +2442,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15">
-        <v>0.2413</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.112</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.0058</v>
-      </c>
-      <c r="D2" s="15">
-        <v>-0.0362</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.2221</v>
+      <c r="A2" s="13">
+        <v>0.2385</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0987</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0007000000000000001</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0263</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2301</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -252,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -891,10 +891,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>174.83</v>
+        <v>176.7</v>
       </c>
       <c r="D2">
-        <v>0.48</v>
+        <v>1.07</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -903,46 +903,46 @@
         <v>112.72</v>
       </c>
       <c r="G2">
-        <v>-16.1</v>
+        <v>-15.2</v>
       </c>
       <c r="H2">
-        <v>55.1</v>
+        <v>56.76</v>
       </c>
       <c r="I2">
-        <v>1.6</v>
+        <v>-0.17</v>
       </c>
       <c r="J2">
-        <v>9.800000000000001</v>
+        <v>13.86</v>
       </c>
       <c r="K2">
-        <v>16.06</v>
+        <v>16.44</v>
       </c>
       <c r="L2">
-        <v>46.77</v>
+        <v>49.86</v>
       </c>
       <c r="M2">
-        <v>23.85</v>
+        <v>24.1</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P2">
-        <v>176.17</v>
+        <v>176.11</v>
       </c>
       <c r="Q2">
-        <v>162.59</v>
+        <v>163.6</v>
       </c>
       <c r="R2">
-        <v>157.73</v>
+        <v>158.33</v>
       </c>
       <c r="S2">
-        <v>166.08</v>
+        <v>166.29</v>
       </c>
       <c r="T2">
-        <v>5.27</v>
+        <v>6.26</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -957,34 +957,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>66.06999999999999</v>
+        <v>67.89</v>
       </c>
       <c r="Z2">
-        <v>5.32</v>
+        <v>5.47</v>
       </c>
       <c r="AA2">
-        <v>3.6</v>
+        <v>3.97</v>
       </c>
       <c r="AB2">
-        <v>1.72</v>
+        <v>1.5</v>
       </c>
       <c r="AC2">
-        <v>85.34999999999999</v>
+        <v>80.84</v>
       </c>
       <c r="AD2">
-        <v>91.81999999999999</v>
+        <v>85.95</v>
       </c>
       <c r="AE2">
-        <v>4.48</v>
+        <v>4.37</v>
       </c>
       <c r="AF2">
-        <v>-5.08</v>
+        <v>-38.71</v>
       </c>
       <c r="AG2">
-        <v>182.94</v>
+        <v>184.67</v>
       </c>
       <c r="AH2">
-        <v>142.25</v>
+        <v>142.53</v>
       </c>
       <c r="AI2">
         <v>163.43</v>
@@ -993,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>45.26</v>
+        <v>44.37</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>429.55</v>
+        <v>431.8</v>
       </c>
       <c r="D3">
-        <v>0.32</v>
+        <v>0.52</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1016,46 +1016,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-3.54</v>
+        <v>-3.03</v>
       </c>
       <c r="H3">
-        <v>90.91</v>
+        <v>91.91</v>
       </c>
       <c r="I3">
-        <v>4.35</v>
+        <v>4.72</v>
       </c>
       <c r="J3">
-        <v>6.6</v>
+        <v>7.04</v>
       </c>
       <c r="K3">
-        <v>40.61</v>
+        <v>43.17</v>
       </c>
       <c r="L3">
-        <v>21.93</v>
+        <v>26.15</v>
       </c>
       <c r="M3">
-        <v>9.869999999999999</v>
+        <v>8.69</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P3">
-        <v>423.78</v>
+        <v>427.67</v>
       </c>
       <c r="Q3">
-        <v>404.74</v>
+        <v>406.17</v>
       </c>
       <c r="R3">
-        <v>406.63</v>
+        <v>407.25</v>
       </c>
       <c r="S3">
-        <v>322.94</v>
+        <v>323.35</v>
       </c>
       <c r="T3">
-        <v>33.01</v>
+        <v>33.54</v>
       </c>
       <c r="U3" t="s">
         <v>44</v>
@@ -1070,43 +1070,43 @@
         <v>2</v>
       </c>
       <c r="Y3">
-        <v>62.79</v>
+        <v>63.7</v>
       </c>
       <c r="Z3">
-        <v>7.36</v>
+        <v>8.19</v>
       </c>
       <c r="AA3">
-        <v>3.77</v>
+        <v>4.65</v>
       </c>
       <c r="AB3">
-        <v>3.59</v>
+        <v>3.54</v>
       </c>
       <c r="AC3">
-        <v>85.23</v>
+        <v>79.18000000000001</v>
       </c>
       <c r="AD3">
-        <v>86.75</v>
+        <v>83.42</v>
       </c>
       <c r="AE3">
-        <v>14.37</v>
+        <v>14.68</v>
       </c>
       <c r="AF3">
-        <v>-49.06</v>
+        <v>3.4</v>
       </c>
       <c r="AG3">
-        <v>434.21</v>
+        <v>438.01</v>
       </c>
       <c r="AH3">
-        <v>375.27</v>
+        <v>374.33</v>
       </c>
       <c r="AI3">
-        <v>387.9</v>
+        <v>390.52</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>39.54</v>
+        <v>43.09</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,37 +1117,37 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>411.3</v>
+        <v>406.75</v>
       </c>
       <c r="D4">
-        <v>-0.29</v>
+        <v>-1.11</v>
       </c>
       <c r="E4">
-        <v>577.7</v>
+        <v>547.1</v>
       </c>
       <c r="F4">
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-28.8</v>
+        <v>-25.65</v>
       </c>
       <c r="H4">
-        <v>19.32</v>
+        <v>18</v>
       </c>
       <c r="I4">
-        <v>-2.41</v>
+        <v>-3.96</v>
       </c>
       <c r="J4">
-        <v>-1.46</v>
+        <v>-10.33</v>
       </c>
       <c r="K4">
-        <v>-0.66</v>
+        <v>-1.5</v>
       </c>
       <c r="L4">
-        <v>-28.43</v>
+        <v>-29.59</v>
       </c>
       <c r="M4">
-        <v>-23.01</v>
+        <v>-23.61</v>
       </c>
       <c r="N4">
         <v>40</v>
@@ -1156,19 +1156,19 @@
         <v>24</v>
       </c>
       <c r="P4">
-        <v>419.75</v>
+        <v>416.4</v>
       </c>
       <c r="Q4">
-        <v>425.88</v>
+        <v>423.93</v>
       </c>
       <c r="R4">
-        <v>421.57</v>
+        <v>421.64</v>
       </c>
       <c r="S4">
-        <v>425.65</v>
+        <v>425.18</v>
       </c>
       <c r="T4">
-        <v>-3.37</v>
+        <v>-4.33</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1183,34 +1183,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>41.42</v>
+        <v>38.71</v>
       </c>
       <c r="Z4">
-        <v>-1.1</v>
+        <v>-2.18</v>
       </c>
       <c r="AA4">
-        <v>0.62</v>
+        <v>0.06</v>
       </c>
       <c r="AB4">
-        <v>-1.71</v>
+        <v>-2.24</v>
       </c>
       <c r="AC4">
-        <v>25.41</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>31.8</v>
+        <v>18.89</v>
       </c>
       <c r="AE4">
-        <v>12.79</v>
+        <v>12.54</v>
       </c>
       <c r="AF4">
-        <v>-86.72</v>
+        <v>-83.25</v>
       </c>
       <c r="AG4">
-        <v>441.18</v>
+        <v>438.47</v>
       </c>
       <c r="AH4">
-        <v>410.59</v>
+        <v>409.39</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1219,7 +1219,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>25.65</v>
+        <v>22.82</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1008.9</v>
+        <v>1017.5</v>
       </c>
       <c r="D5">
-        <v>-1.79</v>
+        <v>0.85</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1242,46 +1242,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-5.65</v>
+        <v>-4.84</v>
       </c>
       <c r="H5">
-        <v>41.55</v>
+        <v>42.76</v>
       </c>
       <c r="I5">
-        <v>-1.67</v>
+        <v>-0.15</v>
       </c>
       <c r="J5">
-        <v>-0.39</v>
+        <v>2.02</v>
       </c>
       <c r="K5">
-        <v>13.04</v>
+        <v>12.07</v>
       </c>
       <c r="L5">
-        <v>23.16</v>
+        <v>26.66</v>
       </c>
       <c r="M5">
-        <v>0.07000000000000001</v>
+        <v>0.35</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>1018.68</v>
+        <v>1018.38</v>
       </c>
       <c r="Q5">
-        <v>1020.03</v>
+        <v>1020.42</v>
       </c>
       <c r="R5">
-        <v>973.02</v>
+        <v>975.12</v>
       </c>
       <c r="S5">
-        <v>896.8</v>
+        <v>898.09</v>
       </c>
       <c r="T5">
-        <v>12.5</v>
+        <v>13.3</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1296,34 +1296,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>51.21</v>
+        <v>53.78</v>
       </c>
       <c r="Z5">
-        <v>11.04</v>
+        <v>10.24</v>
       </c>
       <c r="AA5">
-        <v>14.63</v>
+        <v>13.75</v>
       </c>
       <c r="AB5">
-        <v>-3.59</v>
+        <v>-3.51</v>
       </c>
       <c r="AC5">
-        <v>21.98</v>
+        <v>27.6</v>
       </c>
       <c r="AD5">
-        <v>22.7</v>
+        <v>24.73</v>
       </c>
       <c r="AE5">
-        <v>22.91</v>
+        <v>22.43</v>
       </c>
       <c r="AF5">
-        <v>-31.57</v>
+        <v>-55.86</v>
       </c>
       <c r="AG5">
-        <v>1058.24</v>
+        <v>1058.34</v>
       </c>
       <c r="AH5">
-        <v>981.83</v>
+        <v>982.5</v>
       </c>
       <c r="AI5">
         <v>1076.68</v>
@@ -1332,7 +1332,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>16.61</v>
+        <v>14.58</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1343,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>0.86</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1355,34 +1355,34 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-35.91</v>
+        <v>-35.36</v>
       </c>
       <c r="H6">
-        <v>26.09</v>
+        <v>27.17</v>
       </c>
       <c r="I6">
-        <v>-2.11</v>
+        <v>-1.27</v>
       </c>
       <c r="J6">
-        <v>-2.93</v>
+        <v>-0.85</v>
       </c>
       <c r="K6">
-        <v>-13.43</v>
+        <v>-13.65</v>
       </c>
       <c r="L6">
-        <v>-33.52</v>
+        <v>-32.76</v>
       </c>
       <c r="M6">
-        <v>-2.63</v>
+        <v>-2.6</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="P6">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="Q6">
         <v>2.34</v>
@@ -1391,10 +1391,10 @@
         <v>2.43</v>
       </c>
       <c r="S6">
-        <v>2.74</v>
+        <v>2.73</v>
       </c>
       <c r="T6">
-        <v>-15.24</v>
+        <v>-14.35</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1409,7 +1409,7 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>41.79</v>
+        <v>45.51</v>
       </c>
       <c r="Z6">
         <v>-0.03</v>
@@ -1418,22 +1418,22 @@
         <v>-0.03</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>59.57</v>
+        <v>68.19</v>
       </c>
       <c r="AD6">
-        <v>61.54</v>
+        <v>61.18</v>
       </c>
       <c r="AE6">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="AF6">
-        <v>116.74</v>
+        <v>2.13</v>
       </c>
       <c r="AG6">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
         <v>2.28</v>
@@ -1445,7 +1445,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>26.99</v>
+        <v>24.71</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1643,13 +1643,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>10.48</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="D7" s="5">
-        <v>9.800000000000001</v>
+        <v>13.86</v>
       </c>
       <c r="E7" s="6">
-        <v>-0.68</v>
+        <v>4.06</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1660,13 +1660,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>5.39</v>
+        <v>6.6</v>
       </c>
       <c r="D8" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.21</v>
+        <v>7.04</v>
+      </c>
+      <c r="E8" s="6">
+        <v>0.44</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1677,13 +1677,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-0.18</v>
+        <v>-1.46</v>
       </c>
       <c r="D9" s="5">
-        <v>-1.46</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-1.28</v>
+        <v>-10.33</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-8.869999999999999</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1694,13 +1694,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>1.13</v>
+        <v>-0.39</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.39</v>
+        <v>2.02</v>
       </c>
       <c r="E10" s="6">
-        <v>-1.52</v>
+        <v>2.41</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1711,13 +1711,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.33</v>
+        <v>-2.93</v>
       </c>
       <c r="D11" s="5">
-        <v>-2.93</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.4</v>
+        <v>-0.85</v>
+      </c>
+      <c r="E11" s="6">
+        <v>2.08</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1728,13 +1728,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-0.32</v>
+        <v>1.6</v>
       </c>
       <c r="D12" s="5">
-        <v>1.6</v>
+        <v>-0.17</v>
       </c>
       <c r="E12" s="7">
-        <v>1.92</v>
+        <v>-1.77</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1745,13 +1745,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>2.9</v>
+        <v>4.35</v>
       </c>
       <c r="D13" s="5">
-        <v>4.35</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.45</v>
+        <v>4.72</v>
+      </c>
+      <c r="E13" s="6">
+        <v>0.37</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1762,13 +1762,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-4.19</v>
+        <v>-2.41</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.41</v>
+        <v>-3.96</v>
       </c>
       <c r="E14" s="7">
-        <v>1.78</v>
+        <v>-1.55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1779,489 +1779,540 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-0.16</v>
+        <v>-1.67</v>
       </c>
       <c r="D15" s="5">
-        <v>-1.67</v>
+        <v>-0.15</v>
       </c>
       <c r="E15" s="6">
-        <v>-1.51</v>
+        <v>1.52</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>45.33</v>
+        <v>-2.11</v>
       </c>
       <c r="D16" s="5">
-        <v>46.77</v>
-      </c>
-      <c r="E16" s="7">
-        <v>1.44</v>
+        <v>-1.27</v>
+      </c>
+      <c r="E16" s="6">
+        <v>0.84</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>21.65</v>
+        <v>46.77</v>
       </c>
       <c r="D17" s="5">
-        <v>21.93</v>
-      </c>
-      <c r="E17" s="7">
-        <v>0.28</v>
+        <v>49.86</v>
+      </c>
+      <c r="E17" s="6">
+        <v>3.09</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-29.38</v>
+        <v>21.93</v>
       </c>
       <c r="D18" s="5">
-        <v>-28.43</v>
-      </c>
-      <c r="E18" s="7">
-        <v>0.95</v>
+        <v>26.15</v>
+      </c>
+      <c r="E18" s="6">
+        <v>4.22</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>27.77</v>
+        <v>-28.43</v>
       </c>
       <c r="D19" s="5">
-        <v>23.16</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-4.61</v>
+        <v>-29.59</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.16</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>13.48</v>
+        <v>23.16</v>
       </c>
       <c r="D20" s="5">
-        <v>16.06</v>
-      </c>
-      <c r="E20" s="7">
-        <v>2.58</v>
+        <v>26.66</v>
+      </c>
+      <c r="E20" s="6">
+        <v>3.5</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>39.77</v>
+        <v>-33.52</v>
       </c>
       <c r="D21" s="5">
-        <v>40.61</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.84</v>
+        <v>-32.76</v>
+      </c>
+      <c r="E21" s="6">
+        <v>0.76</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>-0.36</v>
+        <v>16.06</v>
       </c>
       <c r="D22" s="5">
-        <v>-0.66</v>
+        <v>16.44</v>
       </c>
       <c r="E22" s="6">
-        <v>-0.3</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>15.06</v>
+        <v>40.61</v>
       </c>
       <c r="D23" s="5">
-        <v>13.04</v>
+        <v>43.17</v>
       </c>
       <c r="E23" s="6">
-        <v>-2.02</v>
+        <v>2.56</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-13.11</v>
+        <v>-0.66</v>
       </c>
       <c r="D24" s="5">
-        <v>-13.43</v>
-      </c>
-      <c r="E24" s="6">
-        <v>-0.32</v>
+        <v>-1.5</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-16.49</v>
+        <v>13.04</v>
       </c>
       <c r="D25" s="5">
-        <v>-16.1</v>
+        <v>12.07</v>
       </c>
       <c r="E25" s="7">
-        <v>0.39</v>
+        <v>-0.97</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-3.84</v>
+        <v>-13.43</v>
       </c>
       <c r="D26" s="5">
-        <v>-3.54</v>
+        <v>-13.65</v>
       </c>
       <c r="E26" s="7">
-        <v>0.3</v>
+        <v>-0.22</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-28.6</v>
+        <v>-16.1</v>
       </c>
       <c r="D27" s="5">
-        <v>-28.8</v>
+        <v>-15.2</v>
       </c>
       <c r="E27" s="6">
-        <v>-0.2</v>
+        <v>0.9</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-3.93</v>
+        <v>-3.54</v>
       </c>
       <c r="D28" s="5">
-        <v>-5.65</v>
+        <v>-3.03</v>
       </c>
       <c r="E28" s="6">
-        <v>-1.72</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>174</v>
+        <v>-28.8</v>
       </c>
       <c r="D29" s="5">
-        <v>174.83</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.83</v>
+        <v>-25.65</v>
+      </c>
+      <c r="E29" s="6">
+        <v>3.15</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>428.2</v>
+        <v>-5.65</v>
       </c>
       <c r="D30" s="5">
-        <v>429.55</v>
-      </c>
-      <c r="E30" s="7">
-        <v>1.35</v>
+        <v>-4.84</v>
+      </c>
+      <c r="E30" s="6">
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>412.5</v>
+        <v>-35.91</v>
       </c>
       <c r="D31" s="5">
-        <v>411.3</v>
+        <v>-35.36</v>
       </c>
       <c r="E31" s="6">
-        <v>-1.2</v>
+        <v>0.55</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>1027.3</v>
+        <v>174.83</v>
       </c>
       <c r="D32" s="5">
-        <v>1008.9</v>
+        <v>176.7</v>
       </c>
       <c r="E32" s="6">
-        <v>-18.4</v>
+        <v>1.87</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>79</v>
+        <v>429.55</v>
       </c>
       <c r="D33" s="5">
-        <v>99</v>
-      </c>
-      <c r="E33" s="7">
-        <v>20</v>
+        <v>431.8</v>
+      </c>
+      <c r="E33" s="6">
+        <v>2.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>13</v>
+        <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>99</v>
+        <v>411.3</v>
       </c>
       <c r="D34" s="5">
-        <v>79</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-20</v>
+        <v>406.75</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-4.55</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>65.25</v>
+        <v>1008.9</v>
       </c>
       <c r="D35" s="5">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.82</v>
+        <v>1017.5</v>
+      </c>
+      <c r="E35" s="6">
+        <v>8.6</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>62.25</v>
+        <v>2.32</v>
       </c>
       <c r="D36" s="5">
-        <v>62.79</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.54</v>
+        <v>2.34</v>
+      </c>
+      <c r="E36" s="6">
+        <v>0.02</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>42.15</v>
+        <v>66.06999999999999</v>
       </c>
       <c r="D37" s="5">
-        <v>41.42</v>
+        <v>67.89</v>
       </c>
       <c r="E37" s="6">
-        <v>-0.73</v>
+        <v>1.82</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>57.56</v>
+        <v>62.79</v>
       </c>
       <c r="D38" s="5">
-        <v>51.21</v>
+        <v>63.7</v>
       </c>
       <c r="E38" s="6">
-        <v>-6.35</v>
+        <v>0.91</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>-16.84</v>
+        <v>41.42</v>
       </c>
       <c r="D39" s="5">
-        <v>-5.08</v>
+        <v>38.71</v>
       </c>
       <c r="E39" s="7">
-        <v>11.76</v>
+        <v>-2.71</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>-24.31</v>
+        <v>51.21</v>
       </c>
       <c r="D40" s="5">
-        <v>-49.06</v>
+        <v>53.78</v>
       </c>
       <c r="E40" s="6">
-        <v>-24.75</v>
+        <v>2.57</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>-51.02</v>
+        <v>41.79</v>
       </c>
       <c r="D41" s="5">
-        <v>-86.72</v>
+        <v>45.51</v>
       </c>
       <c r="E41" s="6">
-        <v>-35.7</v>
+        <v>3.72</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-49.13</v>
+        <v>-5.08</v>
       </c>
       <c r="D42" s="5">
-        <v>-31.57</v>
+        <v>-38.71</v>
       </c>
       <c r="E42" s="7">
-        <v>17.56</v>
+        <v>-33.63</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>53.68</v>
+        <v>-49.06</v>
       </c>
       <c r="D43" s="5">
+        <v>3.4</v>
+      </c>
+      <c r="E43" s="6">
+        <v>52.46</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-86.72</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-83.25</v>
+      </c>
+      <c r="E44" s="6">
+        <v>3.47</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-31.57</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-55.86</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-24.29</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
         <v>116.74</v>
       </c>
-      <c r="E43" s="7">
-        <v>63.06</v>
+      <c r="D46" s="5">
+        <v>2.13</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-114.61</v>
       </c>
     </row>
   </sheetData>
@@ -2326,7 +2377,7 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>52.7</v>
+        <v>53.9</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
@@ -2335,7 +2386,7 @@
         <v>2.3</v>
       </c>
       <c r="G2" s="10">
-        <v>11.1</v>
+        <v>11.3</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2460,19 +2511,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.2385</v>
+        <v>0.241</v>
       </c>
       <c r="B2" s="13">
-        <v>0.0987</v>
+        <v>0.08689999999999999</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0007000000000000001</v>
+        <v>0.0035</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.0263</v>
+        <v>-0.026</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2301</v>
+        <v>-0.2361</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,28 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -368,17 +389,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -891,10 +913,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>176.7</v>
+        <v>176.23</v>
       </c>
       <c r="D2">
-        <v>1.07</v>
+        <v>-0.27</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -903,46 +925,46 @@
         <v>112.72</v>
       </c>
       <c r="G2">
-        <v>-15.2</v>
+        <v>-15.42</v>
       </c>
       <c r="H2">
-        <v>56.76</v>
+        <v>56.34</v>
       </c>
       <c r="I2">
-        <v>-0.17</v>
+        <v>-0.72</v>
       </c>
       <c r="J2">
-        <v>13.86</v>
+        <v>12.59</v>
       </c>
       <c r="K2">
-        <v>16.44</v>
+        <v>17.05</v>
       </c>
       <c r="L2">
-        <v>49.86</v>
+        <v>50.61</v>
       </c>
       <c r="M2">
-        <v>24.1</v>
+        <v>24.65</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P2">
-        <v>176.11</v>
+        <v>175.85</v>
       </c>
       <c r="Q2">
-        <v>163.6</v>
+        <v>164.67</v>
       </c>
       <c r="R2">
-        <v>158.33</v>
+        <v>158.94</v>
       </c>
       <c r="S2">
-        <v>166.29</v>
+        <v>166.51</v>
       </c>
       <c r="T2">
-        <v>6.26</v>
+        <v>5.84</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -957,43 +979,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>67.89</v>
+        <v>66.92</v>
       </c>
       <c r="Z2">
-        <v>5.47</v>
+        <v>5.49</v>
       </c>
       <c r="AA2">
-        <v>3.97</v>
+        <v>4.28</v>
       </c>
       <c r="AB2">
-        <v>1.5</v>
+        <v>1.21</v>
       </c>
       <c r="AC2">
-        <v>80.84</v>
+        <v>80.54000000000001</v>
       </c>
       <c r="AD2">
-        <v>85.95</v>
+        <v>82.23999999999999</v>
       </c>
       <c r="AE2">
-        <v>4.37</v>
+        <v>4.52</v>
       </c>
       <c r="AF2">
-        <v>-38.71</v>
+        <v>70.31</v>
       </c>
       <c r="AG2">
-        <v>184.67</v>
+        <v>186.03</v>
       </c>
       <c r="AH2">
-        <v>142.53</v>
+        <v>143.3</v>
       </c>
       <c r="AI2">
-        <v>163.43</v>
+        <v>165.9</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>44.37</v>
+        <v>46.04</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1026,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>431.8</v>
+        <v>430.9</v>
       </c>
       <c r="D3">
-        <v>0.52</v>
+        <v>-0.21</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1016,25 +1038,25 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-3.03</v>
+        <v>-3.23</v>
       </c>
       <c r="H3">
-        <v>91.91</v>
+        <v>91.51000000000001</v>
       </c>
       <c r="I3">
-        <v>4.72</v>
+        <v>4.96</v>
       </c>
       <c r="J3">
-        <v>7.04</v>
+        <v>6.86</v>
       </c>
       <c r="K3">
-        <v>43.17</v>
+        <v>43.39</v>
       </c>
       <c r="L3">
-        <v>26.15</v>
+        <v>26.74</v>
       </c>
       <c r="M3">
-        <v>8.69</v>
+        <v>10.65</v>
       </c>
       <c r="N3">
         <v>79</v>
@@ -1043,70 +1065,70 @@
         <v>86</v>
       </c>
       <c r="P3">
-        <v>427.67</v>
+        <v>431.74</v>
       </c>
       <c r="Q3">
-        <v>406.17</v>
+        <v>407.56</v>
       </c>
       <c r="R3">
-        <v>407.25</v>
+        <v>407.5</v>
       </c>
       <c r="S3">
-        <v>323.35</v>
+        <v>323.74</v>
       </c>
       <c r="T3">
-        <v>33.54</v>
+        <v>33.1</v>
       </c>
       <c r="U3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V3" t="s">
         <v>43</v>
       </c>
       <c r="W3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="X3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="Y3">
-        <v>63.7</v>
+        <v>63.03</v>
       </c>
       <c r="Z3">
-        <v>8.19</v>
+        <v>8.67</v>
       </c>
       <c r="AA3">
-        <v>4.65</v>
+        <v>5.46</v>
       </c>
       <c r="AB3">
-        <v>3.54</v>
+        <v>3.22</v>
       </c>
       <c r="AC3">
-        <v>79.18000000000001</v>
+        <v>80.06</v>
       </c>
       <c r="AD3">
-        <v>83.42</v>
+        <v>81.48999999999999</v>
       </c>
       <c r="AE3">
-        <v>14.68</v>
+        <v>14.54</v>
       </c>
       <c r="AF3">
-        <v>3.4</v>
+        <v>-71.22</v>
       </c>
       <c r="AG3">
-        <v>438.01</v>
+        <v>441.21</v>
       </c>
       <c r="AH3">
-        <v>374.33</v>
+        <v>373.92</v>
       </c>
       <c r="AI3">
-        <v>390.52</v>
+        <v>392.36</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>43.09</v>
+        <v>46.16</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,10 +1139,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>406.75</v>
+        <v>404.7</v>
       </c>
       <c r="D4">
-        <v>-1.11</v>
+        <v>-0.5</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1129,46 +1151,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-25.65</v>
+        <v>-26.03</v>
       </c>
       <c r="H4">
-        <v>18</v>
+        <v>17.41</v>
       </c>
       <c r="I4">
-        <v>-3.96</v>
+        <v>-4.34</v>
       </c>
       <c r="J4">
-        <v>-10.33</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="K4">
-        <v>-1.5</v>
+        <v>-0.55</v>
       </c>
       <c r="L4">
-        <v>-29.59</v>
+        <v>-25.16</v>
       </c>
       <c r="M4">
-        <v>-23.61</v>
+        <v>-22.9</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>416.4</v>
+        <v>412.73</v>
       </c>
       <c r="Q4">
-        <v>423.93</v>
+        <v>422.31</v>
       </c>
       <c r="R4">
         <v>421.64</v>
       </c>
       <c r="S4">
-        <v>425.18</v>
+        <v>424.6</v>
       </c>
       <c r="T4">
-        <v>-4.33</v>
+        <v>-4.69</v>
       </c>
       <c r="U4" t="s">
         <v>43</v>
@@ -1183,34 +1205,34 @@
         <v>1</v>
       </c>
       <c r="Y4">
-        <v>38.71</v>
+        <v>37.52</v>
       </c>
       <c r="Z4">
-        <v>-2.18</v>
+        <v>-3.17</v>
       </c>
       <c r="AA4">
-        <v>0.06</v>
+        <v>-0.59</v>
       </c>
       <c r="AB4">
-        <v>-2.24</v>
+        <v>-2.58</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>18.89</v>
+        <v>8.470000000000001</v>
       </c>
       <c r="AE4">
-        <v>12.54</v>
+        <v>12.11</v>
       </c>
       <c r="AF4">
-        <v>-83.25</v>
+        <v>-74.69</v>
       </c>
       <c r="AG4">
-        <v>438.47</v>
+        <v>437.85</v>
       </c>
       <c r="AH4">
-        <v>409.39</v>
+        <v>406.77</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1219,7 +1241,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>22.82</v>
+        <v>21.06</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1252,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1017.5</v>
+        <v>1024.7</v>
       </c>
       <c r="D5">
-        <v>0.85</v>
+        <v>0.71</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1242,46 +1264,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-4.84</v>
+        <v>-4.17</v>
       </c>
       <c r="H5">
-        <v>42.76</v>
+        <v>43.77</v>
       </c>
       <c r="I5">
-        <v>-0.15</v>
+        <v>0.84</v>
       </c>
       <c r="J5">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="K5">
-        <v>12.07</v>
+        <v>15.6</v>
       </c>
       <c r="L5">
-        <v>26.66</v>
+        <v>26.92</v>
       </c>
       <c r="M5">
-        <v>0.35</v>
+        <v>0.71</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1018.38</v>
+        <v>1020.08</v>
       </c>
       <c r="Q5">
-        <v>1020.42</v>
+        <v>1020.98</v>
       </c>
       <c r="R5">
-        <v>975.12</v>
+        <v>977.61</v>
       </c>
       <c r="S5">
-        <v>898.09</v>
+        <v>899.4400000000001</v>
       </c>
       <c r="T5">
-        <v>13.3</v>
+        <v>13.93</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1296,34 +1318,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.78</v>
+        <v>55.87</v>
       </c>
       <c r="Z5">
-        <v>10.24</v>
+        <v>10.08</v>
       </c>
       <c r="AA5">
-        <v>13.75</v>
+        <v>13.01</v>
       </c>
       <c r="AB5">
-        <v>-3.51</v>
+        <v>-2.94</v>
       </c>
       <c r="AC5">
-        <v>27.6</v>
+        <v>39.71</v>
       </c>
       <c r="AD5">
-        <v>24.73</v>
+        <v>29.76</v>
       </c>
       <c r="AE5">
-        <v>22.43</v>
+        <v>21.95</v>
       </c>
       <c r="AF5">
-        <v>-55.86</v>
+        <v>-67.56</v>
       </c>
       <c r="AG5">
-        <v>1058.34</v>
+        <v>1058.8</v>
       </c>
       <c r="AH5">
-        <v>982.5</v>
+        <v>983.16</v>
       </c>
       <c r="AI5">
         <v>1076.68</v>
@@ -1332,7 +1354,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>14.58</v>
+        <v>13.39</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1365,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="D6">
-        <v>0.86</v>
+        <v>0.85</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1355,46 +1377,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-35.36</v>
+        <v>-34.81</v>
       </c>
       <c r="H6">
-        <v>27.17</v>
+        <v>28.26</v>
       </c>
       <c r="I6">
-        <v>-1.27</v>
+        <v>2.16</v>
       </c>
       <c r="J6">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="K6">
-        <v>-13.65</v>
+        <v>-11.94</v>
       </c>
       <c r="L6">
         <v>-32.76</v>
       </c>
       <c r="M6">
-        <v>-2.6</v>
+        <v>-3.36</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.33</v>
       </c>
       <c r="Q6">
         <v>2.34</v>
       </c>
       <c r="R6">
-        <v>2.43</v>
+        <v>2.42</v>
       </c>
       <c r="S6">
         <v>2.73</v>
       </c>
       <c r="T6">
-        <v>-14.35</v>
+        <v>-13.46</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1409,10 +1431,10 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>45.51</v>
+        <v>49.01</v>
       </c>
       <c r="Z6">
-        <v>-0.03</v>
+        <v>-0.02</v>
       </c>
       <c r="AA6">
         <v>-0.03</v>
@@ -1421,22 +1443,22 @@
         <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>68.19</v>
+        <v>81.67</v>
       </c>
       <c r="AD6">
-        <v>61.18</v>
+        <v>69.81</v>
       </c>
       <c r="AE6">
         <v>0.08</v>
       </c>
       <c r="AF6">
-        <v>2.13</v>
+        <v>68.61</v>
       </c>
       <c r="AG6">
-        <v>2.4</v>
+        <v>2.39</v>
       </c>
       <c r="AH6">
-        <v>2.28</v>
+        <v>2.29</v>
       </c>
       <c r="AI6">
         <v>2.53</v>
@@ -1445,7 +1467,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>24.71</v>
+        <v>23.67</v>
       </c>
     </row>
   </sheetData>
@@ -1606,719 +1628,757 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>43</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="6">
         <v>13.86</v>
       </c>
-      <c r="E7" s="6">
-        <v>4.06</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="6">
+        <v>12.59</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-1.27</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>6.6</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="6">
         <v>7.04</v>
       </c>
-      <c r="E8" s="6">
-        <v>0.44</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="6">
+        <v>6.86</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-1.46</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="6">
         <v>-10.33</v>
       </c>
-      <c r="E9" s="7">
-        <v>-8.869999999999999</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="D10" s="6">
+        <v>-9.220000000000001</v>
+      </c>
+      <c r="E10" s="8">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-0.39</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C11" s="6">
         <v>2.02</v>
       </c>
-      <c r="E10" s="6">
-        <v>2.41</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="D11" s="6">
+        <v>1.49</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-2.93</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-0.85</v>
       </c>
-      <c r="E11" s="6">
-        <v>2.08</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-0.84</v>
+      </c>
+      <c r="E12" s="8">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-0.17</v>
       </c>
-      <c r="E12" s="7">
-        <v>-1.77</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>-0.72</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>4.35</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>4.72</v>
       </c>
-      <c r="E13" s="6">
-        <v>0.37</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>4.96</v>
+      </c>
+      <c r="E14" s="8">
+        <v>0.24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-2.41</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-3.96</v>
       </c>
-      <c r="E14" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>-4.34</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-1.67</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-0.15</v>
       </c>
-      <c r="E15" s="6">
-        <v>1.52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>0.84</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.99</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-2.11</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>-1.27</v>
       </c>
-      <c r="E16" s="6">
-        <v>0.84</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>2.16</v>
+      </c>
+      <c r="E17" s="8">
+        <v>3.43</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>46.77</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>49.86</v>
       </c>
-      <c r="E17" s="6">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>50.61</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.75</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>21.93</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>26.15</v>
       </c>
-      <c r="E18" s="6">
-        <v>4.22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>26.74</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-28.43</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>-29.59</v>
       </c>
-      <c r="E19" s="7">
-        <v>-1.16</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>-25.16</v>
+      </c>
+      <c r="E20" s="8">
+        <v>4.43</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>23.16</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C21" s="6">
         <v>26.66</v>
       </c>
-      <c r="E20" s="6">
+      <c r="D21" s="6">
+        <v>26.92</v>
+      </c>
+      <c r="E21" s="8">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>16.44</v>
+      </c>
+      <c r="D22" s="6">
+        <v>17.05</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.61</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>43.17</v>
+      </c>
+      <c r="D23" s="6">
+        <v>43.39</v>
+      </c>
+      <c r="E23" s="8">
+        <v>0.22</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-1.5</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-0.55</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>12.07</v>
+      </c>
+      <c r="D25" s="6">
+        <v>15.6</v>
+      </c>
+      <c r="E25" s="8">
+        <v>3.53</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>-13.65</v>
+      </c>
+      <c r="D26" s="6">
+        <v>-11.94</v>
+      </c>
+      <c r="E26" s="8">
+        <v>1.71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-15.2</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-15.42</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.22</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-3.03</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-3.23</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.2</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-25.65</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-26.03</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-4.84</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-4.17</v>
+      </c>
+      <c r="E30" s="8">
+        <v>0.67</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-35.36</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-34.81</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>176.7</v>
+      </c>
+      <c r="D32" s="6">
+        <v>176.23</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-0.47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>431.8</v>
+      </c>
+      <c r="D33" s="6">
+        <v>430.9</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-0.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>406.75</v>
+      </c>
+      <c r="D34" s="6">
+        <v>404.7</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.05</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1017.5</v>
+      </c>
+      <c r="D35" s="6">
+        <v>1024.7</v>
+      </c>
+      <c r="E35" s="8">
+        <v>7.2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2.34</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2.36</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="6">
+        <v>67.89</v>
+      </c>
+      <c r="D37" s="6">
+        <v>66.92</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-0.97</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>63.7</v>
+      </c>
+      <c r="D38" s="6">
+        <v>63.03</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-0.67</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>38.71</v>
+      </c>
+      <c r="D39" s="6">
+        <v>37.52</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-1.19</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>53.78</v>
+      </c>
+      <c r="D40" s="6">
+        <v>55.87</v>
+      </c>
+      <c r="E40" s="8">
+        <v>2.09</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>45.51</v>
+      </c>
+      <c r="D41" s="6">
+        <v>49.01</v>
+      </c>
+      <c r="E41" s="8">
         <v>3.5</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-38.71</v>
+      </c>
+      <c r="D42" s="6">
+        <v>70.31</v>
+      </c>
+      <c r="E42" s="8">
+        <v>109.02</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>3.4</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-71.22</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-74.62</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-83.25</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-74.69</v>
+      </c>
+      <c r="E44" s="8">
+        <v>8.56</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-55.86</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-67.56</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-11.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-33.52</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-32.76</v>
-      </c>
-      <c r="E21" s="6">
-        <v>0.76</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>16.06</v>
-      </c>
-      <c r="D22" s="5">
-        <v>16.44</v>
-      </c>
-      <c r="E22" s="6">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>40.61</v>
-      </c>
-      <c r="D23" s="5">
-        <v>43.17</v>
-      </c>
-      <c r="E23" s="6">
-        <v>2.56</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-0.66</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-1.5</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-0.84</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>13.04</v>
-      </c>
-      <c r="D25" s="5">
-        <v>12.07</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>-13.43</v>
-      </c>
-      <c r="D26" s="5">
-        <v>-13.65</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-0.22</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-16.1</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-15.2</v>
-      </c>
-      <c r="E27" s="6">
-        <v>0.9</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-3.54</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-3.03</v>
-      </c>
-      <c r="E28" s="6">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-28.8</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-25.65</v>
-      </c>
-      <c r="E29" s="6">
-        <v>3.15</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-5.65</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-4.84</v>
-      </c>
-      <c r="E30" s="6">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-35.91</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-35.36</v>
-      </c>
-      <c r="E31" s="6">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>174.83</v>
-      </c>
-      <c r="D32" s="5">
-        <v>176.7</v>
-      </c>
-      <c r="E32" s="6">
-        <v>1.87</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>429.55</v>
-      </c>
-      <c r="D33" s="5">
-        <v>431.8</v>
-      </c>
-      <c r="E33" s="6">
-        <v>2.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>411.3</v>
-      </c>
-      <c r="D34" s="5">
-        <v>406.75</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-4.55</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>1008.9</v>
-      </c>
-      <c r="D35" s="5">
-        <v>1017.5</v>
-      </c>
-      <c r="E35" s="6">
-        <v>8.6</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="5">
-        <v>2.32</v>
-      </c>
-      <c r="D36" s="5">
-        <v>2.34</v>
-      </c>
-      <c r="E36" s="6">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>66.06999999999999</v>
-      </c>
-      <c r="D37" s="5">
-        <v>67.89</v>
-      </c>
-      <c r="E37" s="6">
-        <v>1.82</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>62.79</v>
-      </c>
-      <c r="D38" s="5">
-        <v>63.7</v>
-      </c>
-      <c r="E38" s="6">
-        <v>0.91</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>41.42</v>
-      </c>
-      <c r="D39" s="5">
-        <v>38.71</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-2.71</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>51.21</v>
-      </c>
-      <c r="D40" s="5">
-        <v>53.78</v>
-      </c>
-      <c r="E40" s="6">
-        <v>2.57</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>41.79</v>
-      </c>
-      <c r="D41" s="5">
-        <v>45.51</v>
-      </c>
-      <c r="E41" s="6">
-        <v>3.72</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="5">
-        <v>-5.08</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-38.71</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-33.63</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>-49.06</v>
-      </c>
-      <c r="D43" s="5">
-        <v>3.4</v>
-      </c>
-      <c r="E43" s="6">
-        <v>52.46</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-86.72</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-83.25</v>
-      </c>
-      <c r="E44" s="6">
-        <v>3.47</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-31.57</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-55.86</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-24.29</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>116.74</v>
-      </c>
-      <c r="D46" s="5">
+      <c r="C46" s="6">
         <v>2.13</v>
       </c>
-      <c r="E46" s="7">
-        <v>-114.61</v>
+      <c r="D46" s="6">
+        <v>68.61</v>
+      </c>
+      <c r="E46" s="8">
+        <v>66.48</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2338,61 +2398,61 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>54.5</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>53.9</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>2.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>11.3</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>2.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>12.7</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
-        <v>20</v>
+      <c r="I2" s="11">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -2493,37 +2553,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.241</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.08689999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0035</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.026</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2361</v>
+      <c r="A2" s="14">
+        <v>0.2465</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1065</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0071</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0336</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.229</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="73">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,13 +181,25 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>63.0 → 44.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>63.0</t>
+  </si>
+  <si>
+    <t>44.2</t>
   </si>
   <si>
     <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +285,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +325,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -399,8 +411,8 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -913,37 +925,37 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>176.23</v>
+        <v>171.64</v>
       </c>
       <c r="D2">
-        <v>-0.27</v>
+        <v>-2.6</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>112.72</v>
+        <v>116.57</v>
       </c>
       <c r="G2">
-        <v>-15.42</v>
+        <v>-17.63</v>
       </c>
       <c r="H2">
-        <v>56.34</v>
+        <v>47.24</v>
       </c>
       <c r="I2">
-        <v>-0.72</v>
+        <v>-3.3</v>
       </c>
       <c r="J2">
-        <v>12.59</v>
+        <v>10.83</v>
       </c>
       <c r="K2">
-        <v>17.05</v>
+        <v>15.5</v>
       </c>
       <c r="L2">
-        <v>50.61</v>
+        <v>52.27</v>
       </c>
       <c r="M2">
-        <v>24.65</v>
+        <v>24.47</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -952,19 +964,19 @@
         <v>86</v>
       </c>
       <c r="P2">
-        <v>175.85</v>
+        <v>174.68</v>
       </c>
       <c r="Q2">
-        <v>164.67</v>
+        <v>165.49</v>
       </c>
       <c r="R2">
-        <v>158.94</v>
+        <v>159.48</v>
       </c>
       <c r="S2">
-        <v>166.51</v>
+        <v>166.68</v>
       </c>
       <c r="T2">
-        <v>5.84</v>
+        <v>2.98</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -979,34 +991,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>66.92</v>
+        <v>58.13</v>
       </c>
       <c r="Z2">
-        <v>5.49</v>
+        <v>5.08</v>
       </c>
       <c r="AA2">
-        <v>4.28</v>
+        <v>4.44</v>
       </c>
       <c r="AB2">
-        <v>1.21</v>
+        <v>0.64</v>
       </c>
       <c r="AC2">
-        <v>80.54000000000001</v>
+        <v>62.58</v>
       </c>
       <c r="AD2">
-        <v>82.23999999999999</v>
+        <v>74.65000000000001</v>
       </c>
       <c r="AE2">
-        <v>4.52</v>
+        <v>4.9</v>
       </c>
       <c r="AF2">
-        <v>70.31</v>
+        <v>125.14</v>
       </c>
       <c r="AG2">
-        <v>186.03</v>
+        <v>186.59</v>
       </c>
       <c r="AH2">
-        <v>143.3</v>
+        <v>144.39</v>
       </c>
       <c r="AI2">
         <v>165.9</v>
@@ -1015,7 +1027,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>46.04</v>
+        <v>41.31</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1026,10 +1038,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>430.9</v>
+        <v>397.1</v>
       </c>
       <c r="D3">
-        <v>-0.21</v>
+        <v>-7.84</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1038,46 +1050,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-3.23</v>
+        <v>-10.82</v>
       </c>
       <c r="H3">
-        <v>91.51000000000001</v>
+        <v>76.48999999999999</v>
       </c>
       <c r="I3">
-        <v>4.96</v>
+        <v>-9.390000000000001</v>
       </c>
       <c r="J3">
-        <v>6.86</v>
+        <v>-1.45</v>
       </c>
       <c r="K3">
-        <v>43.39</v>
+        <v>37.19</v>
       </c>
       <c r="L3">
-        <v>26.74</v>
+        <v>18.18</v>
       </c>
       <c r="M3">
-        <v>10.65</v>
+        <v>9.52</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="P3">
-        <v>431.74</v>
+        <v>423.51</v>
       </c>
       <c r="Q3">
-        <v>407.56</v>
+        <v>407.23</v>
       </c>
       <c r="R3">
-        <v>407.5</v>
+        <v>407.04</v>
       </c>
       <c r="S3">
-        <v>323.74</v>
+        <v>323.9</v>
       </c>
       <c r="T3">
-        <v>33.1</v>
+        <v>22.6</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1092,34 +1104,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>63.03</v>
+        <v>44.22</v>
       </c>
       <c r="Z3">
-        <v>8.67</v>
+        <v>6.25</v>
       </c>
       <c r="AA3">
-        <v>5.46</v>
+        <v>5.61</v>
       </c>
       <c r="AB3">
-        <v>3.22</v>
+        <v>0.64</v>
       </c>
       <c r="AC3">
-        <v>80.06</v>
+        <v>59.17</v>
       </c>
       <c r="AD3">
-        <v>81.48999999999999</v>
+        <v>72.8</v>
       </c>
       <c r="AE3">
-        <v>14.54</v>
+        <v>16.13</v>
       </c>
       <c r="AF3">
-        <v>-71.22</v>
+        <v>1.45</v>
       </c>
       <c r="AG3">
-        <v>441.21</v>
+        <v>441.17</v>
       </c>
       <c r="AH3">
-        <v>373.92</v>
+        <v>373.3</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1128,7 +1140,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>46.16</v>
+        <v>41.51</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1139,10 +1151,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>404.7</v>
+        <v>408.65</v>
       </c>
       <c r="D4">
-        <v>-0.5</v>
+        <v>0.98</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1151,49 +1163,49 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-26.03</v>
+        <v>-25.31</v>
       </c>
       <c r="H4">
-        <v>17.41</v>
+        <v>18.55</v>
       </c>
       <c r="I4">
-        <v>-4.34</v>
+        <v>-4.61</v>
       </c>
       <c r="J4">
-        <v>-9.220000000000001</v>
+        <v>-6.52</v>
       </c>
       <c r="K4">
-        <v>-0.55</v>
+        <v>2.48</v>
       </c>
       <c r="L4">
-        <v>-25.16</v>
+        <v>-23.91</v>
       </c>
       <c r="M4">
-        <v>-22.9</v>
+        <v>-22.1</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>412.73</v>
+        <v>408.78</v>
       </c>
       <c r="Q4">
-        <v>422.31</v>
+        <v>421.16</v>
       </c>
       <c r="R4">
-        <v>421.64</v>
+        <v>421.69</v>
       </c>
       <c r="S4">
-        <v>424.6</v>
+        <v>423.97</v>
       </c>
       <c r="T4">
-        <v>-4.69</v>
+        <v>-3.61</v>
       </c>
       <c r="U4" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V4" t="s">
         <v>44</v>
@@ -1202,37 +1214,37 @@
         <v>44</v>
       </c>
       <c r="X4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.52</v>
+        <v>41.27</v>
       </c>
       <c r="Z4">
-        <v>-3.17</v>
+        <v>-3.6</v>
       </c>
       <c r="AA4">
-        <v>-0.59</v>
+        <v>-1.19</v>
       </c>
       <c r="AB4">
-        <v>-2.58</v>
+        <v>-2.41</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>6.99</v>
       </c>
       <c r="AD4">
-        <v>8.470000000000001</v>
+        <v>2.33</v>
       </c>
       <c r="AE4">
-        <v>12.11</v>
+        <v>11.79</v>
       </c>
       <c r="AF4">
-        <v>-74.69</v>
+        <v>-45.73</v>
       </c>
       <c r="AG4">
-        <v>437.85</v>
+        <v>437.2</v>
       </c>
       <c r="AH4">
-        <v>406.77</v>
+        <v>405.13</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1241,7 +1253,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>21.06</v>
+        <v>20.23</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1252,10 +1264,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1024.7</v>
+        <v>1020.8</v>
       </c>
       <c r="D5">
-        <v>0.71</v>
+        <v>-0.38</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1264,46 +1276,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-4.17</v>
+        <v>-4.54</v>
       </c>
       <c r="H5">
-        <v>43.77</v>
+        <v>43.22</v>
       </c>
       <c r="I5">
-        <v>0.84</v>
+        <v>-0.12</v>
       </c>
       <c r="J5">
-        <v>1.49</v>
+        <v>0.72</v>
       </c>
       <c r="K5">
-        <v>15.6</v>
+        <v>14.42</v>
       </c>
       <c r="L5">
-        <v>26.92</v>
+        <v>30.46</v>
       </c>
       <c r="M5">
-        <v>0.71</v>
+        <v>0.74</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P5">
-        <v>1020.08</v>
+        <v>1019.84</v>
       </c>
       <c r="Q5">
-        <v>1020.98</v>
+        <v>1020.66</v>
       </c>
       <c r="R5">
-        <v>977.61</v>
+        <v>979.96</v>
       </c>
       <c r="S5">
-        <v>899.4400000000001</v>
+        <v>900.6900000000001</v>
       </c>
       <c r="T5">
-        <v>13.93</v>
+        <v>13.33</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1318,34 +1330,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>55.87</v>
+        <v>54.43</v>
       </c>
       <c r="Z5">
-        <v>10.08</v>
+        <v>9.52</v>
       </c>
       <c r="AA5">
-        <v>13.01</v>
+        <v>12.32</v>
       </c>
       <c r="AB5">
-        <v>-2.94</v>
+        <v>-2.8</v>
       </c>
       <c r="AC5">
-        <v>39.71</v>
+        <v>52.94</v>
       </c>
       <c r="AD5">
-        <v>29.76</v>
+        <v>40.08</v>
       </c>
       <c r="AE5">
-        <v>21.95</v>
+        <v>21.27</v>
       </c>
       <c r="AF5">
-        <v>-67.56</v>
+        <v>-49.34</v>
       </c>
       <c r="AG5">
-        <v>1058.8</v>
+        <v>1058.37</v>
       </c>
       <c r="AH5">
-        <v>983.16</v>
+        <v>982.96</v>
       </c>
       <c r="AI5">
         <v>1076.68</v>
@@ -1354,7 +1366,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>13.39</v>
+        <v>12.92</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1365,10 +1377,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="D6">
-        <v>0.85</v>
+        <v>-1.69</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1377,31 +1389,31 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-34.81</v>
+        <v>-35.91</v>
       </c>
       <c r="H6">
-        <v>28.26</v>
+        <v>26.09</v>
       </c>
       <c r="I6">
-        <v>2.16</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>-0.84</v>
+        <v>-3.73</v>
       </c>
       <c r="K6">
-        <v>-11.94</v>
+        <v>-12.12</v>
       </c>
       <c r="L6">
-        <v>-32.76</v>
+        <v>-32.95</v>
       </c>
       <c r="M6">
-        <v>-3.36</v>
+        <v>-3.28</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="P6">
         <v>2.33</v>
@@ -1413,10 +1425,10 @@
         <v>2.42</v>
       </c>
       <c r="S6">
-        <v>2.73</v>
+        <v>2.72</v>
       </c>
       <c r="T6">
-        <v>-13.46</v>
+        <v>-14.76</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1431,7 +1443,7 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>49.01</v>
+        <v>43.05</v>
       </c>
       <c r="Z6">
         <v>-0.02</v>
@@ -1443,22 +1455,22 @@
         <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>81.67</v>
+        <v>82.54000000000001</v>
       </c>
       <c r="AD6">
-        <v>69.81</v>
+        <v>77.47</v>
       </c>
       <c r="AE6">
         <v>0.08</v>
       </c>
       <c r="AF6">
-        <v>68.61</v>
+        <v>10.35</v>
       </c>
       <c r="AG6">
         <v>2.39</v>
       </c>
       <c r="AH6">
-        <v>2.29</v>
+        <v>2.28</v>
       </c>
       <c r="AI6">
         <v>2.53</v>
@@ -1467,7 +1479,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>23.67</v>
+        <v>21.19</v>
       </c>
     </row>
   </sheetData>
@@ -1608,7 +1620,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1651,44 +1663,44 @@
         <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>22</v>
+        <v>53</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B4" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>54</v>
-      </c>
       <c r="E4" s="4" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="4" t="s">
         <v>44</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>43</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>56</v>
+        <v>60</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1700,16 +1712,16 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>57</v>
+        <v>61</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>58</v>
+        <v>62</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>59</v>
+        <v>63</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1720,13 +1732,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>13.86</v>
+        <v>12.59</v>
       </c>
       <c r="D8" s="6">
-        <v>12.59</v>
+        <v>10.83</v>
       </c>
       <c r="E8" s="7">
-        <v>-1.27</v>
+        <v>-1.76</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1737,13 +1749,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>7.04</v>
+        <v>6.86</v>
       </c>
       <c r="D9" s="6">
-        <v>6.86</v>
+        <v>-1.45</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.18</v>
+        <v>-8.31</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1754,13 +1766,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-10.33</v>
+        <v>-9.220000000000001</v>
       </c>
       <c r="D10" s="6">
-        <v>-9.220000000000001</v>
+        <v>-6.52</v>
       </c>
       <c r="E10" s="8">
-        <v>1.11</v>
+        <v>2.7</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1771,13 +1783,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>2.02</v>
+        <v>1.49</v>
       </c>
       <c r="D11" s="6">
-        <v>1.49</v>
+        <v>0.72</v>
       </c>
       <c r="E11" s="7">
-        <v>-0.53</v>
+        <v>-0.77</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1788,13 +1800,13 @@
         <v>9</v>
       </c>
       <c r="C12" s="6">
-        <v>-0.85</v>
+        <v>-0.84</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.01</v>
+        <v>-3.73</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-2.89</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1805,13 +1817,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-0.17</v>
+        <v>-0.72</v>
       </c>
       <c r="D13" s="6">
-        <v>-0.72</v>
+        <v>-3.3</v>
       </c>
       <c r="E13" s="7">
-        <v>-0.55</v>
+        <v>-2.58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1822,13 +1834,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>4.72</v>
+        <v>4.96</v>
       </c>
       <c r="D14" s="6">
-        <v>4.96</v>
-      </c>
-      <c r="E14" s="8">
-        <v>0.24</v>
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-14.35</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1839,13 +1851,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-3.96</v>
+        <v>-4.34</v>
       </c>
       <c r="D15" s="6">
-        <v>-4.34</v>
+        <v>-4.61</v>
       </c>
       <c r="E15" s="7">
-        <v>-0.38</v>
+        <v>-0.27</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1856,13 +1868,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-0.15</v>
+        <v>0.84</v>
       </c>
       <c r="D16" s="6">
-        <v>0.84</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.99</v>
+        <v>-0.12</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-0.96</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1873,13 +1885,13 @@
         <v>8</v>
       </c>
       <c r="C17" s="6">
-        <v>-1.27</v>
+        <v>2.16</v>
       </c>
       <c r="D17" s="6">
-        <v>2.16</v>
-      </c>
-      <c r="E17" s="8">
-        <v>3.43</v>
+        <v>0</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1890,13 +1902,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>49.86</v>
+        <v>50.61</v>
       </c>
       <c r="D18" s="6">
-        <v>50.61</v>
+        <v>52.27</v>
       </c>
       <c r="E18" s="8">
-        <v>0.75</v>
+        <v>1.66</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1907,13 +1919,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>26.15</v>
+        <v>26.74</v>
       </c>
       <c r="D19" s="6">
-        <v>26.74</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.59</v>
+        <v>18.18</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-8.56</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1924,13 +1936,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>-29.59</v>
+        <v>-25.16</v>
       </c>
       <c r="D20" s="6">
-        <v>-25.16</v>
+        <v>-23.91</v>
       </c>
       <c r="E20" s="8">
-        <v>4.43</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1941,438 +1953,455 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>26.66</v>
+        <v>26.92</v>
       </c>
       <c r="D21" s="6">
-        <v>26.92</v>
+        <v>30.46</v>
       </c>
       <c r="E21" s="8">
-        <v>0.26</v>
+        <v>3.54</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B22" s="5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C22" s="6">
-        <v>16.44</v>
+        <v>-32.76</v>
       </c>
       <c r="D22" s="6">
-        <v>17.05</v>
-      </c>
-      <c r="E22" s="8">
-        <v>0.61</v>
+        <v>-32.95</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>43.17</v>
+        <v>17.05</v>
       </c>
       <c r="D23" s="6">
-        <v>43.39</v>
-      </c>
-      <c r="E23" s="8">
-        <v>0.22</v>
+        <v>15.5</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.5</v>
+        <v>43.39</v>
       </c>
       <c r="D24" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.95</v>
+        <v>37.19</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-6.2</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>12.07</v>
+        <v>-0.55</v>
       </c>
       <c r="D25" s="6">
-        <v>15.6</v>
+        <v>2.48</v>
       </c>
       <c r="E25" s="8">
-        <v>3.53</v>
+        <v>3.03</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-13.65</v>
+        <v>15.6</v>
       </c>
       <c r="D26" s="6">
-        <v>-11.94</v>
-      </c>
-      <c r="E26" s="8">
-        <v>1.71</v>
+        <v>14.42</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B27" s="5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C27" s="6">
-        <v>-15.2</v>
+        <v>-11.94</v>
       </c>
       <c r="D27" s="6">
-        <v>-15.42</v>
+        <v>-12.12</v>
       </c>
       <c r="E27" s="7">
-        <v>-0.22</v>
+        <v>-0.18</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-3.03</v>
+        <v>-15.42</v>
       </c>
       <c r="D28" s="6">
-        <v>-3.23</v>
+        <v>-17.63</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.2</v>
+        <v>-2.21</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-25.65</v>
+        <v>-3.23</v>
       </c>
       <c r="D29" s="6">
-        <v>-26.03</v>
+        <v>-10.82</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.38</v>
+        <v>-7.59</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-4.84</v>
+        <v>-26.03</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.17</v>
+        <v>-25.31</v>
       </c>
       <c r="E30" s="8">
-        <v>0.67</v>
+        <v>0.72</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-35.36</v>
+        <v>-4.17</v>
       </c>
       <c r="D31" s="6">
-        <v>-34.81</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.55</v>
+        <v>-4.54</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B32" s="5" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C32" s="6">
-        <v>176.7</v>
+        <v>-34.81</v>
       </c>
       <c r="D32" s="6">
-        <v>176.23</v>
+        <v>-35.91</v>
       </c>
       <c r="E32" s="7">
-        <v>-0.47</v>
+        <v>-1.1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>431.8</v>
+        <v>176.23</v>
       </c>
       <c r="D33" s="6">
-        <v>430.9</v>
+        <v>171.64</v>
       </c>
       <c r="E33" s="7">
-        <v>-0.9</v>
+        <v>-4.59</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>406.75</v>
+        <v>430.9</v>
       </c>
       <c r="D34" s="6">
-        <v>404.7</v>
+        <v>397.1</v>
       </c>
       <c r="E34" s="7">
-        <v>-2.05</v>
+        <v>-33.8</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1017.5</v>
+        <v>404.7</v>
       </c>
       <c r="D35" s="6">
-        <v>1024.7</v>
+        <v>408.65</v>
       </c>
       <c r="E35" s="8">
-        <v>7.2</v>
+        <v>3.95</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2.34</v>
+        <v>1024.7</v>
       </c>
       <c r="D36" s="6">
-        <v>2.36</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.02</v>
+        <v>1020.8</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-3.9</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C37" s="6">
-        <v>67.89</v>
+        <v>2.36</v>
       </c>
       <c r="D37" s="6">
-        <v>66.92</v>
+        <v>2.32</v>
       </c>
       <c r="E37" s="7">
-        <v>-0.97</v>
+        <v>-0.04</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>63.7</v>
+        <v>66.92</v>
       </c>
       <c r="D38" s="6">
-        <v>63.03</v>
+        <v>58.13</v>
       </c>
       <c r="E38" s="7">
-        <v>-0.67</v>
+        <v>-8.789999999999999</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>38.71</v>
+        <v>63.03</v>
       </c>
       <c r="D39" s="6">
-        <v>37.52</v>
+        <v>44.22</v>
       </c>
       <c r="E39" s="7">
-        <v>-1.19</v>
+        <v>-18.81</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>53.78</v>
+        <v>37.52</v>
       </c>
       <c r="D40" s="6">
-        <v>55.87</v>
+        <v>41.27</v>
       </c>
       <c r="E40" s="8">
-        <v>2.09</v>
+        <v>3.75</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>45.51</v>
+        <v>55.87</v>
       </c>
       <c r="D41" s="6">
-        <v>49.01</v>
-      </c>
-      <c r="E41" s="8">
-        <v>3.5</v>
+        <v>54.43</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.44</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>-38.71</v>
+        <v>49.01</v>
       </c>
       <c r="D42" s="6">
-        <v>70.31</v>
-      </c>
-      <c r="E42" s="8">
-        <v>109.02</v>
+        <v>43.05</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-5.96</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>3.4</v>
+        <v>70.31</v>
       </c>
       <c r="D43" s="6">
-        <v>-71.22</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-74.62</v>
+        <v>125.14</v>
+      </c>
+      <c r="E43" s="8">
+        <v>54.83</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-83.25</v>
+        <v>-71.22</v>
       </c>
       <c r="D44" s="6">
-        <v>-74.69</v>
+        <v>1.45</v>
       </c>
       <c r="E44" s="8">
-        <v>8.56</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-55.86</v>
+        <v>-74.69</v>
       </c>
       <c r="D45" s="6">
-        <v>-67.56</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-11.7</v>
+        <v>-45.73</v>
+      </c>
+      <c r="E45" s="8">
+        <v>28.96</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>2.13</v>
+        <v>-67.56</v>
       </c>
       <c r="D46" s="6">
+        <v>-49.34</v>
+      </c>
+      <c r="E46" s="8">
+        <v>18.22</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
         <v>68.61</v>
       </c>
-      <c r="E46" s="8">
-        <v>66.48</v>
+      <c r="D47" s="6">
+        <v>10.35</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-58.26</v>
       </c>
     </row>
   </sheetData>
@@ -2402,28 +2431,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>65</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>67</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2437,16 +2466,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>54.5</v>
+        <v>48.2</v>
       </c>
       <c r="E2" s="11">
         <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>2.2</v>
+        <v>-0</v>
       </c>
       <c r="G2" s="11">
-        <v>12.7</v>
+        <v>11.5</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2571,19 +2600,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2465</v>
+        <v>0.2447</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1065</v>
+        <v>0.09519999999999999</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0071</v>
+        <v>0.0074</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0336</v>
+        <v>-0.0328</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.229</v>
+        <v>-0.221</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="73">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,40 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>63.0 → 44.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>63.0</t>
-  </si>
-  <si>
-    <t>44.2</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -285,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -325,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -401,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -925,10 +891,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>171.64</v>
+        <v>177.1</v>
       </c>
       <c r="D2">
-        <v>-2.6</v>
+        <v>3.18</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -937,46 +903,46 @@
         <v>116.57</v>
       </c>
       <c r="G2">
-        <v>-17.63</v>
+        <v>-15.01</v>
       </c>
       <c r="H2">
-        <v>47.24</v>
+        <v>51.93</v>
       </c>
       <c r="I2">
-        <v>-3.3</v>
+        <v>1.78</v>
       </c>
       <c r="J2">
-        <v>10.83</v>
+        <v>14.09</v>
       </c>
       <c r="K2">
-        <v>15.5</v>
+        <v>18.99</v>
       </c>
       <c r="L2">
-        <v>52.27</v>
+        <v>51.1</v>
       </c>
       <c r="M2">
-        <v>24.47</v>
+        <v>25.54</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="P2">
-        <v>174.68</v>
+        <v>175.3</v>
       </c>
       <c r="Q2">
-        <v>165.49</v>
+        <v>166.6</v>
       </c>
       <c r="R2">
-        <v>159.48</v>
+        <v>160.12</v>
       </c>
       <c r="S2">
-        <v>166.68</v>
+        <v>166.88</v>
       </c>
       <c r="T2">
-        <v>2.98</v>
+        <v>6.12</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -991,34 +957,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.13</v>
+        <v>64.16</v>
       </c>
       <c r="Z2">
+        <v>5.13</v>
+      </c>
+      <c r="AA2">
+        <v>4.58</v>
+      </c>
+      <c r="AB2">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="AC2">
+        <v>52.68</v>
+      </c>
+      <c r="AD2">
+        <v>65.26000000000001</v>
+      </c>
+      <c r="AE2">
         <v>5.08</v>
       </c>
-      <c r="AA2">
-        <v>4.44</v>
-      </c>
-      <c r="AB2">
-        <v>0.64</v>
-      </c>
-      <c r="AC2">
-        <v>62.58</v>
-      </c>
-      <c r="AD2">
-        <v>74.65000000000001</v>
-      </c>
-      <c r="AE2">
-        <v>4.9</v>
-      </c>
       <c r="AF2">
-        <v>125.14</v>
+        <v>105.15</v>
       </c>
       <c r="AG2">
-        <v>186.59</v>
+        <v>187.68</v>
       </c>
       <c r="AH2">
-        <v>144.39</v>
+        <v>145.53</v>
       </c>
       <c r="AI2">
         <v>165.9</v>
@@ -1027,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>41.31</v>
+        <v>37.21</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1038,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>397.1</v>
+        <v>408</v>
       </c>
       <c r="D3">
-        <v>-7.84</v>
+        <v>2.74</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1050,46 +1016,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-10.82</v>
+        <v>-8.380000000000001</v>
       </c>
       <c r="H3">
-        <v>76.48999999999999</v>
+        <v>81.33</v>
       </c>
       <c r="I3">
-        <v>-9.390000000000001</v>
+        <v>-4.72</v>
       </c>
       <c r="J3">
-        <v>-1.45</v>
+        <v>1.07</v>
       </c>
       <c r="K3">
-        <v>37.19</v>
+        <v>37.84</v>
       </c>
       <c r="L3">
-        <v>18.18</v>
+        <v>19.05</v>
       </c>
       <c r="M3">
-        <v>9.52</v>
+        <v>10.4</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="P3">
-        <v>423.51</v>
+        <v>419.47</v>
       </c>
       <c r="Q3">
-        <v>407.23</v>
+        <v>407.58</v>
       </c>
       <c r="R3">
-        <v>407.04</v>
+        <v>406.98</v>
       </c>
       <c r="S3">
-        <v>323.9</v>
+        <v>324.1</v>
       </c>
       <c r="T3">
-        <v>22.6</v>
+        <v>25.89</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1104,34 +1070,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>44.22</v>
+        <v>49.46</v>
       </c>
       <c r="Z3">
-        <v>6.25</v>
+        <v>5.16</v>
       </c>
       <c r="AA3">
-        <v>5.61</v>
+        <v>5.52</v>
       </c>
       <c r="AB3">
-        <v>0.64</v>
+        <v>-0.37</v>
       </c>
       <c r="AC3">
-        <v>59.17</v>
+        <v>43.14</v>
       </c>
       <c r="AD3">
-        <v>72.8</v>
+        <v>60.79</v>
       </c>
       <c r="AE3">
-        <v>16.13</v>
+        <v>16.24</v>
       </c>
       <c r="AF3">
-        <v>1.45</v>
+        <v>-50.54</v>
       </c>
       <c r="AG3">
-        <v>441.17</v>
+        <v>441.39</v>
       </c>
       <c r="AH3">
-        <v>373.3</v>
+        <v>373.77</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1140,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>41.51</v>
+        <v>37.72</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1151,10 +1117,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>408.65</v>
+        <v>413.05</v>
       </c>
       <c r="D4">
-        <v>0.98</v>
+        <v>1.08</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1163,46 +1129,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-25.31</v>
+        <v>-24.5</v>
       </c>
       <c r="H4">
-        <v>18.55</v>
+        <v>19.83</v>
       </c>
       <c r="I4">
-        <v>-4.61</v>
+        <v>0.13</v>
       </c>
       <c r="J4">
-        <v>-6.52</v>
+        <v>-4.29</v>
       </c>
       <c r="K4">
-        <v>2.48</v>
+        <v>2.18</v>
       </c>
       <c r="L4">
-        <v>-23.91</v>
+        <v>-21.86</v>
       </c>
       <c r="M4">
-        <v>-22.1</v>
+        <v>-21.87</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="P4">
-        <v>408.78</v>
+        <v>408.89</v>
       </c>
       <c r="Q4">
-        <v>421.16</v>
+        <v>420.33</v>
       </c>
       <c r="R4">
-        <v>421.69</v>
+        <v>421.87</v>
       </c>
       <c r="S4">
-        <v>423.97</v>
+        <v>423.38</v>
       </c>
       <c r="T4">
-        <v>-3.61</v>
+        <v>-2.44</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1217,34 +1183,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.27</v>
+        <v>45.22</v>
       </c>
       <c r="Z4">
-        <v>-3.6</v>
+        <v>-3.54</v>
       </c>
       <c r="AA4">
-        <v>-1.19</v>
+        <v>-1.66</v>
       </c>
       <c r="AB4">
-        <v>-2.41</v>
+        <v>-1.88</v>
       </c>
       <c r="AC4">
-        <v>6.99</v>
+        <v>21.32</v>
       </c>
       <c r="AD4">
-        <v>2.33</v>
+        <v>9.43</v>
       </c>
       <c r="AE4">
-        <v>11.79</v>
+        <v>11.94</v>
       </c>
       <c r="AF4">
-        <v>-45.73</v>
+        <v>9.48</v>
       </c>
       <c r="AG4">
-        <v>437.2</v>
+        <v>436.22</v>
       </c>
       <c r="AH4">
-        <v>405.13</v>
+        <v>404.44</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1253,7 +1219,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>20.23</v>
+        <v>18.19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1267,7 +1233,7 @@
         <v>1020.8</v>
       </c>
       <c r="D5">
-        <v>-0.38</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1282,40 +1248,40 @@
         <v>43.22</v>
       </c>
       <c r="I5">
-        <v>-0.12</v>
+        <v>-0.63</v>
       </c>
       <c r="J5">
-        <v>0.72</v>
+        <v>-0.62</v>
       </c>
       <c r="K5">
-        <v>14.42</v>
+        <v>14.02</v>
       </c>
       <c r="L5">
-        <v>30.46</v>
+        <v>30.33</v>
       </c>
       <c r="M5">
-        <v>0.74</v>
+        <v>1.01</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1019.84</v>
+        <v>1018.54</v>
       </c>
       <c r="Q5">
-        <v>1020.66</v>
+        <v>1020.06</v>
       </c>
       <c r="R5">
-        <v>979.96</v>
+        <v>982.28</v>
       </c>
       <c r="S5">
-        <v>900.6900000000001</v>
+        <v>901.8</v>
       </c>
       <c r="T5">
-        <v>13.33</v>
+        <v>13.2</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1333,31 +1299,31 @@
         <v>54.43</v>
       </c>
       <c r="Z5">
-        <v>9.52</v>
+        <v>8.98</v>
       </c>
       <c r="AA5">
-        <v>12.32</v>
+        <v>11.65</v>
       </c>
       <c r="AB5">
-        <v>-2.8</v>
+        <v>-2.67</v>
       </c>
       <c r="AC5">
-        <v>52.94</v>
+        <v>53.76</v>
       </c>
       <c r="AD5">
-        <v>40.08</v>
+        <v>48.8</v>
       </c>
       <c r="AE5">
-        <v>21.27</v>
+        <v>20.64</v>
       </c>
       <c r="AF5">
-        <v>-49.34</v>
+        <v>-46.13</v>
       </c>
       <c r="AG5">
-        <v>1058.37</v>
+        <v>1057.33</v>
       </c>
       <c r="AH5">
-        <v>982.96</v>
+        <v>982.79</v>
       </c>
       <c r="AI5">
         <v>1076.68</v>
@@ -1366,7 +1332,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>12.92</v>
+        <v>12.51</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1380,7 +1346,7 @@
         <v>2.32</v>
       </c>
       <c r="D6">
-        <v>-1.69</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1398,16 +1364,16 @@
         <v>0</v>
       </c>
       <c r="J6">
-        <v>-3.73</v>
+        <v>-1.69</v>
       </c>
       <c r="K6">
-        <v>-12.12</v>
+        <v>-12.45</v>
       </c>
       <c r="L6">
-        <v>-32.95</v>
+        <v>-32.16</v>
       </c>
       <c r="M6">
-        <v>-3.28</v>
+        <v>-2.4</v>
       </c>
       <c r="N6">
         <v>21</v>
@@ -1419,16 +1385,16 @@
         <v>2.33</v>
       </c>
       <c r="Q6">
-        <v>2.34</v>
+        <v>2.33</v>
       </c>
       <c r="R6">
-        <v>2.42</v>
+        <v>2.41</v>
       </c>
       <c r="S6">
         <v>2.72</v>
       </c>
       <c r="T6">
-        <v>-14.76</v>
+        <v>-14.6</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1452,19 +1418,19 @@
         <v>-0.03</v>
       </c>
       <c r="AB6">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>82.54000000000001</v>
+        <v>64.94</v>
       </c>
       <c r="AD6">
-        <v>77.47</v>
+        <v>76.39</v>
       </c>
       <c r="AE6">
         <v>0.08</v>
       </c>
       <c r="AF6">
-        <v>10.35</v>
+        <v>-15.54</v>
       </c>
       <c r="AG6">
         <v>2.39</v>
@@ -1479,7 +1445,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>21.19</v>
+        <v>19.04</v>
       </c>
     </row>
   </sheetData>
@@ -1620,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F39"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1640,774 +1606,600 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>64</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>10.83</v>
+      </c>
+      <c r="D7" s="5">
+        <v>14.09</v>
+      </c>
+      <c r="E7" s="6">
+        <v>3.26</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-1.45</v>
+      </c>
+      <c r="D8" s="5">
+        <v>1.07</v>
+      </c>
+      <c r="E8" s="6">
+        <v>2.52</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-6.52</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-4.29</v>
+      </c>
+      <c r="E9" s="6">
+        <v>2.23</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>0.72</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-0.62</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.34</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-3.73</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-1.69</v>
+      </c>
+      <c r="E11" s="6">
+        <v>2.04</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>12.59</v>
-      </c>
-      <c r="D8" s="6">
-        <v>10.83</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-3.3</v>
+      </c>
+      <c r="D12" s="5">
+        <v>1.78</v>
+      </c>
+      <c r="E12" s="6">
+        <v>5.08</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>6.86</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-1.45</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-8.31</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-9.390000000000001</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-4.72</v>
+      </c>
+      <c r="E13" s="6">
+        <v>4.67</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-9.220000000000001</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-6.52</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.7</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-4.61</v>
+      </c>
+      <c r="D14" s="5">
+        <v>0.13</v>
+      </c>
+      <c r="E14" s="6">
+        <v>4.74</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>1.49</v>
-      </c>
-      <c r="D11" s="6">
-        <v>0.72</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-0.12</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-0.63</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5">
+        <v>52.27</v>
+      </c>
+      <c r="D16" s="5">
+        <v>51.1</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.17</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>18.18</v>
+      </c>
+      <c r="D17" s="5">
+        <v>19.05</v>
+      </c>
+      <c r="E17" s="6">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-23.91</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-21.86</v>
+      </c>
+      <c r="E18" s="6">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>30.46</v>
+      </c>
+      <c r="D19" s="5">
+        <v>30.33</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-0.84</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.73</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.89</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>-32.95</v>
+      </c>
+      <c r="D20" s="5">
+        <v>-32.16</v>
+      </c>
+      <c r="E20" s="6">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-0.72</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-3.3</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-2.58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5">
+        <v>15.5</v>
+      </c>
+      <c r="D21" s="5">
+        <v>18.99</v>
+      </c>
+      <c r="E21" s="6">
+        <v>3.49</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>4.96</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-9.390000000000001</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-14.35</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>37.19</v>
+      </c>
+      <c r="D22" s="5">
+        <v>37.84</v>
+      </c>
+      <c r="E22" s="6">
+        <v>0.65</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-4.34</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-4.61</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>2.48</v>
+      </c>
+      <c r="D23" s="5">
+        <v>2.18</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>0.84</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-0.12</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-0.96</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>14.42</v>
+      </c>
+      <c r="D24" s="5">
+        <v>14.02</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>2.16</v>
-      </c>
-      <c r="D17" s="6">
-        <v>0</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.16</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-12.12</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-12.45</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.33</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>50.61</v>
-      </c>
-      <c r="D18" s="6">
-        <v>52.27</v>
-      </c>
-      <c r="E18" s="8">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-17.63</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-15.01</v>
+      </c>
+      <c r="E26" s="6">
+        <v>2.62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>26.74</v>
-      </c>
-      <c r="D19" s="6">
-        <v>18.18</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-8.56</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-10.82</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-8.380000000000001</v>
+      </c>
+      <c r="E27" s="6">
+        <v>2.44</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>-25.16</v>
-      </c>
-      <c r="D20" s="6">
-        <v>-23.91</v>
-      </c>
-      <c r="E20" s="8">
-        <v>1.25</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-25.31</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-24.5</v>
+      </c>
+      <c r="E28" s="6">
+        <v>0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5">
+        <v>171.64</v>
+      </c>
+      <c r="D29" s="5">
+        <v>177.1</v>
+      </c>
+      <c r="E29" s="6">
+        <v>5.46</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5">
+        <v>397.1</v>
+      </c>
+      <c r="D30" s="5">
+        <v>408</v>
+      </c>
+      <c r="E30" s="6">
+        <v>10.9</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5">
+        <v>408.65</v>
+      </c>
+      <c r="D31" s="5">
+        <v>413.05</v>
+      </c>
+      <c r="E31" s="6">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="5">
+        <v>58.13</v>
+      </c>
+      <c r="D32" s="5">
+        <v>64.16</v>
+      </c>
+      <c r="E32" s="6">
+        <v>6.03</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="5">
+        <v>44.22</v>
+      </c>
+      <c r="D33" s="5">
+        <v>49.46</v>
+      </c>
+      <c r="E33" s="6">
+        <v>5.24</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="5">
+        <v>41.27</v>
+      </c>
+      <c r="D34" s="5">
+        <v>45.22</v>
+      </c>
+      <c r="E34" s="6">
+        <v>3.95</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C35" s="5">
+        <v>125.14</v>
+      </c>
+      <c r="D35" s="5">
+        <v>105.15</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-19.99</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-50.54</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-51.99</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-45.73</v>
+      </c>
+      <c r="D37" s="5">
+        <v>9.48</v>
+      </c>
+      <c r="E37" s="6">
+        <v>55.21</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>26.92</v>
-      </c>
-      <c r="D21" s="6">
-        <v>30.46</v>
-      </c>
-      <c r="E21" s="8">
-        <v>3.54</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="5">
+        <v>-49.34</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-46.13</v>
+      </c>
+      <c r="E38" s="6">
+        <v>3.21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="6">
-        <v>-32.76</v>
-      </c>
-      <c r="D22" s="6">
-        <v>-32.95</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>17.05</v>
-      </c>
-      <c r="D23" s="6">
-        <v>15.5</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-1.55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>43.39</v>
-      </c>
-      <c r="D24" s="6">
-        <v>37.19</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-6.2</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>-0.55</v>
-      </c>
-      <c r="D25" s="6">
-        <v>2.48</v>
-      </c>
-      <c r="E25" s="8">
-        <v>3.03</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>15.6</v>
-      </c>
-      <c r="D26" s="6">
-        <v>14.42</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-11.94</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-12.12</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-15.42</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-17.63</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-2.21</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-3.23</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-10.82</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-7.59</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-26.03</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-25.31</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.72</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-4.17</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-4.54</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="6">
-        <v>-34.81</v>
-      </c>
-      <c r="D32" s="6">
-        <v>-35.91</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-1.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>176.23</v>
-      </c>
-      <c r="D33" s="6">
-        <v>171.64</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-4.59</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>430.9</v>
-      </c>
-      <c r="D34" s="6">
-        <v>397.1</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-33.8</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>404.7</v>
-      </c>
-      <c r="D35" s="6">
-        <v>408.65</v>
-      </c>
-      <c r="E35" s="8">
-        <v>3.95</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>1024.7</v>
-      </c>
-      <c r="D36" s="6">
-        <v>1020.8</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-3.9</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="6">
-        <v>2.36</v>
-      </c>
-      <c r="D37" s="6">
-        <v>2.32</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-0.04</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>66.92</v>
-      </c>
-      <c r="D38" s="6">
-        <v>58.13</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-8.789999999999999</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>63.03</v>
-      </c>
-      <c r="D39" s="6">
-        <v>44.22</v>
+      <c r="B39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="5">
+        <v>10.35</v>
+      </c>
+      <c r="D39" s="5">
+        <v>-15.54</v>
       </c>
       <c r="E39" s="7">
-        <v>-18.81</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>37.52</v>
-      </c>
-      <c r="D40" s="6">
-        <v>41.27</v>
-      </c>
-      <c r="E40" s="8">
-        <v>3.75</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>55.87</v>
-      </c>
-      <c r="D41" s="6">
-        <v>54.43</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-1.44</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="6">
-        <v>49.01</v>
-      </c>
-      <c r="D42" s="6">
-        <v>43.05</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-5.96</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>70.31</v>
-      </c>
-      <c r="D43" s="6">
-        <v>125.14</v>
-      </c>
-      <c r="E43" s="8">
-        <v>54.83</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-71.22</v>
-      </c>
-      <c r="D44" s="6">
-        <v>1.45</v>
-      </c>
-      <c r="E44" s="8">
-        <v>72.67</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-74.69</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-45.73</v>
-      </c>
-      <c r="E45" s="8">
-        <v>28.96</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-67.56</v>
-      </c>
-      <c r="D46" s="6">
-        <v>-49.34</v>
-      </c>
-      <c r="E46" s="8">
-        <v>18.22</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>68.61</v>
-      </c>
-      <c r="D47" s="6">
-        <v>10.35</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-58.26</v>
+        <v>-25.89</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2427,60 +2219,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>72</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>48.2</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>51.3</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="11">
-        <v>-0</v>
-      </c>
-      <c r="G2" s="11">
-        <v>11.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>1.7</v>
+      </c>
+      <c r="G2" s="10">
+        <v>12.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -2582,37 +2374,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.2447</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.09519999999999999</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0074</v>
-      </c>
-      <c r="D2" s="14">
-        <v>-0.0328</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.221</v>
+      <c r="A2" s="13">
+        <v>0.2554</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.104</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0101</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.024</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2187</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="193" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -891,37 +891,37 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>177.1</v>
+        <v>176.35</v>
       </c>
       <c r="D2">
-        <v>3.18</v>
+        <v>-0.42</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>116.57</v>
+        <v>116.93</v>
       </c>
       <c r="G2">
-        <v>-15.01</v>
+        <v>-15.37</v>
       </c>
       <c r="H2">
-        <v>51.93</v>
+        <v>50.82</v>
       </c>
       <c r="I2">
-        <v>1.78</v>
+        <v>0.87</v>
       </c>
       <c r="J2">
-        <v>14.09</v>
+        <v>13.92</v>
       </c>
       <c r="K2">
-        <v>18.99</v>
+        <v>16.76</v>
       </c>
       <c r="L2">
-        <v>51.1</v>
+        <v>51.28</v>
       </c>
       <c r="M2">
-        <v>25.54</v>
+        <v>25.68</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -930,19 +930,19 @@
         <v>87</v>
       </c>
       <c r="P2">
-        <v>175.3</v>
+        <v>175.6</v>
       </c>
       <c r="Q2">
-        <v>166.6</v>
+        <v>167.72</v>
       </c>
       <c r="R2">
-        <v>160.12</v>
+        <v>160.83</v>
       </c>
       <c r="S2">
-        <v>166.88</v>
+        <v>167.08</v>
       </c>
       <c r="T2">
-        <v>6.12</v>
+        <v>5.55</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -957,34 +957,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>64.16</v>
+        <v>62.82</v>
       </c>
       <c r="Z2">
-        <v>5.13</v>
+        <v>5.06</v>
       </c>
       <c r="AA2">
-        <v>4.58</v>
+        <v>4.67</v>
       </c>
       <c r="AB2">
-        <v>0.5600000000000001</v>
+        <v>0.38</v>
       </c>
       <c r="AC2">
-        <v>52.68</v>
+        <v>43.14</v>
       </c>
       <c r="AD2">
-        <v>65.26000000000001</v>
+        <v>52.8</v>
       </c>
       <c r="AE2">
-        <v>5.08</v>
+        <v>4.94</v>
       </c>
       <c r="AF2">
-        <v>105.15</v>
+        <v>-28.62</v>
       </c>
       <c r="AG2">
-        <v>187.68</v>
+        <v>188.34</v>
       </c>
       <c r="AH2">
-        <v>145.53</v>
+        <v>147.1</v>
       </c>
       <c r="AI2">
         <v>165.9</v>
@@ -993,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>37.21</v>
+        <v>33.65</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>408</v>
+        <v>401.65</v>
       </c>
       <c r="D3">
-        <v>2.74</v>
+        <v>-1.56</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1016,46 +1016,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-8.380000000000001</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="H3">
-        <v>81.33</v>
+        <v>78.51000000000001</v>
       </c>
       <c r="I3">
-        <v>-4.72</v>
+        <v>-6.5</v>
       </c>
       <c r="J3">
-        <v>1.07</v>
+        <v>0.14</v>
       </c>
       <c r="K3">
-        <v>37.84</v>
+        <v>34.67</v>
       </c>
       <c r="L3">
-        <v>19.05</v>
+        <v>15.47</v>
       </c>
       <c r="M3">
-        <v>10.4</v>
+        <v>10.68</v>
       </c>
       <c r="N3">
         <v>79</v>
       </c>
       <c r="O3">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P3">
-        <v>419.47</v>
+        <v>413.89</v>
       </c>
       <c r="Q3">
-        <v>407.58</v>
+        <v>407.69</v>
       </c>
       <c r="R3">
-        <v>406.98</v>
+        <v>407.08</v>
       </c>
       <c r="S3">
-        <v>324.1</v>
+        <v>324.28</v>
       </c>
       <c r="T3">
-        <v>25.89</v>
+        <v>23.86</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1070,34 +1070,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>49.46</v>
+        <v>46.71</v>
       </c>
       <c r="Z3">
-        <v>5.16</v>
+        <v>3.73</v>
       </c>
       <c r="AA3">
-        <v>5.52</v>
+        <v>5.17</v>
       </c>
       <c r="AB3">
-        <v>-0.37</v>
+        <v>-1.43</v>
       </c>
       <c r="AC3">
-        <v>43.14</v>
+        <v>20.7</v>
       </c>
       <c r="AD3">
-        <v>60.79</v>
+        <v>41</v>
       </c>
       <c r="AE3">
-        <v>16.24</v>
+        <v>15.94</v>
       </c>
       <c r="AF3">
-        <v>-50.54</v>
+        <v>-71.98999999999999</v>
       </c>
       <c r="AG3">
-        <v>441.39</v>
+        <v>441.41</v>
       </c>
       <c r="AH3">
-        <v>373.77</v>
+        <v>373.98</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1106,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>37.72</v>
+        <v>33.81</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,10 +1117,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>413.05</v>
+        <v>406.95</v>
       </c>
       <c r="D4">
-        <v>1.08</v>
+        <v>-1.48</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1129,46 +1129,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-24.5</v>
+        <v>-25.62</v>
       </c>
       <c r="H4">
-        <v>19.83</v>
+        <v>18.06</v>
       </c>
       <c r="I4">
-        <v>0.13</v>
+        <v>-1.06</v>
       </c>
       <c r="J4">
-        <v>-4.29</v>
+        <v>-5.31</v>
       </c>
       <c r="K4">
-        <v>2.18</v>
+        <v>1.46</v>
       </c>
       <c r="L4">
-        <v>-21.86</v>
+        <v>-23.43</v>
       </c>
       <c r="M4">
-        <v>-21.87</v>
+        <v>-21.7</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>408.89</v>
+        <v>408.02</v>
       </c>
       <c r="Q4">
-        <v>420.33</v>
+        <v>419.14</v>
       </c>
       <c r="R4">
-        <v>421.87</v>
+        <v>421.96</v>
       </c>
       <c r="S4">
-        <v>423.38</v>
+        <v>422.78</v>
       </c>
       <c r="T4">
-        <v>-2.44</v>
+        <v>-3.74</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1183,34 +1183,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>45.22</v>
+        <v>41.1</v>
       </c>
       <c r="Z4">
-        <v>-3.54</v>
+        <v>-3.94</v>
       </c>
       <c r="AA4">
-        <v>-1.66</v>
+        <v>-2.11</v>
       </c>
       <c r="AB4">
-        <v>-1.88</v>
+        <v>-1.82</v>
       </c>
       <c r="AC4">
-        <v>21.32</v>
+        <v>27.97</v>
       </c>
       <c r="AD4">
-        <v>9.43</v>
+        <v>18.76</v>
       </c>
       <c r="AE4">
-        <v>11.94</v>
+        <v>11.83</v>
       </c>
       <c r="AF4">
-        <v>9.48</v>
+        <v>-39</v>
       </c>
       <c r="AG4">
-        <v>436.22</v>
+        <v>435.31</v>
       </c>
       <c r="AH4">
-        <v>404.44</v>
+        <v>402.97</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1219,7 +1219,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>18.19</v>
+        <v>16.42</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1020.8</v>
+        <v>1015</v>
       </c>
       <c r="D5">
-        <v>0</v>
+        <v>-0.57</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1242,46 +1242,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-4.54</v>
+        <v>-5.08</v>
       </c>
       <c r="H5">
-        <v>43.22</v>
+        <v>42.41</v>
       </c>
       <c r="I5">
-        <v>-0.63</v>
+        <v>0.6</v>
       </c>
       <c r="J5">
-        <v>-0.62</v>
+        <v>-1.73</v>
       </c>
       <c r="K5">
-        <v>14.02</v>
+        <v>13.14</v>
       </c>
       <c r="L5">
-        <v>30.33</v>
+        <v>29.62</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="N5">
         <v>60</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>1018.54</v>
+        <v>1019.76</v>
       </c>
       <c r="Q5">
-        <v>1020.06</v>
+        <v>1017.64</v>
       </c>
       <c r="R5">
-        <v>982.28</v>
+        <v>984.6799999999999</v>
       </c>
       <c r="S5">
-        <v>901.8</v>
+        <v>902.84</v>
       </c>
       <c r="T5">
-        <v>13.2</v>
+        <v>12.42</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1296,43 +1296,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>54.43</v>
+        <v>52.12</v>
       </c>
       <c r="Z5">
-        <v>8.98</v>
+        <v>7.99</v>
       </c>
       <c r="AA5">
-        <v>11.65</v>
+        <v>10.92</v>
       </c>
       <c r="AB5">
-        <v>-2.67</v>
+        <v>-2.93</v>
       </c>
       <c r="AC5">
-        <v>53.76</v>
+        <v>35.43</v>
       </c>
       <c r="AD5">
-        <v>48.8</v>
+        <v>47.38</v>
       </c>
       <c r="AE5">
-        <v>20.64</v>
+        <v>20.15</v>
       </c>
       <c r="AF5">
-        <v>-46.13</v>
+        <v>-73.06</v>
       </c>
       <c r="AG5">
-        <v>1057.33</v>
+        <v>1048.83</v>
       </c>
       <c r="AH5">
-        <v>982.79</v>
+        <v>986.4400000000001</v>
       </c>
       <c r="AI5">
-        <v>1076.68</v>
+        <v>1073.7</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>12.51</v>
+        <v>12.24</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1343,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.32</v>
+        <v>2.27</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-2.16</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1355,25 +1355,25 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-35.91</v>
+        <v>-37.29</v>
       </c>
       <c r="H6">
-        <v>26.09</v>
+        <v>23.37</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>-2.16</v>
       </c>
       <c r="J6">
-        <v>-1.69</v>
+        <v>-3.4</v>
       </c>
       <c r="K6">
-        <v>-12.45</v>
+        <v>-14.02</v>
       </c>
       <c r="L6">
-        <v>-32.16</v>
+        <v>-33.82</v>
       </c>
       <c r="M6">
-        <v>-2.4</v>
+        <v>-2.3</v>
       </c>
       <c r="N6">
         <v>21</v>
@@ -1382,7 +1382,7 @@
         <v>11</v>
       </c>
       <c r="P6">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="Q6">
         <v>2.33</v>
@@ -1391,10 +1391,10 @@
         <v>2.41</v>
       </c>
       <c r="S6">
-        <v>2.72</v>
+        <v>2.71</v>
       </c>
       <c r="T6">
-        <v>-14.6</v>
+        <v>-16.27</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1409,10 +1409,10 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>43.05</v>
+        <v>36.6</v>
       </c>
       <c r="Z6">
-        <v>-0.02</v>
+        <v>-0.03</v>
       </c>
       <c r="AA6">
         <v>-0.03</v>
@@ -1421,22 +1421,22 @@
         <v>0</v>
       </c>
       <c r="AC6">
-        <v>64.94</v>
+        <v>31.61</v>
       </c>
       <c r="AD6">
-        <v>76.39</v>
+        <v>59.7</v>
       </c>
       <c r="AE6">
         <v>0.08</v>
       </c>
       <c r="AF6">
-        <v>-15.54</v>
+        <v>76.48</v>
       </c>
       <c r="AG6">
         <v>2.39</v>
       </c>
       <c r="AH6">
-        <v>2.28</v>
+        <v>2.27</v>
       </c>
       <c r="AI6">
         <v>2.53</v>
@@ -1445,7 +1445,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>19.04</v>
+        <v>19.86</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F39"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1646,10 +1646,10 @@
         <v>10.83</v>
       </c>
       <c r="D7" s="5">
-        <v>14.09</v>
+        <v>13.92</v>
       </c>
       <c r="E7" s="6">
-        <v>3.26</v>
+        <v>3.09</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1663,10 +1663,10 @@
         <v>-1.45</v>
       </c>
       <c r="D8" s="5">
-        <v>1.07</v>
+        <v>0.14</v>
       </c>
       <c r="E8" s="6">
-        <v>2.52</v>
+        <v>1.59</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1680,10 +1680,10 @@
         <v>-6.52</v>
       </c>
       <c r="D9" s="5">
-        <v>-4.29</v>
+        <v>-5.31</v>
       </c>
       <c r="E9" s="6">
-        <v>2.23</v>
+        <v>1.21</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1697,10 +1697,10 @@
         <v>0.72</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.62</v>
+        <v>-1.73</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.34</v>
+        <v>-2.45</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1714,10 +1714,10 @@
         <v>-3.73</v>
       </c>
       <c r="D11" s="5">
-        <v>-1.69</v>
+        <v>-3.4</v>
       </c>
       <c r="E11" s="6">
-        <v>2.04</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1731,10 +1731,10 @@
         <v>-3.3</v>
       </c>
       <c r="D12" s="5">
-        <v>1.78</v>
+        <v>0.87</v>
       </c>
       <c r="E12" s="6">
-        <v>5.08</v>
+        <v>4.17</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1748,10 +1748,10 @@
         <v>-9.390000000000001</v>
       </c>
       <c r="D13" s="5">
-        <v>-4.72</v>
+        <v>-6.5</v>
       </c>
       <c r="E13" s="6">
-        <v>4.67</v>
+        <v>2.89</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1765,10 +1765,10 @@
         <v>-4.61</v>
       </c>
       <c r="D14" s="5">
-        <v>0.13</v>
+        <v>-1.06</v>
       </c>
       <c r="E14" s="6">
-        <v>4.74</v>
+        <v>3.55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1782,282 +1782,282 @@
         <v>-0.12</v>
       </c>
       <c r="D15" s="5">
-        <v>-0.63</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-0.51</v>
+        <v>0.6</v>
+      </c>
+      <c r="E15" s="6">
+        <v>0.72</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>52.27</v>
+        <v>0</v>
       </c>
       <c r="D16" s="5">
-        <v>51.1</v>
+        <v>-2.16</v>
       </c>
       <c r="E16" s="7">
-        <v>-1.17</v>
+        <v>-2.16</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>18.18</v>
+        <v>52.27</v>
       </c>
       <c r="D17" s="5">
-        <v>19.05</v>
-      </c>
-      <c r="E17" s="6">
-        <v>0.87</v>
+        <v>51.28</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.99</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>-23.91</v>
+        <v>18.18</v>
       </c>
       <c r="D18" s="5">
-        <v>-21.86</v>
-      </c>
-      <c r="E18" s="6">
-        <v>2.05</v>
+        <v>15.47</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.71</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>30.46</v>
+        <v>-23.91</v>
       </c>
       <c r="D19" s="5">
-        <v>30.33</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.13</v>
+        <v>-23.43</v>
+      </c>
+      <c r="E19" s="6">
+        <v>0.48</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>-32.95</v>
+        <v>30.46</v>
       </c>
       <c r="D20" s="5">
-        <v>-32.16</v>
-      </c>
-      <c r="E20" s="6">
-        <v>0.79</v>
+        <v>29.62</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-0.84</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>15.5</v>
+        <v>-32.95</v>
       </c>
       <c r="D21" s="5">
-        <v>18.99</v>
-      </c>
-      <c r="E21" s="6">
-        <v>3.49</v>
+        <v>-33.82</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.87</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>37.19</v>
+        <v>15.5</v>
       </c>
       <c r="D22" s="5">
-        <v>37.84</v>
+        <v>16.76</v>
       </c>
       <c r="E22" s="6">
-        <v>0.65</v>
+        <v>1.26</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>2.48</v>
+        <v>37.19</v>
       </c>
       <c r="D23" s="5">
-        <v>2.18</v>
+        <v>34.67</v>
       </c>
       <c r="E23" s="7">
-        <v>-0.3</v>
+        <v>-2.52</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>14.42</v>
+        <v>2.48</v>
       </c>
       <c r="D24" s="5">
-        <v>14.02</v>
+        <v>1.46</v>
       </c>
       <c r="E24" s="7">
-        <v>-0.4</v>
+        <v>-1.02</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>-12.12</v>
+        <v>14.42</v>
       </c>
       <c r="D25" s="5">
-        <v>-12.45</v>
+        <v>13.14</v>
       </c>
       <c r="E25" s="7">
-        <v>-0.33</v>
+        <v>-1.28</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>-17.63</v>
+        <v>-12.12</v>
       </c>
       <c r="D26" s="5">
-        <v>-15.01</v>
-      </c>
-      <c r="E26" s="6">
-        <v>2.62</v>
+        <v>-14.02</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-10.82</v>
+        <v>-17.63</v>
       </c>
       <c r="D27" s="5">
-        <v>-8.380000000000001</v>
+        <v>-15.37</v>
       </c>
       <c r="E27" s="6">
-        <v>2.44</v>
+        <v>2.26</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-25.31</v>
+        <v>-10.82</v>
       </c>
       <c r="D28" s="5">
-        <v>-24.5</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="E28" s="6">
-        <v>0.8100000000000001</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>171.64</v>
+        <v>-25.31</v>
       </c>
       <c r="D29" s="5">
-        <v>177.1</v>
-      </c>
-      <c r="E29" s="6">
-        <v>5.46</v>
+        <v>-25.62</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>397.1</v>
+        <v>-4.54</v>
       </c>
       <c r="D30" s="5">
-        <v>408</v>
-      </c>
-      <c r="E30" s="6">
-        <v>10.9</v>
+        <v>-5.08</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>408.65</v>
+        <v>-35.91</v>
       </c>
       <c r="D31" s="5">
-        <v>413.05</v>
-      </c>
-      <c r="E31" s="6">
-        <v>4.4</v>
+        <v>-37.29</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.38</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2065,16 +2065,16 @@
         <v>37</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>58.13</v>
+        <v>171.64</v>
       </c>
       <c r="D32" s="5">
-        <v>64.16</v>
+        <v>176.35</v>
       </c>
       <c r="E32" s="6">
-        <v>6.03</v>
+        <v>4.71</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2082,16 +2082,16 @@
         <v>38</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>44.22</v>
+        <v>397.1</v>
       </c>
       <c r="D33" s="5">
-        <v>49.46</v>
+        <v>401.65</v>
       </c>
       <c r="E33" s="6">
-        <v>5.24</v>
+        <v>4.55</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2099,101 +2099,220 @@
         <v>39</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>41.27</v>
+        <v>408.65</v>
       </c>
       <c r="D34" s="5">
-        <v>45.22</v>
-      </c>
-      <c r="E34" s="6">
-        <v>3.95</v>
+        <v>406.95</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-1.7</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>125.14</v>
+        <v>1020.8</v>
       </c>
       <c r="D35" s="5">
-        <v>105.15</v>
+        <v>1015</v>
       </c>
       <c r="E35" s="7">
-        <v>-19.99</v>
+        <v>-5.8</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>1.45</v>
+        <v>2.32</v>
       </c>
       <c r="D36" s="5">
-        <v>-50.54</v>
+        <v>2.27</v>
       </c>
       <c r="E36" s="7">
-        <v>-51.99</v>
+        <v>-0.05</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>-45.73</v>
+        <v>58.13</v>
       </c>
       <c r="D37" s="5">
-        <v>9.48</v>
+        <v>62.82</v>
       </c>
       <c r="E37" s="6">
-        <v>55.21</v>
+        <v>4.69</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>-49.34</v>
+        <v>44.22</v>
       </c>
       <c r="D38" s="5">
-        <v>-46.13</v>
+        <v>46.71</v>
       </c>
       <c r="E38" s="6">
-        <v>3.21</v>
+        <v>2.49</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>41.27</v>
+      </c>
+      <c r="D39" s="5">
+        <v>41.1</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>54.43</v>
+      </c>
+      <c r="D40" s="5">
+        <v>52.12</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-2.31</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>43.05</v>
+      </c>
+      <c r="D41" s="5">
+        <v>36.6</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-6.45</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B42" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="5">
+      <c r="C42" s="5">
+        <v>125.14</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-28.62</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-153.76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>1.45</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-71.98999999999999</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-73.44</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-45.73</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-39</v>
+      </c>
+      <c r="E44" s="6">
+        <v>6.73</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-49.34</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-73.06</v>
+      </c>
+      <c r="E45" s="7">
+        <v>-23.72</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B46" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="5">
         <v>10.35</v>
       </c>
-      <c r="D39" s="5">
-        <v>-15.54</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-25.89</v>
+      <c r="D46" s="5">
+        <v>76.48</v>
+      </c>
+      <c r="E46" s="6">
+        <v>66.13</v>
       </c>
     </row>
   </sheetData>
@@ -2258,16 +2377,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>51.3</v>
+        <v>47.9</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>1.7</v>
+        <v>0.7</v>
       </c>
       <c r="G2" s="10">
-        <v>12.1</v>
+        <v>10.4</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2392,19 +2511,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.2554</v>
+        <v>0.2568</v>
       </c>
       <c r="B2" s="13">
-        <v>0.104</v>
+        <v>0.1068</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0101</v>
+        <v>0.0111</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.024</v>
+        <v>-0.023</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2187</v>
+        <v>-0.217</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -252,14 +252,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +292,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -750,7 +750,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
     <col min="18" max="18" width="8.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
@@ -891,58 +892,58 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>176.35</v>
+        <v>173.1</v>
       </c>
       <c r="D2">
-        <v>-0.42</v>
+        <v>-1.84</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>116.93</v>
+        <v>119.11</v>
       </c>
       <c r="G2">
-        <v>-15.37</v>
+        <v>-16.93</v>
       </c>
       <c r="H2">
-        <v>50.82</v>
+        <v>45.33</v>
       </c>
       <c r="I2">
-        <v>0.87</v>
+        <v>-2.04</v>
       </c>
       <c r="J2">
-        <v>13.92</v>
+        <v>12.45</v>
       </c>
       <c r="K2">
-        <v>16.76</v>
+        <v>13.96</v>
       </c>
       <c r="L2">
-        <v>51.28</v>
+        <v>48.04</v>
       </c>
       <c r="M2">
-        <v>25.68</v>
+        <v>26.5</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="P2">
-        <v>175.6</v>
+        <v>174.88</v>
       </c>
       <c r="Q2">
-        <v>167.72</v>
+        <v>168.75</v>
       </c>
       <c r="R2">
-        <v>160.83</v>
+        <v>161.41</v>
       </c>
       <c r="S2">
-        <v>167.08</v>
+        <v>167.26</v>
       </c>
       <c r="T2">
-        <v>5.55</v>
+        <v>3.49</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -957,34 +958,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>62.82</v>
+        <v>57.25</v>
       </c>
       <c r="Z2">
-        <v>5.06</v>
+        <v>4.68</v>
       </c>
       <c r="AA2">
-        <v>4.67</v>
+        <v>4.68</v>
       </c>
       <c r="AB2">
-        <v>0.38</v>
+        <v>0.01</v>
       </c>
       <c r="AC2">
-        <v>43.14</v>
+        <v>34.47</v>
       </c>
       <c r="AD2">
-        <v>52.8</v>
+        <v>43.43</v>
       </c>
       <c r="AE2">
-        <v>4.94</v>
+        <v>4.82</v>
       </c>
       <c r="AF2">
-        <v>-28.62</v>
+        <v>-50.01</v>
       </c>
       <c r="AG2">
-        <v>188.34</v>
+        <v>188.2</v>
       </c>
       <c r="AH2">
-        <v>147.1</v>
+        <v>149.31</v>
       </c>
       <c r="AI2">
         <v>165.9</v>
@@ -993,7 +994,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>33.65</v>
+        <v>29.26</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1005,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>401.65</v>
+        <v>398.55</v>
       </c>
       <c r="D3">
-        <v>-1.56</v>
+        <v>-0.77</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1016,46 +1017,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-9.800000000000001</v>
+        <v>-10.5</v>
       </c>
       <c r="H3">
-        <v>78.51000000000001</v>
+        <v>77.13</v>
       </c>
       <c r="I3">
-        <v>-6.5</v>
+        <v>-7.7</v>
       </c>
       <c r="J3">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="K3">
-        <v>34.67</v>
+        <v>29.95</v>
       </c>
       <c r="L3">
-        <v>15.47</v>
+        <v>8.01</v>
       </c>
       <c r="M3">
-        <v>10.68</v>
+        <v>10.48</v>
       </c>
       <c r="N3">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O3">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>413.89</v>
+        <v>407.24</v>
       </c>
       <c r="Q3">
-        <v>407.69</v>
+        <v>407.97</v>
       </c>
       <c r="R3">
         <v>407.08</v>
       </c>
       <c r="S3">
-        <v>324.28</v>
+        <v>324.46</v>
       </c>
       <c r="T3">
-        <v>23.86</v>
+        <v>22.84</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1070,34 +1071,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>46.71</v>
+        <v>45.38</v>
       </c>
       <c r="Z3">
-        <v>3.73</v>
+        <v>2.33</v>
       </c>
       <c r="AA3">
-        <v>5.17</v>
+        <v>4.6</v>
       </c>
       <c r="AB3">
-        <v>-1.43</v>
+        <v>-2.27</v>
       </c>
       <c r="AC3">
-        <v>20.7</v>
+        <v>16.89</v>
       </c>
       <c r="AD3">
-        <v>41</v>
+        <v>26.91</v>
       </c>
       <c r="AE3">
-        <v>15.94</v>
+        <v>15.43</v>
       </c>
       <c r="AF3">
-        <v>-71.98999999999999</v>
+        <v>-76.69</v>
       </c>
       <c r="AG3">
-        <v>441.41</v>
+        <v>441.27</v>
       </c>
       <c r="AH3">
-        <v>373.98</v>
+        <v>374.67</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1106,7 +1107,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>33.81</v>
+        <v>31.46</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,10 +1118,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>406.95</v>
+        <v>408</v>
       </c>
       <c r="D4">
-        <v>-1.48</v>
+        <v>0.26</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1129,46 +1130,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-25.62</v>
+        <v>-25.42</v>
       </c>
       <c r="H4">
-        <v>18.06</v>
+        <v>18.36</v>
       </c>
       <c r="I4">
-        <v>-1.06</v>
+        <v>0.31</v>
       </c>
       <c r="J4">
-        <v>-5.31</v>
+        <v>-5.28</v>
       </c>
       <c r="K4">
-        <v>1.46</v>
+        <v>0.83</v>
       </c>
       <c r="L4">
-        <v>-23.43</v>
+        <v>-24.14</v>
       </c>
       <c r="M4">
-        <v>-21.7</v>
+        <v>-21.18</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>408.02</v>
+        <v>408.27</v>
       </c>
       <c r="Q4">
-        <v>419.14</v>
+        <v>418.15</v>
       </c>
       <c r="R4">
-        <v>421.96</v>
+        <v>422.12</v>
       </c>
       <c r="S4">
-        <v>422.78</v>
+        <v>422.21</v>
       </c>
       <c r="T4">
-        <v>-3.74</v>
+        <v>-3.37</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1183,34 +1184,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.1</v>
+        <v>42.07</v>
       </c>
       <c r="Z4">
-        <v>-3.94</v>
+        <v>-4.12</v>
       </c>
       <c r="AA4">
-        <v>-2.11</v>
+        <v>-2.52</v>
       </c>
       <c r="AB4">
-        <v>-1.82</v>
+        <v>-1.6</v>
       </c>
       <c r="AC4">
-        <v>27.97</v>
+        <v>29.47</v>
       </c>
       <c r="AD4">
-        <v>18.76</v>
+        <v>26.25</v>
       </c>
       <c r="AE4">
-        <v>11.83</v>
+        <v>12.04</v>
       </c>
       <c r="AF4">
-        <v>-39</v>
+        <v>-51.67</v>
       </c>
       <c r="AG4">
-        <v>435.31</v>
+        <v>434.5</v>
       </c>
       <c r="AH4">
-        <v>402.97</v>
+        <v>401.79</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1219,7 +1220,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>16.42</v>
+        <v>16.84</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1231,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1015</v>
+        <v>1016.7</v>
       </c>
       <c r="D5">
-        <v>-0.57</v>
+        <v>0.17</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1242,46 +1243,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-5.08</v>
+        <v>-4.92</v>
       </c>
       <c r="H5">
-        <v>42.41</v>
+        <v>42.64</v>
       </c>
       <c r="I5">
-        <v>0.6</v>
+        <v>-0.08</v>
       </c>
       <c r="J5">
-        <v>-1.73</v>
+        <v>-4.4</v>
       </c>
       <c r="K5">
-        <v>13.14</v>
+        <v>12.97</v>
       </c>
       <c r="L5">
-        <v>29.62</v>
+        <v>31.45</v>
       </c>
       <c r="M5">
-        <v>1.11</v>
+        <v>1.36</v>
       </c>
       <c r="N5">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1019.76</v>
+        <v>1019.6</v>
       </c>
       <c r="Q5">
-        <v>1017.64</v>
+        <v>1015.01</v>
       </c>
       <c r="R5">
-        <v>984.6799999999999</v>
+        <v>986.5599999999999</v>
       </c>
       <c r="S5">
-        <v>902.84</v>
+        <v>903.92</v>
       </c>
       <c r="T5">
-        <v>12.42</v>
+        <v>12.48</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1296,43 +1297,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>52.12</v>
+        <v>52.75</v>
       </c>
       <c r="Z5">
-        <v>7.99</v>
+        <v>7.25</v>
       </c>
       <c r="AA5">
-        <v>10.92</v>
+        <v>10.18</v>
       </c>
       <c r="AB5">
         <v>-2.93</v>
       </c>
       <c r="AC5">
-        <v>35.43</v>
+        <v>25.89</v>
       </c>
       <c r="AD5">
-        <v>47.38</v>
+        <v>38.36</v>
       </c>
       <c r="AE5">
-        <v>20.15</v>
+        <v>19.36</v>
       </c>
       <c r="AF5">
-        <v>-73.06</v>
+        <v>-77.75</v>
       </c>
       <c r="AG5">
-        <v>1048.83</v>
+        <v>1034.56</v>
       </c>
       <c r="AH5">
-        <v>986.4400000000001</v>
+        <v>995.45</v>
       </c>
       <c r="AI5">
-        <v>1073.7</v>
+        <v>1070.23</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>12.24</v>
+        <v>11.99</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1344,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.27</v>
+        <v>2.25</v>
       </c>
       <c r="D6">
-        <v>-2.16</v>
+        <v>-0.88</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1355,25 +1356,25 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-37.29</v>
+        <v>-37.85</v>
       </c>
       <c r="H6">
-        <v>23.37</v>
+        <v>22.28</v>
       </c>
       <c r="I6">
-        <v>-2.16</v>
+        <v>-3.85</v>
       </c>
       <c r="J6">
-        <v>-3.4</v>
+        <v>-4.26</v>
       </c>
       <c r="K6">
-        <v>-14.02</v>
+        <v>-14.12</v>
       </c>
       <c r="L6">
         <v>-33.82</v>
       </c>
       <c r="M6">
-        <v>-2.3</v>
+        <v>-2.01</v>
       </c>
       <c r="N6">
         <v>21</v>
@@ -1382,19 +1383,19 @@
         <v>11</v>
       </c>
       <c r="P6">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="Q6">
         <v>2.33</v>
       </c>
       <c r="R6">
-        <v>2.41</v>
+        <v>2.4</v>
       </c>
       <c r="S6">
         <v>2.71</v>
       </c>
       <c r="T6">
-        <v>-16.27</v>
+        <v>-16.85</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1409,7 +1410,7 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>36.6</v>
+        <v>34.38</v>
       </c>
       <c r="Z6">
         <v>-0.03</v>
@@ -1418,34 +1419,34 @@
         <v>-0.03</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC6">
-        <v>31.61</v>
+        <v>10.88</v>
       </c>
       <c r="AD6">
-        <v>59.7</v>
+        <v>35.81</v>
       </c>
       <c r="AE6">
         <v>0.08</v>
       </c>
       <c r="AF6">
-        <v>76.48</v>
+        <v>9.74</v>
       </c>
       <c r="AG6">
-        <v>2.39</v>
+        <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>2.27</v>
+        <v>2.26</v>
       </c>
       <c r="AI6">
-        <v>2.53</v>
+        <v>2.49</v>
       </c>
       <c r="AJ6" t="s">
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>19.86</v>
+        <v>21.09</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1643,13 +1644,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>10.83</v>
+        <v>13.92</v>
       </c>
       <c r="D7" s="5">
-        <v>13.92</v>
+        <v>12.45</v>
       </c>
       <c r="E7" s="6">
-        <v>3.09</v>
+        <v>-1.47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1660,13 +1661,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>-1.45</v>
+        <v>0.14</v>
       </c>
       <c r="D8" s="5">
-        <v>0.14</v>
+        <v>-0.2</v>
       </c>
       <c r="E8" s="6">
-        <v>1.59</v>
+        <v>-0.34</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1677,13 +1678,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-6.52</v>
+        <v>-5.31</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.31</v>
-      </c>
-      <c r="E9" s="6">
-        <v>1.21</v>
+        <v>-5.28</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.03</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1694,13 +1695,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>0.72</v>
+        <v>-1.73</v>
       </c>
       <c r="D10" s="5">
-        <v>-1.73</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-2.45</v>
+        <v>-4.4</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.67</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1711,13 +1712,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>-3.73</v>
+        <v>-3.4</v>
       </c>
       <c r="D11" s="5">
-        <v>-3.4</v>
+        <v>-4.26</v>
       </c>
       <c r="E11" s="6">
-        <v>0.33</v>
+        <v>-0.86</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1728,13 +1729,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-3.3</v>
+        <v>0.87</v>
       </c>
       <c r="D12" s="5">
-        <v>0.87</v>
+        <v>-2.04</v>
       </c>
       <c r="E12" s="6">
-        <v>4.17</v>
+        <v>-2.91</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1745,13 +1746,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-9.390000000000001</v>
+        <v>-6.5</v>
       </c>
       <c r="D13" s="5">
-        <v>-6.5</v>
+        <v>-7.7</v>
       </c>
       <c r="E13" s="6">
-        <v>2.89</v>
+        <v>-1.2</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1762,13 +1763,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-4.61</v>
+        <v>-1.06</v>
       </c>
       <c r="D14" s="5">
-        <v>-1.06</v>
-      </c>
-      <c r="E14" s="6">
-        <v>3.55</v>
+        <v>0.31</v>
+      </c>
+      <c r="E14" s="7">
+        <v>1.37</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1779,13 +1780,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-0.12</v>
+        <v>0.6</v>
       </c>
       <c r="D15" s="5">
-        <v>0.6</v>
+        <v>-0.08</v>
       </c>
       <c r="E15" s="6">
-        <v>0.72</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1796,13 +1797,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>0</v>
+        <v>-2.16</v>
       </c>
       <c r="D16" s="5">
-        <v>-2.16</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.16</v>
+        <v>-3.85</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-1.69</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1813,13 +1814,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>52.27</v>
+        <v>51.28</v>
       </c>
       <c r="D17" s="5">
-        <v>51.28</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.99</v>
+        <v>48.04</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-3.24</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1830,13 +1831,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>18.18</v>
+        <v>15.47</v>
       </c>
       <c r="D18" s="5">
-        <v>15.47</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.71</v>
+        <v>8.01</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-7.46</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1847,13 +1848,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-23.91</v>
+        <v>-23.43</v>
       </c>
       <c r="D19" s="5">
-        <v>-23.43</v>
+        <v>-24.14</v>
       </c>
       <c r="E19" s="6">
-        <v>0.48</v>
+        <v>-0.71</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1864,455 +1865,472 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>30.46</v>
+        <v>29.62</v>
       </c>
       <c r="D20" s="5">
-        <v>29.62</v>
+        <v>31.45</v>
       </c>
       <c r="E20" s="7">
-        <v>-0.84</v>
+        <v>1.83</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C21" s="5">
-        <v>-32.95</v>
+        <v>16.76</v>
       </c>
       <c r="D21" s="5">
-        <v>-33.82</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-0.87</v>
+        <v>13.96</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-2.8</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>15.5</v>
+        <v>34.67</v>
       </c>
       <c r="D22" s="5">
-        <v>16.76</v>
+        <v>29.95</v>
       </c>
       <c r="E22" s="6">
-        <v>1.26</v>
+        <v>-4.72</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>37.19</v>
+        <v>1.46</v>
       </c>
       <c r="D23" s="5">
-        <v>34.67</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-2.52</v>
+        <v>0.83</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>2.48</v>
+        <v>13.14</v>
       </c>
       <c r="D24" s="5">
-        <v>1.46</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-1.02</v>
+        <v>12.97</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.17</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>14.42</v>
+        <v>-14.02</v>
       </c>
       <c r="D25" s="5">
-        <v>13.14</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.28</v>
+        <v>-14.12</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="C26" s="5">
-        <v>-12.12</v>
+        <v>-15.37</v>
       </c>
       <c r="D26" s="5">
-        <v>-14.02</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.9</v>
+        <v>-16.93</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.56</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-17.63</v>
+        <v>-9.800000000000001</v>
       </c>
       <c r="D27" s="5">
-        <v>-15.37</v>
+        <v>-10.5</v>
       </c>
       <c r="E27" s="6">
-        <v>2.26</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-10.82</v>
+        <v>-25.62</v>
       </c>
       <c r="D28" s="5">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="E28" s="6">
-        <v>1.02</v>
+        <v>-25.42</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.2</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-25.31</v>
+        <v>-5.08</v>
       </c>
       <c r="D29" s="5">
-        <v>-25.62</v>
+        <v>-4.92</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.31</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-4.54</v>
+        <v>-37.29</v>
       </c>
       <c r="D30" s="5">
-        <v>-5.08</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.54</v>
+        <v>-37.85</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.5600000000000001</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C31" s="5">
-        <v>-35.91</v>
+        <v>176.35</v>
       </c>
       <c r="D31" s="5">
-        <v>-37.29</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-1.38</v>
+        <v>173.1</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-3.25</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>171.64</v>
+        <v>401.65</v>
       </c>
       <c r="D32" s="5">
-        <v>176.35</v>
+        <v>398.55</v>
       </c>
       <c r="E32" s="6">
-        <v>4.71</v>
+        <v>-3.1</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="3" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>397.1</v>
+        <v>406.95</v>
       </c>
       <c r="D33" s="5">
-        <v>401.65</v>
-      </c>
-      <c r="E33" s="6">
-        <v>4.55</v>
+        <v>408</v>
+      </c>
+      <c r="E33" s="7">
+        <v>1.05</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>408.65</v>
+        <v>1015</v>
       </c>
       <c r="D34" s="5">
-        <v>406.95</v>
+        <v>1016.7</v>
       </c>
       <c r="E34" s="7">
-        <v>-1.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1020.8</v>
+        <v>2.27</v>
       </c>
       <c r="D35" s="5">
-        <v>1015</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-5.8</v>
+        <v>2.25</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-0.02</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2</v>
+        <v>13</v>
       </c>
       <c r="C36" s="5">
-        <v>2.32</v>
+        <v>79</v>
       </c>
       <c r="D36" s="5">
-        <v>2.27</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.05</v>
+        <v>60</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-19</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="5">
-        <v>58.13</v>
+        <v>60</v>
       </c>
       <c r="D37" s="5">
-        <v>62.82</v>
-      </c>
-      <c r="E37" s="6">
-        <v>4.69</v>
+        <v>79</v>
+      </c>
+      <c r="E37" s="7">
+        <v>19</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>44.22</v>
+        <v>62.82</v>
       </c>
       <c r="D38" s="5">
-        <v>46.71</v>
+        <v>57.25</v>
       </c>
       <c r="E38" s="6">
-        <v>2.49</v>
+        <v>-5.57</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>41.27</v>
+        <v>46.71</v>
       </c>
       <c r="D39" s="5">
-        <v>41.1</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-0.17</v>
+        <v>45.38</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>54.43</v>
+        <v>41.1</v>
       </c>
       <c r="D40" s="5">
-        <v>52.12</v>
+        <v>42.07</v>
       </c>
       <c r="E40" s="7">
-        <v>-2.31</v>
+        <v>0.97</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>43.05</v>
+        <v>52.12</v>
       </c>
       <c r="D41" s="5">
-        <v>36.6</v>
+        <v>52.75</v>
       </c>
       <c r="E41" s="7">
-        <v>-6.45</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="5">
-        <v>125.14</v>
+        <v>36.6</v>
       </c>
       <c r="D42" s="5">
-        <v>-28.62</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-153.76</v>
+        <v>34.38</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-2.22</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>1.45</v>
+        <v>-28.62</v>
       </c>
       <c r="D43" s="5">
-        <v>-71.98999999999999</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-73.44</v>
+        <v>-50.01</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-21.39</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-45.73</v>
+        <v>-71.98999999999999</v>
       </c>
       <c r="D44" s="5">
-        <v>-39</v>
+        <v>-76.69</v>
       </c>
       <c r="E44" s="6">
-        <v>6.73</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-49.34</v>
+        <v>-39</v>
       </c>
       <c r="D45" s="5">
-        <v>-73.06</v>
-      </c>
-      <c r="E45" s="7">
-        <v>-23.72</v>
+        <v>-51.67</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-12.67</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>10.35</v>
+        <v>-73.06</v>
       </c>
       <c r="D46" s="5">
+        <v>-77.75</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-4.69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
         <v>76.48</v>
       </c>
-      <c r="E46" s="6">
-        <v>66.13</v>
+      <c r="D47" s="5">
+        <v>9.74</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-66.73999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2377,16 +2395,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>47.9</v>
+        <v>46.4</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>0.7</v>
+        <v>-0.3</v>
       </c>
       <c r="G2" s="10">
-        <v>10.4</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2511,19 +2529,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.2568</v>
+        <v>0.265</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1068</v>
+        <v>0.1048</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0111</v>
+        <v>0.0136</v>
       </c>
       <c r="D2" s="13">
-        <v>-0.023</v>
+        <v>-0.0201</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.217</v>
+        <v>-0.2118</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="209" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.8 → 49.2</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.8</t>
+  </si>
+  <si>
+    <t>49.2</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -368,17 +395,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -750,8 +778,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
     <col min="18" max="18" width="8.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
@@ -892,58 +919,58 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>173.1</v>
+        <v>173.8</v>
       </c>
       <c r="D2">
-        <v>-1.84</v>
+        <v>0.4</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>119.11</v>
+        <v>124.01</v>
       </c>
       <c r="G2">
-        <v>-16.93</v>
+        <v>-16.59</v>
       </c>
       <c r="H2">
-        <v>45.33</v>
+        <v>40.15</v>
       </c>
       <c r="I2">
-        <v>-2.04</v>
+        <v>-1.38</v>
       </c>
       <c r="J2">
-        <v>12.45</v>
+        <v>13.97</v>
       </c>
       <c r="K2">
-        <v>13.96</v>
+        <v>11.73</v>
       </c>
       <c r="L2">
-        <v>48.04</v>
+        <v>45.92</v>
       </c>
       <c r="M2">
-        <v>26.5</v>
+        <v>26.59</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>174.88</v>
+        <v>174.4</v>
       </c>
       <c r="Q2">
-        <v>168.75</v>
+        <v>169.91</v>
       </c>
       <c r="R2">
-        <v>161.41</v>
+        <v>162.06</v>
       </c>
       <c r="S2">
-        <v>167.26</v>
+        <v>167.44</v>
       </c>
       <c r="T2">
-        <v>3.49</v>
+        <v>3.8</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -958,34 +985,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57.25</v>
+        <v>58.11</v>
       </c>
       <c r="Z2">
+        <v>4.39</v>
+      </c>
+      <c r="AA2">
+        <v>4.62</v>
+      </c>
+      <c r="AB2">
+        <v>-0.23</v>
+      </c>
+      <c r="AC2">
+        <v>17.83</v>
+      </c>
+      <c r="AD2">
+        <v>31.81</v>
+      </c>
+      <c r="AE2">
         <v>4.68</v>
       </c>
-      <c r="AA2">
-        <v>4.68</v>
-      </c>
-      <c r="AB2">
-        <v>0.01</v>
-      </c>
-      <c r="AC2">
-        <v>34.47</v>
-      </c>
-      <c r="AD2">
-        <v>43.43</v>
-      </c>
-      <c r="AE2">
-        <v>4.82</v>
-      </c>
       <c r="AF2">
-        <v>-50.01</v>
+        <v>-73.02</v>
       </c>
       <c r="AG2">
-        <v>188.2</v>
+        <v>187.48</v>
       </c>
       <c r="AH2">
-        <v>149.31</v>
+        <v>152.34</v>
       </c>
       <c r="AI2">
         <v>165.9</v>
@@ -994,7 +1021,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>29.26</v>
+        <v>25.73</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1005,10 +1032,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>398.55</v>
+        <v>398.25</v>
       </c>
       <c r="D3">
-        <v>-0.77</v>
+        <v>-0.08</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1017,46 +1044,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-10.5</v>
+        <v>-10.57</v>
       </c>
       <c r="H3">
-        <v>77.13</v>
+        <v>77</v>
       </c>
       <c r="I3">
-        <v>-7.7</v>
+        <v>-7.58</v>
       </c>
       <c r="J3">
-        <v>-0.2</v>
+        <v>1.31</v>
       </c>
       <c r="K3">
-        <v>29.95</v>
+        <v>21.25</v>
       </c>
       <c r="L3">
-        <v>8.01</v>
+        <v>11.52</v>
       </c>
       <c r="M3">
-        <v>10.48</v>
+        <v>10.45</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="P3">
-        <v>407.24</v>
+        <v>400.71</v>
       </c>
       <c r="Q3">
-        <v>407.97</v>
+        <v>408.34</v>
       </c>
       <c r="R3">
-        <v>407.08</v>
+        <v>407.32</v>
       </c>
       <c r="S3">
-        <v>324.46</v>
+        <v>324.68</v>
       </c>
       <c r="T3">
-        <v>22.84</v>
+        <v>22.66</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1071,34 +1098,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.38</v>
+        <v>45.24</v>
       </c>
       <c r="Z3">
-        <v>2.33</v>
+        <v>1.18</v>
       </c>
       <c r="AA3">
-        <v>4.6</v>
+        <v>3.91</v>
       </c>
       <c r="AB3">
-        <v>-2.27</v>
+        <v>-2.74</v>
       </c>
       <c r="AC3">
-        <v>16.89</v>
+        <v>7.02</v>
       </c>
       <c r="AD3">
-        <v>26.91</v>
+        <v>14.87</v>
       </c>
       <c r="AE3">
-        <v>15.43</v>
+        <v>14.76</v>
       </c>
       <c r="AF3">
-        <v>-76.69</v>
+        <v>-78.65000000000001</v>
       </c>
       <c r="AG3">
-        <v>441.27</v>
+        <v>440.99</v>
       </c>
       <c r="AH3">
-        <v>374.67</v>
+        <v>375.69</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1107,7 +1134,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>31.46</v>
+        <v>29.43</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,10 +1145,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>408</v>
+        <v>406.5</v>
       </c>
       <c r="D4">
-        <v>0.26</v>
+        <v>-0.37</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1130,46 +1157,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-25.42</v>
+        <v>-25.7</v>
       </c>
       <c r="H4">
-        <v>18.36</v>
+        <v>17.93</v>
       </c>
       <c r="I4">
-        <v>0.31</v>
+        <v>0.44</v>
       </c>
       <c r="J4">
-        <v>-5.28</v>
+        <v>-4.99</v>
       </c>
       <c r="K4">
-        <v>0.83</v>
+        <v>0</v>
       </c>
       <c r="L4">
-        <v>-24.14</v>
+        <v>-24.17</v>
       </c>
       <c r="M4">
-        <v>-21.18</v>
+        <v>-21.23</v>
       </c>
       <c r="N4">
         <v>40</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>408.27</v>
+        <v>408.63</v>
       </c>
       <c r="Q4">
-        <v>418.15</v>
+        <v>417.19</v>
       </c>
       <c r="R4">
-        <v>422.12</v>
+        <v>421.24</v>
       </c>
       <c r="S4">
-        <v>422.21</v>
+        <v>421.66</v>
       </c>
       <c r="T4">
-        <v>-3.37</v>
+        <v>-3.59</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1184,34 +1211,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>42.07</v>
+        <v>41.03</v>
       </c>
       <c r="Z4">
-        <v>-4.12</v>
+        <v>-4.34</v>
       </c>
       <c r="AA4">
-        <v>-2.52</v>
+        <v>-2.88</v>
       </c>
       <c r="AB4">
-        <v>-1.6</v>
+        <v>-1.46</v>
       </c>
       <c r="AC4">
-        <v>29.47</v>
+        <v>21.66</v>
       </c>
       <c r="AD4">
-        <v>26.25</v>
+        <v>26.37</v>
       </c>
       <c r="AE4">
-        <v>12.04</v>
+        <v>11.89</v>
       </c>
       <c r="AF4">
-        <v>-51.67</v>
+        <v>-32.09</v>
       </c>
       <c r="AG4">
-        <v>434.5</v>
+        <v>433.92</v>
       </c>
       <c r="AH4">
-        <v>401.79</v>
+        <v>400.45</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1220,7 +1247,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>16.84</v>
+        <v>17.21</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1231,10 +1258,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1016.7</v>
+        <v>1008</v>
       </c>
       <c r="D5">
-        <v>0.17</v>
+        <v>-0.86</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1243,46 +1270,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-4.92</v>
+        <v>-5.73</v>
       </c>
       <c r="H5">
-        <v>42.64</v>
+        <v>41.42</v>
       </c>
       <c r="I5">
-        <v>-0.08</v>
+        <v>-1.63</v>
       </c>
       <c r="J5">
-        <v>-4.4</v>
+        <v>-5.73</v>
       </c>
       <c r="K5">
-        <v>12.97</v>
+        <v>10.75</v>
       </c>
       <c r="L5">
-        <v>31.45</v>
+        <v>30.95</v>
       </c>
       <c r="M5">
-        <v>1.36</v>
+        <v>1.18</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1019.6</v>
+        <v>1016.26</v>
       </c>
       <c r="Q5">
-        <v>1015.01</v>
+        <v>1015.13</v>
       </c>
       <c r="R5">
-        <v>986.5599999999999</v>
+        <v>989.04</v>
       </c>
       <c r="S5">
-        <v>903.92</v>
+        <v>904.98</v>
       </c>
       <c r="T5">
-        <v>12.48</v>
+        <v>11.38</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1297,43 +1324,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>52.75</v>
+        <v>49.17</v>
       </c>
       <c r="Z5">
-        <v>7.25</v>
+        <v>5.9</v>
       </c>
       <c r="AA5">
-        <v>10.18</v>
+        <v>9.33</v>
       </c>
       <c r="AB5">
-        <v>-2.93</v>
+        <v>-3.42</v>
       </c>
       <c r="AC5">
-        <v>25.89</v>
+        <v>11.19</v>
       </c>
       <c r="AD5">
-        <v>38.36</v>
+        <v>24.17</v>
       </c>
       <c r="AE5">
-        <v>19.36</v>
+        <v>19.03</v>
       </c>
       <c r="AF5">
-        <v>-77.75</v>
+        <v>-50.23</v>
       </c>
       <c r="AG5">
-        <v>1034.56</v>
+        <v>1034.46</v>
       </c>
       <c r="AH5">
-        <v>995.45</v>
+        <v>995.8</v>
       </c>
       <c r="AI5">
-        <v>1070.23</v>
+        <v>1065.33</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>11.99</v>
+        <v>13.7</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,10 +1371,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.25</v>
+        <v>2.26</v>
       </c>
       <c r="D6">
-        <v>-0.88</v>
+        <v>0.44</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1356,46 +1383,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-37.85</v>
+        <v>-37.57</v>
       </c>
       <c r="H6">
-        <v>22.28</v>
+        <v>22.83</v>
       </c>
       <c r="I6">
-        <v>-3.85</v>
+        <v>-4.24</v>
       </c>
       <c r="J6">
-        <v>-4.26</v>
+        <v>-3.42</v>
       </c>
       <c r="K6">
-        <v>-14.12</v>
+        <v>-13.74</v>
       </c>
       <c r="L6">
-        <v>-33.82</v>
+        <v>-33.72</v>
       </c>
       <c r="M6">
-        <v>-2.01</v>
+        <v>-1.92</v>
       </c>
       <c r="N6">
         <v>21</v>
       </c>
       <c r="O6">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="Q6">
-        <v>2.33</v>
+        <v>2.32</v>
       </c>
       <c r="R6">
         <v>2.4</v>
       </c>
       <c r="S6">
-        <v>2.71</v>
+        <v>2.7</v>
       </c>
       <c r="T6">
-        <v>-16.85</v>
+        <v>-16.32</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1410,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="Y6">
-        <v>34.38</v>
+        <v>36.46</v>
       </c>
       <c r="Z6">
         <v>-0.03</v>
@@ -1422,22 +1449,22 @@
         <v>-0</v>
       </c>
       <c r="AC6">
-        <v>10.88</v>
+        <v>4.73</v>
       </c>
       <c r="AD6">
-        <v>35.81</v>
+        <v>15.74</v>
       </c>
       <c r="AE6">
-        <v>0.08</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="AF6">
-        <v>9.74</v>
+        <v>-12.63</v>
       </c>
       <c r="AG6">
         <v>2.4</v>
       </c>
       <c r="AH6">
-        <v>2.26</v>
+        <v>2.25</v>
       </c>
       <c r="AI6">
         <v>2.49</v>
@@ -1446,7 +1473,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>21.09</v>
+        <v>22.16</v>
       </c>
     </row>
   </sheetData>
@@ -1587,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1607,12 +1634,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1620,717 +1682,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>13.92</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>12.45</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.47</v>
+      <c r="D7" s="6">
+        <v>13.97</v>
+      </c>
+      <c r="E7" s="7">
+        <v>1.52</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>0.14</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-0.2</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.34</v>
+      <c r="D8" s="6">
+        <v>1.31</v>
+      </c>
+      <c r="E8" s="7">
+        <v>1.51</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.31</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-5.28</v>
       </c>
+      <c r="D9" s="6">
+        <v>-4.99</v>
+      </c>
       <c r="E9" s="7">
-        <v>0.03</v>
+        <v>0.29</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-1.73</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-4.4</v>
       </c>
-      <c r="E10" s="6">
-        <v>-2.67</v>
+      <c r="D10" s="6">
+        <v>-5.73</v>
+      </c>
+      <c r="E10" s="8">
+        <v>-1.33</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>-3.4</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>-4.26</v>
       </c>
-      <c r="E11" s="6">
-        <v>-0.86</v>
+      <c r="D11" s="6">
+        <v>-3.42</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.84</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>0.87</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-2.04</v>
       </c>
-      <c r="E12" s="6">
-        <v>-2.91</v>
+      <c r="D12" s="6">
+        <v>-1.38</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.66</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-6.5</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>-7.7</v>
       </c>
-      <c r="E13" s="6">
-        <v>-1.2</v>
+      <c r="D13" s="6">
+        <v>-7.58</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.12</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-1.06</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>0.31</v>
       </c>
+      <c r="D14" s="6">
+        <v>0.44</v>
+      </c>
       <c r="E14" s="7">
-        <v>1.37</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>0.6</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-0.08</v>
       </c>
-      <c r="E15" s="6">
-        <v>-0.68</v>
+      <c r="D15" s="6">
+        <v>-1.63</v>
+      </c>
+      <c r="E15" s="8">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>-2.16</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>-3.85</v>
       </c>
-      <c r="E16" s="6">
-        <v>-1.69</v>
+      <c r="D16" s="6">
+        <v>-4.24</v>
+      </c>
+      <c r="E16" s="8">
+        <v>-0.39</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>51.28</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>48.04</v>
       </c>
-      <c r="E17" s="6">
-        <v>-3.24</v>
+      <c r="D17" s="6">
+        <v>45.92</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-2.12</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>15.47</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>8.01</v>
       </c>
-      <c r="E18" s="6">
-        <v>-7.46</v>
+      <c r="D18" s="6">
+        <v>11.52</v>
+      </c>
+      <c r="E18" s="7">
+        <v>3.51</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-23.43</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-24.14</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.71</v>
+      <c r="D19" s="6">
+        <v>-24.17</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>29.62</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>31.45</v>
       </c>
-      <c r="E20" s="7">
-        <v>1.83</v>
+      <c r="D20" s="6">
+        <v>30.95</v>
+      </c>
+      <c r="E20" s="8">
+        <v>-0.5</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-33.82</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-33.72</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="5">
-        <v>16.76</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C22" s="6">
         <v>13.96</v>
       </c>
-      <c r="E21" s="6">
-        <v>-2.8</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D22" s="6">
+        <v>11.73</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>34.67</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C23" s="6">
         <v>29.95</v>
       </c>
-      <c r="E22" s="6">
-        <v>-4.72</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D23" s="6">
+        <v>21.25</v>
+      </c>
+      <c r="E23" s="8">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>1.46</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C24" s="6">
         <v>0.83</v>
       </c>
-      <c r="E23" s="6">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D24" s="6">
+        <v>0</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-0.83</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>13.14</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C25" s="6">
         <v>12.97</v>
       </c>
-      <c r="E24" s="6">
-        <v>-0.17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D25" s="6">
+        <v>10.75</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-2.22</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>-14.02</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C26" s="6">
         <v>-14.12</v>
       </c>
-      <c r="E25" s="6">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D26" s="6">
+        <v>-13.74</v>
+      </c>
+      <c r="E26" s="7">
+        <v>0.38</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="5">
-        <v>-15.37</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C27" s="6">
         <v>-16.93</v>
       </c>
-      <c r="E26" s="6">
-        <v>-1.56</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D27" s="6">
+        <v>-16.59</v>
+      </c>
+      <c r="E27" s="7">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-9.800000000000001</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C28" s="6">
         <v>-10.5</v>
       </c>
-      <c r="E27" s="6">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D28" s="6">
+        <v>-10.57</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-25.62</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C29" s="6">
         <v>-25.42</v>
       </c>
-      <c r="E28" s="7">
-        <v>0.2</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-25.7</v>
+      </c>
+      <c r="E29" s="8">
+        <v>-0.28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-5.08</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C30" s="6">
         <v>-4.92</v>
       </c>
-      <c r="E29" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-5.73</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.8100000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-37.29</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C31" s="6">
         <v>-37.85</v>
       </c>
-      <c r="E30" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D31" s="6">
+        <v>-37.57</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="5">
-        <v>176.35</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C32" s="6">
         <v>173.1</v>
       </c>
-      <c r="E31" s="6">
-        <v>-3.25</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="D32" s="6">
+        <v>173.8</v>
+      </c>
+      <c r="E32" s="7">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>401.65</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C33" s="6">
         <v>398.55</v>
       </c>
-      <c r="E32" s="6">
-        <v>-3.1</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D33" s="6">
+        <v>398.25</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.3</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>406.95</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C34" s="6">
         <v>408</v>
       </c>
-      <c r="E33" s="7">
-        <v>1.05</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D34" s="6">
+        <v>406.5</v>
+      </c>
+      <c r="E34" s="8">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>1015</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C35" s="6">
         <v>1016.7</v>
       </c>
-      <c r="E34" s="7">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D35" s="6">
+        <v>1008</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-8.699999999999999</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>2.27</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C36" s="6">
         <v>2.25</v>
       </c>
-      <c r="E35" s="6">
-        <v>-0.02</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D36" s="6">
+        <v>2.26</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="6">
+        <v>57.25</v>
+      </c>
+      <c r="D37" s="6">
+        <v>58.11</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.86</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C36" s="5">
-        <v>79</v>
-      </c>
-      <c r="D36" s="5">
-        <v>60</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-19</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>45.38</v>
+      </c>
+      <c r="D38" s="6">
+        <v>45.24</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.14</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>42.07</v>
+      </c>
+      <c r="D39" s="6">
+        <v>41.03</v>
+      </c>
+      <c r="E39" s="8">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C37" s="5">
-        <v>60</v>
-      </c>
-      <c r="D37" s="5">
-        <v>79</v>
-      </c>
-      <c r="E37" s="7">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>52.75</v>
+      </c>
+      <c r="D40" s="6">
+        <v>49.17</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-3.58</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>34.38</v>
+      </c>
+      <c r="D41" s="6">
+        <v>36.46</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>62.82</v>
-      </c>
-      <c r="D38" s="5">
-        <v>57.25</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-5.57</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-50.01</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-73.02</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-23.01</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>46.71</v>
-      </c>
-      <c r="D39" s="5">
-        <v>45.38</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.33</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-76.69</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-78.65000000000001</v>
+      </c>
+      <c r="E43" s="8">
+        <v>-1.96</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>41.1</v>
-      </c>
-      <c r="D40" s="5">
-        <v>42.07</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-51.67</v>
+      </c>
+      <c r="D44" s="6">
+        <v>-32.09</v>
+      </c>
+      <c r="E44" s="7">
+        <v>19.58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>52.12</v>
-      </c>
-      <c r="D41" s="5">
-        <v>52.75</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-77.75</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-50.23</v>
+      </c>
+      <c r="E45" s="7">
+        <v>27.52</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>36.6</v>
-      </c>
-      <c r="D42" s="5">
-        <v>34.38</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-2.22</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="5">
-        <v>-28.62</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-50.01</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-21.39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-71.98999999999999</v>
-      </c>
-      <c r="D44" s="5">
-        <v>-76.69</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-4.7</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-39</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-51.67</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-12.67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-73.06</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-77.75</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-4.69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>76.48</v>
-      </c>
-      <c r="D47" s="5">
+      <c r="C46" s="6">
         <v>9.74</v>
       </c>
-      <c r="E47" s="6">
-        <v>-66.73999999999999</v>
+      <c r="D46" s="6">
+        <v>-12.63</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-22.37</v>
       </c>
     </row>
   </sheetData>
@@ -2356,60 +2401,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>46.4</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>-0.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>8.699999999999999</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>0.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>6</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2511,37 +2556,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.265</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1048</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0136</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0201</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2118</v>
+      <c r="A2" s="14">
+        <v>0.2659</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1045</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0118</v>
+      </c>
+      <c r="D2" s="14">
+        <v>-0.0192</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2123</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,16 +184,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>52.8 → 49.2</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.8</t>
-  </si>
-  <si>
-    <t>49.2</t>
+    <t>48.2 → 53.5</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>48.2</t>
+  </si>
+  <si>
+    <t>53.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -279,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -319,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -778,8 +778,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="18" width="8.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
@@ -919,10 +919,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>173.8</v>
+        <v>173.29</v>
       </c>
       <c r="D2">
-        <v>0.4</v>
+        <v>0.17</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -931,46 +931,46 @@
         <v>124.01</v>
       </c>
       <c r="G2">
-        <v>-16.59</v>
+        <v>-16.84</v>
       </c>
       <c r="H2">
-        <v>40.15</v>
+        <v>39.74</v>
       </c>
       <c r="I2">
-        <v>-1.38</v>
+        <v>-2.15</v>
       </c>
       <c r="J2">
-        <v>13.97</v>
+        <v>14.71</v>
       </c>
       <c r="K2">
-        <v>11.73</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="L2">
-        <v>45.92</v>
+        <v>33.14</v>
       </c>
       <c r="M2">
-        <v>26.59</v>
+        <v>26.36</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>174.4</v>
+        <v>173.91</v>
       </c>
       <c r="Q2">
-        <v>169.91</v>
+        <v>171.92</v>
       </c>
       <c r="R2">
-        <v>162.06</v>
+        <v>163.16</v>
       </c>
       <c r="S2">
-        <v>167.44</v>
+        <v>167.8</v>
       </c>
       <c r="T2">
-        <v>3.8</v>
+        <v>3.27</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -985,34 +985,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.11</v>
+        <v>57.11</v>
       </c>
       <c r="Z2">
-        <v>4.39</v>
+        <v>3.76</v>
       </c>
       <c r="AA2">
-        <v>4.62</v>
+        <v>4.35</v>
       </c>
       <c r="AB2">
-        <v>-0.23</v>
+        <v>-0.6</v>
       </c>
       <c r="AC2">
-        <v>17.83</v>
+        <v>2.78</v>
       </c>
       <c r="AD2">
-        <v>31.81</v>
+        <v>7.5</v>
       </c>
       <c r="AE2">
-        <v>4.68</v>
+        <v>4.28</v>
       </c>
       <c r="AF2">
-        <v>-73.02</v>
+        <v>-54.49</v>
       </c>
       <c r="AG2">
-        <v>187.48</v>
+        <v>185.15</v>
       </c>
       <c r="AH2">
-        <v>152.34</v>
+        <v>158.69</v>
       </c>
       <c r="AI2">
         <v>165.9</v>
@@ -1021,7 +1021,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>25.73</v>
+        <v>21.34</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1032,10 +1032,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>398.25</v>
+        <v>398.4</v>
       </c>
       <c r="D3">
-        <v>-0.08</v>
+        <v>-0.55</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1044,46 +1044,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-10.57</v>
+        <v>-10.53</v>
       </c>
       <c r="H3">
-        <v>77</v>
+        <v>77.06999999999999</v>
       </c>
       <c r="I3">
-        <v>-7.58</v>
+        <v>-2.35</v>
       </c>
       <c r="J3">
-        <v>1.31</v>
+        <v>0.47</v>
       </c>
       <c r="K3">
-        <v>21.25</v>
+        <v>5.37</v>
       </c>
       <c r="L3">
-        <v>11.52</v>
+        <v>10.57</v>
       </c>
       <c r="M3">
-        <v>10.45</v>
+        <v>10.9</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O3">
-        <v>72</v>
+        <v>63</v>
       </c>
       <c r="P3">
-        <v>400.71</v>
+        <v>399.49</v>
       </c>
       <c r="Q3">
-        <v>408.34</v>
+        <v>408.66</v>
       </c>
       <c r="R3">
-        <v>407.32</v>
+        <v>407.61</v>
       </c>
       <c r="S3">
-        <v>324.68</v>
+        <v>325.14</v>
       </c>
       <c r="T3">
-        <v>22.66</v>
+        <v>22.53</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1098,34 +1098,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.24</v>
+        <v>45.46</v>
       </c>
       <c r="Z3">
-        <v>1.18</v>
+        <v>-0.3</v>
       </c>
       <c r="AA3">
-        <v>3.91</v>
+        <v>2.52</v>
       </c>
       <c r="AB3">
-        <v>-2.74</v>
+        <v>-2.82</v>
       </c>
       <c r="AC3">
-        <v>7.02</v>
+        <v>6.2</v>
       </c>
       <c r="AD3">
-        <v>14.87</v>
+        <v>6.43</v>
       </c>
       <c r="AE3">
-        <v>14.76</v>
+        <v>13.58</v>
       </c>
       <c r="AF3">
-        <v>-78.65000000000001</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="AG3">
-        <v>440.99</v>
+        <v>440.88</v>
       </c>
       <c r="AH3">
-        <v>375.69</v>
+        <v>376.45</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1134,7 +1134,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>29.43</v>
+        <v>25.57</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1145,10 +1145,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>406.5</v>
+        <v>402.05</v>
       </c>
       <c r="D4">
-        <v>-0.37</v>
+        <v>-0.05</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1157,46 +1157,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-25.7</v>
+        <v>-26.51</v>
       </c>
       <c r="H4">
-        <v>17.93</v>
+        <v>16.64</v>
       </c>
       <c r="I4">
-        <v>0.44</v>
+        <v>-2.66</v>
       </c>
       <c r="J4">
-        <v>-4.99</v>
+        <v>-4.85</v>
       </c>
       <c r="K4">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="L4">
-        <v>-24.17</v>
+        <v>-25.19</v>
       </c>
       <c r="M4">
-        <v>-21.23</v>
+        <v>-20.87</v>
       </c>
       <c r="N4">
-        <v>40</v>
+        <v>21</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>408.63</v>
+        <v>405.15</v>
       </c>
       <c r="Q4">
-        <v>417.19</v>
+        <v>415.15</v>
       </c>
       <c r="R4">
-        <v>421.24</v>
+        <v>420.23</v>
       </c>
       <c r="S4">
-        <v>421.66</v>
+        <v>420.52</v>
       </c>
       <c r="T4">
-        <v>-3.59</v>
+        <v>-4.39</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1211,34 +1211,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41.03</v>
+        <v>37.99</v>
       </c>
       <c r="Z4">
-        <v>-4.34</v>
+        <v>-5.12</v>
       </c>
       <c r="AA4">
-        <v>-2.88</v>
+        <v>-3.63</v>
       </c>
       <c r="AB4">
-        <v>-1.46</v>
+        <v>-1.48</v>
       </c>
       <c r="AC4">
-        <v>21.66</v>
+        <v>8.74</v>
       </c>
       <c r="AD4">
-        <v>26.37</v>
+        <v>15.55</v>
       </c>
       <c r="AE4">
-        <v>11.89</v>
+        <v>12.11</v>
       </c>
       <c r="AF4">
-        <v>-32.09</v>
+        <v>-38.83</v>
       </c>
       <c r="AG4">
-        <v>433.92</v>
+        <v>433.74</v>
       </c>
       <c r="AH4">
-        <v>400.45</v>
+        <v>396.55</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1247,7 +1247,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>17.21</v>
+        <v>15.98</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1258,10 +1258,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1008</v>
+        <v>1018.4</v>
       </c>
       <c r="D5">
-        <v>-0.86</v>
+        <v>1.27</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1270,46 +1270,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-5.73</v>
+        <v>-4.76</v>
       </c>
       <c r="H5">
-        <v>41.42</v>
+        <v>42.88</v>
       </c>
       <c r="I5">
-        <v>-1.63</v>
+        <v>-0.24</v>
       </c>
       <c r="J5">
-        <v>-5.73</v>
+        <v>2.24</v>
       </c>
       <c r="K5">
-        <v>10.75</v>
+        <v>9.24</v>
       </c>
       <c r="L5">
-        <v>30.95</v>
+        <v>29.65</v>
       </c>
       <c r="M5">
-        <v>1.18</v>
+        <v>0.87</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>1016.26</v>
+        <v>1012.74</v>
       </c>
       <c r="Q5">
-        <v>1015.13</v>
+        <v>1016.2</v>
       </c>
       <c r="R5">
-        <v>989.04</v>
+        <v>993.4</v>
       </c>
       <c r="S5">
-        <v>904.98</v>
+        <v>907.17</v>
       </c>
       <c r="T5">
-        <v>11.38</v>
+        <v>12.26</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1324,43 +1324,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.17</v>
+        <v>53.48</v>
       </c>
       <c r="Z5">
-        <v>5.9</v>
+        <v>4.52</v>
       </c>
       <c r="AA5">
-        <v>9.33</v>
+        <v>7.61</v>
       </c>
       <c r="AB5">
-        <v>-3.42</v>
+        <v>-3.08</v>
       </c>
       <c r="AC5">
-        <v>11.19</v>
+        <v>18.82</v>
       </c>
       <c r="AD5">
-        <v>24.17</v>
+        <v>12.35</v>
       </c>
       <c r="AE5">
-        <v>19.03</v>
+        <v>18.13</v>
       </c>
       <c r="AF5">
-        <v>-50.23</v>
+        <v>-22.03</v>
       </c>
       <c r="AG5">
-        <v>1034.46</v>
+        <v>1033.47</v>
       </c>
       <c r="AH5">
-        <v>995.8</v>
+        <v>998.92</v>
       </c>
       <c r="AI5">
-        <v>1065.33</v>
+        <v>1057.76</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>13.7</v>
+        <v>14.47</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1371,10 +1371,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.26</v>
+        <v>3.04</v>
       </c>
       <c r="D6">
-        <v>0.44</v>
+        <v>12.18</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1383,46 +1383,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-37.57</v>
+        <v>-16.02</v>
       </c>
       <c r="H6">
-        <v>22.83</v>
+        <v>65.22</v>
       </c>
       <c r="I6">
-        <v>-4.24</v>
+        <v>31.03</v>
       </c>
       <c r="J6">
-        <v>-3.42</v>
+        <v>31.6</v>
       </c>
       <c r="K6">
-        <v>-13.74</v>
+        <v>16.03</v>
       </c>
       <c r="L6">
-        <v>-33.72</v>
+        <v>-11.88</v>
       </c>
       <c r="M6">
-        <v>-1.92</v>
+        <v>5.11</v>
       </c>
       <c r="N6">
-        <v>21</v>
+        <v>60</v>
       </c>
       <c r="O6">
-        <v>9</v>
+        <v>66</v>
       </c>
       <c r="P6">
-        <v>2.28</v>
+        <v>2.51</v>
       </c>
       <c r="Q6">
-        <v>2.32</v>
+        <v>2.38</v>
       </c>
       <c r="R6">
-        <v>2.4</v>
+        <v>2.41</v>
       </c>
       <c r="S6">
         <v>2.7</v>
       </c>
       <c r="T6">
-        <v>-16.32</v>
+        <v>12.74</v>
       </c>
       <c r="U6" t="s">
         <v>44</v>
@@ -1434,46 +1434,46 @@
         <v>44</v>
       </c>
       <c r="X6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y6">
-        <v>36.46</v>
+        <v>83.02</v>
       </c>
       <c r="Z6">
-        <v>-0.03</v>
+        <v>0.06</v>
       </c>
       <c r="AA6">
-        <v>-0.03</v>
+        <v>-0.01</v>
       </c>
       <c r="AB6">
-        <v>-0</v>
+        <v>0.06</v>
       </c>
       <c r="AC6">
-        <v>4.73</v>
+        <v>71.39</v>
       </c>
       <c r="AD6">
-        <v>15.74</v>
+        <v>38.06</v>
       </c>
       <c r="AE6">
-        <v>0.07000000000000001</v>
+        <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-12.63</v>
+        <v>1327.17</v>
       </c>
       <c r="AG6">
-        <v>2.4</v>
+        <v>2.74</v>
       </c>
       <c r="AH6">
-        <v>2.25</v>
+        <v>2.02</v>
       </c>
       <c r="AI6">
-        <v>2.49</v>
+        <v>2.64</v>
       </c>
       <c r="AJ6" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK6">
-        <v>22.16</v>
+        <v>35.53</v>
       </c>
     </row>
   </sheetData>
@@ -1614,7 +1614,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1706,13 +1706,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>12.45</v>
+        <v>14.84</v>
       </c>
       <c r="D7" s="6">
-        <v>13.97</v>
+        <v>14.71</v>
       </c>
       <c r="E7" s="7">
-        <v>1.52</v>
+        <v>-0.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1723,13 +1723,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-0.2</v>
+        <v>2.51</v>
       </c>
       <c r="D8" s="6">
-        <v>1.31</v>
+        <v>0.47</v>
       </c>
       <c r="E8" s="7">
-        <v>1.51</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1740,13 +1740,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.28</v>
+        <v>-5.51</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.99</v>
-      </c>
-      <c r="E9" s="7">
-        <v>0.29</v>
+        <v>-4.85</v>
+      </c>
+      <c r="E9" s="8">
+        <v>0.66</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1757,13 +1757,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.4</v>
+        <v>0.01</v>
       </c>
       <c r="D10" s="6">
-        <v>-5.73</v>
+        <v>2.24</v>
       </c>
       <c r="E10" s="8">
-        <v>-1.33</v>
+        <v>2.23</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1774,13 +1774,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>-4.26</v>
+        <v>16.81</v>
       </c>
       <c r="D11" s="6">
-        <v>-3.42</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.84</v>
+        <v>31.6</v>
+      </c>
+      <c r="E11" s="8">
+        <v>14.79</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1791,13 +1791,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.04</v>
+        <v>0.79</v>
       </c>
       <c r="D12" s="6">
-        <v>-1.38</v>
+        <v>-2.15</v>
       </c>
       <c r="E12" s="7">
-        <v>0.66</v>
+        <v>-2.94</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1808,13 +1808,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-7.7</v>
+        <v>0.88</v>
       </c>
       <c r="D13" s="6">
-        <v>-7.58</v>
+        <v>-2.35</v>
       </c>
       <c r="E13" s="7">
-        <v>0.12</v>
+        <v>-3.23</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1825,13 +1825,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>0.31</v>
+        <v>-1.57</v>
       </c>
       <c r="D14" s="6">
-        <v>0.44</v>
+        <v>-2.66</v>
       </c>
       <c r="E14" s="7">
-        <v>0.13</v>
+        <v>-1.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1842,13 +1842,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.08</v>
+        <v>-1.49</v>
       </c>
       <c r="D15" s="6">
-        <v>-1.63</v>
+        <v>-0.24</v>
       </c>
       <c r="E15" s="8">
-        <v>-1.55</v>
+        <v>1.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1859,13 +1859,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-3.85</v>
+        <v>16.81</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.24</v>
+        <v>31.03</v>
       </c>
       <c r="E16" s="8">
-        <v>-0.39</v>
+        <v>14.22</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1876,13 +1876,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>48.04</v>
+        <v>34.44</v>
       </c>
       <c r="D17" s="6">
-        <v>45.92</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-2.12</v>
+        <v>33.14</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-1.3</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1893,13 +1893,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>8.01</v>
+        <v>12.46</v>
       </c>
       <c r="D18" s="6">
-        <v>11.52</v>
+        <v>10.57</v>
       </c>
       <c r="E18" s="7">
-        <v>3.51</v>
+        <v>-1.89</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1910,13 +1910,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-24.14</v>
+        <v>-24.93</v>
       </c>
       <c r="D19" s="6">
-        <v>-24.17</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.03</v>
+        <v>-25.19</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.26</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1927,13 +1927,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>31.45</v>
+        <v>27.51</v>
       </c>
       <c r="D20" s="6">
-        <v>30.95</v>
+        <v>29.65</v>
       </c>
       <c r="E20" s="8">
-        <v>-0.5</v>
+        <v>2.14</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1944,13 +1944,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-33.82</v>
+        <v>-21.9</v>
       </c>
       <c r="D21" s="6">
-        <v>-33.72</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.1</v>
+        <v>-11.88</v>
+      </c>
+      <c r="E21" s="8">
+        <v>10.02</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1961,13 +1961,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>13.96</v>
+        <v>7.23</v>
       </c>
       <c r="D22" s="6">
-        <v>11.73</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="E22" s="8">
-        <v>-2.23</v>
+        <v>2.55</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1978,13 +1978,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>29.95</v>
+        <v>15.63</v>
       </c>
       <c r="D23" s="6">
-        <v>21.25</v>
-      </c>
-      <c r="E23" s="8">
-        <v>-8.699999999999999</v>
+        <v>5.37</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-10.26</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1995,13 +1995,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>0.83</v>
+        <v>-1.67</v>
       </c>
       <c r="D24" s="6">
-        <v>0</v>
+        <v>-1.54</v>
       </c>
       <c r="E24" s="8">
-        <v>-0.83</v>
+        <v>0.13</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2012,13 +2012,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>12.97</v>
+        <v>8.58</v>
       </c>
       <c r="D25" s="6">
-        <v>10.75</v>
+        <v>9.24</v>
       </c>
       <c r="E25" s="8">
-        <v>-2.22</v>
+        <v>0.66</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2029,13 +2029,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>-14.12</v>
+        <v>1.88</v>
       </c>
       <c r="D26" s="6">
-        <v>-13.74</v>
-      </c>
-      <c r="E26" s="7">
-        <v>0.38</v>
+        <v>16.03</v>
+      </c>
+      <c r="E26" s="8">
+        <v>14.15</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2046,13 +2046,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-16.93</v>
+        <v>-16.97</v>
       </c>
       <c r="D27" s="6">
-        <v>-16.59</v>
-      </c>
-      <c r="E27" s="7">
-        <v>0.34</v>
+        <v>-16.84</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.13</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2063,13 +2063,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-10.5</v>
+        <v>-10.04</v>
       </c>
       <c r="D28" s="6">
-        <v>-10.57</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.07000000000000001</v>
+        <v>-10.53</v>
+      </c>
+      <c r="E28" s="7">
+        <v>-0.49</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2080,13 +2080,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-25.42</v>
+        <v>-26.48</v>
       </c>
       <c r="D29" s="6">
-        <v>-25.7</v>
-      </c>
-      <c r="E29" s="8">
-        <v>-0.28</v>
+        <v>-26.51</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2097,13 +2097,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-4.92</v>
+        <v>-5.96</v>
       </c>
       <c r="D30" s="6">
-        <v>-5.73</v>
+        <v>-4.76</v>
       </c>
       <c r="E30" s="8">
-        <v>-0.8100000000000001</v>
+        <v>1.2</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2114,13 +2114,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-37.85</v>
+        <v>-25.14</v>
       </c>
       <c r="D31" s="6">
-        <v>-37.57</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.28</v>
+        <v>-16.02</v>
+      </c>
+      <c r="E31" s="8">
+        <v>9.119999999999999</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2131,13 +2131,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>173.1</v>
+        <v>173</v>
       </c>
       <c r="D32" s="6">
-        <v>173.8</v>
-      </c>
-      <c r="E32" s="7">
-        <v>0.7</v>
+        <v>173.29</v>
+      </c>
+      <c r="E32" s="8">
+        <v>0.29</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2148,13 +2148,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>398.55</v>
+        <v>400.6</v>
       </c>
       <c r="D33" s="6">
-        <v>398.25</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.3</v>
+        <v>398.4</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-2.2</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2165,13 +2165,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>408</v>
+        <v>402.25</v>
       </c>
       <c r="D34" s="6">
-        <v>406.5</v>
-      </c>
-      <c r="E34" s="8">
-        <v>-1.5</v>
+        <v>402.05</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.2</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2182,13 +2182,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1016.7</v>
+        <v>1005.6</v>
       </c>
       <c r="D35" s="6">
-        <v>1008</v>
+        <v>1018.4</v>
       </c>
       <c r="E35" s="8">
-        <v>-8.699999999999999</v>
+        <v>12.8</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2199,183 +2199,217 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2.25</v>
+        <v>2.71</v>
       </c>
       <c r="D36" s="6">
-        <v>2.26</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.01</v>
+        <v>3.04</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.33</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="6">
-        <v>57.25</v>
+        <v>60</v>
       </c>
       <c r="D37" s="6">
-        <v>58.11</v>
+        <v>40</v>
       </c>
       <c r="E37" s="7">
-        <v>0.86</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C38" s="6">
-        <v>45.38</v>
+        <v>40</v>
       </c>
       <c r="D38" s="6">
-        <v>45.24</v>
+        <v>60</v>
       </c>
       <c r="E38" s="8">
-        <v>-0.14</v>
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>42.07</v>
+        <v>56.7</v>
       </c>
       <c r="D39" s="6">
-        <v>41.03</v>
+        <v>57.11</v>
       </c>
       <c r="E39" s="8">
-        <v>-1.04</v>
+        <v>0.41</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>52.75</v>
+        <v>46.57</v>
       </c>
       <c r="D40" s="6">
-        <v>49.17</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-3.58</v>
+        <v>45.46</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-1.11</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>34.38</v>
+        <v>38.13</v>
       </c>
       <c r="D41" s="6">
-        <v>36.46</v>
+        <v>37.99</v>
       </c>
       <c r="E41" s="7">
-        <v>2.08</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="6">
-        <v>-50.01</v>
+        <v>48.19</v>
       </c>
       <c r="D42" s="6">
-        <v>-73.02</v>
+        <v>53.48</v>
       </c>
       <c r="E42" s="8">
-        <v>-23.01</v>
+        <v>5.29</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="6">
-        <v>-76.69</v>
+        <v>74.90000000000001</v>
       </c>
       <c r="D43" s="6">
-        <v>-78.65000000000001</v>
+        <v>83.02</v>
       </c>
       <c r="E43" s="8">
-        <v>-1.96</v>
+        <v>8.119999999999999</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-51.67</v>
+        <v>-70.81999999999999</v>
       </c>
       <c r="D44" s="6">
-        <v>-32.09</v>
-      </c>
-      <c r="E44" s="7">
-        <v>19.58</v>
+        <v>-54.49</v>
+      </c>
+      <c r="E44" s="8">
+        <v>16.33</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-77.75</v>
+        <v>-85.31</v>
       </c>
       <c r="D45" s="6">
-        <v>-50.23</v>
-      </c>
-      <c r="E45" s="7">
-        <v>27.52</v>
+        <v>-82.34999999999999</v>
+      </c>
+      <c r="E45" s="8">
+        <v>2.96</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>9.74</v>
+        <v>11.68</v>
       </c>
       <c r="D46" s="6">
-        <v>-12.63</v>
-      </c>
-      <c r="E46" s="8">
-        <v>-22.37</v>
+        <v>-38.83</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-50.51</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-31.51</v>
+      </c>
+      <c r="D47" s="6">
+        <v>-22.03</v>
+      </c>
+      <c r="E47" s="8">
+        <v>9.48</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="6">
+        <v>616.8099999999999</v>
+      </c>
+      <c r="D48" s="6">
+        <v>1327.17</v>
+      </c>
+      <c r="E48" s="8">
+        <v>710.36</v>
       </c>
     </row>
   </sheetData>
@@ -2434,22 +2468,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="11">
-        <v>57.92</v>
+        <v>65.92</v>
       </c>
       <c r="C2" s="12">
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>46</v>
+        <v>55.4</v>
       </c>
       <c r="E2" s="11">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="F2" s="11">
-        <v>0.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G2" s="11">
-        <v>6</v>
+        <v>7.8</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2563,10 +2597,10 @@
         <v>38</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>41</v>
+      </c>
+      <c r="D1" s="13" t="s">
         <v>40</v>
-      </c>
-      <c r="D1" s="13" t="s">
-        <v>41</v>
       </c>
       <c r="E1" s="13" t="s">
         <v>39</v>
@@ -2574,19 +2608,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2659</v>
+        <v>0.2636</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1045</v>
+        <v>0.109</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0118</v>
+        <v>0.05110000000000001</v>
       </c>
       <c r="D2" s="14">
-        <v>-0.0192</v>
+        <v>0.008699999999999999</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2123</v>
+        <v>-0.2087</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="69">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,13 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>48.2 → 53.5</t>
+    <t>20 DMA &gt; 50 DMA</t>
+  </si>
+  <si>
+    <t>No → Yes</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>48.2</t>
-  </si>
-  <si>
-    <t>53.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -778,8 +772,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="18" width="8.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
@@ -919,10 +913,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>173.29</v>
+        <v>174.69</v>
       </c>
       <c r="D2">
-        <v>0.17</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -931,25 +925,25 @@
         <v>124.01</v>
       </c>
       <c r="G2">
-        <v>-16.84</v>
+        <v>-16.16</v>
       </c>
       <c r="H2">
-        <v>39.74</v>
+        <v>40.87</v>
       </c>
       <c r="I2">
-        <v>-2.15</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="J2">
-        <v>14.71</v>
+        <v>12.66</v>
       </c>
       <c r="K2">
-        <v>9.779999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="L2">
-        <v>33.14</v>
+        <v>34.39</v>
       </c>
       <c r="M2">
-        <v>26.36</v>
+        <v>26.73</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -958,19 +952,19 @@
         <v>80</v>
       </c>
       <c r="P2">
-        <v>173.91</v>
+        <v>173.58</v>
       </c>
       <c r="Q2">
-        <v>171.92</v>
+        <v>172.78</v>
       </c>
       <c r="R2">
-        <v>163.16</v>
+        <v>163.5</v>
       </c>
       <c r="S2">
-        <v>167.8</v>
+        <v>167.98</v>
       </c>
       <c r="T2">
-        <v>3.27</v>
+        <v>3.99</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -985,34 +979,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57.11</v>
+        <v>59.1</v>
       </c>
       <c r="Z2">
-        <v>3.76</v>
+        <v>3.6</v>
       </c>
       <c r="AA2">
-        <v>4.35</v>
+        <v>4.2</v>
       </c>
       <c r="AB2">
-        <v>-0.6</v>
+        <v>-0.61</v>
       </c>
       <c r="AC2">
-        <v>2.78</v>
+        <v>6.09</v>
       </c>
       <c r="AD2">
-        <v>7.5</v>
+        <v>3.59</v>
       </c>
       <c r="AE2">
-        <v>4.28</v>
+        <v>4.2</v>
       </c>
       <c r="AF2">
-        <v>-54.49</v>
+        <v>-55.89</v>
       </c>
       <c r="AG2">
-        <v>185.15</v>
+        <v>184.17</v>
       </c>
       <c r="AH2">
-        <v>158.69</v>
+        <v>161.39</v>
       </c>
       <c r="AI2">
         <v>165.9</v>
@@ -1021,7 +1015,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>21.34</v>
+        <v>18.53</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1032,10 +1026,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>398.4</v>
+        <v>395.7</v>
       </c>
       <c r="D3">
-        <v>-0.55</v>
+        <v>-0.68</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1044,46 +1038,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-10.53</v>
+        <v>-11.14</v>
       </c>
       <c r="H3">
-        <v>77.06999999999999</v>
+        <v>75.87</v>
       </c>
       <c r="I3">
-        <v>-2.35</v>
+        <v>-1.48</v>
       </c>
       <c r="J3">
-        <v>0.47</v>
+        <v>-0.06</v>
       </c>
       <c r="K3">
-        <v>5.37</v>
+        <v>3.69</v>
       </c>
       <c r="L3">
-        <v>10.57</v>
+        <v>4.24</v>
       </c>
       <c r="M3">
-        <v>10.9</v>
+        <v>10.8</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>63</v>
+        <v>59</v>
       </c>
       <c r="P3">
-        <v>399.49</v>
+        <v>398.3</v>
       </c>
       <c r="Q3">
-        <v>408.66</v>
+        <v>409.04</v>
       </c>
       <c r="R3">
-        <v>407.61</v>
+        <v>407.43</v>
       </c>
       <c r="S3">
-        <v>325.14</v>
+        <v>325.42</v>
       </c>
       <c r="T3">
-        <v>22.53</v>
+        <v>21.59</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1098,34 +1092,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.46</v>
+        <v>44.07</v>
       </c>
       <c r="Z3">
-        <v>-0.3</v>
+        <v>-1.1</v>
       </c>
       <c r="AA3">
-        <v>2.52</v>
+        <v>1.79</v>
       </c>
       <c r="AB3">
-        <v>-2.82</v>
+        <v>-2.89</v>
       </c>
       <c r="AC3">
-        <v>6.2</v>
+        <v>4.82</v>
       </c>
       <c r="AD3">
-        <v>6.43</v>
+        <v>5.7</v>
       </c>
       <c r="AE3">
-        <v>13.58</v>
+        <v>13.52</v>
       </c>
       <c r="AF3">
-        <v>-82.34999999999999</v>
+        <v>-80.84999999999999</v>
       </c>
       <c r="AG3">
-        <v>440.88</v>
+        <v>440.41</v>
       </c>
       <c r="AH3">
-        <v>376.45</v>
+        <v>377.68</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1134,7 +1128,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>25.57</v>
+        <v>24.55</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1145,10 +1139,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>402.05</v>
+        <v>401.3</v>
       </c>
       <c r="D4">
-        <v>-0.05</v>
+        <v>-0.19</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1157,46 +1151,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-26.51</v>
+        <v>-26.65</v>
       </c>
       <c r="H4">
-        <v>16.64</v>
+        <v>16.42</v>
       </c>
       <c r="I4">
-        <v>-2.66</v>
+        <v>-1.39</v>
       </c>
       <c r="J4">
-        <v>-4.85</v>
+        <v>-5.03</v>
       </c>
       <c r="K4">
-        <v>-1.54</v>
+        <v>-3.09</v>
       </c>
       <c r="L4">
-        <v>-25.19</v>
+        <v>-26.07</v>
       </c>
       <c r="M4">
-        <v>-20.87</v>
+        <v>-20.64</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>405.15</v>
+        <v>404.02</v>
       </c>
       <c r="Q4">
-        <v>415.15</v>
+        <v>414.16</v>
       </c>
       <c r="R4">
-        <v>420.23</v>
+        <v>419.68</v>
       </c>
       <c r="S4">
-        <v>420.52</v>
+        <v>420.01</v>
       </c>
       <c r="T4">
-        <v>-4.39</v>
+        <v>-4.45</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1211,34 +1205,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.99</v>
+        <v>37.45</v>
       </c>
       <c r="Z4">
-        <v>-5.12</v>
+        <v>-5.37</v>
       </c>
       <c r="AA4">
-        <v>-3.63</v>
+        <v>-3.98</v>
       </c>
       <c r="AB4">
-        <v>-1.48</v>
+        <v>-1.39</v>
       </c>
       <c r="AC4">
-        <v>8.74</v>
+        <v>2.21</v>
       </c>
       <c r="AD4">
-        <v>15.55</v>
+        <v>9.07</v>
       </c>
       <c r="AE4">
-        <v>12.11</v>
+        <v>11.77</v>
       </c>
       <c r="AF4">
-        <v>-38.83</v>
+        <v>-62.91</v>
       </c>
       <c r="AG4">
-        <v>433.74</v>
+        <v>433.52</v>
       </c>
       <c r="AH4">
-        <v>396.55</v>
+        <v>394.8</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1247,7 +1241,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>15.98</v>
+        <v>16.45</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1258,10 +1252,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1018.4</v>
+        <v>1015</v>
       </c>
       <c r="D5">
-        <v>1.27</v>
+        <v>-0.33</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1270,46 +1264,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-4.76</v>
+        <v>-5.08</v>
       </c>
       <c r="H5">
-        <v>42.88</v>
+        <v>42.41</v>
       </c>
       <c r="I5">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
       <c r="J5">
-        <v>2.24</v>
+        <v>0.83</v>
       </c>
       <c r="K5">
-        <v>9.24</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="L5">
-        <v>29.65</v>
+        <v>30.43</v>
       </c>
       <c r="M5">
-        <v>0.87</v>
+        <v>0.79</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P5">
         <v>1012.74</v>
       </c>
       <c r="Q5">
-        <v>1016.2</v>
+        <v>1017.35</v>
       </c>
       <c r="R5">
-        <v>993.4</v>
+        <v>995.03</v>
       </c>
       <c r="S5">
-        <v>907.17</v>
+        <v>908.3099999999999</v>
       </c>
       <c r="T5">
-        <v>12.26</v>
+        <v>11.75</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1324,34 +1318,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.48</v>
+        <v>51.97</v>
       </c>
       <c r="Z5">
-        <v>4.52</v>
+        <v>4.15</v>
       </c>
       <c r="AA5">
-        <v>7.61</v>
+        <v>6.92</v>
       </c>
       <c r="AB5">
-        <v>-3.08</v>
+        <v>-2.76</v>
       </c>
       <c r="AC5">
-        <v>18.82</v>
+        <v>32.24</v>
       </c>
       <c r="AD5">
-        <v>12.35</v>
+        <v>19.37</v>
       </c>
       <c r="AE5">
-        <v>18.13</v>
+        <v>18.15</v>
       </c>
       <c r="AF5">
-        <v>-22.03</v>
+        <v>22.43</v>
       </c>
       <c r="AG5">
-        <v>1033.47</v>
+        <v>1030.36</v>
       </c>
       <c r="AH5">
-        <v>998.92</v>
+        <v>1004.34</v>
       </c>
       <c r="AI5">
         <v>1057.76</v>
@@ -1360,7 +1354,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>14.47</v>
+        <v>13.69</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1371,10 +1365,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="D6">
-        <v>12.18</v>
+        <v>1.32</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1383,49 +1377,49 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-16.02</v>
+        <v>-14.92</v>
       </c>
       <c r="H6">
-        <v>65.22</v>
+        <v>67.39</v>
       </c>
       <c r="I6">
-        <v>31.03</v>
+        <v>35.68</v>
       </c>
       <c r="J6">
-        <v>31.6</v>
+        <v>32.76</v>
       </c>
       <c r="K6">
-        <v>16.03</v>
+        <v>16.67</v>
       </c>
       <c r="L6">
-        <v>-11.88</v>
+        <v>-9.68</v>
       </c>
       <c r="M6">
-        <v>5.11</v>
+        <v>4.35</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>66</v>
+        <v>69</v>
       </c>
       <c r="P6">
-        <v>2.51</v>
+        <v>2.67</v>
       </c>
       <c r="Q6">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="R6">
-        <v>2.41</v>
+        <v>2.42</v>
       </c>
       <c r="S6">
         <v>2.7</v>
       </c>
       <c r="T6">
-        <v>12.74</v>
+        <v>14.25</v>
       </c>
       <c r="U6" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="V6" t="s">
         <v>44</v>
@@ -1434,46 +1428,46 @@
         <v>44</v>
       </c>
       <c r="X6">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y6">
-        <v>83.02</v>
+        <v>83.7</v>
       </c>
       <c r="Z6">
-        <v>0.06</v>
+        <v>0.1</v>
       </c>
       <c r="AA6">
-        <v>-0.01</v>
+        <v>0.02</v>
       </c>
       <c r="AB6">
-        <v>0.06</v>
+        <v>0.09</v>
       </c>
       <c r="AC6">
-        <v>71.39</v>
+        <v>100</v>
       </c>
       <c r="AD6">
-        <v>38.06</v>
+        <v>69.81999999999999</v>
       </c>
       <c r="AE6">
         <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>1327.17</v>
+        <v>323.56</v>
       </c>
       <c r="AG6">
-        <v>2.74</v>
+        <v>2.9</v>
       </c>
       <c r="AH6">
-        <v>2.02</v>
+        <v>1.94</v>
       </c>
       <c r="AI6">
-        <v>2.64</v>
+        <v>2.65</v>
       </c>
       <c r="AJ6" t="s">
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>35.53</v>
+        <v>41.92</v>
       </c>
     </row>
   </sheetData>
@@ -1614,7 +1608,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1654,7 +1648,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1666,15 +1660,15 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1686,16 +1680,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>58</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="E6" s="3" t="s">
         <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1706,13 +1700,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>14.84</v>
+        <v>14.71</v>
       </c>
       <c r="D7" s="6">
-        <v>14.71</v>
+        <v>12.66</v>
       </c>
       <c r="E7" s="7">
-        <v>-0.13</v>
+        <v>-2.05</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1723,13 +1717,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>2.51</v>
+        <v>0.47</v>
       </c>
       <c r="D8" s="6">
-        <v>0.47</v>
+        <v>-0.06</v>
       </c>
       <c r="E8" s="7">
-        <v>-2.04</v>
+        <v>-0.53</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1740,13 +1734,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-5.51</v>
+        <v>-4.85</v>
       </c>
       <c r="D9" s="6">
-        <v>-4.85</v>
-      </c>
-      <c r="E9" s="8">
-        <v>0.66</v>
+        <v>-5.03</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-0.18</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1757,13 +1751,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>0.01</v>
+        <v>2.24</v>
       </c>
       <c r="D10" s="6">
-        <v>2.24</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.23</v>
+        <v>0.83</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1774,13 +1768,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>16.81</v>
+        <v>31.6</v>
       </c>
       <c r="D11" s="6">
-        <v>31.6</v>
+        <v>32.76</v>
       </c>
       <c r="E11" s="8">
-        <v>14.79</v>
+        <v>1.16</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1791,13 +1785,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>0.79</v>
+        <v>-2.15</v>
       </c>
       <c r="D12" s="6">
-        <v>-2.15</v>
-      </c>
-      <c r="E12" s="7">
-        <v>-2.94</v>
+        <v>-0.9399999999999999</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.21</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1808,13 +1802,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>0.88</v>
+        <v>-2.35</v>
       </c>
       <c r="D13" s="6">
-        <v>-2.35</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.23</v>
+        <v>-1.48</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.87</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1825,13 +1819,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-1.57</v>
+        <v>-2.66</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.66</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-1.09</v>
+        <v>-1.39</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.27</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1842,13 +1836,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-1.49</v>
+        <v>-0.24</v>
       </c>
       <c r="D15" s="6">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
       <c r="E15" s="8">
-        <v>1.25</v>
+        <v>0.24</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1859,13 +1853,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>16.81</v>
+        <v>31.03</v>
       </c>
       <c r="D16" s="6">
-        <v>31.03</v>
+        <v>35.68</v>
       </c>
       <c r="E16" s="8">
-        <v>14.22</v>
+        <v>4.65</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1876,13 +1870,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>34.44</v>
+        <v>33.14</v>
       </c>
       <c r="D17" s="6">
-        <v>33.14</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-1.3</v>
+        <v>34.39</v>
+      </c>
+      <c r="E17" s="8">
+        <v>1.25</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1893,13 +1887,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>12.46</v>
+        <v>10.57</v>
       </c>
       <c r="D18" s="6">
-        <v>10.57</v>
+        <v>4.24</v>
       </c>
       <c r="E18" s="7">
-        <v>-1.89</v>
+        <v>-6.33</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1910,13 +1904,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-24.93</v>
+        <v>-25.19</v>
       </c>
       <c r="D19" s="6">
-        <v>-25.19</v>
+        <v>-26.07</v>
       </c>
       <c r="E19" s="7">
-        <v>-0.26</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1927,13 +1921,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>27.51</v>
+        <v>29.65</v>
       </c>
       <c r="D20" s="6">
-        <v>29.65</v>
+        <v>30.43</v>
       </c>
       <c r="E20" s="8">
-        <v>2.14</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1944,13 +1938,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-21.9</v>
+        <v>-11.88</v>
       </c>
       <c r="D21" s="6">
-        <v>-11.88</v>
+        <v>-9.68</v>
       </c>
       <c r="E21" s="8">
-        <v>10.02</v>
+        <v>2.2</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1961,13 +1955,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>7.23</v>
+        <v>9.779999999999999</v>
       </c>
       <c r="D22" s="6">
-        <v>9.779999999999999</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.55</v>
+        <v>8.58</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1978,13 +1972,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>15.63</v>
+        <v>5.37</v>
       </c>
       <c r="D23" s="6">
-        <v>5.37</v>
+        <v>3.69</v>
       </c>
       <c r="E23" s="7">
-        <v>-10.26</v>
+        <v>-1.68</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1995,13 +1989,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.67</v>
+        <v>-1.54</v>
       </c>
       <c r="D24" s="6">
-        <v>-1.54</v>
-      </c>
-      <c r="E24" s="8">
-        <v>0.13</v>
+        <v>-3.09</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-1.55</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2012,13 +2006,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>8.58</v>
+        <v>9.24</v>
       </c>
       <c r="D25" s="6">
-        <v>9.24</v>
-      </c>
-      <c r="E25" s="8">
-        <v>0.66</v>
+        <v>8.869999999999999</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-0.37</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2029,13 +2023,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>1.88</v>
+        <v>16.03</v>
       </c>
       <c r="D26" s="6">
-        <v>16.03</v>
+        <v>16.67</v>
       </c>
       <c r="E26" s="8">
-        <v>14.15</v>
+        <v>0.64</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2046,13 +2040,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-16.97</v>
+        <v>-16.84</v>
       </c>
       <c r="D27" s="6">
-        <v>-16.84</v>
+        <v>-16.16</v>
       </c>
       <c r="E27" s="8">
-        <v>0.13</v>
+        <v>0.68</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2063,13 +2057,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-10.04</v>
+        <v>-10.53</v>
       </c>
       <c r="D28" s="6">
-        <v>-10.53</v>
+        <v>-11.14</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.49</v>
+        <v>-0.61</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2080,13 +2074,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-26.48</v>
+        <v>-26.51</v>
       </c>
       <c r="D29" s="6">
-        <v>-26.51</v>
+        <v>-26.65</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.03</v>
+        <v>-0.14</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2097,13 +2091,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-5.96</v>
+        <v>-4.76</v>
       </c>
       <c r="D30" s="6">
-        <v>-4.76</v>
-      </c>
-      <c r="E30" s="8">
-        <v>1.2</v>
+        <v>-5.08</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-0.32</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2114,13 +2108,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-25.14</v>
+        <v>-16.02</v>
       </c>
       <c r="D31" s="6">
-        <v>-16.02</v>
+        <v>-14.92</v>
       </c>
       <c r="E31" s="8">
-        <v>9.119999999999999</v>
+        <v>1.1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2131,13 +2125,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>173</v>
+        <v>173.29</v>
       </c>
       <c r="D32" s="6">
-        <v>173.29</v>
+        <v>174.69</v>
       </c>
       <c r="E32" s="8">
-        <v>0.29</v>
+        <v>1.4</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2148,13 +2142,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>400.6</v>
+        <v>398.4</v>
       </c>
       <c r="D33" s="6">
-        <v>398.4</v>
+        <v>395.7</v>
       </c>
       <c r="E33" s="7">
-        <v>-2.2</v>
+        <v>-2.7</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2165,13 +2159,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>402.25</v>
+        <v>402.05</v>
       </c>
       <c r="D34" s="6">
-        <v>402.05</v>
+        <v>401.3</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.2</v>
+        <v>-0.75</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2182,13 +2176,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1005.6</v>
+        <v>1018.4</v>
       </c>
       <c r="D35" s="6">
-        <v>1018.4</v>
-      </c>
-      <c r="E35" s="8">
-        <v>12.8</v>
+        <v>1015</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-3.4</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2199,217 +2193,183 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>2.71</v>
+        <v>3.04</v>
       </c>
       <c r="D36" s="6">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="E36" s="8">
-        <v>0.33</v>
+        <v>0.04</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>60</v>
+        <v>57.11</v>
       </c>
       <c r="D37" s="6">
-        <v>40</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-20</v>
+        <v>59.1</v>
+      </c>
+      <c r="E37" s="8">
+        <v>1.99</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>40</v>
+        <v>45.46</v>
       </c>
       <c r="D38" s="6">
-        <v>60</v>
-      </c>
-      <c r="E38" s="8">
-        <v>20</v>
+        <v>44.07</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-1.39</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>56.7</v>
+        <v>37.99</v>
       </c>
       <c r="D39" s="6">
-        <v>57.11</v>
-      </c>
-      <c r="E39" s="8">
-        <v>0.41</v>
+        <v>37.45</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-0.54</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>46.57</v>
+        <v>53.48</v>
       </c>
       <c r="D40" s="6">
-        <v>45.46</v>
+        <v>51.97</v>
       </c>
       <c r="E40" s="7">
-        <v>-1.11</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>38.13</v>
+        <v>83.02</v>
       </c>
       <c r="D41" s="6">
-        <v>37.99</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-0.14</v>
+        <v>83.7</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.68</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>48.19</v>
+        <v>-54.49</v>
       </c>
       <c r="D42" s="6">
-        <v>53.48</v>
-      </c>
-      <c r="E42" s="8">
-        <v>5.29</v>
+        <v>-55.89</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-1.4</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>74.90000000000001</v>
+        <v>-82.34999999999999</v>
       </c>
       <c r="D43" s="6">
-        <v>83.02</v>
+        <v>-80.84999999999999</v>
       </c>
       <c r="E43" s="8">
-        <v>8.119999999999999</v>
+        <v>1.5</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-70.81999999999999</v>
+        <v>-38.83</v>
       </c>
       <c r="D44" s="6">
-        <v>-54.49</v>
-      </c>
-      <c r="E44" s="8">
-        <v>16.33</v>
+        <v>-62.91</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-24.08</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="5" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-85.31</v>
+        <v>-22.03</v>
       </c>
       <c r="D45" s="6">
-        <v>-82.34999999999999</v>
+        <v>22.43</v>
       </c>
       <c r="E45" s="8">
-        <v>2.96</v>
+        <v>44.46</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="5" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>11.68</v>
+        <v>1327.17</v>
       </c>
       <c r="D46" s="6">
-        <v>-38.83</v>
+        <v>323.56</v>
       </c>
       <c r="E46" s="7">
-        <v>-50.51</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>-31.51</v>
-      </c>
-      <c r="D47" s="6">
-        <v>-22.03</v>
-      </c>
-      <c r="E47" s="8">
-        <v>9.48</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>616.8099999999999</v>
-      </c>
-      <c r="D48" s="6">
-        <v>1327.17</v>
-      </c>
-      <c r="E48" s="8">
-        <v>710.36</v>
+        <v>-1003.61</v>
       </c>
     </row>
   </sheetData>
@@ -2439,28 +2399,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
+        <v>61</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>62</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>63</v>
       </c>
-      <c r="C1" s="9" t="s">
+      <c r="E1" s="9" t="s">
         <v>64</v>
       </c>
-      <c r="D1" s="9" t="s">
+      <c r="F1" s="9" t="s">
         <v>65</v>
       </c>
-      <c r="E1" s="9" t="s">
+      <c r="G1" s="9" t="s">
         <v>66</v>
       </c>
-      <c r="F1" s="9" t="s">
+      <c r="H1" s="9" t="s">
         <v>67</v>
       </c>
-      <c r="G1" s="9" t="s">
+      <c r="I1" s="9" t="s">
         <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2474,16 +2434,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>55.4</v>
+        <v>55.3</v>
       </c>
       <c r="E2" s="11">
         <v>80</v>
       </c>
       <c r="F2" s="11">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G2" s="11">
-        <v>7.8</v>
+        <v>6.9</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2608,19 +2568,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2636</v>
+        <v>0.2673</v>
       </c>
       <c r="B2" s="14">
-        <v>0.109</v>
+        <v>0.108</v>
       </c>
       <c r="C2" s="14">
-        <v>0.05110000000000001</v>
+        <v>0.0435</v>
       </c>
       <c r="D2" s="14">
-        <v>0.008699999999999999</v>
+        <v>0.007900000000000001</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2087</v>
+        <v>-0.2064</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="69">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,13 +181,19 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>20 DMA &gt; 50 DMA</t>
-  </si>
-  <si>
-    <t>No → Yes</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>52.0 → 47.3</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>52.0</t>
+  </si>
+  <si>
+    <t>47.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -273,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -313,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -772,7 +778,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
     <col min="18" max="18" width="8.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
@@ -913,10 +920,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>174.69</v>
+        <v>179.05</v>
       </c>
       <c r="D2">
-        <v>0.8100000000000001</v>
+        <v>2.5</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -925,46 +932,46 @@
         <v>124.01</v>
       </c>
       <c r="G2">
-        <v>-16.16</v>
+        <v>-14.07</v>
       </c>
       <c r="H2">
-        <v>40.87</v>
+        <v>44.38</v>
       </c>
       <c r="I2">
-        <v>-0.9399999999999999</v>
+        <v>3.44</v>
       </c>
       <c r="J2">
-        <v>12.66</v>
+        <v>13.68</v>
       </c>
       <c r="K2">
-        <v>8.58</v>
+        <v>11.29</v>
       </c>
       <c r="L2">
-        <v>34.39</v>
+        <v>39.95</v>
       </c>
       <c r="M2">
-        <v>26.73</v>
+        <v>27.65</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>173.58</v>
+        <v>174.77</v>
       </c>
       <c r="Q2">
-        <v>172.78</v>
+        <v>173.83</v>
       </c>
       <c r="R2">
-        <v>163.5</v>
+        <v>163.91</v>
       </c>
       <c r="S2">
-        <v>167.98</v>
+        <v>168.19</v>
       </c>
       <c r="T2">
-        <v>3.99</v>
+        <v>6.46</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -979,34 +986,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>59.1</v>
+        <v>64.61</v>
       </c>
       <c r="Z2">
-        <v>3.6</v>
+        <v>3.78</v>
       </c>
       <c r="AA2">
-        <v>4.2</v>
+        <v>4.12</v>
       </c>
       <c r="AB2">
-        <v>-0.61</v>
+        <v>-0.34</v>
       </c>
       <c r="AC2">
-        <v>6.09</v>
+        <v>23.29</v>
       </c>
       <c r="AD2">
-        <v>3.59</v>
+        <v>10.72</v>
       </c>
       <c r="AE2">
-        <v>4.2</v>
+        <v>4.24</v>
       </c>
       <c r="AF2">
-        <v>-55.89</v>
+        <v>-8.44</v>
       </c>
       <c r="AG2">
-        <v>184.17</v>
+        <v>183.16</v>
       </c>
       <c r="AH2">
-        <v>161.39</v>
+        <v>164.51</v>
       </c>
       <c r="AI2">
         <v>165.9</v>
@@ -1015,7 +1022,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>18.53</v>
+        <v>20.51</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1026,10 +1033,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>395.7</v>
+        <v>397.4</v>
       </c>
       <c r="D3">
-        <v>-0.68</v>
+        <v>0.43</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1038,46 +1045,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-11.14</v>
+        <v>-10.76</v>
       </c>
       <c r="H3">
-        <v>75.87</v>
+        <v>76.62</v>
       </c>
       <c r="I3">
-        <v>-1.48</v>
+        <v>-0.29</v>
       </c>
       <c r="J3">
-        <v>-0.06</v>
+        <v>2.38</v>
       </c>
       <c r="K3">
-        <v>3.69</v>
+        <v>4.14</v>
       </c>
       <c r="L3">
-        <v>4.24</v>
+        <v>2.26</v>
       </c>
       <c r="M3">
-        <v>10.8</v>
+        <v>11.4</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="P3">
-        <v>398.3</v>
+        <v>398.07</v>
       </c>
       <c r="Q3">
-        <v>409.04</v>
+        <v>409.76</v>
       </c>
       <c r="R3">
-        <v>407.43</v>
+        <v>407.34</v>
       </c>
       <c r="S3">
-        <v>325.42</v>
+        <v>325.72</v>
       </c>
       <c r="T3">
-        <v>21.59</v>
+        <v>22.01</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1092,34 +1099,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>44.07</v>
+        <v>45.21</v>
       </c>
       <c r="Z3">
-        <v>-1.1</v>
+        <v>-1.58</v>
       </c>
       <c r="AA3">
-        <v>1.79</v>
+        <v>1.12</v>
       </c>
       <c r="AB3">
-        <v>-2.89</v>
+        <v>-2.7</v>
       </c>
       <c r="AC3">
-        <v>4.82</v>
+        <v>3.18</v>
       </c>
       <c r="AD3">
-        <v>5.7</v>
+        <v>4.74</v>
       </c>
       <c r="AE3">
-        <v>13.52</v>
+        <v>13.25</v>
       </c>
       <c r="AF3">
-        <v>-80.84999999999999</v>
+        <v>-73.44</v>
       </c>
       <c r="AG3">
-        <v>440.41</v>
+        <v>439.21</v>
       </c>
       <c r="AH3">
-        <v>377.68</v>
+        <v>380.32</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1128,7 +1135,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>24.55</v>
+        <v>23.66</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1139,10 +1146,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>401.3</v>
+        <v>401.95</v>
       </c>
       <c r="D4">
-        <v>-0.19</v>
+        <v>0.16</v>
       </c>
       <c r="E4">
         <v>547.1</v>
@@ -1151,46 +1158,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-26.65</v>
+        <v>-26.53</v>
       </c>
       <c r="H4">
-        <v>16.42</v>
+        <v>16.61</v>
       </c>
       <c r="I4">
-        <v>-1.39</v>
+        <v>-1.48</v>
       </c>
       <c r="J4">
-        <v>-5.03</v>
+        <v>-4.52</v>
       </c>
       <c r="K4">
-        <v>-3.09</v>
+        <v>-2.93</v>
       </c>
       <c r="L4">
-        <v>-26.07</v>
+        <v>-26.26</v>
       </c>
       <c r="M4">
-        <v>-20.64</v>
+        <v>-20.27</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="P4">
-        <v>404.02</v>
+        <v>402.81</v>
       </c>
       <c r="Q4">
-        <v>414.16</v>
+        <v>413.07</v>
       </c>
       <c r="R4">
-        <v>419.68</v>
+        <v>419.14</v>
       </c>
       <c r="S4">
-        <v>420.01</v>
+        <v>419.49</v>
       </c>
       <c r="T4">
-        <v>-4.45</v>
+        <v>-4.18</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1205,34 +1212,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.45</v>
+        <v>38.27</v>
       </c>
       <c r="Z4">
-        <v>-5.37</v>
+        <v>-5.46</v>
       </c>
       <c r="AA4">
-        <v>-3.98</v>
+        <v>-4.28</v>
       </c>
       <c r="AB4">
-        <v>-1.39</v>
+        <v>-1.18</v>
       </c>
       <c r="AC4">
-        <v>2.21</v>
+        <v>2.65</v>
       </c>
       <c r="AD4">
-        <v>9.07</v>
+        <v>4.53</v>
       </c>
       <c r="AE4">
-        <v>11.77</v>
+        <v>11.48</v>
       </c>
       <c r="AF4">
-        <v>-62.91</v>
+        <v>-62.1</v>
       </c>
       <c r="AG4">
-        <v>433.52</v>
+        <v>432.6</v>
       </c>
       <c r="AH4">
-        <v>394.8</v>
+        <v>393.54</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1241,7 +1248,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>16.45</v>
+        <v>14.73</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1252,10 +1259,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1015</v>
+        <v>1004</v>
       </c>
       <c r="D5">
-        <v>-0.33</v>
+        <v>-1.08</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1264,46 +1271,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-5.08</v>
+        <v>-6.11</v>
       </c>
       <c r="H5">
-        <v>42.41</v>
+        <v>40.86</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="J5">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="K5">
-        <v>8.869999999999999</v>
+        <v>7.69</v>
       </c>
       <c r="L5">
-        <v>30.43</v>
+        <v>30.82</v>
       </c>
       <c r="M5">
-        <v>0.79</v>
+        <v>0.65</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>1012.74</v>
+        <v>1010.2</v>
       </c>
       <c r="Q5">
-        <v>1017.35</v>
+        <v>1016.94</v>
       </c>
       <c r="R5">
-        <v>995.03</v>
+        <v>996.59</v>
       </c>
       <c r="S5">
-        <v>908.3099999999999</v>
+        <v>909.34</v>
       </c>
       <c r="T5">
-        <v>11.75</v>
+        <v>10.41</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1318,34 +1325,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>51.97</v>
+        <v>47.29</v>
       </c>
       <c r="Z5">
-        <v>4.15</v>
+        <v>2.94</v>
       </c>
       <c r="AA5">
-        <v>6.92</v>
+        <v>6.12</v>
       </c>
       <c r="AB5">
-        <v>-2.76</v>
+        <v>-3.18</v>
       </c>
       <c r="AC5">
         <v>32.24</v>
       </c>
       <c r="AD5">
-        <v>19.37</v>
+        <v>27.77</v>
       </c>
       <c r="AE5">
-        <v>18.15</v>
+        <v>18.94</v>
       </c>
       <c r="AF5">
-        <v>22.43</v>
+        <v>-3.58</v>
       </c>
       <c r="AG5">
-        <v>1030.36</v>
+        <v>1031.11</v>
       </c>
       <c r="AH5">
-        <v>1004.34</v>
+        <v>1002.76</v>
       </c>
       <c r="AI5">
         <v>1057.76</v>
@@ -1354,7 +1361,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>13.69</v>
+        <v>14.98</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1365,10 +1372,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="D6">
-        <v>1.32</v>
+        <v>-2.27</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1377,46 +1384,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-14.92</v>
+        <v>-16.85</v>
       </c>
       <c r="H6">
-        <v>67.39</v>
+        <v>63.59</v>
       </c>
       <c r="I6">
-        <v>35.68</v>
+        <v>33.78</v>
       </c>
       <c r="J6">
-        <v>32.76</v>
+        <v>32.6</v>
       </c>
       <c r="K6">
-        <v>16.67</v>
+        <v>14.02</v>
       </c>
       <c r="L6">
-        <v>-9.68</v>
+        <v>-12.75</v>
       </c>
       <c r="M6">
-        <v>4.35</v>
+        <v>2.89</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="P6">
-        <v>2.67</v>
+        <v>2.82</v>
       </c>
       <c r="Q6">
-        <v>2.42</v>
+        <v>2.45</v>
       </c>
       <c r="R6">
-        <v>2.42</v>
+        <v>2.43</v>
       </c>
       <c r="S6">
-        <v>2.7</v>
+        <v>2.69</v>
       </c>
       <c r="T6">
-        <v>14.25</v>
+        <v>11.71</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1431,34 +1438,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>83.7</v>
+        <v>77.77</v>
       </c>
       <c r="Z6">
-        <v>0.1</v>
+        <v>0.13</v>
       </c>
       <c r="AA6">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="AB6">
         <v>0.09</v>
       </c>
       <c r="AC6">
-        <v>100</v>
+        <v>95.98999999999999</v>
       </c>
       <c r="AD6">
-        <v>69.81999999999999</v>
+        <v>89.13</v>
       </c>
       <c r="AE6">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>323.56</v>
+        <v>8.74</v>
       </c>
       <c r="AG6">
-        <v>2.9</v>
+        <v>2.99</v>
       </c>
       <c r="AH6">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1467,7 +1474,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>41.92</v>
+        <v>47.46</v>
       </c>
     </row>
   </sheetData>
@@ -1648,7 +1655,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1660,15 +1667,15 @@
         <v>55</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>44</v>
+        <v>56</v>
       </c>
       <c r="F3" s="4" t="s">
-        <v>43</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1680,16 +1687,16 @@
         <v>0</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -1700,13 +1707,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>14.71</v>
+        <v>12.66</v>
       </c>
       <c r="D7" s="6">
-        <v>12.66</v>
+        <v>13.68</v>
       </c>
       <c r="E7" s="7">
-        <v>-2.05</v>
+        <v>1.02</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1717,13 +1724,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>0.47</v>
+        <v>-0.06</v>
       </c>
       <c r="D8" s="6">
-        <v>-0.06</v>
+        <v>2.38</v>
       </c>
       <c r="E8" s="7">
-        <v>-0.53</v>
+        <v>2.44</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1734,13 +1741,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-4.85</v>
+        <v>-5.03</v>
       </c>
       <c r="D9" s="6">
-        <v>-5.03</v>
+        <v>-4.52</v>
       </c>
       <c r="E9" s="7">
-        <v>-0.18</v>
+        <v>0.51</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1751,13 +1758,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>2.24</v>
+        <v>0.83</v>
       </c>
       <c r="D10" s="6">
-        <v>0.83</v>
+        <v>1.21</v>
       </c>
       <c r="E10" s="7">
-        <v>-1.41</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1768,13 +1775,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>31.6</v>
+        <v>32.76</v>
       </c>
       <c r="D11" s="6">
-        <v>32.76</v>
+        <v>32.6</v>
       </c>
       <c r="E11" s="8">
-        <v>1.16</v>
+        <v>-0.16</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1785,13 +1792,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-2.15</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="D12" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="E12" s="8">
-        <v>1.21</v>
+        <v>3.44</v>
+      </c>
+      <c r="E12" s="7">
+        <v>4.38</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1802,13 +1809,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-2.35</v>
+        <v>-1.48</v>
       </c>
       <c r="D13" s="6">
-        <v>-1.48</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.87</v>
+        <v>-0.29</v>
+      </c>
+      <c r="E13" s="7">
+        <v>1.19</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1819,13 +1826,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.66</v>
+        <v>-1.39</v>
       </c>
       <c r="D14" s="6">
-        <v>-1.39</v>
+        <v>-1.48</v>
       </c>
       <c r="E14" s="8">
-        <v>1.27</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1836,13 +1843,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-0.24</v>
+        <v>0</v>
       </c>
       <c r="D15" s="6">
-        <v>0</v>
+        <v>-1.25</v>
       </c>
       <c r="E15" s="8">
-        <v>0.24</v>
+        <v>-1.25</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1853,13 +1860,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>31.03</v>
+        <v>35.68</v>
       </c>
       <c r="D16" s="6">
-        <v>35.68</v>
+        <v>33.78</v>
       </c>
       <c r="E16" s="8">
-        <v>4.65</v>
+        <v>-1.9</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1870,13 +1877,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>33.14</v>
+        <v>34.39</v>
       </c>
       <c r="D17" s="6">
-        <v>34.39</v>
-      </c>
-      <c r="E17" s="8">
-        <v>1.25</v>
+        <v>39.95</v>
+      </c>
+      <c r="E17" s="7">
+        <v>5.56</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1887,13 +1894,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>10.57</v>
+        <v>4.24</v>
       </c>
       <c r="D18" s="6">
-        <v>4.24</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-6.33</v>
+        <v>2.26</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-1.98</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1904,13 +1911,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-25.19</v>
+        <v>-26.07</v>
       </c>
       <c r="D19" s="6">
-        <v>-26.07</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.88</v>
+        <v>-26.26</v>
+      </c>
+      <c r="E19" s="8">
+        <v>-0.19</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1921,13 +1928,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>29.65</v>
+        <v>30.43</v>
       </c>
       <c r="D20" s="6">
-        <v>30.43</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.78</v>
+        <v>30.82</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.39</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1938,13 +1945,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-11.88</v>
+        <v>-9.68</v>
       </c>
       <c r="D21" s="6">
-        <v>-9.68</v>
+        <v>-12.75</v>
       </c>
       <c r="E21" s="8">
-        <v>2.2</v>
+        <v>-3.07</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1955,13 +1962,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>9.779999999999999</v>
+        <v>8.58</v>
       </c>
       <c r="D22" s="6">
-        <v>8.58</v>
+        <v>11.29</v>
       </c>
       <c r="E22" s="7">
-        <v>-1.2</v>
+        <v>2.71</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1972,13 +1979,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>5.37</v>
+        <v>3.69</v>
       </c>
       <c r="D23" s="6">
-        <v>3.69</v>
+        <v>4.14</v>
       </c>
       <c r="E23" s="7">
-        <v>-1.68</v>
+        <v>0.45</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1989,13 +1996,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-1.54</v>
+        <v>-3.09</v>
       </c>
       <c r="D24" s="6">
-        <v>-3.09</v>
+        <v>-2.93</v>
       </c>
       <c r="E24" s="7">
-        <v>-1.55</v>
+        <v>0.16</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2006,13 +2013,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>9.24</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="D25" s="6">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-0.37</v>
+        <v>7.69</v>
+      </c>
+      <c r="E25" s="8">
+        <v>-1.18</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2023,13 +2030,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>16.03</v>
+        <v>16.67</v>
       </c>
       <c r="D26" s="6">
-        <v>16.67</v>
+        <v>14.02</v>
       </c>
       <c r="E26" s="8">
-        <v>0.64</v>
+        <v>-2.65</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2040,13 +2047,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-16.84</v>
+        <v>-16.16</v>
       </c>
       <c r="D27" s="6">
-        <v>-16.16</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.68</v>
+        <v>-14.07</v>
+      </c>
+      <c r="E27" s="7">
+        <v>2.09</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2057,13 +2064,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-10.53</v>
+        <v>-11.14</v>
       </c>
       <c r="D28" s="6">
-        <v>-11.14</v>
+        <v>-10.76</v>
       </c>
       <c r="E28" s="7">
-        <v>-0.61</v>
+        <v>0.38</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2074,13 +2081,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-26.51</v>
+        <v>-26.65</v>
       </c>
       <c r="D29" s="6">
-        <v>-26.65</v>
+        <v>-26.53</v>
       </c>
       <c r="E29" s="7">
-        <v>-0.14</v>
+        <v>0.12</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2091,13 +2098,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-4.76</v>
+        <v>-5.08</v>
       </c>
       <c r="D30" s="6">
-        <v>-5.08</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-0.32</v>
+        <v>-6.11</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-1.03</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2108,13 +2115,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="6">
-        <v>-16.02</v>
+        <v>-14.92</v>
       </c>
       <c r="D31" s="6">
-        <v>-14.92</v>
+        <v>-16.85</v>
       </c>
       <c r="E31" s="8">
-        <v>1.1</v>
+        <v>-1.93</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2125,13 +2132,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>173.29</v>
+        <v>174.69</v>
       </c>
       <c r="D32" s="6">
-        <v>174.69</v>
-      </c>
-      <c r="E32" s="8">
-        <v>1.4</v>
+        <v>179.05</v>
+      </c>
+      <c r="E32" s="7">
+        <v>4.36</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2142,13 +2149,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>398.4</v>
+        <v>395.7</v>
       </c>
       <c r="D33" s="6">
-        <v>395.7</v>
+        <v>397.4</v>
       </c>
       <c r="E33" s="7">
-        <v>-2.7</v>
+        <v>1.7</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2159,13 +2166,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>402.05</v>
+        <v>401.3</v>
       </c>
       <c r="D34" s="6">
-        <v>401.3</v>
+        <v>401.95</v>
       </c>
       <c r="E34" s="7">
-        <v>-0.75</v>
+        <v>0.65</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2176,13 +2183,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="6">
-        <v>1018.4</v>
+        <v>1015</v>
       </c>
       <c r="D35" s="6">
-        <v>1015</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-3.4</v>
+        <v>1004</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-11</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2193,13 +2200,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="6">
-        <v>3.04</v>
+        <v>3.08</v>
       </c>
       <c r="D36" s="6">
-        <v>3.08</v>
+        <v>3.01</v>
       </c>
       <c r="E36" s="8">
-        <v>0.04</v>
+        <v>-0.07000000000000001</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2210,13 +2217,13 @@
         <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>57.11</v>
+        <v>59.1</v>
       </c>
       <c r="D37" s="6">
-        <v>59.1</v>
-      </c>
-      <c r="E37" s="8">
-        <v>1.99</v>
+        <v>64.61</v>
+      </c>
+      <c r="E37" s="7">
+        <v>5.51</v>
       </c>
     </row>
     <row r="38" spans="1:5">
@@ -2227,13 +2234,13 @@
         <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>45.46</v>
+        <v>44.07</v>
       </c>
       <c r="D38" s="6">
-        <v>44.07</v>
+        <v>45.21</v>
       </c>
       <c r="E38" s="7">
-        <v>-1.39</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2244,13 +2251,13 @@
         <v>24</v>
       </c>
       <c r="C39" s="6">
-        <v>37.99</v>
+        <v>37.45</v>
       </c>
       <c r="D39" s="6">
-        <v>37.45</v>
+        <v>38.27</v>
       </c>
       <c r="E39" s="7">
-        <v>-0.54</v>
+        <v>0.82</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2261,13 +2268,13 @@
         <v>24</v>
       </c>
       <c r="C40" s="6">
-        <v>53.48</v>
+        <v>51.97</v>
       </c>
       <c r="D40" s="6">
-        <v>51.97</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-1.51</v>
+        <v>47.29</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-4.68</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2278,13 +2285,13 @@
         <v>24</v>
       </c>
       <c r="C41" s="6">
-        <v>83.02</v>
+        <v>83.7</v>
       </c>
       <c r="D41" s="6">
-        <v>83.7</v>
+        <v>77.77</v>
       </c>
       <c r="E41" s="8">
-        <v>0.68</v>
+        <v>-5.93</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2295,13 +2302,13 @@
         <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>-54.49</v>
+        <v>-55.89</v>
       </c>
       <c r="D42" s="6">
-        <v>-55.89</v>
+        <v>-8.44</v>
       </c>
       <c r="E42" s="7">
-        <v>-1.4</v>
+        <v>47.45</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2312,13 +2319,13 @@
         <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>-82.34999999999999</v>
+        <v>-80.84999999999999</v>
       </c>
       <c r="D43" s="6">
-        <v>-80.84999999999999</v>
-      </c>
-      <c r="E43" s="8">
-        <v>1.5</v>
+        <v>-73.44</v>
+      </c>
+      <c r="E43" s="7">
+        <v>7.41</v>
       </c>
     </row>
     <row r="44" spans="1:5">
@@ -2329,13 +2336,13 @@
         <v>31</v>
       </c>
       <c r="C44" s="6">
-        <v>-38.83</v>
+        <v>-62.91</v>
       </c>
       <c r="D44" s="6">
-        <v>-62.91</v>
+        <v>-62.1</v>
       </c>
       <c r="E44" s="7">
-        <v>-24.08</v>
+        <v>0.8100000000000001</v>
       </c>
     </row>
     <row r="45" spans="1:5">
@@ -2346,13 +2353,13 @@
         <v>31</v>
       </c>
       <c r="C45" s="6">
-        <v>-22.03</v>
+        <v>22.43</v>
       </c>
       <c r="D45" s="6">
-        <v>22.43</v>
+        <v>-3.58</v>
       </c>
       <c r="E45" s="8">
-        <v>44.46</v>
+        <v>-26.01</v>
       </c>
     </row>
     <row r="46" spans="1:5">
@@ -2363,13 +2370,13 @@
         <v>31</v>
       </c>
       <c r="C46" s="6">
-        <v>1327.17</v>
+        <v>323.56</v>
       </c>
       <c r="D46" s="6">
-        <v>323.56</v>
-      </c>
-      <c r="E46" s="7">
-        <v>-1003.61</v>
+        <v>8.74</v>
+      </c>
+      <c r="E46" s="8">
+        <v>-314.82</v>
       </c>
     </row>
   </sheetData>
@@ -2399,28 +2406,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="9" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C1" s="9" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="D1" s="9" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="E1" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="F1" s="9" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="G1" s="9" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="H1" s="9" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="I1" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2434,16 +2441,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>55.3</v>
+        <v>54.6</v>
       </c>
       <c r="E2" s="11">
         <v>80</v>
       </c>
       <c r="F2" s="11">
-        <v>8.199999999999999</v>
+        <v>9.1</v>
       </c>
       <c r="G2" s="11">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2568,19 +2575,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2673</v>
+        <v>0.2765</v>
       </c>
       <c r="B2" s="14">
-        <v>0.108</v>
+        <v>0.114</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0435</v>
+        <v>0.0289</v>
       </c>
       <c r="D2" s="14">
-        <v>0.007900000000000001</v>
+        <v>0.006500000000000001</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2064</v>
+        <v>-0.2027</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="218" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,34 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>52.0 → 47.3</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>52.0</t>
-  </si>
-  <si>
-    <t>47.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -395,18 +368,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -778,8 +750,7 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="9.7109375" customWidth="1"/>
     <col min="18" max="18" width="8.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
@@ -920,10 +891,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>179.05</v>
+        <v>177.4</v>
       </c>
       <c r="D2">
-        <v>2.5</v>
+        <v>-0.92</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -932,46 +903,46 @@
         <v>124.01</v>
       </c>
       <c r="G2">
-        <v>-14.07</v>
+        <v>-14.86</v>
       </c>
       <c r="H2">
-        <v>44.38</v>
+        <v>43.05</v>
       </c>
       <c r="I2">
-        <v>3.44</v>
+        <v>2.07</v>
       </c>
       <c r="J2">
-        <v>13.68</v>
+        <v>12.31</v>
       </c>
       <c r="K2">
-        <v>11.29</v>
+        <v>16.08</v>
       </c>
       <c r="L2">
-        <v>39.95</v>
+        <v>38.45</v>
       </c>
       <c r="M2">
-        <v>27.65</v>
+        <v>26.84</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P2">
-        <v>174.77</v>
+        <v>175.49</v>
       </c>
       <c r="Q2">
-        <v>173.83</v>
+        <v>174.8</v>
       </c>
       <c r="R2">
-        <v>163.91</v>
+        <v>164.27</v>
       </c>
       <c r="S2">
-        <v>168.19</v>
+        <v>168.38</v>
       </c>
       <c r="T2">
-        <v>6.46</v>
+        <v>5.36</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -986,43 +957,43 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>64.61</v>
+        <v>61.25</v>
       </c>
       <c r="Z2">
-        <v>3.78</v>
+        <v>3.75</v>
       </c>
       <c r="AA2">
-        <v>4.12</v>
+        <v>4.04</v>
       </c>
       <c r="AB2">
-        <v>-0.34</v>
+        <v>-0.3</v>
       </c>
       <c r="AC2">
-        <v>23.29</v>
+        <v>35.94</v>
       </c>
       <c r="AD2">
-        <v>10.72</v>
+        <v>21.78</v>
       </c>
       <c r="AE2">
-        <v>4.24</v>
+        <v>4.3</v>
       </c>
       <c r="AF2">
-        <v>-8.44</v>
+        <v>-28.13</v>
       </c>
       <c r="AG2">
-        <v>183.16</v>
+        <v>180.59</v>
       </c>
       <c r="AH2">
-        <v>164.51</v>
+        <v>169.01</v>
       </c>
       <c r="AI2">
-        <v>165.9</v>
+        <v>166.42</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>20.51</v>
+        <v>23.64</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1033,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>397.4</v>
+        <v>397.35</v>
       </c>
       <c r="D3">
-        <v>0.43</v>
+        <v>-0.01</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1045,46 +1016,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-10.76</v>
+        <v>-10.77</v>
       </c>
       <c r="H3">
-        <v>76.62</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="I3">
-        <v>-0.29</v>
+        <v>-0.23</v>
       </c>
       <c r="J3">
-        <v>2.38</v>
+        <v>3.76</v>
       </c>
       <c r="K3">
-        <v>4.14</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="L3">
-        <v>2.26</v>
+        <v>0.03</v>
       </c>
       <c r="M3">
-        <v>11.4</v>
+        <v>11.11</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="P3">
-        <v>398.07</v>
+        <v>397.89</v>
       </c>
       <c r="Q3">
-        <v>409.76</v>
+        <v>410.25</v>
       </c>
       <c r="R3">
-        <v>407.34</v>
+        <v>407.22</v>
       </c>
       <c r="S3">
-        <v>325.72</v>
+        <v>326.03</v>
       </c>
       <c r="T3">
-        <v>22.01</v>
+        <v>21.87</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1099,34 +1070,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.21</v>
+        <v>45.18</v>
       </c>
       <c r="Z3">
-        <v>-1.58</v>
+        <v>-1.94</v>
       </c>
       <c r="AA3">
-        <v>1.12</v>
+        <v>0.51</v>
       </c>
       <c r="AB3">
-        <v>-2.7</v>
+        <v>-2.45</v>
       </c>
       <c r="AC3">
-        <v>3.18</v>
+        <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>4.74</v>
+        <v>3.8</v>
       </c>
       <c r="AE3">
-        <v>13.25</v>
+        <v>12.88</v>
       </c>
       <c r="AF3">
-        <v>-73.44</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="AG3">
-        <v>439.21</v>
+        <v>438.46</v>
       </c>
       <c r="AH3">
-        <v>380.32</v>
+        <v>382.04</v>
       </c>
       <c r="AI3">
         <v>392.36</v>
@@ -1135,7 +1106,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>23.66</v>
+        <v>22.89</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1146,58 +1117,58 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>401.95</v>
+        <v>402.55</v>
       </c>
       <c r="D4">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="E4">
-        <v>547.1</v>
+        <v>535.55</v>
       </c>
       <c r="F4">
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-26.53</v>
+        <v>-24.83</v>
       </c>
       <c r="H4">
-        <v>16.61</v>
+        <v>16.78</v>
       </c>
       <c r="I4">
-        <v>-1.48</v>
+        <v>-0.97</v>
       </c>
       <c r="J4">
-        <v>-4.52</v>
+        <v>-5.03</v>
       </c>
       <c r="K4">
-        <v>-2.93</v>
+        <v>-2.51</v>
       </c>
       <c r="L4">
-        <v>-26.26</v>
+        <v>-26.42</v>
       </c>
       <c r="M4">
-        <v>-20.27</v>
+        <v>-20.36</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>402.81</v>
+        <v>402.02</v>
       </c>
       <c r="Q4">
-        <v>413.07</v>
+        <v>411.92</v>
       </c>
       <c r="R4">
-        <v>419.14</v>
+        <v>418.71</v>
       </c>
       <c r="S4">
-        <v>419.49</v>
+        <v>418.96</v>
       </c>
       <c r="T4">
-        <v>-4.18</v>
+        <v>-3.92</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1212,34 +1183,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>38.27</v>
+        <v>39.06</v>
       </c>
       <c r="Z4">
-        <v>-5.46</v>
+        <v>-5.41</v>
       </c>
       <c r="AA4">
-        <v>-4.28</v>
+        <v>-4.5</v>
       </c>
       <c r="AB4">
-        <v>-1.18</v>
+        <v>-0.91</v>
       </c>
       <c r="AC4">
-        <v>2.65</v>
+        <v>8.6</v>
       </c>
       <c r="AD4">
-        <v>4.53</v>
+        <v>4.49</v>
       </c>
       <c r="AE4">
-        <v>11.48</v>
+        <v>10.96</v>
       </c>
       <c r="AF4">
-        <v>-62.1</v>
+        <v>-50.6</v>
       </c>
       <c r="AG4">
-        <v>432.6</v>
+        <v>431.06</v>
       </c>
       <c r="AH4">
-        <v>393.54</v>
+        <v>392.78</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1248,7 +1219,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>14.73</v>
+        <v>13.29</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1259,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1004</v>
+        <v>1002.9</v>
       </c>
       <c r="D5">
-        <v>-1.08</v>
+        <v>-0.11</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1271,46 +1242,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-6.11</v>
+        <v>-6.21</v>
       </c>
       <c r="H5">
-        <v>40.86</v>
+        <v>40.71</v>
       </c>
       <c r="I5">
-        <v>-1.25</v>
+        <v>-0.51</v>
       </c>
       <c r="J5">
-        <v>1.21</v>
+        <v>-0.93</v>
       </c>
       <c r="K5">
-        <v>7.69</v>
+        <v>9.68</v>
       </c>
       <c r="L5">
-        <v>30.82</v>
+        <v>31.94</v>
       </c>
       <c r="M5">
-        <v>0.65</v>
+        <v>0.86</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1010.2</v>
+        <v>1009.18</v>
       </c>
       <c r="Q5">
-        <v>1016.94</v>
+        <v>1016.51</v>
       </c>
       <c r="R5">
-        <v>996.59</v>
+        <v>997.9299999999999</v>
       </c>
       <c r="S5">
-        <v>909.34</v>
+        <v>910.36</v>
       </c>
       <c r="T5">
-        <v>10.41</v>
+        <v>10.16</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1325,43 +1296,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>47.29</v>
+        <v>46.84</v>
       </c>
       <c r="Z5">
-        <v>2.94</v>
+        <v>1.86</v>
       </c>
       <c r="AA5">
-        <v>6.12</v>
+        <v>5.27</v>
       </c>
       <c r="AB5">
-        <v>-3.18</v>
+        <v>-3.41</v>
       </c>
       <c r="AC5">
-        <v>32.24</v>
+        <v>13.42</v>
       </c>
       <c r="AD5">
-        <v>27.77</v>
+        <v>25.97</v>
       </c>
       <c r="AE5">
-        <v>18.94</v>
+        <v>18.36</v>
       </c>
       <c r="AF5">
-        <v>-3.58</v>
+        <v>6.67</v>
       </c>
       <c r="AG5">
-        <v>1031.11</v>
+        <v>1031.84</v>
       </c>
       <c r="AH5">
-        <v>1002.76</v>
+        <v>1001.17</v>
       </c>
       <c r="AI5">
-        <v>1057.76</v>
+        <v>1054.97</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>14.98</v>
+        <v>16.09</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1372,10 +1343,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>3.01</v>
+        <v>2.96</v>
       </c>
       <c r="D6">
-        <v>-2.27</v>
+        <v>-1.66</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1384,46 +1355,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-16.85</v>
+        <v>-18.23</v>
       </c>
       <c r="H6">
-        <v>63.59</v>
+        <v>60.87</v>
       </c>
       <c r="I6">
-        <v>33.78</v>
+        <v>30.97</v>
       </c>
       <c r="J6">
-        <v>32.6</v>
+        <v>25.42</v>
       </c>
       <c r="K6">
-        <v>14.02</v>
+        <v>12.98</v>
       </c>
       <c r="L6">
-        <v>-12.75</v>
+        <v>-13.2</v>
       </c>
       <c r="M6">
-        <v>2.89</v>
+        <v>1.71</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>65</v>
+        <v>62</v>
       </c>
       <c r="P6">
-        <v>2.82</v>
+        <v>2.96</v>
       </c>
       <c r="Q6">
-        <v>2.45</v>
+        <v>2.48</v>
       </c>
       <c r="R6">
-        <v>2.43</v>
+        <v>2.44</v>
       </c>
       <c r="S6">
         <v>2.69</v>
       </c>
       <c r="T6">
-        <v>11.71</v>
+        <v>9.9</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1438,34 +1409,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>77.77</v>
+        <v>73.75</v>
       </c>
       <c r="Z6">
-        <v>0.13</v>
+        <v>0.15</v>
       </c>
       <c r="AA6">
-        <v>0.04</v>
+        <v>0.06</v>
       </c>
       <c r="AB6">
         <v>0.09</v>
       </c>
       <c r="AC6">
-        <v>95.98999999999999</v>
+        <v>89.26000000000001</v>
       </c>
       <c r="AD6">
-        <v>89.13</v>
+        <v>95.08</v>
       </c>
       <c r="AE6">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>8.74</v>
+        <v>-24.54</v>
       </c>
       <c r="AG6">
-        <v>2.99</v>
+        <v>3.07</v>
       </c>
       <c r="AH6">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1474,7 +1445,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>47.46</v>
+        <v>51.15</v>
       </c>
     </row>
   </sheetData>
@@ -1635,47 +1606,12 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="3" t="s">
         <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>50</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>51</v>
-      </c>
-      <c r="F2" s="3" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B3" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1683,700 +1619,700 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
+      <c r="B6" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
-        <v>12.66</v>
-      </c>
-      <c r="D7" s="6">
+      <c r="C7" s="5">
         <v>13.68</v>
       </c>
-      <c r="E7" s="7">
-        <v>1.02</v>
+      <c r="D7" s="5">
+        <v>12.31</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
+      <c r="B8" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="6">
-        <v>-0.06</v>
-      </c>
-      <c r="D8" s="6">
+      <c r="C8" s="5">
         <v>2.38</v>
       </c>
+      <c r="D8" s="5">
+        <v>3.76</v>
+      </c>
       <c r="E8" s="7">
-        <v>2.44</v>
+        <v>1.38</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
+      <c r="B9" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="6">
+      <c r="C9" s="5">
+        <v>-4.52</v>
+      </c>
+      <c r="D9" s="5">
         <v>-5.03</v>
       </c>
-      <c r="D9" s="6">
-        <v>-4.52</v>
-      </c>
-      <c r="E9" s="7">
+      <c r="E9" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>1.21</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-0.93</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-2.14</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>32.6</v>
+      </c>
+      <c r="D11" s="5">
+        <v>25.42</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-7.18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>3.44</v>
+      </c>
+      <c r="D12" s="5">
+        <v>2.07</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-0.29</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-0.23</v>
+      </c>
+      <c r="E13" s="7">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.48</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-0.97</v>
+      </c>
+      <c r="E14" s="7">
         <v>0.51</v>
       </c>
     </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>0.83</v>
-      </c>
-      <c r="D10" s="6">
-        <v>1.21</v>
-      </c>
-      <c r="E10" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-1.25</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-0.51</v>
+      </c>
+      <c r="E15" s="7">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>32.76</v>
-      </c>
-      <c r="D11" s="6">
-        <v>32.6</v>
-      </c>
-      <c r="E11" s="8">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>33.78</v>
+      </c>
+      <c r="D16" s="5">
+        <v>30.97</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-2.81</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>39.95</v>
+      </c>
+      <c r="D17" s="5">
+        <v>38.45</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-1.5</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>2.26</v>
+      </c>
+      <c r="D18" s="5">
+        <v>0.03</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-2.23</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-26.26</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.42</v>
+      </c>
+      <c r="E19" s="6">
         <v>-0.16</v>
       </c>
     </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>30.82</v>
+      </c>
+      <c r="D20" s="5">
+        <v>31.94</v>
+      </c>
+      <c r="E20" s="7">
+        <v>1.12</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-12.75</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-13.2</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-0.9399999999999999</v>
-      </c>
-      <c r="D12" s="6">
-        <v>3.44</v>
-      </c>
-      <c r="E12" s="7">
-        <v>4.38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>11.29</v>
+      </c>
+      <c r="D22" s="5">
+        <v>16.08</v>
+      </c>
+      <c r="E22" s="7">
+        <v>4.79</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>-1.48</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-0.29</v>
-      </c>
-      <c r="E13" s="7">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>4.14</v>
+      </c>
+      <c r="D23" s="5">
+        <v>8.140000000000001</v>
+      </c>
+      <c r="E23" s="7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-1.48</v>
-      </c>
-      <c r="E14" s="8">
-        <v>-0.09</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-2.93</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-2.51</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-1.25</v>
-      </c>
-      <c r="E15" s="8">
-        <v>-1.25</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>7.69</v>
+      </c>
+      <c r="D25" s="5">
+        <v>9.68</v>
+      </c>
+      <c r="E25" s="7">
+        <v>1.99</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>35.68</v>
-      </c>
-      <c r="D16" s="6">
-        <v>33.78</v>
-      </c>
-      <c r="E16" s="8">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>14.02</v>
+      </c>
+      <c r="D26" s="5">
+        <v>12.98</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-1.04</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>34.39</v>
-      </c>
-      <c r="D17" s="6">
-        <v>39.95</v>
-      </c>
-      <c r="E17" s="7">
-        <v>5.56</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-14.07</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-14.86</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.79</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>4.24</v>
-      </c>
-      <c r="D18" s="6">
-        <v>2.26</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-1.98</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-10.76</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-10.77</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-26.07</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-26.26</v>
-      </c>
-      <c r="E19" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-26.53</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-24.83</v>
+      </c>
+      <c r="E29" s="7">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>30.43</v>
-      </c>
-      <c r="D20" s="6">
-        <v>30.82</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.39</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-6.11</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-6.21</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-9.68</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-12.75</v>
-      </c>
-      <c r="E21" s="8">
-        <v>-3.07</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-16.85</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-18.23</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-1.38</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>8.58</v>
-      </c>
-      <c r="D22" s="6">
-        <v>11.29</v>
-      </c>
-      <c r="E22" s="7">
-        <v>2.71</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>179.05</v>
+      </c>
+      <c r="D32" s="5">
+        <v>177.4</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-1.65</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>3.69</v>
-      </c>
-      <c r="D23" s="6">
-        <v>4.14</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.45</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>397.4</v>
+      </c>
+      <c r="D33" s="5">
+        <v>397.35</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-3.09</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.93</v>
-      </c>
-      <c r="E24" s="7">
-        <v>0.16</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>401.95</v>
+      </c>
+      <c r="D34" s="5">
+        <v>402.55</v>
+      </c>
+      <c r="E34" s="7">
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>8.869999999999999</v>
-      </c>
-      <c r="D25" s="6">
-        <v>7.69</v>
-      </c>
-      <c r="E25" s="8">
-        <v>-1.18</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>1004</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1002.9</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-1.1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>16.67</v>
-      </c>
-      <c r="D26" s="6">
-        <v>14.02</v>
-      </c>
-      <c r="E26" s="8">
-        <v>-2.65</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>3.01</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.96</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.05</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-16.16</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-14.07</v>
-      </c>
-      <c r="E27" s="7">
-        <v>2.09</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>64.61</v>
+      </c>
+      <c r="D37" s="5">
+        <v>61.25</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-3.36</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-11.14</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-10.76</v>
-      </c>
-      <c r="E28" s="7">
-        <v>0.38</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>45.21</v>
+      </c>
+      <c r="D38" s="5">
+        <v>45.18</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-0.03</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-26.65</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-26.53</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.12</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>38.27</v>
+      </c>
+      <c r="D39" s="5">
+        <v>39.06</v>
+      </c>
+      <c r="E39" s="7">
+        <v>0.79</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-5.08</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-6.11</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-1.03</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>47.29</v>
+      </c>
+      <c r="D40" s="5">
+        <v>46.84</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-0.45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-14.92</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-16.85</v>
-      </c>
-      <c r="E31" s="8">
-        <v>-1.93</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>77.77</v>
+      </c>
+      <c r="D41" s="5">
+        <v>73.75</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-4.02</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>174.69</v>
-      </c>
-      <c r="D32" s="6">
-        <v>179.05</v>
-      </c>
-      <c r="E32" s="7">
-        <v>4.36</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-8.44</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-28.13</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-19.69</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>395.7</v>
-      </c>
-      <c r="D33" s="6">
-        <v>397.4</v>
-      </c>
-      <c r="E33" s="7">
-        <v>1.7</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-73.44</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-82.68000000000001</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-9.24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>401.3</v>
-      </c>
-      <c r="D34" s="6">
-        <v>401.95</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.65</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>-62.1</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-50.6</v>
+      </c>
+      <c r="E44" s="7">
+        <v>11.5</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1015</v>
-      </c>
-      <c r="D35" s="6">
-        <v>1004</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-11</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-3.58</v>
+      </c>
+      <c r="D45" s="5">
+        <v>6.67</v>
+      </c>
+      <c r="E45" s="7">
+        <v>10.25</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>3.08</v>
-      </c>
-      <c r="D36" s="6">
-        <v>3.01</v>
-      </c>
-      <c r="E36" s="8">
-        <v>-0.07000000000000001</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>59.1</v>
-      </c>
-      <c r="D37" s="6">
-        <v>64.61</v>
-      </c>
-      <c r="E37" s="7">
-        <v>5.51</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>44.07</v>
-      </c>
-      <c r="D38" s="6">
-        <v>45.21</v>
-      </c>
-      <c r="E38" s="7">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>37.45</v>
-      </c>
-      <c r="D39" s="6">
-        <v>38.27</v>
-      </c>
-      <c r="E39" s="7">
-        <v>0.82</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>51.97</v>
-      </c>
-      <c r="D40" s="6">
-        <v>47.29</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-4.68</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>83.7</v>
-      </c>
-      <c r="D41" s="6">
-        <v>77.77</v>
-      </c>
-      <c r="E41" s="8">
-        <v>-5.93</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>-55.89</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-8.44</v>
-      </c>
-      <c r="E42" s="7">
-        <v>47.45</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-80.84999999999999</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-73.44</v>
-      </c>
-      <c r="E43" s="7">
-        <v>7.41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-62.91</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-62.1</v>
-      </c>
-      <c r="E44" s="7">
-        <v>0.8100000000000001</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>22.43</v>
-      </c>
-      <c r="D45" s="6">
-        <v>-3.58</v>
-      </c>
-      <c r="E45" s="8">
-        <v>-26.01</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>323.56</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C46" s="5">
         <v>8.74</v>
       </c>
-      <c r="E46" s="8">
-        <v>-314.82</v>
+      <c r="D46" s="5">
+        <v>-24.54</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-33.28</v>
       </c>
     </row>
   </sheetData>
@@ -2402,60 +2338,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>70</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
+      <c r="B2" s="10">
         <v>65.92</v>
       </c>
-      <c r="C2" s="12">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>54.6</v>
-      </c>
-      <c r="E2" s="11">
+      <c r="D2" s="10">
+        <v>53.2</v>
+      </c>
+      <c r="E2" s="10">
         <v>80</v>
       </c>
-      <c r="F2" s="11">
-        <v>9.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>6.8</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="F2" s="10">
+        <v>7.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>8.9</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -2557,37 +2493,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.2765</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.114</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0289</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.006500000000000001</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2027</v>
+      <c r="A2" s="13">
+        <v>0.2684</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1111</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0171</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0086</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2036</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -891,7 +891,7 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>177.4</v>
+        <v>175.77</v>
       </c>
       <c r="D2">
         <v>-0.92</v>
@@ -903,46 +903,46 @@
         <v>124.01</v>
       </c>
       <c r="G2">
-        <v>-14.86</v>
+        <v>-15.65</v>
       </c>
       <c r="H2">
-        <v>43.05</v>
+        <v>41.74</v>
       </c>
       <c r="I2">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="J2">
-        <v>12.31</v>
+        <v>11.18</v>
       </c>
       <c r="K2">
-        <v>16.08</v>
+        <v>19.35</v>
       </c>
       <c r="L2">
-        <v>38.45</v>
+        <v>37.38</v>
       </c>
       <c r="M2">
-        <v>26.84</v>
+        <v>26.33</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="P2">
-        <v>175.49</v>
+        <v>176.04</v>
       </c>
       <c r="Q2">
-        <v>174.8</v>
+        <v>175.28</v>
       </c>
       <c r="R2">
-        <v>164.27</v>
+        <v>164.62</v>
       </c>
       <c r="S2">
-        <v>168.38</v>
+        <v>168.55</v>
       </c>
       <c r="T2">
-        <v>5.36</v>
+        <v>4.29</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -957,34 +957,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>61.25</v>
+        <v>58.03</v>
       </c>
       <c r="Z2">
-        <v>3.75</v>
+        <v>3.55</v>
       </c>
       <c r="AA2">
-        <v>4.04</v>
+        <v>3.94</v>
       </c>
       <c r="AB2">
-        <v>-0.3</v>
+        <v>-0.4</v>
       </c>
       <c r="AC2">
-        <v>35.94</v>
+        <v>34.7</v>
       </c>
       <c r="AD2">
-        <v>21.78</v>
+        <v>31.31</v>
       </c>
       <c r="AE2">
-        <v>4.3</v>
+        <v>4.23</v>
       </c>
       <c r="AF2">
-        <v>-28.13</v>
+        <v>-40.02</v>
       </c>
       <c r="AG2">
-        <v>180.59</v>
+        <v>179.42</v>
       </c>
       <c r="AH2">
-        <v>169.01</v>
+        <v>171.14</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -993,7 +993,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>23.64</v>
+        <v>23.77</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1004,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>397.35</v>
+        <v>388.25</v>
       </c>
       <c r="D3">
-        <v>-0.01</v>
+        <v>-2.29</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1016,46 +1016,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-10.77</v>
+        <v>-12.81</v>
       </c>
       <c r="H3">
-        <v>76.59999999999999</v>
+        <v>72.56</v>
       </c>
       <c r="I3">
-        <v>-0.23</v>
+        <v>-3.08</v>
       </c>
       <c r="J3">
-        <v>3.76</v>
+        <v>0.14</v>
       </c>
       <c r="K3">
-        <v>8.140000000000001</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="L3">
-        <v>0.03</v>
+        <v>2.78</v>
       </c>
       <c r="M3">
-        <v>11.11</v>
+        <v>8.94</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>59</v>
+        <v>53</v>
       </c>
       <c r="P3">
-        <v>397.89</v>
+        <v>395.42</v>
       </c>
       <c r="Q3">
-        <v>410.25</v>
+        <v>409.53</v>
       </c>
       <c r="R3">
-        <v>407.22</v>
+        <v>406.48</v>
       </c>
       <c r="S3">
-        <v>326.03</v>
+        <v>326.32</v>
       </c>
       <c r="T3">
-        <v>21.87</v>
+        <v>18.98</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1070,43 +1070,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>45.18</v>
+        <v>40.11</v>
       </c>
       <c r="Z3">
-        <v>-1.94</v>
+        <v>-2.93</v>
       </c>
       <c r="AA3">
-        <v>0.51</v>
+        <v>-0.18</v>
       </c>
       <c r="AB3">
-        <v>-2.45</v>
+        <v>-2.75</v>
       </c>
       <c r="AC3">
         <v>3.4</v>
       </c>
       <c r="AD3">
-        <v>3.8</v>
+        <v>3.33</v>
       </c>
       <c r="AE3">
-        <v>12.88</v>
+        <v>12.96</v>
       </c>
       <c r="AF3">
-        <v>-82.68000000000001</v>
+        <v>-27.29</v>
       </c>
       <c r="AG3">
-        <v>438.46</v>
+        <v>439.25</v>
       </c>
       <c r="AH3">
-        <v>382.04</v>
+        <v>379.82</v>
       </c>
       <c r="AI3">
-        <v>392.36</v>
+        <v>430.89</v>
       </c>
       <c r="AJ3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>22.89</v>
+        <v>25.49</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1120,55 +1120,55 @@
         <v>402.55</v>
       </c>
       <c r="D4">
-        <v>0.15</v>
+        <v>0</v>
       </c>
       <c r="E4">
-        <v>535.55</v>
+        <v>534</v>
       </c>
       <c r="F4">
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-24.83</v>
+        <v>-24.62</v>
       </c>
       <c r="H4">
         <v>16.78</v>
       </c>
       <c r="I4">
-        <v>-0.97</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="J4">
-        <v>-5.03</v>
+        <v>-5.4</v>
       </c>
       <c r="K4">
-        <v>-2.51</v>
+        <v>-0.95</v>
       </c>
       <c r="L4">
-        <v>-26.42</v>
+        <v>-24.83</v>
       </c>
       <c r="M4">
-        <v>-20.36</v>
+        <v>-19.57</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>402.02</v>
+        <v>402.08</v>
       </c>
       <c r="Q4">
-        <v>411.92</v>
+        <v>410.9</v>
       </c>
       <c r="R4">
-        <v>418.71</v>
+        <v>418.28</v>
       </c>
       <c r="S4">
-        <v>418.96</v>
+        <v>418.48</v>
       </c>
       <c r="T4">
-        <v>-3.92</v>
+        <v>-3.81</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1186,31 +1186,31 @@
         <v>39.06</v>
       </c>
       <c r="Z4">
-        <v>-5.41</v>
+        <v>-5.32</v>
       </c>
       <c r="AA4">
-        <v>-4.5</v>
+        <v>-4.67</v>
       </c>
       <c r="AB4">
-        <v>-0.91</v>
+        <v>-0.65</v>
       </c>
       <c r="AC4">
-        <v>8.6</v>
+        <v>15.51</v>
       </c>
       <c r="AD4">
-        <v>4.49</v>
+        <v>8.92</v>
       </c>
       <c r="AE4">
-        <v>10.96</v>
+        <v>10.77</v>
       </c>
       <c r="AF4">
-        <v>-50.6</v>
+        <v>-42.35</v>
       </c>
       <c r="AG4">
-        <v>431.06</v>
+        <v>429.74</v>
       </c>
       <c r="AH4">
-        <v>392.78</v>
+        <v>392.06</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1219,7 +1219,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>13.29</v>
+        <v>12.71</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1230,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1002.9</v>
+        <v>994</v>
       </c>
       <c r="D5">
-        <v>-0.11</v>
+        <v>-0.89</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1242,46 +1242,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-6.21</v>
+        <v>-7.04</v>
       </c>
       <c r="H5">
-        <v>40.71</v>
+        <v>39.46</v>
       </c>
       <c r="I5">
-        <v>-0.51</v>
+        <v>-1.15</v>
       </c>
       <c r="J5">
-        <v>-0.93</v>
+        <v>-1.73</v>
       </c>
       <c r="K5">
-        <v>9.68</v>
+        <v>10.3</v>
       </c>
       <c r="L5">
-        <v>31.94</v>
+        <v>28.95</v>
       </c>
       <c r="M5">
-        <v>0.86</v>
+        <v>0.38</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1009.18</v>
+        <v>1006.86</v>
       </c>
       <c r="Q5">
-        <v>1016.51</v>
+        <v>1015.59</v>
       </c>
       <c r="R5">
-        <v>997.9299999999999</v>
+        <v>999.03</v>
       </c>
       <c r="S5">
-        <v>910.36</v>
+        <v>911.2</v>
       </c>
       <c r="T5">
-        <v>10.16</v>
+        <v>9.09</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1296,43 +1296,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>46.84</v>
+        <v>43.22</v>
       </c>
       <c r="Z5">
-        <v>1.86</v>
+        <v>0.29</v>
       </c>
       <c r="AA5">
-        <v>5.27</v>
+        <v>4.27</v>
       </c>
       <c r="AB5">
-        <v>-3.41</v>
+        <v>-3.98</v>
       </c>
       <c r="AC5">
-        <v>13.42</v>
+        <v>0</v>
       </c>
       <c r="AD5">
-        <v>25.97</v>
+        <v>15.22</v>
       </c>
       <c r="AE5">
-        <v>18.36</v>
+        <v>18.16</v>
       </c>
       <c r="AF5">
-        <v>6.67</v>
+        <v>-7.63</v>
       </c>
       <c r="AG5">
-        <v>1031.84</v>
+        <v>1033.88</v>
       </c>
       <c r="AH5">
-        <v>1001.17</v>
+        <v>997.29</v>
       </c>
       <c r="AI5">
-        <v>1054.97</v>
+        <v>1048.43</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>16.09</v>
+        <v>18.75</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1343,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="D6">
-        <v>-1.66</v>
+        <v>2.03</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1355,37 +1355,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-18.23</v>
+        <v>-16.57</v>
       </c>
       <c r="H6">
-        <v>60.87</v>
+        <v>64.13</v>
       </c>
       <c r="I6">
-        <v>30.97</v>
+        <v>11.44</v>
       </c>
       <c r="J6">
-        <v>25.42</v>
+        <v>28.51</v>
       </c>
       <c r="K6">
-        <v>12.98</v>
+        <v>16.15</v>
       </c>
       <c r="L6">
-        <v>-13.2</v>
+        <v>-10.65</v>
       </c>
       <c r="M6">
-        <v>1.71</v>
+        <v>2.65</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>68</v>
       </c>
       <c r="P6">
-        <v>2.96</v>
+        <v>3.02</v>
       </c>
       <c r="Q6">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="R6">
         <v>2.44</v>
@@ -1394,7 +1394,7 @@
         <v>2.69</v>
       </c>
       <c r="T6">
-        <v>9.9</v>
+        <v>12.18</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1409,34 +1409,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>73.75</v>
+        <v>75.39</v>
       </c>
       <c r="Z6">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="AA6">
-        <v>0.06</v>
+        <v>0.08</v>
       </c>
       <c r="AB6">
-        <v>0.09</v>
+        <v>0.08</v>
       </c>
       <c r="AC6">
-        <v>89.26000000000001</v>
+        <v>83.64</v>
       </c>
       <c r="AD6">
-        <v>95.08</v>
+        <v>89.63</v>
       </c>
       <c r="AE6">
         <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-24.54</v>
+        <v>-38.45</v>
       </c>
       <c r="AG6">
-        <v>3.07</v>
+        <v>3.14</v>
       </c>
       <c r="AH6">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1445,7 +1445,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>51.15</v>
+        <v>54.34</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1586,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1643,13 +1643,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>13.68</v>
+        <v>12.31</v>
       </c>
       <c r="D7" s="5">
-        <v>12.31</v>
+        <v>11.18</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.37</v>
+        <v>-1.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1660,13 +1660,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>2.38</v>
+        <v>3.76</v>
       </c>
       <c r="D8" s="5">
-        <v>3.76</v>
-      </c>
-      <c r="E8" s="7">
-        <v>1.38</v>
+        <v>0.14</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-3.62</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1677,13 +1677,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-4.52</v>
+        <v>-5.03</v>
       </c>
       <c r="D9" s="5">
-        <v>-5.03</v>
+        <v>-5.4</v>
       </c>
       <c r="E9" s="6">
-        <v>-0.51</v>
+        <v>-0.37</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1694,13 +1694,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>1.21</v>
+        <v>-0.93</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.93</v>
+        <v>-1.73</v>
       </c>
       <c r="E10" s="6">
-        <v>-2.14</v>
+        <v>-0.8</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1711,13 +1711,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>32.6</v>
+        <v>25.42</v>
       </c>
       <c r="D11" s="5">
-        <v>25.42</v>
-      </c>
-      <c r="E11" s="6">
-        <v>-7.18</v>
+        <v>28.51</v>
+      </c>
+      <c r="E11" s="7">
+        <v>3.09</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1728,13 +1728,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>3.44</v>
+        <v>2.07</v>
       </c>
       <c r="D12" s="5">
-        <v>2.07</v>
+        <v>1.6</v>
       </c>
       <c r="E12" s="6">
-        <v>-1.37</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1745,13 +1745,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>-0.29</v>
+        <v>-0.23</v>
       </c>
       <c r="D13" s="5">
-        <v>-0.23</v>
-      </c>
-      <c r="E13" s="7">
-        <v>0.06</v>
+        <v>-3.08</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.85</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1762,13 +1762,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-1.48</v>
+        <v>-0.97</v>
       </c>
       <c r="D14" s="5">
-        <v>-0.97</v>
+        <v>0.07000000000000001</v>
       </c>
       <c r="E14" s="7">
-        <v>0.51</v>
+        <v>1.04</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1779,13 +1779,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>-1.25</v>
+        <v>-0.51</v>
       </c>
       <c r="D15" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="E15" s="7">
-        <v>0.74</v>
+        <v>-1.15</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-0.64</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1796,13 +1796,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>33.78</v>
+        <v>30.97</v>
       </c>
       <c r="D16" s="5">
-        <v>30.97</v>
+        <v>11.44</v>
       </c>
       <c r="E16" s="6">
-        <v>-2.81</v>
+        <v>-19.53</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1813,13 +1813,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>39.95</v>
+        <v>38.45</v>
       </c>
       <c r="D17" s="5">
-        <v>38.45</v>
+        <v>37.38</v>
       </c>
       <c r="E17" s="6">
-        <v>-1.5</v>
+        <v>-1.07</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1830,13 +1830,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>2.26</v>
+        <v>0.03</v>
       </c>
       <c r="D18" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-2.23</v>
+        <v>2.78</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2.75</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1847,13 +1847,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-26.26</v>
+        <v>-26.42</v>
       </c>
       <c r="D19" s="5">
-        <v>-26.42</v>
-      </c>
-      <c r="E19" s="6">
-        <v>-0.16</v>
+        <v>-24.83</v>
+      </c>
+      <c r="E19" s="7">
+        <v>1.59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1864,13 +1864,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>30.82</v>
+        <v>31.94</v>
       </c>
       <c r="D20" s="5">
-        <v>31.94</v>
-      </c>
-      <c r="E20" s="7">
-        <v>1.12</v>
+        <v>28.95</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-2.99</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1881,13 +1881,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-12.75</v>
+        <v>-13.2</v>
       </c>
       <c r="D21" s="5">
-        <v>-13.2</v>
-      </c>
-      <c r="E21" s="6">
-        <v>-0.45</v>
+        <v>-10.65</v>
+      </c>
+      <c r="E21" s="7">
+        <v>2.55</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1898,13 +1898,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>11.29</v>
+        <v>16.08</v>
       </c>
       <c r="D22" s="5">
-        <v>16.08</v>
+        <v>19.35</v>
       </c>
       <c r="E22" s="7">
-        <v>4.79</v>
+        <v>3.27</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1915,13 +1915,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>4.14</v>
+        <v>8.140000000000001</v>
       </c>
       <c r="D23" s="5">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="E23" s="7">
-        <v>4</v>
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-8.699999999999999</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1932,13 +1932,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-2.93</v>
+        <v>-2.51</v>
       </c>
       <c r="D24" s="5">
-        <v>-2.51</v>
+        <v>-0.95</v>
       </c>
       <c r="E24" s="7">
-        <v>0.42</v>
+        <v>1.56</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1949,13 +1949,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>7.69</v>
+        <v>9.68</v>
       </c>
       <c r="D25" s="5">
-        <v>9.68</v>
+        <v>10.3</v>
       </c>
       <c r="E25" s="7">
-        <v>1.99</v>
+        <v>0.62</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1966,13 +1966,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>14.02</v>
+        <v>12.98</v>
       </c>
       <c r="D26" s="5">
-        <v>12.98</v>
-      </c>
-      <c r="E26" s="6">
-        <v>-1.04</v>
+        <v>16.15</v>
+      </c>
+      <c r="E26" s="7">
+        <v>3.17</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1983,10 +1983,10 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-14.07</v>
+        <v>-14.86</v>
       </c>
       <c r="D27" s="5">
-        <v>-14.86</v>
+        <v>-15.65</v>
       </c>
       <c r="E27" s="6">
         <v>-0.79</v>
@@ -2000,13 +2000,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-10.76</v>
+        <v>-10.77</v>
       </c>
       <c r="D28" s="5">
-        <v>-10.77</v>
+        <v>-12.81</v>
       </c>
       <c r="E28" s="6">
-        <v>-0.01</v>
+        <v>-2.04</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2017,13 +2017,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-26.53</v>
+        <v>-24.83</v>
       </c>
       <c r="D29" s="5">
-        <v>-24.83</v>
+        <v>-24.62</v>
       </c>
       <c r="E29" s="7">
-        <v>1.7</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2034,13 +2034,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-6.11</v>
+        <v>-6.21</v>
       </c>
       <c r="D30" s="5">
-        <v>-6.21</v>
+        <v>-7.04</v>
       </c>
       <c r="E30" s="6">
-        <v>-0.1</v>
+        <v>-0.83</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2051,13 +2051,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-16.85</v>
+        <v>-18.23</v>
       </c>
       <c r="D31" s="5">
-        <v>-18.23</v>
-      </c>
-      <c r="E31" s="6">
-        <v>-1.38</v>
+        <v>-16.57</v>
+      </c>
+      <c r="E31" s="7">
+        <v>1.66</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2068,13 +2068,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>179.05</v>
+        <v>177.4</v>
       </c>
       <c r="D32" s="5">
-        <v>177.4</v>
+        <v>175.77</v>
       </c>
       <c r="E32" s="6">
-        <v>-1.65</v>
+        <v>-1.63</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2085,234 +2085,200 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>397.4</v>
+        <v>397.35</v>
       </c>
       <c r="D33" s="5">
-        <v>397.35</v>
+        <v>388.25</v>
       </c>
       <c r="E33" s="6">
-        <v>-0.05</v>
+        <v>-9.1</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="3" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>401.95</v>
+        <v>1002.9</v>
       </c>
       <c r="D34" s="5">
-        <v>402.55</v>
-      </c>
-      <c r="E34" s="7">
-        <v>0.6</v>
+        <v>994</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-8.9</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>1004</v>
+        <v>2.96</v>
       </c>
       <c r="D35" s="5">
-        <v>1002.9</v>
-      </c>
-      <c r="E35" s="6">
-        <v>-1.1</v>
+        <v>3.02</v>
+      </c>
+      <c r="E35" s="7">
+        <v>0.06</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C36" s="5">
-        <v>3.01</v>
+        <v>61.25</v>
       </c>
       <c r="D36" s="5">
-        <v>2.96</v>
+        <v>58.03</v>
       </c>
       <c r="E36" s="6">
-        <v>-0.05</v>
+        <v>-3.22</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C37" s="5">
-        <v>64.61</v>
+        <v>45.18</v>
       </c>
       <c r="D37" s="5">
-        <v>61.25</v>
+        <v>40.11</v>
       </c>
       <c r="E37" s="6">
-        <v>-3.36</v>
+        <v>-5.07</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C38" s="5">
-        <v>45.21</v>
+        <v>46.84</v>
       </c>
       <c r="D38" s="5">
-        <v>45.18</v>
+        <v>43.22</v>
       </c>
       <c r="E38" s="6">
-        <v>-0.03</v>
+        <v>-3.62</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>38.27</v>
+        <v>73.75</v>
       </c>
       <c r="D39" s="5">
-        <v>39.06</v>
+        <v>75.39</v>
       </c>
       <c r="E39" s="7">
-        <v>0.79</v>
+        <v>1.64</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C40" s="5">
-        <v>47.29</v>
+        <v>-28.13</v>
       </c>
       <c r="D40" s="5">
-        <v>46.84</v>
+        <v>-40.02</v>
       </c>
       <c r="E40" s="6">
-        <v>-0.45</v>
+        <v>-11.89</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C41" s="5">
-        <v>77.77</v>
+        <v>-82.68000000000001</v>
       </c>
       <c r="D41" s="5">
-        <v>73.75</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-4.02</v>
+        <v>-27.29</v>
+      </c>
+      <c r="E41" s="7">
+        <v>55.39</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C42" s="5">
-        <v>-8.44</v>
+        <v>-50.6</v>
       </c>
       <c r="D42" s="5">
-        <v>-28.13</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-19.69</v>
+        <v>-42.35</v>
+      </c>
+      <c r="E42" s="7">
+        <v>8.25</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C43" s="5">
-        <v>-73.44</v>
+        <v>6.67</v>
       </c>
       <c r="D43" s="5">
-        <v>-82.68000000000001</v>
+        <v>-7.63</v>
       </c>
       <c r="E43" s="6">
-        <v>-9.24</v>
+        <v>-14.3</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>-62.1</v>
+        <v>-24.54</v>
       </c>
       <c r="D44" s="5">
-        <v>-50.6</v>
-      </c>
-      <c r="E44" s="7">
-        <v>11.5</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-3.58</v>
-      </c>
-      <c r="D45" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="E45" s="7">
-        <v>10.25</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>8.74</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-24.54</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-33.28</v>
+        <v>-38.45</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-13.91</v>
       </c>
     </row>
   </sheetData>
@@ -2377,13 +2343,13 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>53.2</v>
+        <v>51.2</v>
       </c>
       <c r="E2" s="10">
         <v>80</v>
       </c>
       <c r="F2" s="10">
-        <v>7.1</v>
+        <v>6.5</v>
       </c>
       <c r="G2" s="10">
         <v>8.9</v>
@@ -2511,19 +2477,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.2684</v>
+        <v>0.2633</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1111</v>
+        <v>0.08939999999999999</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0171</v>
+        <v>0.0265</v>
       </c>
       <c r="D2" s="13">
-        <v>0.0086</v>
+        <v>0.0038</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2036</v>
+        <v>-0.1957</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="203" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,49 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>43.2 → 53.1</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>43.2</t>
+  </si>
+  <si>
+    <t>53.1</t>
+  </si>
+  <si>
+    <t>RSI Overbought Exit</t>
+  </si>
+  <si>
+    <t>75.4 → 62.1</t>
+  </si>
+  <si>
+    <t>🔵 COOLING</t>
+  </si>
+  <si>
+    <t>75.4</t>
+  </si>
+  <si>
+    <t>62.1</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -218,7 +260,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -252,20 +294,27 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -292,13 +341,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,21 +423,23 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -391,7 +448,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -750,9 +807,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -891,10 +947,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>175.77</v>
+        <v>175.64</v>
       </c>
       <c r="D2">
-        <v>-0.92</v>
+        <v>-0.07000000000000001</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -903,46 +959,46 @@
         <v>124.01</v>
       </c>
       <c r="G2">
-        <v>-15.65</v>
+        <v>-15.71</v>
       </c>
       <c r="H2">
-        <v>41.74</v>
+        <v>41.63</v>
       </c>
       <c r="I2">
-        <v>1.6</v>
+        <v>1.36</v>
       </c>
       <c r="J2">
-        <v>11.18</v>
+        <v>5.69</v>
       </c>
       <c r="K2">
-        <v>19.35</v>
+        <v>19.85</v>
       </c>
       <c r="L2">
-        <v>37.38</v>
+        <v>36.9</v>
       </c>
       <c r="M2">
-        <v>26.33</v>
+        <v>25.94</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="P2">
-        <v>176.04</v>
+        <v>176.51</v>
       </c>
       <c r="Q2">
-        <v>175.28</v>
+        <v>175.33</v>
       </c>
       <c r="R2">
-        <v>164.62</v>
+        <v>165</v>
       </c>
       <c r="S2">
-        <v>168.55</v>
+        <v>168.73</v>
       </c>
       <c r="T2">
-        <v>4.29</v>
+        <v>4.1</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -957,34 +1013,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>58.03</v>
+        <v>57.77</v>
       </c>
       <c r="Z2">
-        <v>3.55</v>
+        <v>3.34</v>
       </c>
       <c r="AA2">
-        <v>3.94</v>
+        <v>3.82</v>
       </c>
       <c r="AB2">
-        <v>-0.4</v>
+        <v>-0.48</v>
       </c>
       <c r="AC2">
-        <v>34.7</v>
+        <v>20.69</v>
       </c>
       <c r="AD2">
-        <v>31.31</v>
+        <v>30.44</v>
       </c>
       <c r="AE2">
-        <v>4.23</v>
+        <v>4.13</v>
       </c>
       <c r="AF2">
-        <v>-40.02</v>
+        <v>-26.69</v>
       </c>
       <c r="AG2">
-        <v>179.42</v>
+        <v>179.46</v>
       </c>
       <c r="AH2">
-        <v>171.14</v>
+        <v>171.2</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -993,7 +1049,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>23.77</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1004,10 +1060,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>388.25</v>
+        <v>392.5</v>
       </c>
       <c r="D3">
-        <v>-2.29</v>
+        <v>1.09</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1016,46 +1072,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-12.81</v>
+        <v>-11.86</v>
       </c>
       <c r="H3">
-        <v>72.56</v>
+        <v>74.44</v>
       </c>
       <c r="I3">
-        <v>-3.08</v>
+        <v>-1.48</v>
       </c>
       <c r="J3">
-        <v>0.14</v>
+        <v>-2.5</v>
       </c>
       <c r="K3">
-        <v>-0.5600000000000001</v>
+        <v>-2.07</v>
       </c>
       <c r="L3">
-        <v>2.78</v>
+        <v>7.39</v>
       </c>
       <c r="M3">
-        <v>8.94</v>
+        <v>9.41</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="P3">
-        <v>395.42</v>
+        <v>394.24</v>
       </c>
       <c r="Q3">
-        <v>409.53</v>
+        <v>408.35</v>
       </c>
       <c r="R3">
-        <v>406.48</v>
+        <v>405.58</v>
       </c>
       <c r="S3">
-        <v>326.32</v>
+        <v>326.58</v>
       </c>
       <c r="T3">
-        <v>18.98</v>
+        <v>20.18</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1070,43 +1126,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>40.11</v>
+        <v>43.31</v>
       </c>
       <c r="Z3">
-        <v>-2.93</v>
+        <v>-3.33</v>
       </c>
       <c r="AA3">
-        <v>-0.18</v>
+        <v>-0.8100000000000001</v>
       </c>
       <c r="AB3">
-        <v>-2.75</v>
+        <v>-2.52</v>
       </c>
       <c r="AC3">
-        <v>3.4</v>
+        <v>6.4</v>
       </c>
       <c r="AD3">
-        <v>3.33</v>
+        <v>4.4</v>
       </c>
       <c r="AE3">
-        <v>12.96</v>
+        <v>12.81</v>
       </c>
       <c r="AF3">
-        <v>-27.29</v>
+        <v>-79.11</v>
       </c>
       <c r="AG3">
-        <v>439.25</v>
+        <v>438.83</v>
       </c>
       <c r="AH3">
-        <v>379.82</v>
+        <v>377.87</v>
       </c>
       <c r="AI3">
-        <v>430.89</v>
+        <v>428.96</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>25.49</v>
+        <v>27.75</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1117,10 +1173,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>402.55</v>
+        <v>400.55</v>
       </c>
       <c r="D4">
-        <v>0</v>
+        <v>-0.5</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1129,25 +1185,25 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-24.62</v>
+        <v>-24.99</v>
       </c>
       <c r="H4">
-        <v>16.78</v>
+        <v>16.2</v>
       </c>
       <c r="I4">
-        <v>0.07000000000000001</v>
+        <v>-0.37</v>
       </c>
       <c r="J4">
-        <v>-5.4</v>
+        <v>-5.28</v>
       </c>
       <c r="K4">
-        <v>-0.95</v>
+        <v>-0.61</v>
       </c>
       <c r="L4">
-        <v>-24.83</v>
+        <v>-23.37</v>
       </c>
       <c r="M4">
-        <v>-19.57</v>
+        <v>-20.18</v>
       </c>
       <c r="N4">
         <v>21</v>
@@ -1156,19 +1212,19 @@
         <v>28</v>
       </c>
       <c r="P4">
-        <v>402.08</v>
+        <v>401.78</v>
       </c>
       <c r="Q4">
-        <v>410.9</v>
+        <v>409.4</v>
       </c>
       <c r="R4">
-        <v>418.28</v>
+        <v>417.79</v>
       </c>
       <c r="S4">
-        <v>418.48</v>
+        <v>417.99</v>
       </c>
       <c r="T4">
-        <v>-3.81</v>
+        <v>-4.17</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1183,34 +1239,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>39.06</v>
+        <v>37.21</v>
       </c>
       <c r="Z4">
-        <v>-5.32</v>
+        <v>-5.34</v>
       </c>
       <c r="AA4">
-        <v>-4.67</v>
+        <v>-4.8</v>
       </c>
       <c r="AB4">
-        <v>-0.65</v>
+        <v>-0.54</v>
       </c>
       <c r="AC4">
-        <v>15.51</v>
+        <v>13.83</v>
       </c>
       <c r="AD4">
-        <v>8.92</v>
+        <v>12.65</v>
       </c>
       <c r="AE4">
-        <v>10.77</v>
+        <v>10.85</v>
       </c>
       <c r="AF4">
-        <v>-42.35</v>
+        <v>-3.68</v>
       </c>
       <c r="AG4">
-        <v>429.74</v>
+        <v>426.34</v>
       </c>
       <c r="AH4">
-        <v>392.06</v>
+        <v>392.46</v>
       </c>
       <c r="AI4">
         <v>397.37</v>
@@ -1219,7 +1275,7 @@
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>12.71</v>
+        <v>11.55</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1230,10 +1286,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>994</v>
+        <v>1016.6</v>
       </c>
       <c r="D5">
-        <v>-0.89</v>
+        <v>2.27</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1242,46 +1298,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-7.04</v>
+        <v>-4.93</v>
       </c>
       <c r="H5">
-        <v>39.46</v>
+        <v>42.63</v>
       </c>
       <c r="I5">
-        <v>-1.15</v>
+        <v>-0.18</v>
       </c>
       <c r="J5">
-        <v>-1.73</v>
+        <v>0.41</v>
       </c>
       <c r="K5">
-        <v>10.3</v>
+        <v>11.41</v>
       </c>
       <c r="L5">
-        <v>28.95</v>
+        <v>34.4</v>
       </c>
       <c r="M5">
-        <v>0.38</v>
+        <v>1.09</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>78</v>
       </c>
       <c r="P5">
-        <v>1006.86</v>
+        <v>1006.5</v>
       </c>
       <c r="Q5">
-        <v>1015.59</v>
+        <v>1014.97</v>
       </c>
       <c r="R5">
-        <v>999.03</v>
+        <v>1000.41</v>
       </c>
       <c r="S5">
-        <v>911.2</v>
+        <v>911.96</v>
       </c>
       <c r="T5">
-        <v>9.09</v>
+        <v>11.47</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1296,34 +1352,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>43.22</v>
+        <v>53.12</v>
       </c>
       <c r="Z5">
-        <v>0.29</v>
+        <v>0.86</v>
       </c>
       <c r="AA5">
-        <v>4.27</v>
+        <v>3.59</v>
       </c>
       <c r="AB5">
-        <v>-3.98</v>
+        <v>-2.73</v>
       </c>
       <c r="AC5">
-        <v>0</v>
+        <v>26.07</v>
       </c>
       <c r="AD5">
-        <v>15.22</v>
+        <v>13.16</v>
       </c>
       <c r="AE5">
-        <v>18.16</v>
+        <v>19.45</v>
       </c>
       <c r="AF5">
-        <v>-7.63</v>
+        <v>34.06</v>
       </c>
       <c r="AG5">
-        <v>1033.88</v>
+        <v>1032.18</v>
       </c>
       <c r="AH5">
-        <v>997.29</v>
+        <v>997.76</v>
       </c>
       <c r="AI5">
         <v>1048.43</v>
@@ -1332,7 +1388,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>18.75</v>
+        <v>16.86</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1343,10 +1399,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>3.02</v>
+        <v>2.83</v>
       </c>
       <c r="D6">
-        <v>2.03</v>
+        <v>-6.29</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1355,46 +1411,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-16.57</v>
+        <v>-21.82</v>
       </c>
       <c r="H6">
-        <v>64.13</v>
+        <v>53.8</v>
       </c>
       <c r="I6">
-        <v>11.44</v>
+        <v>-6.91</v>
       </c>
       <c r="J6">
-        <v>28.51</v>
+        <v>19.92</v>
       </c>
       <c r="K6">
-        <v>16.15</v>
+        <v>13.65</v>
       </c>
       <c r="L6">
-        <v>-10.65</v>
+        <v>-15.77</v>
       </c>
       <c r="M6">
-        <v>2.65</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>68</v>
+        <v>55</v>
       </c>
       <c r="P6">
-        <v>3.02</v>
+        <v>2.98</v>
       </c>
       <c r="Q6">
-        <v>2.52</v>
+        <v>2.54</v>
       </c>
       <c r="R6">
-        <v>2.44</v>
+        <v>2.45</v>
       </c>
       <c r="S6">
         <v>2.69</v>
       </c>
       <c r="T6">
-        <v>12.18</v>
+        <v>5.2</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1409,34 +1465,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>75.39</v>
+        <v>62.12</v>
       </c>
       <c r="Z6">
         <v>0.16</v>
       </c>
       <c r="AA6">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="AB6">
-        <v>0.08</v>
+        <v>0.06</v>
       </c>
       <c r="AC6">
-        <v>83.64</v>
+        <v>73.06</v>
       </c>
       <c r="AD6">
-        <v>89.63</v>
+        <v>81.98999999999999</v>
       </c>
       <c r="AE6">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-38.45</v>
+        <v>-16.35</v>
       </c>
       <c r="AG6">
-        <v>3.14</v>
+        <v>3.18</v>
       </c>
       <c r="AH6">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1445,7 +1501,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>54.34</v>
+        <v>51.42</v>
       </c>
     </row>
   </sheetData>
@@ -1586,7 +1642,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F44"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1606,685 +1662,774 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+      <c r="C2" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
-      </c>
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>12.31</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C8" s="7">
         <v>11.18</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.13</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="D8" s="7">
+        <v>5.69</v>
+      </c>
+      <c r="E8" s="8">
+        <v>-5.49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>3.76</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C9" s="7">
         <v>0.14</v>
       </c>
-      <c r="E8" s="6">
-        <v>-3.62</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="D9" s="7">
+        <v>-2.5</v>
+      </c>
+      <c r="E9" s="8">
+        <v>-2.64</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-5.03</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C10" s="7">
         <v>-5.4</v>
       </c>
-      <c r="E9" s="6">
+      <c r="D10" s="7">
+        <v>-5.28</v>
+      </c>
+      <c r="E10" s="9">
+        <v>0.12</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-1.73</v>
+      </c>
+      <c r="D11" s="7">
+        <v>0.41</v>
+      </c>
+      <c r="E11" s="9">
+        <v>2.14</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>28.51</v>
+      </c>
+      <c r="D12" s="7">
+        <v>19.92</v>
+      </c>
+      <c r="E12" s="8">
+        <v>-8.59</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7">
+        <v>1.6</v>
+      </c>
+      <c r="D13" s="7">
+        <v>1.36</v>
+      </c>
+      <c r="E13" s="8">
+        <v>-0.24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7">
+        <v>-3.08</v>
+      </c>
+      <c r="D14" s="7">
+        <v>-1.48</v>
+      </c>
+      <c r="E14" s="9">
+        <v>1.6</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+      <c r="D15" s="7">
         <v>-0.37</v>
       </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="E15" s="8">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="5">
-        <v>-0.93</v>
-      </c>
-      <c r="D10" s="5">
-        <v>-1.73</v>
-      </c>
-      <c r="E10" s="6">
-        <v>-0.8</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>-1.15</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-0.18</v>
+      </c>
+      <c r="E16" s="9">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="5">
-        <v>25.42</v>
-      </c>
-      <c r="D11" s="5">
-        <v>28.51</v>
-      </c>
-      <c r="E11" s="7">
-        <v>3.09</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>11.44</v>
+      </c>
+      <c r="D17" s="7">
+        <v>-6.91</v>
+      </c>
+      <c r="E17" s="8">
+        <v>-18.35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="5">
-        <v>2.07</v>
-      </c>
-      <c r="D12" s="5">
-        <v>1.6</v>
-      </c>
-      <c r="E12" s="6">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="B18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="7">
+        <v>37.38</v>
+      </c>
+      <c r="D18" s="7">
+        <v>36.9</v>
+      </c>
+      <c r="E18" s="8">
+        <v>-0.48</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="5">
-        <v>-0.23</v>
-      </c>
-      <c r="D13" s="5">
-        <v>-3.08</v>
-      </c>
-      <c r="E13" s="6">
-        <v>-2.85</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="B19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7">
+        <v>2.78</v>
+      </c>
+      <c r="D19" s="7">
+        <v>7.39</v>
+      </c>
+      <c r="E19" s="9">
+        <v>4.61</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="5">
-        <v>-0.97</v>
-      </c>
-      <c r="D14" s="5">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="E14" s="7">
-        <v>1.04</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-24.83</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-23.37</v>
+      </c>
+      <c r="E20" s="9">
+        <v>1.46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="5">
-        <v>-0.51</v>
-      </c>
-      <c r="D15" s="5">
-        <v>-1.15</v>
-      </c>
-      <c r="E15" s="6">
-        <v>-0.64</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>28.95</v>
+      </c>
+      <c r="D21" s="7">
+        <v>34.4</v>
+      </c>
+      <c r="E21" s="9">
+        <v>5.45</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="5">
-        <v>30.97</v>
-      </c>
-      <c r="D16" s="5">
-        <v>11.44</v>
-      </c>
-      <c r="E16" s="6">
-        <v>-19.53</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-10.65</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-15.77</v>
+      </c>
+      <c r="E22" s="8">
+        <v>-5.12</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="5">
-        <v>38.45</v>
-      </c>
-      <c r="D17" s="5">
-        <v>37.38</v>
-      </c>
-      <c r="E17" s="6">
-        <v>-1.07</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="B23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="7">
+        <v>19.35</v>
+      </c>
+      <c r="D23" s="7">
+        <v>19.85</v>
+      </c>
+      <c r="E23" s="9">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="5">
-        <v>0.03</v>
-      </c>
-      <c r="D18" s="5">
-        <v>2.78</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2.75</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="B24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="D24" s="7">
+        <v>-2.07</v>
+      </c>
+      <c r="E24" s="8">
+        <v>-1.51</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="5">
-        <v>-26.42</v>
-      </c>
-      <c r="D19" s="5">
-        <v>-24.83</v>
-      </c>
-      <c r="E19" s="7">
-        <v>1.59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-0.95</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-0.61</v>
+      </c>
+      <c r="E25" s="9">
+        <v>0.34</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="5">
-        <v>31.94</v>
-      </c>
-      <c r="D20" s="5">
-        <v>28.95</v>
-      </c>
-      <c r="E20" s="6">
-        <v>-2.99</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>10.3</v>
+      </c>
+      <c r="D26" s="7">
+        <v>11.41</v>
+      </c>
+      <c r="E26" s="9">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="5">
-        <v>-13.2</v>
-      </c>
-      <c r="D21" s="5">
-        <v>-10.65</v>
-      </c>
-      <c r="E21" s="7">
-        <v>2.55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>16.15</v>
+      </c>
+      <c r="D27" s="7">
+        <v>13.65</v>
+      </c>
+      <c r="E27" s="8">
+        <v>-2.5</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="5">
-        <v>16.08</v>
-      </c>
-      <c r="D22" s="5">
-        <v>19.35</v>
-      </c>
-      <c r="E22" s="7">
-        <v>3.27</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="B28" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-15.65</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-15.71</v>
+      </c>
+      <c r="E28" s="8">
+        <v>-0.06</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="5">
-        <v>8.140000000000001</v>
-      </c>
-      <c r="D23" s="5">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="E23" s="6">
-        <v>-8.699999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="B29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-12.81</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-11.86</v>
+      </c>
+      <c r="E29" s="9">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="5">
-        <v>-2.51</v>
-      </c>
-      <c r="D24" s="5">
-        <v>-0.95</v>
-      </c>
-      <c r="E24" s="7">
-        <v>1.56</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="B30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-24.62</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-24.99</v>
+      </c>
+      <c r="E30" s="8">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="5">
-        <v>9.68</v>
-      </c>
-      <c r="D25" s="5">
-        <v>10.3</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="B31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-7.04</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-4.93</v>
+      </c>
+      <c r="E31" s="9">
+        <v>2.11</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="5">
-        <v>12.98</v>
-      </c>
-      <c r="D26" s="5">
-        <v>16.15</v>
-      </c>
-      <c r="E26" s="7">
-        <v>3.17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-16.57</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-21.82</v>
+      </c>
+      <c r="E32" s="8">
+        <v>-5.25</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="5">
-        <v>-14.86</v>
-      </c>
-      <c r="D27" s="5">
-        <v>-15.65</v>
-      </c>
-      <c r="E27" s="6">
-        <v>-0.79</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="B33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="7">
+        <v>175.77</v>
+      </c>
+      <c r="D33" s="7">
+        <v>175.64</v>
+      </c>
+      <c r="E33" s="8">
+        <v>-0.13</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="5">
-        <v>-10.77</v>
-      </c>
-      <c r="D28" s="5">
-        <v>-12.81</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-2.04</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="B34" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="7">
+        <v>388.25</v>
+      </c>
+      <c r="D34" s="7">
+        <v>392.5</v>
+      </c>
+      <c r="E34" s="9">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="5">
-        <v>-24.83</v>
-      </c>
-      <c r="D29" s="5">
-        <v>-24.62</v>
-      </c>
-      <c r="E29" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="B35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="7">
+        <v>402.55</v>
+      </c>
+      <c r="D35" s="7">
+        <v>400.55</v>
+      </c>
+      <c r="E35" s="8">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="5">
-        <v>-6.21</v>
-      </c>
-      <c r="D30" s="5">
-        <v>-7.04</v>
-      </c>
-      <c r="E30" s="6">
-        <v>-0.83</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="B36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7">
+        <v>994</v>
+      </c>
+      <c r="D36" s="7">
+        <v>1016.6</v>
+      </c>
+      <c r="E36" s="9">
+        <v>22.6</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="5">
-        <v>-18.23</v>
-      </c>
-      <c r="D31" s="5">
-        <v>-16.57</v>
-      </c>
-      <c r="E31" s="7">
-        <v>1.66</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="B37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7">
+        <v>3.02</v>
+      </c>
+      <c r="D37" s="7">
+        <v>2.83</v>
+      </c>
+      <c r="E37" s="8">
+        <v>-0.19</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="5">
-        <v>177.4</v>
-      </c>
-      <c r="D32" s="5">
-        <v>175.77</v>
-      </c>
-      <c r="E32" s="6">
-        <v>-1.63</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="B38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="7">
+        <v>58.03</v>
+      </c>
+      <c r="D38" s="7">
+        <v>57.77</v>
+      </c>
+      <c r="E38" s="8">
+        <v>-0.26</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="5">
-        <v>397.35</v>
-      </c>
-      <c r="D33" s="5">
-        <v>388.25</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-9.1</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="B39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="7">
+        <v>40.11</v>
+      </c>
+      <c r="D39" s="7">
+        <v>43.31</v>
+      </c>
+      <c r="E39" s="9">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="7">
+        <v>39.06</v>
+      </c>
+      <c r="D40" s="7">
+        <v>37.21</v>
+      </c>
+      <c r="E40" s="8">
+        <v>-1.85</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B34" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="5">
-        <v>1002.9</v>
-      </c>
-      <c r="D34" s="5">
-        <v>994</v>
-      </c>
-      <c r="E34" s="6">
-        <v>-8.9</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="B41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="7">
+        <v>43.22</v>
+      </c>
+      <c r="D41" s="7">
+        <v>53.12</v>
+      </c>
+      <c r="E41" s="9">
+        <v>9.9</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B35" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="5">
-        <v>2.96</v>
-      </c>
-      <c r="D35" s="5">
-        <v>3.02</v>
-      </c>
-      <c r="E35" s="7">
-        <v>0.06</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="B42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="7">
+        <v>75.39</v>
+      </c>
+      <c r="D42" s="7">
+        <v>62.12</v>
+      </c>
+      <c r="E42" s="8">
+        <v>-13.27</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="5">
-        <v>61.25</v>
-      </c>
-      <c r="D36" s="5">
-        <v>58.03</v>
-      </c>
-      <c r="E36" s="6">
-        <v>-3.22</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="B43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-40.02</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-26.69</v>
+      </c>
+      <c r="E43" s="9">
+        <v>13.33</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="5">
-        <v>45.18</v>
-      </c>
-      <c r="D37" s="5">
-        <v>40.11</v>
-      </c>
-      <c r="E37" s="6">
-        <v>-5.07</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="B44" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-27.29</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-79.11</v>
+      </c>
+      <c r="E44" s="8">
+        <v>-51.82</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-42.35</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-3.68</v>
+      </c>
+      <c r="E45" s="9">
+        <v>38.67</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="5">
-        <v>46.84</v>
-      </c>
-      <c r="D38" s="5">
-        <v>43.22</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-3.62</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B46" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="7">
+        <v>-7.63</v>
+      </c>
+      <c r="D46" s="7">
+        <v>34.06</v>
+      </c>
+      <c r="E46" s="9">
+        <v>41.69</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>73.75</v>
-      </c>
-      <c r="D39" s="5">
-        <v>75.39</v>
-      </c>
-      <c r="E39" s="7">
-        <v>1.64</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B40" s="3" t="s">
+      <c r="B47" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="5">
-        <v>-28.13</v>
-      </c>
-      <c r="D40" s="5">
-        <v>-40.02</v>
-      </c>
-      <c r="E40" s="6">
-        <v>-11.89</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B41" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="5">
-        <v>-82.68000000000001</v>
-      </c>
-      <c r="D41" s="5">
-        <v>-27.29</v>
-      </c>
-      <c r="E41" s="7">
-        <v>55.39</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="5">
-        <v>-50.6</v>
-      </c>
-      <c r="D42" s="5">
-        <v>-42.35</v>
-      </c>
-      <c r="E42" s="7">
-        <v>8.25</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B43" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="5">
-        <v>6.67</v>
-      </c>
-      <c r="D43" s="5">
-        <v>-7.63</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-14.3</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="5">
-        <v>-24.54</v>
-      </c>
-      <c r="D44" s="5">
+      <c r="C47" s="7">
         <v>-38.45</v>
       </c>
-      <c r="E44" s="6">
-        <v>-13.91</v>
+      <c r="D47" s="7">
+        <v>-16.35</v>
+      </c>
+      <c r="E47" s="9">
+        <v>22.1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2304,60 +2449,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="10" t="s">
+        <v>68</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>69</v>
+      </c>
+      <c r="D1" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
+      <c r="B2" s="12">
         <v>65.92</v>
       </c>
-      <c r="C2" s="11">
+      <c r="C2" s="13">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>51.2</v>
-      </c>
-      <c r="E2" s="10">
+      <c r="D2" s="12">
+        <v>50.7</v>
+      </c>
+      <c r="E2" s="12">
         <v>80</v>
       </c>
-      <c r="F2" s="10">
-        <v>6.5</v>
-      </c>
-      <c r="G2" s="10">
-        <v>8.9</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="12">
+        <v>3.6</v>
+      </c>
+      <c r="G2" s="12">
+        <v>8.4</v>
+      </c>
+      <c r="H2" s="12">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -2459,37 +2604,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.2633</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.08939999999999999</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0265</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0038</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.1957</v>
+      <c r="A2" s="15">
+        <v>0.2594</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.0941</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.0117</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0109</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.2018</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,31 +184,25 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>43.2 → 53.1</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>43.2</t>
+    <t>57.8 → 48.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
+  </si>
+  <si>
+    <t>57.8</t>
+  </si>
+  <si>
+    <t>48.5</t>
+  </si>
+  <si>
+    <t>53.1 → 44.3</t>
   </si>
   <si>
     <t>53.1</t>
   </si>
   <si>
-    <t>RSI Overbought Exit</t>
-  </si>
-  <si>
-    <t>75.4 → 62.1</t>
-  </si>
-  <si>
-    <t>🔵 COOLING</t>
-  </si>
-  <si>
-    <t>75.4</t>
-  </si>
-  <si>
-    <t>62.1</t>
+    <t>44.3</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -260,7 +254,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,27 +288,20 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -341,19 +328,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -423,7 +404,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -431,15 +412,14 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -448,7 +428,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -807,8 +787,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="9.7109375" customWidth="1"/>
+    <col min="17" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -947,10 +928,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>175.64</v>
+        <v>170.53</v>
       </c>
       <c r="D2">
-        <v>-0.07000000000000001</v>
+        <v>-2.91</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -959,46 +940,46 @@
         <v>124.01</v>
       </c>
       <c r="G2">
-        <v>-15.71</v>
+        <v>-18.16</v>
       </c>
       <c r="H2">
-        <v>41.63</v>
+        <v>37.51</v>
       </c>
       <c r="I2">
-        <v>1.36</v>
+        <v>-2.38</v>
       </c>
       <c r="J2">
-        <v>5.69</v>
+        <v>-2.3</v>
       </c>
       <c r="K2">
-        <v>19.85</v>
+        <v>16.93</v>
       </c>
       <c r="L2">
-        <v>36.9</v>
+        <v>34.51</v>
       </c>
       <c r="M2">
-        <v>25.94</v>
+        <v>25.25</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="P2">
-        <v>176.51</v>
+        <v>175.68</v>
       </c>
       <c r="Q2">
-        <v>175.33</v>
+        <v>175.26</v>
       </c>
       <c r="R2">
-        <v>165</v>
+        <v>165.26</v>
       </c>
       <c r="S2">
-        <v>168.73</v>
+        <v>168.85</v>
       </c>
       <c r="T2">
-        <v>4.1</v>
+        <v>1</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -1013,34 +994,34 @@
         <v>2</v>
       </c>
       <c r="Y2">
-        <v>57.77</v>
+        <v>48.55</v>
       </c>
       <c r="Z2">
-        <v>3.34</v>
+        <v>2.73</v>
       </c>
       <c r="AA2">
-        <v>3.82</v>
+        <v>3.61</v>
       </c>
       <c r="AB2">
-        <v>-0.48</v>
+        <v>-0.87</v>
       </c>
       <c r="AC2">
-        <v>20.69</v>
+        <v>7.15</v>
       </c>
       <c r="AD2">
-        <v>30.44</v>
+        <v>20.85</v>
       </c>
       <c r="AE2">
-        <v>4.13</v>
+        <v>4.4</v>
       </c>
       <c r="AF2">
-        <v>-26.69</v>
+        <v>-6.17</v>
       </c>
       <c r="AG2">
-        <v>179.46</v>
+        <v>179.69</v>
       </c>
       <c r="AH2">
-        <v>171.2</v>
+        <v>170.82</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -1049,7 +1030,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>22.7</v>
+        <v>22.31</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1060,10 +1041,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>392.5</v>
+        <v>387.35</v>
       </c>
       <c r="D3">
-        <v>1.09</v>
+        <v>-1.31</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1072,19 +1053,19 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-11.86</v>
+        <v>-13.01</v>
       </c>
       <c r="H3">
-        <v>74.44</v>
+        <v>72.16</v>
       </c>
       <c r="I3">
-        <v>-1.48</v>
+        <v>-2.11</v>
       </c>
       <c r="J3">
-        <v>-2.5</v>
+        <v>-6.92</v>
       </c>
       <c r="K3">
-        <v>-2.07</v>
+        <v>-7.35</v>
       </c>
       <c r="L3">
         <v>7.39</v>
@@ -1096,22 +1077,22 @@
         <v>40</v>
       </c>
       <c r="O3">
-        <v>54</v>
+        <v>48</v>
       </c>
       <c r="P3">
-        <v>394.24</v>
+        <v>392.57</v>
       </c>
       <c r="Q3">
-        <v>408.35</v>
+        <v>407.13</v>
       </c>
       <c r="R3">
-        <v>405.58</v>
+        <v>404.42</v>
       </c>
       <c r="S3">
-        <v>326.58</v>
+        <v>326.85</v>
       </c>
       <c r="T3">
-        <v>20.18</v>
+        <v>18.51</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1126,43 +1107,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>43.31</v>
+        <v>40.49</v>
       </c>
       <c r="Z3">
-        <v>-3.33</v>
+        <v>-4.02</v>
       </c>
       <c r="AA3">
-        <v>-0.8100000000000001</v>
+        <v>-1.45</v>
       </c>
       <c r="AB3">
-        <v>-2.52</v>
+        <v>-2.56</v>
       </c>
       <c r="AC3">
-        <v>6.4</v>
+        <v>5.07</v>
       </c>
       <c r="AD3">
-        <v>4.4</v>
+        <v>4.96</v>
       </c>
       <c r="AE3">
-        <v>12.81</v>
+        <v>12.68</v>
       </c>
       <c r="AF3">
-        <v>-79.11</v>
+        <v>-85.47</v>
       </c>
       <c r="AG3">
-        <v>438.83</v>
+        <v>438.97</v>
       </c>
       <c r="AH3">
-        <v>377.87</v>
+        <v>375.3</v>
       </c>
       <c r="AI3">
-        <v>428.96</v>
+        <v>427.57</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>27.75</v>
+        <v>29.98</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1173,10 +1154,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>400.55</v>
+        <v>393.7</v>
       </c>
       <c r="D4">
-        <v>-0.5</v>
+        <v>-1.71</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1185,46 +1166,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-24.99</v>
+        <v>-26.27</v>
       </c>
       <c r="H4">
-        <v>16.2</v>
+        <v>14.22</v>
       </c>
       <c r="I4">
-        <v>-0.37</v>
+        <v>-1.89</v>
       </c>
       <c r="J4">
-        <v>-5.28</v>
+        <v>-8.56</v>
       </c>
       <c r="K4">
-        <v>-0.61</v>
+        <v>-2.78</v>
       </c>
       <c r="L4">
-        <v>-23.37</v>
+        <v>-24.83</v>
       </c>
       <c r="M4">
-        <v>-20.18</v>
+        <v>-20.4</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="P4">
-        <v>401.78</v>
+        <v>400.26</v>
       </c>
       <c r="Q4">
-        <v>409.4</v>
+        <v>408.01</v>
       </c>
       <c r="R4">
-        <v>417.79</v>
+        <v>417</v>
       </c>
       <c r="S4">
-        <v>417.99</v>
+        <v>417.46</v>
       </c>
       <c r="T4">
-        <v>-4.17</v>
+        <v>-5.69</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1239,43 +1220,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.21</v>
+        <v>31.69</v>
       </c>
       <c r="Z4">
-        <v>-5.34</v>
+        <v>-5.85</v>
       </c>
       <c r="AA4">
-        <v>-4.8</v>
+        <v>-5.01</v>
       </c>
       <c r="AB4">
-        <v>-0.54</v>
+        <v>-0.84</v>
       </c>
       <c r="AC4">
-        <v>13.83</v>
+        <v>6.92</v>
       </c>
       <c r="AD4">
-        <v>12.65</v>
+        <v>12.09</v>
       </c>
       <c r="AE4">
-        <v>10.85</v>
+        <v>10.87</v>
       </c>
       <c r="AF4">
-        <v>-3.68</v>
+        <v>9.039999999999999</v>
       </c>
       <c r="AG4">
-        <v>426.34</v>
+        <v>425.33</v>
       </c>
       <c r="AH4">
-        <v>392.46</v>
+        <v>390.69</v>
       </c>
       <c r="AI4">
-        <v>397.37</v>
+        <v>429.19</v>
       </c>
       <c r="AJ4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK4">
-        <v>11.55</v>
+        <v>13.22</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1286,10 +1267,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1016.6</v>
+        <v>992.6</v>
       </c>
       <c r="D5">
-        <v>2.27</v>
+        <v>-2.36</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1298,46 +1279,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-4.93</v>
+        <v>-7.17</v>
       </c>
       <c r="H5">
-        <v>42.63</v>
+        <v>39.26</v>
       </c>
       <c r="I5">
-        <v>-0.18</v>
+        <v>-2.21</v>
       </c>
       <c r="J5">
-        <v>0.41</v>
+        <v>-3.53</v>
       </c>
       <c r="K5">
-        <v>11.41</v>
+        <v>10.3</v>
       </c>
       <c r="L5">
-        <v>34.4</v>
+        <v>32.95</v>
       </c>
       <c r="M5">
-        <v>1.09</v>
+        <v>0.48</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1006.5</v>
+        <v>1002.02</v>
       </c>
       <c r="Q5">
-        <v>1014.97</v>
+        <v>1013.3</v>
       </c>
       <c r="R5">
-        <v>1000.41</v>
+        <v>1001.84</v>
       </c>
       <c r="S5">
-        <v>911.96</v>
+        <v>912.61</v>
       </c>
       <c r="T5">
-        <v>11.47</v>
+        <v>8.77</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1352,34 +1333,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>53.12</v>
+        <v>44.29</v>
       </c>
       <c r="Z5">
-        <v>0.86</v>
+        <v>-0.62</v>
       </c>
       <c r="AA5">
-        <v>3.59</v>
+        <v>2.75</v>
       </c>
       <c r="AB5">
-        <v>-2.73</v>
+        <v>-3.37</v>
       </c>
       <c r="AC5">
-        <v>26.07</v>
+        <v>28.89</v>
       </c>
       <c r="AD5">
-        <v>13.16</v>
+        <v>18.32</v>
       </c>
       <c r="AE5">
-        <v>19.45</v>
+        <v>20.32</v>
       </c>
       <c r="AF5">
-        <v>34.06</v>
+        <v>68.76000000000001</v>
       </c>
       <c r="AG5">
-        <v>1032.18</v>
+        <v>1032.38</v>
       </c>
       <c r="AH5">
-        <v>997.76</v>
+        <v>994.22</v>
       </c>
       <c r="AI5">
         <v>1048.43</v>
@@ -1388,7 +1369,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>16.86</v>
+        <v>15.22</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1399,10 +1380,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.83</v>
+        <v>2.85</v>
       </c>
       <c r="D6">
-        <v>-6.29</v>
+        <v>0.71</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1411,37 +1392,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-21.82</v>
+        <v>-21.27</v>
       </c>
       <c r="H6">
-        <v>53.8</v>
+        <v>54.89</v>
       </c>
       <c r="I6">
-        <v>-6.91</v>
+        <v>-7.47</v>
       </c>
       <c r="J6">
-        <v>19.92</v>
+        <v>20.25</v>
       </c>
       <c r="K6">
-        <v>13.65</v>
+        <v>10.89</v>
       </c>
       <c r="L6">
-        <v>-15.77</v>
+        <v>-14.16</v>
       </c>
       <c r="M6">
-        <v>1.17</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N6">
         <v>60</v>
       </c>
       <c r="O6">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="P6">
-        <v>2.98</v>
+        <v>2.93</v>
       </c>
       <c r="Q6">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R6">
         <v>2.45</v>
@@ -1450,7 +1431,7 @@
         <v>2.69</v>
       </c>
       <c r="T6">
-        <v>5.2</v>
+        <v>6.02</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1465,34 +1446,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>62.12</v>
+        <v>62.86</v>
       </c>
       <c r="Z6">
-        <v>0.16</v>
+        <v>0.15</v>
       </c>
       <c r="AA6">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="AB6">
-        <v>0.06</v>
+        <v>0.05</v>
       </c>
       <c r="AC6">
-        <v>73.06</v>
+        <v>65.70999999999999</v>
       </c>
       <c r="AD6">
-        <v>81.98999999999999</v>
+        <v>74.14</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-16.35</v>
+        <v>-44.78</v>
       </c>
       <c r="AG6">
-        <v>3.18</v>
+        <v>3.21</v>
       </c>
       <c r="AH6">
-        <v>1.9</v>
+        <v>1.91</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1501,7 +1482,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>51.42</v>
+        <v>48.88</v>
       </c>
     </row>
   </sheetData>
@@ -1642,7 +1623,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1682,7 +1663,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1701,28 +1682,28 @@
       </c>
     </row>
     <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B4" s="5" t="s">
+      <c r="A4" s="4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C4" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E4" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>60</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>61</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="B6" s="2"/>
       <c r="C6" s="2"/>
@@ -1734,696 +1715,679 @@
         <v>0</v>
       </c>
       <c r="B7" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E7" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
-      </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
+      <c r="A8" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="7">
-        <v>11.18</v>
-      </c>
-      <c r="D8" s="7">
+      <c r="C8" s="6">
         <v>5.69</v>
       </c>
-      <c r="E8" s="8">
-        <v>-5.49</v>
+      <c r="D8" s="6">
+        <v>-2.3</v>
+      </c>
+      <c r="E8" s="7">
+        <v>-7.99</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="7">
-        <v>0.14</v>
-      </c>
-      <c r="D9" s="7">
+      <c r="C9" s="6">
         <v>-2.5</v>
       </c>
-      <c r="E9" s="8">
-        <v>-2.64</v>
+      <c r="D9" s="6">
+        <v>-6.92</v>
+      </c>
+      <c r="E9" s="7">
+        <v>-4.42</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="A10" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="7">
-        <v>-5.4</v>
-      </c>
-      <c r="D10" s="7">
+      <c r="C10" s="6">
         <v>-5.28</v>
       </c>
-      <c r="E10" s="9">
-        <v>0.12</v>
+      <c r="D10" s="6">
+        <v>-8.56</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-3.28</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="A11" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="7">
-        <v>-1.73</v>
-      </c>
-      <c r="D11" s="7">
+      <c r="C11" s="6">
         <v>0.41</v>
       </c>
-      <c r="E11" s="9">
-        <v>2.14</v>
+      <c r="D11" s="6">
+        <v>-3.53</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-3.94</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B12" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C12" s="7">
-        <v>28.51</v>
-      </c>
-      <c r="D12" s="7">
+      <c r="C12" s="6">
         <v>19.92</v>
       </c>
+      <c r="D12" s="6">
+        <v>20.25</v>
+      </c>
       <c r="E12" s="8">
-        <v>-8.59</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="A13" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="7">
-        <v>1.6</v>
-      </c>
-      <c r="D13" s="7">
+      <c r="C13" s="6">
         <v>1.36</v>
       </c>
-      <c r="E13" s="8">
-        <v>-0.24</v>
+      <c r="D13" s="6">
+        <v>-2.38</v>
+      </c>
+      <c r="E13" s="7">
+        <v>-3.74</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="A14" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="6" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="7">
-        <v>-3.08</v>
-      </c>
-      <c r="D14" s="7">
+      <c r="C14" s="6">
         <v>-1.48</v>
       </c>
-      <c r="E14" s="9">
-        <v>1.6</v>
+      <c r="D14" s="6">
+        <v>-2.11</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.63</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="A15" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="6" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="7">
-        <v>0.07000000000000001</v>
-      </c>
-      <c r="D15" s="7">
+      <c r="C15" s="6">
         <v>-0.37</v>
       </c>
-      <c r="E15" s="8">
-        <v>-0.44</v>
+      <c r="D15" s="6">
+        <v>-1.89</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.52</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="A16" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="7">
+      <c r="C16" s="6">
+        <v>-0.18</v>
+      </c>
+      <c r="D16" s="6">
+        <v>-2.21</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-2.03</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="5" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-6.91</v>
+      </c>
+      <c r="D17" s="6">
+        <v>-7.47</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="6">
+        <v>36.9</v>
+      </c>
+      <c r="D18" s="6">
+        <v>34.51</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-2.39</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B19" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-23.37</v>
+      </c>
+      <c r="D19" s="6">
+        <v>-24.83</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-1.46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="6">
+        <v>34.4</v>
+      </c>
+      <c r="D20" s="6">
+        <v>32.95</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-15.77</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-14.16</v>
+      </c>
+      <c r="E21" s="8">
+        <v>1.61</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="6">
+        <v>19.85</v>
+      </c>
+      <c r="D22" s="6">
+        <v>16.93</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-2.92</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="6">
+        <v>-2.07</v>
+      </c>
+      <c r="D23" s="6">
+        <v>-7.35</v>
+      </c>
+      <c r="E23" s="7">
+        <v>-5.28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="6">
+        <v>-0.61</v>
+      </c>
+      <c r="D24" s="6">
+        <v>-2.78</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-2.17</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="6">
+        <v>11.41</v>
+      </c>
+      <c r="D25" s="6">
+        <v>10.3</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-1.11</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>13.65</v>
+      </c>
+      <c r="D26" s="6">
+        <v>10.89</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-2.76</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B27" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="6">
+        <v>-15.71</v>
+      </c>
+      <c r="D27" s="6">
+        <v>-18.16</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-2.45</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B28" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="6">
+        <v>-11.86</v>
+      </c>
+      <c r="D28" s="6">
+        <v>-13.01</v>
+      </c>
+      <c r="E28" s="7">
         <v>-1.15</v>
       </c>
-      <c r="D16" s="7">
-        <v>-0.18</v>
-      </c>
-      <c r="E16" s="9">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="6">
+        <v>-24.99</v>
+      </c>
+      <c r="D29" s="6">
+        <v>-26.27</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-1.28</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="6">
+        <v>-4.93</v>
+      </c>
+      <c r="D30" s="6">
+        <v>-7.17</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-2.24</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>11.44</v>
-      </c>
-      <c r="D17" s="7">
-        <v>-6.91</v>
-      </c>
-      <c r="E17" s="8">
-        <v>-18.35</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-21.82</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-21.27</v>
+      </c>
+      <c r="E31" s="8">
+        <v>0.55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="7">
-        <v>37.38</v>
-      </c>
-      <c r="D18" s="7">
-        <v>36.9</v>
-      </c>
-      <c r="E18" s="8">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B32" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="6">
+        <v>175.64</v>
+      </c>
+      <c r="D32" s="6">
+        <v>170.53</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-5.11</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7">
-        <v>2.78</v>
-      </c>
-      <c r="D19" s="7">
-        <v>7.39</v>
-      </c>
-      <c r="E19" s="9">
-        <v>4.61</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B33" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="6">
+        <v>392.5</v>
+      </c>
+      <c r="D33" s="6">
+        <v>387.35</v>
+      </c>
+      <c r="E33" s="7">
+        <v>-5.15</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>-24.83</v>
-      </c>
-      <c r="D20" s="7">
-        <v>-23.37</v>
-      </c>
-      <c r="E20" s="9">
-        <v>1.46</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B34" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="6">
+        <v>400.55</v>
+      </c>
+      <c r="D34" s="6">
+        <v>393.7</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-6.85</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>28.95</v>
-      </c>
-      <c r="D21" s="7">
-        <v>34.4</v>
-      </c>
-      <c r="E21" s="9">
-        <v>5.45</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B35" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="6">
+        <v>1016.6</v>
+      </c>
+      <c r="D35" s="6">
+        <v>992.6</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-24</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>-10.65</v>
-      </c>
-      <c r="D22" s="7">
-        <v>-15.77</v>
-      </c>
-      <c r="E22" s="8">
-        <v>-5.12</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2.83</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2.85</v>
+      </c>
+      <c r="E36" s="8">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="7">
-        <v>19.35</v>
-      </c>
-      <c r="D23" s="7">
-        <v>19.85</v>
-      </c>
-      <c r="E23" s="9">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B37" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="6">
+        <v>57.77</v>
+      </c>
+      <c r="D37" s="6">
+        <v>48.55</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-9.220000000000001</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D24" s="7">
-        <v>-2.07</v>
-      </c>
-      <c r="E24" s="8">
-        <v>-1.51</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B38" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="6">
+        <v>43.31</v>
+      </c>
+      <c r="D38" s="6">
+        <v>40.49</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-2.82</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>-0.95</v>
-      </c>
-      <c r="D25" s="7">
-        <v>-0.61</v>
-      </c>
-      <c r="E25" s="9">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>37.21</v>
+      </c>
+      <c r="D39" s="6">
+        <v>31.69</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-5.52</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>10.3</v>
-      </c>
-      <c r="D26" s="7">
-        <v>11.41</v>
-      </c>
-      <c r="E26" s="9">
-        <v>1.11</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>53.12</v>
+      </c>
+      <c r="D40" s="6">
+        <v>44.29</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-8.83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>16.15</v>
-      </c>
-      <c r="D27" s="7">
-        <v>13.65</v>
-      </c>
-      <c r="E27" s="8">
-        <v>-2.5</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>62.12</v>
+      </c>
+      <c r="D41" s="6">
+        <v>62.86</v>
+      </c>
+      <c r="E41" s="8">
+        <v>0.74</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="7">
-        <v>-15.65</v>
-      </c>
-      <c r="D28" s="7">
-        <v>-15.71</v>
-      </c>
-      <c r="E28" s="8">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B42" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="6">
+        <v>-26.69</v>
+      </c>
+      <c r="D42" s="6">
+        <v>-6.17</v>
+      </c>
+      <c r="E42" s="8">
+        <v>20.52</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-12.81</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-11.86</v>
-      </c>
-      <c r="E29" s="9">
-        <v>0.95</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B43" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="6">
+        <v>-79.11</v>
+      </c>
+      <c r="D43" s="6">
+        <v>-85.47</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-6.36</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-24.62</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-24.99</v>
-      </c>
-      <c r="E30" s="8">
-        <v>-0.37</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>-3.68</v>
+      </c>
+      <c r="D44" s="6">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="E44" s="8">
+        <v>12.72</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-7.04</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-4.93</v>
-      </c>
-      <c r="E31" s="9">
-        <v>2.11</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>34.06</v>
+      </c>
+      <c r="D45" s="6">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="E45" s="8">
+        <v>34.7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-16.57</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-21.82</v>
-      </c>
-      <c r="E32" s="8">
-        <v>-5.25</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B33" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="7">
-        <v>175.77</v>
-      </c>
-      <c r="D33" s="7">
-        <v>175.64</v>
-      </c>
-      <c r="E33" s="8">
-        <v>-0.13</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="7">
-        <v>388.25</v>
-      </c>
-      <c r="D34" s="7">
-        <v>392.5</v>
-      </c>
-      <c r="E34" s="9">
-        <v>4.25</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B35" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="7">
-        <v>402.55</v>
-      </c>
-      <c r="D35" s="7">
-        <v>400.55</v>
-      </c>
-      <c r="E35" s="8">
-        <v>-2</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B36" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="7">
-        <v>994</v>
-      </c>
-      <c r="D36" s="7">
-        <v>1016.6</v>
-      </c>
-      <c r="E36" s="9">
-        <v>22.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B37" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="7">
-        <v>3.02</v>
-      </c>
-      <c r="D37" s="7">
-        <v>2.83</v>
-      </c>
-      <c r="E37" s="8">
-        <v>-0.19</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B38" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="7">
-        <v>58.03</v>
-      </c>
-      <c r="D38" s="7">
-        <v>57.77</v>
-      </c>
-      <c r="E38" s="8">
-        <v>-0.26</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="7">
-        <v>40.11</v>
-      </c>
-      <c r="D39" s="7">
-        <v>43.31</v>
-      </c>
-      <c r="E39" s="9">
-        <v>3.2</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="7">
-        <v>39.06</v>
-      </c>
-      <c r="D40" s="7">
-        <v>37.21</v>
-      </c>
-      <c r="E40" s="8">
-        <v>-1.85</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="7">
-        <v>43.22</v>
-      </c>
-      <c r="D41" s="7">
-        <v>53.12</v>
-      </c>
-      <c r="E41" s="9">
-        <v>9.9</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="7">
-        <v>75.39</v>
-      </c>
-      <c r="D42" s="7">
-        <v>62.12</v>
-      </c>
-      <c r="E42" s="8">
-        <v>-13.27</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B43" s="6" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C43" s="7">
-        <v>-40.02</v>
-      </c>
-      <c r="D43" s="7">
-        <v>-26.69</v>
-      </c>
-      <c r="E43" s="9">
-        <v>13.33</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B44" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="7">
-        <v>-27.29</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-79.11</v>
-      </c>
-      <c r="E44" s="8">
-        <v>-51.82</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-42.35</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-3.68</v>
-      </c>
-      <c r="E45" s="9">
-        <v>38.67</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-7.63</v>
-      </c>
-      <c r="D46" s="7">
-        <v>34.06</v>
-      </c>
-      <c r="E46" s="9">
-        <v>41.69</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="7">
-        <v>-38.45</v>
-      </c>
-      <c r="D47" s="7">
+      <c r="C46" s="6">
         <v>-16.35</v>
       </c>
-      <c r="E47" s="9">
-        <v>22.1</v>
+      <c r="D46" s="6">
+        <v>-44.78</v>
+      </c>
+      <c r="E46" s="7">
+        <v>-28.43</v>
       </c>
     </row>
   </sheetData>
@@ -2449,60 +2413,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
+      <c r="B1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="9" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="9" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="9" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="9" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="9" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="9" t="s">
         <v>73</v>
       </c>
-      <c r="H1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>75</v>
-      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="11">
         <v>65.92</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
-        <v>50.7</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="11">
+        <v>45.6</v>
+      </c>
+      <c r="E2" s="11">
         <v>80</v>
       </c>
-      <c r="F2" s="12">
-        <v>3.6</v>
-      </c>
-      <c r="G2" s="12">
-        <v>8.4</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="11">
+        <v>-0.2</v>
+      </c>
+      <c r="G2" s="11">
+        <v>5.6</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2604,37 +2568,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15">
-        <v>0.2594</v>
-      </c>
-      <c r="B2" s="15">
+      <c r="A2" s="14">
+        <v>0.2525</v>
+      </c>
+      <c r="B2" s="14">
         <v>0.0941</v>
       </c>
-      <c r="C2" s="15">
-        <v>0.0117</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.0109</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.2018</v>
+      <c r="C2" s="14">
+        <v>0.009399999999999999</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0048</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.204</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,43 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>57.8 → 48.5</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>57.8</t>
-  </si>
-  <si>
-    <t>48.5</t>
-  </si>
-  <si>
-    <t>53.1 → 44.3</t>
-  </si>
-  <si>
-    <t>53.1</t>
-  </si>
-  <si>
-    <t>44.3</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -404,15 +368,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -776,7 +739,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.7109375" customWidth="1"/>
+    <col min="3" max="3" width="7.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -787,9 +750,10 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="9.7109375" customWidth="1"/>
-    <col min="17" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -928,37 +892,37 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>170.53</v>
+        <v>167.9</v>
       </c>
       <c r="D2">
-        <v>-2.91</v>
+        <v>-1.54</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>124.01</v>
+        <v>125.02</v>
       </c>
       <c r="G2">
-        <v>-18.16</v>
+        <v>-19.42</v>
       </c>
       <c r="H2">
-        <v>37.51</v>
+        <v>34.3</v>
       </c>
       <c r="I2">
-        <v>-2.38</v>
+        <v>-6.23</v>
       </c>
       <c r="J2">
-        <v>-2.3</v>
+        <v>-2.43</v>
       </c>
       <c r="K2">
-        <v>16.93</v>
+        <v>16.24</v>
       </c>
       <c r="L2">
-        <v>34.51</v>
+        <v>35.39</v>
       </c>
       <c r="M2">
-        <v>25.25</v>
+        <v>24.99</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -967,19 +931,19 @@
         <v>80</v>
       </c>
       <c r="P2">
-        <v>175.68</v>
+        <v>173.45</v>
       </c>
       <c r="Q2">
-        <v>175.26</v>
+        <v>174.8</v>
       </c>
       <c r="R2">
-        <v>165.26</v>
+        <v>165.59</v>
       </c>
       <c r="S2">
-        <v>168.85</v>
+        <v>168.96</v>
       </c>
       <c r="T2">
-        <v>1</v>
+        <v>-0.63</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -991,37 +955,37 @@
         <v>44</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>48.55</v>
+        <v>44.6</v>
       </c>
       <c r="Z2">
-        <v>2.73</v>
+        <v>2.02</v>
       </c>
       <c r="AA2">
-        <v>3.61</v>
+        <v>3.29</v>
       </c>
       <c r="AB2">
-        <v>-0.87</v>
+        <v>-1.27</v>
       </c>
       <c r="AC2">
-        <v>7.15</v>
+        <v>3.19</v>
       </c>
       <c r="AD2">
-        <v>20.85</v>
+        <v>10.34</v>
       </c>
       <c r="AE2">
-        <v>4.4</v>
+        <v>4.48</v>
       </c>
       <c r="AF2">
-        <v>-6.17</v>
+        <v>-0.5600000000000001</v>
       </c>
       <c r="AG2">
-        <v>179.69</v>
+        <v>180.24</v>
       </c>
       <c r="AH2">
-        <v>170.82</v>
+        <v>169.37</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -1030,7 +994,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>22.31</v>
+        <v>24.01</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1041,10 +1005,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>387.35</v>
+        <v>391.7</v>
       </c>
       <c r="D3">
-        <v>-1.31</v>
+        <v>1.12</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1053,46 +1017,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-13.01</v>
+        <v>-12.04</v>
       </c>
       <c r="H3">
-        <v>72.16</v>
+        <v>74.09</v>
       </c>
       <c r="I3">
-        <v>-2.11</v>
+        <v>-1.43</v>
       </c>
       <c r="J3">
-        <v>-6.92</v>
+        <v>-4.85</v>
       </c>
       <c r="K3">
-        <v>-7.35</v>
+        <v>-6.84</v>
       </c>
       <c r="L3">
-        <v>7.39</v>
+        <v>10.2</v>
       </c>
       <c r="M3">
-        <v>9.41</v>
+        <v>9.25</v>
       </c>
       <c r="N3">
         <v>40</v>
       </c>
       <c r="O3">
-        <v>48</v>
+        <v>54</v>
       </c>
       <c r="P3">
-        <v>392.57</v>
+        <v>391.43</v>
       </c>
       <c r="Q3">
-        <v>407.13</v>
+        <v>406.1</v>
       </c>
       <c r="R3">
-        <v>404.42</v>
+        <v>403.74</v>
       </c>
       <c r="S3">
-        <v>326.85</v>
+        <v>327.18</v>
       </c>
       <c r="T3">
-        <v>18.51</v>
+        <v>19.72</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1107,43 +1071,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>40.49</v>
+        <v>43.82</v>
       </c>
       <c r="Z3">
-        <v>-4.02</v>
+        <v>-4.16</v>
       </c>
       <c r="AA3">
-        <v>-1.45</v>
+        <v>-1.99</v>
       </c>
       <c r="AB3">
-        <v>-2.56</v>
+        <v>-2.17</v>
       </c>
       <c r="AC3">
-        <v>5.07</v>
+        <v>18.28</v>
       </c>
       <c r="AD3">
-        <v>4.96</v>
+        <v>9.92</v>
       </c>
       <c r="AE3">
-        <v>12.68</v>
+        <v>12.66</v>
       </c>
       <c r="AF3">
-        <v>-85.47</v>
+        <v>-84.59999999999999</v>
       </c>
       <c r="AG3">
-        <v>438.97</v>
+        <v>438.56</v>
       </c>
       <c r="AH3">
-        <v>375.3</v>
+        <v>373.65</v>
       </c>
       <c r="AI3">
-        <v>427.57</v>
+        <v>426.77</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>29.98</v>
+        <v>32.36</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1154,10 +1118,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>393.7</v>
+        <v>393.1</v>
       </c>
       <c r="D4">
-        <v>-1.71</v>
+        <v>-0.15</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1166,46 +1130,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-26.27</v>
+        <v>-26.39</v>
       </c>
       <c r="H4">
-        <v>14.22</v>
+        <v>14.04</v>
       </c>
       <c r="I4">
-        <v>-1.89</v>
+        <v>-2.2</v>
       </c>
       <c r="J4">
-        <v>-8.56</v>
+        <v>-6.73</v>
       </c>
       <c r="K4">
-        <v>-2.78</v>
+        <v>-3.17</v>
       </c>
       <c r="L4">
-        <v>-24.83</v>
+        <v>-23.28</v>
       </c>
       <c r="M4">
-        <v>-20.4</v>
+        <v>-20.26</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="P4">
-        <v>400.26</v>
+        <v>398.49</v>
       </c>
       <c r="Q4">
-        <v>408.01</v>
+        <v>406.49</v>
       </c>
       <c r="R4">
-        <v>417</v>
+        <v>416.36</v>
       </c>
       <c r="S4">
-        <v>417.46</v>
+        <v>416.91</v>
       </c>
       <c r="T4">
-        <v>-5.69</v>
+        <v>-5.71</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1220,43 +1184,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.69</v>
+        <v>31.25</v>
       </c>
       <c r="Z4">
-        <v>-5.85</v>
+        <v>-6.22</v>
       </c>
       <c r="AA4">
-        <v>-5.01</v>
+        <v>-5.25</v>
       </c>
       <c r="AB4">
-        <v>-0.84</v>
+        <v>-0.97</v>
       </c>
       <c r="AC4">
+        <v>0</v>
+      </c>
+      <c r="AD4">
         <v>6.92</v>
       </c>
-      <c r="AD4">
-        <v>12.09</v>
-      </c>
       <c r="AE4">
-        <v>10.87</v>
+        <v>10.71</v>
       </c>
       <c r="AF4">
-        <v>9.039999999999999</v>
+        <v>-36.47</v>
       </c>
       <c r="AG4">
-        <v>425.33</v>
+        <v>423.42</v>
       </c>
       <c r="AH4">
-        <v>390.69</v>
+        <v>389.56</v>
       </c>
       <c r="AI4">
-        <v>429.19</v>
+        <v>426.99</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>13.22</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1267,10 +1231,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>992.6</v>
+        <v>978</v>
       </c>
       <c r="D5">
-        <v>-2.36</v>
+        <v>-1.47</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1279,46 +1243,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-7.17</v>
+        <v>-8.539999999999999</v>
       </c>
       <c r="H5">
-        <v>39.26</v>
+        <v>37.22</v>
       </c>
       <c r="I5">
-        <v>-2.21</v>
+        <v>-2.59</v>
       </c>
       <c r="J5">
-        <v>-3.53</v>
+        <v>-4.68</v>
       </c>
       <c r="K5">
-        <v>10.3</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L5">
-        <v>32.95</v>
+        <v>32.25</v>
       </c>
       <c r="M5">
-        <v>0.48</v>
+        <v>-0.05</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>1002.02</v>
+        <v>996.8200000000001</v>
       </c>
       <c r="Q5">
-        <v>1013.3</v>
+        <v>1011.25</v>
       </c>
       <c r="R5">
-        <v>1001.84</v>
+        <v>1003.3</v>
       </c>
       <c r="S5">
-        <v>912.61</v>
+        <v>913.26</v>
       </c>
       <c r="T5">
-        <v>8.77</v>
+        <v>7.09</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1333,43 +1297,43 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>44.29</v>
+        <v>39.94</v>
       </c>
       <c r="Z5">
-        <v>-0.62</v>
+        <v>-2.94</v>
       </c>
       <c r="AA5">
-        <v>2.75</v>
+        <v>1.61</v>
       </c>
       <c r="AB5">
-        <v>-3.37</v>
+        <v>-4.55</v>
       </c>
       <c r="AC5">
         <v>28.89</v>
       </c>
       <c r="AD5">
-        <v>18.32</v>
+        <v>27.95</v>
       </c>
       <c r="AE5">
-        <v>20.32</v>
+        <v>20.96</v>
       </c>
       <c r="AF5">
-        <v>68.76000000000001</v>
+        <v>149.05</v>
       </c>
       <c r="AG5">
-        <v>1032.38</v>
+        <v>1035.78</v>
       </c>
       <c r="AH5">
-        <v>994.22</v>
+        <v>986.72</v>
       </c>
       <c r="AI5">
-        <v>1048.43</v>
+        <v>1038.34</v>
       </c>
       <c r="AJ5" t="s">
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>15.22</v>
+        <v>17.46</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1383,7 +1347,7 @@
         <v>2.85</v>
       </c>
       <c r="D6">
-        <v>0.71</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1398,7 +1362,7 @@
         <v>54.89</v>
       </c>
       <c r="I6">
-        <v>-7.47</v>
+        <v>-5.32</v>
       </c>
       <c r="J6">
         <v>20.25</v>
@@ -1410,7 +1374,7 @@
         <v>-14.16</v>
       </c>
       <c r="M6">
-        <v>0.9399999999999999</v>
+        <v>1.16</v>
       </c>
       <c r="N6">
         <v>60</v>
@@ -1419,19 +1383,19 @@
         <v>57</v>
       </c>
       <c r="P6">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="Q6">
-        <v>2.56</v>
+        <v>2.59</v>
       </c>
       <c r="R6">
-        <v>2.45</v>
+        <v>2.46</v>
       </c>
       <c r="S6">
         <v>2.69</v>
       </c>
       <c r="T6">
-        <v>6.02</v>
+        <v>6.09</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1452,28 +1416,28 @@
         <v>0.15</v>
       </c>
       <c r="AA6">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="AB6">
-        <v>0.05</v>
+        <v>0.03</v>
       </c>
       <c r="AC6">
-        <v>65.70999999999999</v>
+        <v>57.24</v>
       </c>
       <c r="AD6">
-        <v>74.14</v>
+        <v>65.34</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-44.78</v>
+        <v>-61.35</v>
       </c>
       <c r="AG6">
-        <v>3.21</v>
+        <v>3.24</v>
       </c>
       <c r="AH6">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1482,7 +1446,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>48.88</v>
+        <v>46.68</v>
       </c>
     </row>
   </sheetData>
@@ -1623,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1643,757 +1607,617 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>37</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="4" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="4" t="s">
-        <v>53</v>
-      </c>
-      <c r="C4" s="4" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E4" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F4" s="4" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
     </row>
     <row r="7" spans="1:6">
       <c r="A7" s="3" t="s">
-        <v>0</v>
+        <v>37</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>65</v>
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-2.3</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-2.43</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-0.13</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>-6.92</v>
+      </c>
+      <c r="D8" s="5">
+        <v>-4.85</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2.07</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-8.56</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-6.73</v>
+      </c>
+      <c r="E9" s="7">
+        <v>1.83</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-3.53</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-4.68</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.15</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>5.69</v>
-      </c>
-      <c r="D8" s="6">
-        <v>-2.3</v>
-      </c>
-      <c r="E8" s="7">
-        <v>-7.99</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B11" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C11" s="5">
+        <v>-2.38</v>
+      </c>
+      <c r="D11" s="5">
+        <v>-6.23</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-3.85</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-2.5</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-6.92</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-4.42</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-2.11</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-1.43</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-5.28</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-8.56</v>
-      </c>
-      <c r="E10" s="7">
-        <v>-3.28</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>-1.89</v>
+      </c>
+      <c r="D13" s="5">
+        <v>-2.2</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-0.31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>0.41</v>
-      </c>
-      <c r="D11" s="6">
-        <v>-3.53</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-3.94</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-2.21</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.59</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.38</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="6">
-        <v>19.92</v>
-      </c>
-      <c r="D12" s="6">
-        <v>20.25</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.33</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>-7.47</v>
+      </c>
+      <c r="D15" s="5">
+        <v>-5.32</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>1.36</v>
-      </c>
-      <c r="D13" s="6">
-        <v>-2.38</v>
-      </c>
-      <c r="E13" s="7">
-        <v>-3.74</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B16" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C16" s="5">
+        <v>34.51</v>
+      </c>
+      <c r="D16" s="5">
+        <v>35.39</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.88</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-1.48</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-2.11</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.63</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>7.39</v>
+      </c>
+      <c r="D17" s="5">
+        <v>10.2</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2.81</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>-0.37</v>
-      </c>
-      <c r="D15" s="6">
-        <v>-1.89</v>
-      </c>
-      <c r="E15" s="7">
-        <v>-1.52</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>-24.83</v>
+      </c>
+      <c r="D18" s="5">
+        <v>-23.28</v>
+      </c>
+      <c r="E18" s="7">
+        <v>1.55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-0.18</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-2.21</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-2.03</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>32.95</v>
+      </c>
+      <c r="D19" s="5">
+        <v>32.25</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C20" s="5">
+        <v>16.93</v>
+      </c>
+      <c r="D20" s="5">
+        <v>16.24</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B21" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-7.35</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-6.84</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.51</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>-2.78</v>
+      </c>
+      <c r="D22" s="5">
+        <v>-3.17</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-0.39</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>10.3</v>
+      </c>
+      <c r="D23" s="5">
+        <v>8.279999999999999</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-2.02</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B24" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-18.16</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-19.42</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-1.26</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B25" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C25" s="5">
+        <v>-13.01</v>
+      </c>
+      <c r="D25" s="5">
+        <v>-12.04</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.97</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C26" s="5">
+        <v>-26.27</v>
+      </c>
+      <c r="D26" s="5">
+        <v>-26.39</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-0.12</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-7.17</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-8.539999999999999</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-1.37</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B28" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C28" s="5">
+        <v>170.53</v>
+      </c>
+      <c r="D28" s="5">
+        <v>167.9</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-2.63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B29" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C29" s="5">
+        <v>387.35</v>
+      </c>
+      <c r="D29" s="5">
+        <v>391.7</v>
+      </c>
+      <c r="E29" s="7">
+        <v>4.35</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B30" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C30" s="5">
+        <v>393.7</v>
+      </c>
+      <c r="D30" s="5">
+        <v>393.1</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B31" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C31" s="5">
+        <v>992.6</v>
+      </c>
+      <c r="D31" s="5">
+        <v>978</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-14.6</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B32" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C32" s="5">
+        <v>48.55</v>
+      </c>
+      <c r="D32" s="5">
+        <v>44.6</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-3.95</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B33" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C33" s="5">
+        <v>40.49</v>
+      </c>
+      <c r="D33" s="5">
+        <v>43.82</v>
+      </c>
+      <c r="E33" s="7">
+        <v>3.33</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B34" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C34" s="5">
+        <v>31.69</v>
+      </c>
+      <c r="D34" s="5">
+        <v>31.25</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-0.44</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B35" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C35" s="5">
+        <v>44.29</v>
+      </c>
+      <c r="D35" s="5">
+        <v>39.94</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-4.35</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B36" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C36" s="5">
+        <v>-6.17</v>
+      </c>
+      <c r="D36" s="5">
+        <v>-0.5600000000000001</v>
+      </c>
+      <c r="E36" s="7">
+        <v>5.61</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C37" s="5">
+        <v>-85.47</v>
+      </c>
+      <c r="D37" s="5">
+        <v>-84.59999999999999</v>
+      </c>
+      <c r="E37" s="7">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B38" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C38" s="5">
+        <v>9.039999999999999</v>
+      </c>
+      <c r="D38" s="5">
+        <v>-36.47</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-45.51</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B39" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" s="5">
+        <v>68.76000000000001</v>
+      </c>
+      <c r="D39" s="5">
+        <v>149.05</v>
+      </c>
+      <c r="E39" s="7">
+        <v>80.29000000000001</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="6">
-        <v>-6.91</v>
-      </c>
-      <c r="D17" s="6">
-        <v>-7.47</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-0.5600000000000001</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>36.9</v>
-      </c>
-      <c r="D18" s="6">
-        <v>34.51</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-2.39</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-23.37</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-24.83</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-1.46</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>34.4</v>
-      </c>
-      <c r="D20" s="6">
-        <v>32.95</v>
-      </c>
-      <c r="E20" s="7">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-15.77</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-14.16</v>
-      </c>
-      <c r="E21" s="8">
-        <v>1.61</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>19.85</v>
-      </c>
-      <c r="D22" s="6">
-        <v>16.93</v>
-      </c>
-      <c r="E22" s="7">
-        <v>-2.92</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>-2.07</v>
-      </c>
-      <c r="D23" s="6">
-        <v>-7.35</v>
-      </c>
-      <c r="E23" s="7">
-        <v>-5.28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-0.61</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-2.78</v>
-      </c>
-      <c r="E24" s="7">
-        <v>-2.17</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>11.41</v>
-      </c>
-      <c r="D25" s="6">
-        <v>10.3</v>
-      </c>
-      <c r="E25" s="7">
-        <v>-1.11</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>13.65</v>
-      </c>
-      <c r="D26" s="6">
-        <v>10.89</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-2.76</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-15.71</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-18.16</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-2.45</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-11.86</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-13.01</v>
-      </c>
-      <c r="E28" s="7">
-        <v>-1.15</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-24.99</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-26.27</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-1.28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-4.93</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-7.17</v>
-      </c>
-      <c r="E30" s="7">
-        <v>-2.24</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="6">
-        <v>-21.82</v>
-      </c>
-      <c r="D31" s="6">
-        <v>-21.27</v>
-      </c>
-      <c r="E31" s="8">
-        <v>0.55</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>175.64</v>
-      </c>
-      <c r="D32" s="6">
-        <v>170.53</v>
-      </c>
-      <c r="E32" s="7">
-        <v>-5.11</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>392.5</v>
-      </c>
-      <c r="D33" s="6">
-        <v>387.35</v>
-      </c>
-      <c r="E33" s="7">
-        <v>-5.15</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>400.55</v>
-      </c>
-      <c r="D34" s="6">
-        <v>393.7</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-6.85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="6">
-        <v>1016.6</v>
-      </c>
-      <c r="D35" s="6">
-        <v>992.6</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-24</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="6">
-        <v>2.83</v>
-      </c>
-      <c r="D36" s="6">
-        <v>2.85</v>
-      </c>
-      <c r="E36" s="8">
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>57.77</v>
-      </c>
-      <c r="D37" s="6">
-        <v>48.55</v>
-      </c>
-      <c r="E37" s="7">
-        <v>-9.220000000000001</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>43.31</v>
-      </c>
-      <c r="D38" s="6">
-        <v>40.49</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-2.82</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B39" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="6">
-        <v>37.21</v>
-      </c>
-      <c r="D39" s="6">
-        <v>31.69</v>
-      </c>
-      <c r="E39" s="7">
-        <v>-5.52</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="6">
-        <v>53.12</v>
-      </c>
-      <c r="D40" s="6">
-        <v>44.29</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-8.83</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="6">
-        <v>62.12</v>
-      </c>
-      <c r="D41" s="6">
-        <v>62.86</v>
-      </c>
-      <c r="E41" s="8">
-        <v>0.74</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B42" s="5" t="s">
+      <c r="B40" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="6">
-        <v>-26.69</v>
-      </c>
-      <c r="D42" s="6">
-        <v>-6.17</v>
-      </c>
-      <c r="E42" s="8">
-        <v>20.52</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-79.11</v>
-      </c>
-      <c r="D43" s="6">
-        <v>-85.47</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-6.36</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-3.68</v>
-      </c>
-      <c r="D44" s="6">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="E44" s="8">
-        <v>12.72</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>34.06</v>
-      </c>
-      <c r="D45" s="6">
-        <v>68.76000000000001</v>
-      </c>
-      <c r="E45" s="8">
-        <v>34.7</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-16.35</v>
-      </c>
-      <c r="D46" s="6">
+      <c r="C40" s="5">
         <v>-44.78</v>
       </c>
-      <c r="E46" s="7">
-        <v>-28.43</v>
+      <c r="D40" s="5">
+        <v>-61.35</v>
+      </c>
+      <c r="E40" s="6">
+        <v>-16.57</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2413,60 +2237,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="9" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="9" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="9" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>65.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="10">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>45.6</v>
-      </c>
-      <c r="E2" s="11">
-        <v>80</v>
-      </c>
-      <c r="F2" s="11">
-        <v>-0.2</v>
-      </c>
-      <c r="G2" s="11">
-        <v>5.6</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="10">
+        <v>44.5</v>
+      </c>
+      <c r="E2" s="10">
+        <v>60</v>
+      </c>
+      <c r="F2" s="10">
+        <v>0.3</v>
+      </c>
+      <c r="G2" s="10">
+        <v>5.1</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="10">
         <v>40</v>
       </c>
     </row>
@@ -2568,37 +2392,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.2525</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.0941</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.009399999999999999</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.0048</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.204</v>
+      <c r="A2" s="13">
+        <v>0.2499</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.0925</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0116</v>
+      </c>
+      <c r="D2" s="13">
+        <v>-0.0005</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2026</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>RSI Momentum</t>
+  </si>
+  <si>
+    <t>43.8 → 60.8</t>
+  </si>
+  <si>
+    <t>🟢 BULLISH</t>
+  </si>
+  <si>
+    <t>43.8</t>
+  </si>
+  <si>
+    <t>60.8</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,17 +395,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -739,7 +767,7 @@
   <cols>
     <col min="1" max="1" width="12.7109375" customWidth="1"/>
     <col min="2" max="2" width="9.7109375" customWidth="1"/>
-    <col min="3" max="3" width="7.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.7109375" customWidth="1"/>
     <col min="4" max="4" width="11.7109375" customWidth="1"/>
     <col min="5" max="5" width="10.7109375" customWidth="1"/>
     <col min="6" max="6" width="9.7109375" customWidth="1"/>
@@ -751,9 +779,7 @@
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
     <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -892,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>167.9</v>
+        <v>169.35</v>
       </c>
       <c r="D2">
-        <v>-1.54</v>
+        <v>0.86</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -904,46 +930,46 @@
         <v>125.02</v>
       </c>
       <c r="G2">
-        <v>-19.42</v>
+        <v>-18.73</v>
       </c>
       <c r="H2">
-        <v>34.3</v>
+        <v>35.46</v>
       </c>
       <c r="I2">
-        <v>-6.23</v>
+        <v>-4.54</v>
       </c>
       <c r="J2">
-        <v>-2.43</v>
+        <v>-4.32</v>
       </c>
       <c r="K2">
-        <v>16.24</v>
+        <v>16.56</v>
       </c>
       <c r="L2">
-        <v>35.39</v>
+        <v>35.45</v>
       </c>
       <c r="M2">
-        <v>24.99</v>
+        <v>25.47</v>
       </c>
       <c r="N2">
         <v>99</v>
       </c>
       <c r="O2">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P2">
-        <v>173.45</v>
+        <v>171.84</v>
       </c>
       <c r="Q2">
-        <v>174.8</v>
+        <v>174.39</v>
       </c>
       <c r="R2">
-        <v>165.59</v>
+        <v>165.88</v>
       </c>
       <c r="S2">
-        <v>168.96</v>
+        <v>169.08</v>
       </c>
       <c r="T2">
-        <v>-0.63</v>
+        <v>0.16</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -955,37 +981,37 @@
         <v>44</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>44.6</v>
+        <v>47.15</v>
       </c>
       <c r="Z2">
-        <v>2.02</v>
+        <v>1.55</v>
       </c>
       <c r="AA2">
-        <v>3.29</v>
+        <v>2.94</v>
       </c>
       <c r="AB2">
-        <v>-1.27</v>
+        <v>-1.39</v>
       </c>
       <c r="AC2">
-        <v>3.19</v>
+        <v>4.25</v>
       </c>
       <c r="AD2">
-        <v>10.34</v>
+        <v>4.86</v>
       </c>
       <c r="AE2">
-        <v>4.48</v>
+        <v>4.4</v>
       </c>
       <c r="AF2">
-        <v>-0.5600000000000001</v>
+        <v>-44.9</v>
       </c>
       <c r="AG2">
-        <v>180.24</v>
+        <v>180.19</v>
       </c>
       <c r="AH2">
-        <v>169.37</v>
+        <v>168.6</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -994,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>24.01</v>
+        <v>25.41</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1005,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>391.7</v>
+        <v>422.95</v>
       </c>
       <c r="D3">
-        <v>1.12</v>
+        <v>7.98</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1017,46 +1043,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-12.04</v>
+        <v>-5.02</v>
       </c>
       <c r="H3">
-        <v>74.09</v>
+        <v>87.98</v>
       </c>
       <c r="I3">
-        <v>-1.43</v>
+        <v>6.44</v>
       </c>
       <c r="J3">
-        <v>-4.85</v>
+        <v>2.57</v>
       </c>
       <c r="K3">
-        <v>-6.84</v>
+        <v>2.95</v>
       </c>
       <c r="L3">
-        <v>10.2</v>
+        <v>20.19</v>
       </c>
       <c r="M3">
-        <v>9.25</v>
+        <v>10.79</v>
       </c>
       <c r="N3">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="O3">
-        <v>54</v>
+        <v>68</v>
       </c>
       <c r="P3">
-        <v>391.43</v>
+        <v>396.55</v>
       </c>
       <c r="Q3">
-        <v>406.1</v>
+        <v>406.72</v>
       </c>
       <c r="R3">
-        <v>403.74</v>
+        <v>403.72</v>
       </c>
       <c r="S3">
-        <v>327.18</v>
+        <v>327.68</v>
       </c>
       <c r="T3">
-        <v>19.72</v>
+        <v>29.07</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1071,34 +1097,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>43.82</v>
+        <v>60.79</v>
       </c>
       <c r="Z3">
-        <v>-4.16</v>
+        <v>-1.74</v>
       </c>
       <c r="AA3">
-        <v>-1.99</v>
+        <v>-1.94</v>
       </c>
       <c r="AB3">
-        <v>-2.17</v>
+        <v>0.21</v>
       </c>
       <c r="AC3">
-        <v>18.28</v>
+        <v>47.1</v>
       </c>
       <c r="AD3">
-        <v>9.92</v>
+        <v>23.48</v>
       </c>
       <c r="AE3">
-        <v>12.66</v>
+        <v>15.78</v>
       </c>
       <c r="AF3">
-        <v>-84.59999999999999</v>
+        <v>4056.8</v>
       </c>
       <c r="AG3">
-        <v>438.56</v>
+        <v>440</v>
       </c>
       <c r="AH3">
-        <v>373.65</v>
+        <v>373.45</v>
       </c>
       <c r="AI3">
         <v>426.77</v>
@@ -1107,7 +1133,7 @@
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>32.36</v>
+        <v>35.65</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>393.1</v>
+        <v>393</v>
       </c>
       <c r="D4">
-        <v>-0.15</v>
+        <v>-0.03</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1130,46 +1156,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-26.39</v>
+        <v>-26.4</v>
       </c>
       <c r="H4">
-        <v>14.04</v>
+        <v>14.01</v>
       </c>
       <c r="I4">
-        <v>-2.2</v>
+        <v>-2.37</v>
       </c>
       <c r="J4">
-        <v>-6.73</v>
+        <v>-7.2</v>
       </c>
       <c r="K4">
-        <v>-3.17</v>
+        <v>-2.77</v>
       </c>
       <c r="L4">
-        <v>-23.28</v>
+        <v>-23.81</v>
       </c>
       <c r="M4">
-        <v>-20.26</v>
+        <v>-20.48</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="P4">
-        <v>398.49</v>
+        <v>396.58</v>
       </c>
       <c r="Q4">
-        <v>406.49</v>
+        <v>404.99</v>
       </c>
       <c r="R4">
-        <v>416.36</v>
+        <v>415.72</v>
       </c>
       <c r="S4">
-        <v>416.91</v>
+        <v>416.3</v>
       </c>
       <c r="T4">
-        <v>-5.71</v>
+        <v>-5.6</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1184,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.25</v>
+        <v>31.17</v>
       </c>
       <c r="Z4">
-        <v>-6.22</v>
+        <v>-6.46</v>
       </c>
       <c r="AA4">
-        <v>-5.25</v>
+        <v>-5.49</v>
       </c>
       <c r="AB4">
-        <v>-0.97</v>
+        <v>-0.96</v>
       </c>
       <c r="AC4">
         <v>0</v>
       </c>
       <c r="AD4">
-        <v>6.92</v>
+        <v>2.31</v>
       </c>
       <c r="AE4">
-        <v>10.71</v>
+        <v>10.93</v>
       </c>
       <c r="AF4">
-        <v>-36.47</v>
+        <v>247.59</v>
       </c>
       <c r="AG4">
-        <v>423.42</v>
+        <v>421.04</v>
       </c>
       <c r="AH4">
-        <v>389.56</v>
+        <v>388.94</v>
       </c>
       <c r="AI4">
         <v>426.99</v>
@@ -1220,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>14.87</v>
+        <v>12.98</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1231,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>978</v>
+        <v>1004.8</v>
       </c>
       <c r="D5">
-        <v>-1.47</v>
+        <v>2.74</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1243,46 +1269,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-8.539999999999999</v>
+        <v>-6.03</v>
       </c>
       <c r="H5">
-        <v>37.22</v>
+        <v>40.98</v>
       </c>
       <c r="I5">
-        <v>-2.59</v>
+        <v>0.19</v>
       </c>
       <c r="J5">
-        <v>-4.68</v>
+        <v>-1.39</v>
       </c>
       <c r="K5">
-        <v>8.279999999999999</v>
+        <v>11.05</v>
       </c>
       <c r="L5">
-        <v>32.25</v>
+        <v>33.47</v>
       </c>
       <c r="M5">
-        <v>-0.05</v>
+        <v>0.62</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>996.8200000000001</v>
+        <v>997.2</v>
       </c>
       <c r="Q5">
-        <v>1011.25</v>
+        <v>1010.68</v>
       </c>
       <c r="R5">
-        <v>1003.3</v>
+        <v>1004.84</v>
       </c>
       <c r="S5">
-        <v>913.26</v>
+        <v>914.01</v>
       </c>
       <c r="T5">
-        <v>7.09</v>
+        <v>9.93</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1297,34 +1323,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>39.94</v>
+        <v>49.7</v>
       </c>
       <c r="Z5">
-        <v>-2.94</v>
+        <v>-2.58</v>
       </c>
       <c r="AA5">
-        <v>1.61</v>
+        <v>0.77</v>
       </c>
       <c r="AB5">
-        <v>-4.55</v>
+        <v>-3.35</v>
       </c>
       <c r="AC5">
-        <v>28.89</v>
+        <v>25.27</v>
       </c>
       <c r="AD5">
-        <v>27.95</v>
+        <v>27.68</v>
       </c>
       <c r="AE5">
-        <v>20.96</v>
+        <v>21.41</v>
       </c>
       <c r="AF5">
-        <v>149.05</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="AG5">
-        <v>1035.78</v>
+        <v>1035.26</v>
       </c>
       <c r="AH5">
-        <v>986.72</v>
+        <v>986.1</v>
       </c>
       <c r="AI5">
         <v>1038.34</v>
@@ -1333,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>17.46</v>
+        <v>15.14</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.85</v>
+        <v>2.83</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>-0.7</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1356,46 +1382,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-21.27</v>
+        <v>-21.82</v>
       </c>
       <c r="H6">
-        <v>54.89</v>
+        <v>53.8</v>
       </c>
       <c r="I6">
-        <v>-5.32</v>
+        <v>-4.39</v>
       </c>
       <c r="J6">
-        <v>20.25</v>
+        <v>19.41</v>
       </c>
       <c r="K6">
-        <v>10.89</v>
+        <v>9.27</v>
       </c>
       <c r="L6">
-        <v>-14.16</v>
+        <v>-15.02</v>
       </c>
       <c r="M6">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="N6">
-        <v>60</v>
+        <v>40</v>
       </c>
       <c r="O6">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="P6">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="Q6">
-        <v>2.59</v>
+        <v>2.61</v>
       </c>
       <c r="R6">
-        <v>2.46</v>
+        <v>2.47</v>
       </c>
       <c r="S6">
-        <v>2.69</v>
+        <v>2.68</v>
       </c>
       <c r="T6">
-        <v>6.09</v>
+        <v>5.42</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1410,34 +1436,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>62.86</v>
+        <v>61.47</v>
       </c>
       <c r="Z6">
-        <v>0.15</v>
+        <v>0.14</v>
       </c>
       <c r="AA6">
         <v>0.12</v>
       </c>
       <c r="AB6">
-        <v>0.03</v>
+        <v>0.02</v>
       </c>
       <c r="AC6">
-        <v>57.24</v>
+        <v>56.8</v>
       </c>
       <c r="AD6">
-        <v>65.34</v>
+        <v>59.91</v>
       </c>
       <c r="AE6">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-61.35</v>
+        <v>-67.61</v>
       </c>
       <c r="AG6">
-        <v>3.24</v>
+        <v>3.26</v>
       </c>
       <c r="AH6">
-        <v>1.93</v>
+        <v>1.96</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1446,7 +1472,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>46.68</v>
+        <v>44.78</v>
       </c>
     </row>
   </sheetData>
@@ -1587,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1607,12 +1633,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1620,598 +1681,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-2.3</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-2.43</v>
       </c>
-      <c r="E7" s="6">
-        <v>-0.13</v>
+      <c r="D7" s="6">
+        <v>-4.32</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>-6.92</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>-4.85</v>
       </c>
-      <c r="E8" s="7">
-        <v>2.07</v>
+      <c r="D8" s="6">
+        <v>2.57</v>
+      </c>
+      <c r="E8" s="8">
+        <v>7.42</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-8.56</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-6.73</v>
       </c>
+      <c r="D9" s="6">
+        <v>-7.2</v>
+      </c>
       <c r="E9" s="7">
-        <v>1.83</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-3.53</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-4.68</v>
       </c>
-      <c r="E10" s="6">
-        <v>-1.15</v>
+      <c r="D10" s="6">
+        <v>-1.39</v>
+      </c>
+      <c r="E10" s="8">
+        <v>3.29</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="6">
+        <v>20.25</v>
+      </c>
+      <c r="D11" s="6">
+        <v>19.41</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-0.84</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C11" s="5">
-        <v>-2.38</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C12" s="6">
         <v>-6.23</v>
       </c>
-      <c r="E11" s="6">
-        <v>-3.85</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="D12" s="6">
+        <v>-4.54</v>
+      </c>
+      <c r="E12" s="8">
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-2.11</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C13" s="6">
         <v>-1.43</v>
       </c>
-      <c r="E12" s="7">
-        <v>0.68</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="D13" s="6">
+        <v>6.44</v>
+      </c>
+      <c r="E13" s="8">
+        <v>7.87</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>-1.89</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C14" s="6">
         <v>-2.2</v>
       </c>
-      <c r="E13" s="6">
-        <v>-0.31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="D14" s="6">
+        <v>-2.37</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-0.17</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-2.21</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C15" s="6">
         <v>-2.59</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.38</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="D15" s="6">
+        <v>0.19</v>
+      </c>
+      <c r="E15" s="8">
+        <v>2.78</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>-7.47</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C16" s="6">
         <v>-5.32</v>
       </c>
-      <c r="E15" s="7">
-        <v>2.15</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="D16" s="6">
+        <v>-4.39</v>
+      </c>
+      <c r="E16" s="8">
+        <v>0.93</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C16" s="5">
-        <v>34.51</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C17" s="6">
         <v>35.39</v>
       </c>
-      <c r="E16" s="7">
-        <v>0.88</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="D17" s="6">
+        <v>35.45</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.06</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>7.39</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C18" s="6">
         <v>10.2</v>
       </c>
-      <c r="E17" s="7">
-        <v>2.81</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="D18" s="6">
+        <v>20.19</v>
+      </c>
+      <c r="E18" s="8">
+        <v>9.99</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>-24.83</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C19" s="6">
         <v>-23.28</v>
       </c>
-      <c r="E18" s="7">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="D19" s="6">
+        <v>-23.81</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>32.95</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C20" s="6">
         <v>32.25</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.7</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="D20" s="6">
+        <v>33.47</v>
+      </c>
+      <c r="E20" s="8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="6">
+        <v>-14.16</v>
+      </c>
+      <c r="D21" s="6">
+        <v>-15.02</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.86</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C20" s="5">
-        <v>16.93</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C22" s="6">
         <v>16.24</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="D22" s="6">
+        <v>16.56</v>
+      </c>
+      <c r="E22" s="8">
+        <v>0.32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C21" s="5">
-        <v>-7.35</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C23" s="6">
         <v>-6.84</v>
       </c>
-      <c r="E21" s="7">
-        <v>0.51</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="D23" s="6">
+        <v>2.95</v>
+      </c>
+      <c r="E23" s="8">
+        <v>9.789999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>-2.78</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C24" s="6">
         <v>-3.17</v>
       </c>
-      <c r="E22" s="6">
-        <v>-0.39</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="D24" s="6">
+        <v>-2.77</v>
+      </c>
+      <c r="E24" s="8">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>10.3</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C25" s="6">
         <v>8.279999999999999</v>
       </c>
-      <c r="E23" s="6">
-        <v>-2.02</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="D25" s="6">
+        <v>11.05</v>
+      </c>
+      <c r="E25" s="8">
+        <v>2.77</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="6">
+        <v>10.89</v>
+      </c>
+      <c r="D26" s="6">
+        <v>9.27</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C24" s="5">
-        <v>-18.16</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C27" s="6">
         <v>-19.42</v>
       </c>
-      <c r="E24" s="6">
-        <v>-1.26</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="D27" s="6">
+        <v>-18.73</v>
+      </c>
+      <c r="E27" s="8">
+        <v>0.6899999999999999</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C25" s="5">
-        <v>-13.01</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C28" s="6">
         <v>-12.04</v>
       </c>
-      <c r="E25" s="7">
-        <v>0.97</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="D28" s="6">
+        <v>-5.02</v>
+      </c>
+      <c r="E28" s="8">
+        <v>7.02</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C26" s="5">
-        <v>-26.27</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C29" s="6">
         <v>-26.39</v>
       </c>
-      <c r="E26" s="6">
-        <v>-0.12</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="D29" s="6">
+        <v>-26.4</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.01</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-7.17</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C30" s="6">
         <v>-8.539999999999999</v>
       </c>
-      <c r="E27" s="6">
-        <v>-1.37</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="D30" s="6">
+        <v>-6.03</v>
+      </c>
+      <c r="E30" s="8">
+        <v>2.51</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="6">
+        <v>-21.27</v>
+      </c>
+      <c r="D31" s="6">
+        <v>-21.82</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-0.55</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C28" s="5">
-        <v>170.53</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C32" s="6">
         <v>167.9</v>
       </c>
-      <c r="E28" s="6">
-        <v>-2.63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="D32" s="6">
+        <v>169.35</v>
+      </c>
+      <c r="E32" s="8">
+        <v>1.45</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C29" s="5">
-        <v>387.35</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C33" s="6">
         <v>391.7</v>
       </c>
-      <c r="E29" s="7">
-        <v>4.35</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="D33" s="6">
+        <v>422.95</v>
+      </c>
+      <c r="E33" s="8">
+        <v>31.25</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C30" s="5">
-        <v>393.7</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C34" s="6">
         <v>393.1</v>
       </c>
-      <c r="E30" s="6">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="D34" s="6">
+        <v>393</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-0.1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C31" s="5">
-        <v>992.6</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C35" s="6">
         <v>978</v>
       </c>
-      <c r="E31" s="6">
-        <v>-14.6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="D35" s="6">
+        <v>1004.8</v>
+      </c>
+      <c r="E35" s="8">
+        <v>26.8</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B36" s="5" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="6">
+        <v>2.85</v>
+      </c>
+      <c r="D36" s="6">
+        <v>2.83</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.02</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B37" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C37" s="6">
+        <v>40</v>
+      </c>
+      <c r="D37" s="6">
+        <v>60</v>
+      </c>
+      <c r="E37" s="8">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>60</v>
+      </c>
+      <c r="D38" s="6">
+        <v>40</v>
+      </c>
+      <c r="E38" s="7">
+        <v>-20</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B39" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C32" s="5">
-        <v>48.55</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C39" s="6">
         <v>44.6</v>
       </c>
-      <c r="E32" s="6">
-        <v>-3.95</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="D39" s="6">
+        <v>47.15</v>
+      </c>
+      <c r="E39" s="8">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B40" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C33" s="5">
-        <v>40.49</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C40" s="6">
         <v>43.82</v>
       </c>
-      <c r="E33" s="7">
-        <v>3.33</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="D40" s="6">
+        <v>60.79</v>
+      </c>
+      <c r="E40" s="8">
+        <v>16.97</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B41" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C34" s="5">
-        <v>31.69</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C41" s="6">
         <v>31.25</v>
       </c>
-      <c r="E34" s="6">
-        <v>-0.44</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="D41" s="6">
+        <v>31.17</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-0.08</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B42" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="C35" s="5">
-        <v>44.29</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C42" s="6">
         <v>39.94</v>
       </c>
-      <c r="E35" s="6">
-        <v>-4.35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="D42" s="6">
+        <v>49.7</v>
+      </c>
+      <c r="E42" s="8">
+        <v>9.76</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>62.86</v>
+      </c>
+      <c r="D43" s="6">
+        <v>61.47</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-1.39</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B44" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C36" s="5">
-        <v>-6.17</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C44" s="6">
         <v>-0.5600000000000001</v>
       </c>
-      <c r="E36" s="7">
-        <v>5.61</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="D44" s="6">
+        <v>-44.9</v>
+      </c>
+      <c r="E44" s="7">
+        <v>-44.34</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B45" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C37" s="5">
-        <v>-85.47</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C45" s="6">
         <v>-84.59999999999999</v>
       </c>
-      <c r="E37" s="7">
-        <v>0.87</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="D45" s="6">
+        <v>4056.8</v>
+      </c>
+      <c r="E45" s="8">
+        <v>4141.4</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B38" s="3" t="s">
+      <c r="B46" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C38" s="5">
-        <v>9.039999999999999</v>
-      </c>
-      <c r="D38" s="5">
+      <c r="C46" s="6">
         <v>-36.47</v>
       </c>
-      <c r="E38" s="6">
-        <v>-45.51</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="D46" s="6">
+        <v>247.59</v>
+      </c>
+      <c r="E46" s="8">
+        <v>284.06</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B39" s="3" t="s">
+      <c r="B47" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="5">
-        <v>68.76000000000001</v>
-      </c>
-      <c r="D39" s="5">
+      <c r="C47" s="6">
         <v>149.05</v>
       </c>
-      <c r="E39" s="7">
-        <v>80.29000000000001</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="D47" s="6">
+        <v>68.04000000000001</v>
+      </c>
+      <c r="E47" s="7">
+        <v>-81.01000000000001</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B40" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C40" s="5">
-        <v>-44.78</v>
-      </c>
-      <c r="D40" s="5">
+      <c r="C48" s="6">
         <v>-61.35</v>
       </c>
-      <c r="E40" s="6">
-        <v>-16.57</v>
+      <c r="D48" s="6">
+        <v>-67.61</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-6.26</v>
       </c>
     </row>
   </sheetData>
@@ -2237,60 +2434,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
-        <v>60</v>
-      </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
+      <c r="A2" s="10" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
+      <c r="B2" s="11">
+        <v>65.92</v>
+      </c>
+      <c r="C2" s="12">
         <v>5</v>
       </c>
-      <c r="D2" s="10">
-        <v>44.5</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>0.3</v>
-      </c>
-      <c r="G2" s="10">
-        <v>5.1</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="D2" s="11">
+        <v>50.1</v>
+      </c>
+      <c r="E2" s="11">
+        <v>80</v>
+      </c>
+      <c r="F2" s="11">
+        <v>1.8</v>
+      </c>
+      <c r="G2" s="11">
+        <v>7.4</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>40</v>
       </c>
     </row>
@@ -2392,37 +2589,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.2499</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.0925</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0116</v>
-      </c>
-      <c r="D2" s="13">
-        <v>-0.0005</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2026</v>
+      <c r="A2" s="14">
+        <v>0.2547</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1079</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0117</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0062</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2048</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -184,16 +184,16 @@
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>43.8 → 60.8</t>
+    <t>49.7 → 50.9</t>
   </si>
   <si>
     <t>🟢 BULLISH</t>
   </si>
   <si>
-    <t>43.8</t>
-  </si>
-  <si>
-    <t>60.8</t>
+    <t>49.7</t>
+  </si>
+  <si>
+    <t>50.9</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -778,8 +778,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -918,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>169.35</v>
+        <v>169</v>
       </c>
       <c r="D2">
-        <v>0.86</v>
+        <v>-0.21</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -930,25 +930,25 @@
         <v>125.02</v>
       </c>
       <c r="G2">
-        <v>-18.73</v>
+        <v>-18.89</v>
       </c>
       <c r="H2">
-        <v>35.46</v>
+        <v>35.18</v>
       </c>
       <c r="I2">
-        <v>-4.54</v>
+        <v>-3.85</v>
       </c>
       <c r="J2">
-        <v>-4.32</v>
+        <v>-4.79</v>
       </c>
       <c r="K2">
-        <v>16.56</v>
+        <v>19.84</v>
       </c>
       <c r="L2">
-        <v>35.45</v>
+        <v>32.72</v>
       </c>
       <c r="M2">
-        <v>25.47</v>
+        <v>25.2</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -957,19 +957,19 @@
         <v>79</v>
       </c>
       <c r="P2">
-        <v>171.84</v>
+        <v>170.48</v>
       </c>
       <c r="Q2">
-        <v>174.39</v>
+        <v>173.97</v>
       </c>
       <c r="R2">
-        <v>165.88</v>
+        <v>166.05</v>
       </c>
       <c r="S2">
-        <v>169.08</v>
+        <v>169.2</v>
       </c>
       <c r="T2">
-        <v>0.16</v>
+        <v>-0.12</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -981,37 +981,37 @@
         <v>44</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>47.15</v>
+        <v>46.6</v>
       </c>
       <c r="Z2">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="AA2">
-        <v>2.94</v>
+        <v>2.58</v>
       </c>
       <c r="AB2">
-        <v>-1.39</v>
+        <v>-1.44</v>
       </c>
       <c r="AC2">
-        <v>4.25</v>
+        <v>7.57</v>
       </c>
       <c r="AD2">
-        <v>4.86</v>
+        <v>5</v>
       </c>
       <c r="AE2">
-        <v>4.4</v>
+        <v>4.45</v>
       </c>
       <c r="AF2">
-        <v>-44.9</v>
+        <v>-13.28</v>
       </c>
       <c r="AG2">
-        <v>180.19</v>
+        <v>180.04</v>
       </c>
       <c r="AH2">
-        <v>168.6</v>
+        <v>167.89</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -1020,7 +1020,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>25.41</v>
+        <v>22.67</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>422.95</v>
+        <v>427.45</v>
       </c>
       <c r="D3">
-        <v>7.98</v>
+        <v>1.06</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1043,46 +1043,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-5.02</v>
+        <v>-4.01</v>
       </c>
       <c r="H3">
-        <v>87.98</v>
+        <v>89.98</v>
       </c>
       <c r="I3">
-        <v>6.44</v>
+        <v>10.1</v>
       </c>
       <c r="J3">
-        <v>2.57</v>
+        <v>4.12</v>
       </c>
       <c r="K3">
-        <v>2.95</v>
+        <v>7.85</v>
       </c>
       <c r="L3">
-        <v>20.19</v>
+        <v>19.42</v>
       </c>
       <c r="M3">
-        <v>10.79</v>
+        <v>11.5</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>396.55</v>
+        <v>404.39</v>
       </c>
       <c r="Q3">
-        <v>406.72</v>
+        <v>406.18</v>
       </c>
       <c r="R3">
-        <v>403.72</v>
+        <v>404.09</v>
       </c>
       <c r="S3">
-        <v>327.68</v>
+        <v>328.23</v>
       </c>
       <c r="T3">
-        <v>29.07</v>
+        <v>30.23</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,43 +1097,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>60.79</v>
+        <v>62.54</v>
       </c>
       <c r="Z3">
-        <v>-1.74</v>
+        <v>0.54</v>
       </c>
       <c r="AA3">
-        <v>-1.94</v>
+        <v>-1.44</v>
       </c>
       <c r="AB3">
-        <v>0.21</v>
+        <v>1.99</v>
       </c>
       <c r="AC3">
-        <v>47.1</v>
+        <v>79.88</v>
       </c>
       <c r="AD3">
-        <v>23.48</v>
+        <v>48.42</v>
       </c>
       <c r="AE3">
-        <v>15.78</v>
+        <v>15.23</v>
       </c>
       <c r="AF3">
-        <v>4056.8</v>
+        <v>-29.42</v>
       </c>
       <c r="AG3">
-        <v>440</v>
+        <v>437.6</v>
       </c>
       <c r="AH3">
-        <v>373.45</v>
+        <v>374.76</v>
       </c>
       <c r="AI3">
-        <v>426.77</v>
+        <v>383.11</v>
       </c>
       <c r="AJ3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK3">
-        <v>35.65</v>
+        <v>38.5</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>393</v>
+        <v>399.25</v>
       </c>
       <c r="D4">
-        <v>-0.03</v>
+        <v>1.59</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1156,46 +1156,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-26.4</v>
+        <v>-25.23</v>
       </c>
       <c r="H4">
-        <v>14.01</v>
+        <v>15.83</v>
       </c>
       <c r="I4">
-        <v>-2.37</v>
+        <v>-0.82</v>
       </c>
       <c r="J4">
-        <v>-7.2</v>
+        <v>-5.63</v>
       </c>
       <c r="K4">
-        <v>-2.77</v>
+        <v>-0.76</v>
       </c>
       <c r="L4">
-        <v>-23.81</v>
+        <v>-23.71</v>
       </c>
       <c r="M4">
-        <v>-20.48</v>
+        <v>-20.43</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="P4">
-        <v>396.58</v>
+        <v>395.92</v>
       </c>
       <c r="Q4">
-        <v>404.99</v>
+        <v>403.53</v>
       </c>
       <c r="R4">
-        <v>415.72</v>
+        <v>415.3</v>
       </c>
       <c r="S4">
-        <v>416.3</v>
+        <v>415.77</v>
       </c>
       <c r="T4">
-        <v>-5.6</v>
+        <v>-3.97</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1210,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.17</v>
+        <v>41</v>
       </c>
       <c r="Z4">
-        <v>-6.46</v>
+        <v>-6.07</v>
       </c>
       <c r="AA4">
-        <v>-5.49</v>
+        <v>-5.61</v>
       </c>
       <c r="AB4">
-        <v>-0.96</v>
+        <v>-0.46</v>
       </c>
       <c r="AC4">
-        <v>0</v>
+        <v>30.04</v>
       </c>
       <c r="AD4">
-        <v>2.31</v>
+        <v>10.01</v>
       </c>
       <c r="AE4">
-        <v>10.93</v>
+        <v>11.43</v>
       </c>
       <c r="AF4">
-        <v>247.59</v>
+        <v>-51.19</v>
       </c>
       <c r="AG4">
-        <v>421.04</v>
+        <v>415.38</v>
       </c>
       <c r="AH4">
-        <v>388.94</v>
+        <v>391.69</v>
       </c>
       <c r="AI4">
         <v>426.99</v>
@@ -1246,7 +1246,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>12.98</v>
+        <v>13.99</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1004.8</v>
+        <v>1008.5</v>
       </c>
       <c r="D5">
-        <v>2.74</v>
+        <v>0.37</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1269,46 +1269,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-6.03</v>
+        <v>-5.69</v>
       </c>
       <c r="H5">
-        <v>40.98</v>
+        <v>41.49</v>
       </c>
       <c r="I5">
-        <v>0.19</v>
+        <v>1.46</v>
       </c>
       <c r="J5">
-        <v>-1.39</v>
+        <v>-0.76</v>
       </c>
       <c r="K5">
-        <v>11.05</v>
+        <v>12.68</v>
       </c>
       <c r="L5">
-        <v>33.47</v>
+        <v>34.25</v>
       </c>
       <c r="M5">
-        <v>0.62</v>
+        <v>0.9399999999999999</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P5">
-        <v>997.2</v>
+        <v>1000.1</v>
       </c>
       <c r="Q5">
-        <v>1010.68</v>
+        <v>1010</v>
       </c>
       <c r="R5">
-        <v>1004.84</v>
+        <v>1006.63</v>
       </c>
       <c r="S5">
-        <v>914.01</v>
+        <v>914.8099999999999</v>
       </c>
       <c r="T5">
-        <v>9.93</v>
+        <v>10.24</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1323,34 +1323,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>49.7</v>
+        <v>50.89</v>
       </c>
       <c r="Z5">
-        <v>-2.58</v>
+        <v>-1.98</v>
       </c>
       <c r="AA5">
-        <v>0.77</v>
+        <v>0.22</v>
       </c>
       <c r="AB5">
-        <v>-3.35</v>
+        <v>-2.2</v>
       </c>
       <c r="AC5">
-        <v>25.27</v>
+        <v>49.4</v>
       </c>
       <c r="AD5">
-        <v>27.68</v>
+        <v>34.52</v>
       </c>
       <c r="AE5">
-        <v>21.41</v>
+        <v>20.64</v>
       </c>
       <c r="AF5">
-        <v>68.04000000000001</v>
+        <v>10.58</v>
       </c>
       <c r="AG5">
-        <v>1035.26</v>
+        <v>1034.01</v>
       </c>
       <c r="AH5">
-        <v>986.1</v>
+        <v>986</v>
       </c>
       <c r="AI5">
         <v>1038.34</v>
@@ -1359,7 +1359,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>15.14</v>
+        <v>13.89</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1373,7 +1373,7 @@
         <v>2.83</v>
       </c>
       <c r="D6">
-        <v>-0.7</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1388,19 +1388,19 @@
         <v>53.8</v>
       </c>
       <c r="I6">
-        <v>-4.39</v>
+        <v>-6.29</v>
       </c>
       <c r="J6">
-        <v>19.41</v>
+        <v>22.51</v>
       </c>
       <c r="K6">
-        <v>9.27</v>
+        <v>12.75</v>
       </c>
       <c r="L6">
-        <v>-15.02</v>
+        <v>-18.21</v>
       </c>
       <c r="M6">
-        <v>1.17</v>
+        <v>1.56</v>
       </c>
       <c r="N6">
         <v>40</v>
@@ -1409,10 +1409,10 @@
         <v>55</v>
       </c>
       <c r="P6">
-        <v>2.88</v>
+        <v>2.84</v>
       </c>
       <c r="Q6">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="R6">
         <v>2.47</v>
@@ -1421,7 +1421,7 @@
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>5.42</v>
+        <v>5.48</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1439,31 +1439,31 @@
         <v>61.47</v>
       </c>
       <c r="Z6">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AA6">
         <v>0.12</v>
       </c>
       <c r="AB6">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>56.8</v>
+        <v>55.85</v>
       </c>
       <c r="AD6">
-        <v>59.91</v>
+        <v>56.63</v>
       </c>
       <c r="AE6">
         <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-67.61</v>
+        <v>-49.62</v>
       </c>
       <c r="AG6">
-        <v>3.26</v>
+        <v>3.28</v>
       </c>
       <c r="AH6">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1472,7 +1472,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>44.78</v>
+        <v>42.22</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1613,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F43"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1653,7 +1653,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1705,13 +1705,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="6">
-        <v>-2.43</v>
+        <v>-4.32</v>
       </c>
       <c r="D7" s="6">
-        <v>-4.32</v>
+        <v>-4.79</v>
       </c>
       <c r="E7" s="7">
-        <v>-1.89</v>
+        <v>-0.47</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1722,13 +1722,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="6">
-        <v>-4.85</v>
+        <v>2.57</v>
       </c>
       <c r="D8" s="6">
-        <v>2.57</v>
+        <v>4.12</v>
       </c>
       <c r="E8" s="8">
-        <v>7.42</v>
+        <v>1.55</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1739,13 +1739,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="6">
-        <v>-6.73</v>
+        <v>-7.2</v>
       </c>
       <c r="D9" s="6">
-        <v>-7.2</v>
-      </c>
-      <c r="E9" s="7">
-        <v>-0.47</v>
+        <v>-5.63</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.57</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1756,13 +1756,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="6">
-        <v>-4.68</v>
+        <v>-1.39</v>
       </c>
       <c r="D10" s="6">
-        <v>-1.39</v>
+        <v>-0.76</v>
       </c>
       <c r="E10" s="8">
-        <v>3.29</v>
+        <v>0.63</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1773,13 +1773,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="6">
-        <v>20.25</v>
+        <v>19.41</v>
       </c>
       <c r="D11" s="6">
-        <v>19.41</v>
-      </c>
-      <c r="E11" s="7">
-        <v>-0.84</v>
+        <v>22.51</v>
+      </c>
+      <c r="E11" s="8">
+        <v>3.1</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1790,13 +1790,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="6">
-        <v>-6.23</v>
+        <v>-4.54</v>
       </c>
       <c r="D12" s="6">
-        <v>-4.54</v>
+        <v>-3.85</v>
       </c>
       <c r="E12" s="8">
-        <v>1.69</v>
+        <v>0.6899999999999999</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1807,13 +1807,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="6">
-        <v>-1.43</v>
+        <v>6.44</v>
       </c>
       <c r="D13" s="6">
-        <v>6.44</v>
+        <v>10.1</v>
       </c>
       <c r="E13" s="8">
-        <v>7.87</v>
+        <v>3.66</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1824,13 +1824,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="6">
-        <v>-2.2</v>
+        <v>-2.37</v>
       </c>
       <c r="D14" s="6">
-        <v>-2.37</v>
-      </c>
-      <c r="E14" s="7">
-        <v>-0.17</v>
+        <v>-0.82</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.55</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1841,13 +1841,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="6">
-        <v>-2.59</v>
+        <v>0.19</v>
       </c>
       <c r="D15" s="6">
-        <v>0.19</v>
+        <v>1.46</v>
       </c>
       <c r="E15" s="8">
-        <v>2.78</v>
+        <v>1.27</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1858,13 +1858,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="6">
-        <v>-5.32</v>
+        <v>-4.39</v>
       </c>
       <c r="D16" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="E16" s="8">
-        <v>0.93</v>
+        <v>-6.29</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.9</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1875,13 +1875,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="6">
-        <v>35.39</v>
+        <v>35.45</v>
       </c>
       <c r="D17" s="6">
-        <v>35.45</v>
-      </c>
-      <c r="E17" s="8">
-        <v>0.06</v>
+        <v>32.72</v>
+      </c>
+      <c r="E17" s="7">
+        <v>-2.73</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1892,13 +1892,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="6">
-        <v>10.2</v>
+        <v>20.19</v>
       </c>
       <c r="D18" s="6">
-        <v>20.19</v>
-      </c>
-      <c r="E18" s="8">
-        <v>9.99</v>
+        <v>19.42</v>
+      </c>
+      <c r="E18" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1909,13 +1909,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="6">
-        <v>-23.28</v>
+        <v>-23.81</v>
       </c>
       <c r="D19" s="6">
-        <v>-23.81</v>
-      </c>
-      <c r="E19" s="7">
-        <v>-0.53</v>
+        <v>-23.71</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.1</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1926,13 +1926,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="6">
-        <v>32.25</v>
+        <v>33.47</v>
       </c>
       <c r="D20" s="6">
-        <v>33.47</v>
+        <v>34.25</v>
       </c>
       <c r="E20" s="8">
-        <v>1.22</v>
+        <v>0.78</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1943,13 +1943,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="6">
-        <v>-14.16</v>
+        <v>-15.02</v>
       </c>
       <c r="D21" s="6">
-        <v>-15.02</v>
+        <v>-18.21</v>
       </c>
       <c r="E21" s="7">
-        <v>-0.86</v>
+        <v>-3.19</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1960,13 +1960,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="6">
-        <v>16.24</v>
+        <v>16.56</v>
       </c>
       <c r="D22" s="6">
-        <v>16.56</v>
+        <v>19.84</v>
       </c>
       <c r="E22" s="8">
-        <v>0.32</v>
+        <v>3.28</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1977,13 +1977,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="6">
-        <v>-6.84</v>
+        <v>2.95</v>
       </c>
       <c r="D23" s="6">
-        <v>2.95</v>
+        <v>7.85</v>
       </c>
       <c r="E23" s="8">
-        <v>9.789999999999999</v>
+        <v>4.9</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1994,13 +1994,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="6">
-        <v>-3.17</v>
+        <v>-2.77</v>
       </c>
       <c r="D24" s="6">
-        <v>-2.77</v>
+        <v>-0.76</v>
       </c>
       <c r="E24" s="8">
-        <v>0.4</v>
+        <v>2.01</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -2011,13 +2011,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="6">
-        <v>8.279999999999999</v>
+        <v>11.05</v>
       </c>
       <c r="D25" s="6">
-        <v>11.05</v>
+        <v>12.68</v>
       </c>
       <c r="E25" s="8">
-        <v>2.77</v>
+        <v>1.63</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -2028,13 +2028,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="6">
-        <v>10.89</v>
+        <v>9.27</v>
       </c>
       <c r="D26" s="6">
-        <v>9.27</v>
-      </c>
-      <c r="E26" s="7">
-        <v>-1.62</v>
+        <v>12.75</v>
+      </c>
+      <c r="E26" s="8">
+        <v>3.48</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -2045,13 +2045,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="6">
-        <v>-19.42</v>
+        <v>-18.73</v>
       </c>
       <c r="D27" s="6">
-        <v>-18.73</v>
-      </c>
-      <c r="E27" s="8">
-        <v>0.6899999999999999</v>
+        <v>-18.89</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-0.16</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -2062,13 +2062,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="6">
-        <v>-12.04</v>
+        <v>-5.02</v>
       </c>
       <c r="D28" s="6">
-        <v>-5.02</v>
+        <v>-4.01</v>
       </c>
       <c r="E28" s="8">
-        <v>7.02</v>
+        <v>1.01</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2079,13 +2079,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="6">
-        <v>-26.39</v>
+        <v>-26.4</v>
       </c>
       <c r="D29" s="6">
-        <v>-26.4</v>
-      </c>
-      <c r="E29" s="7">
-        <v>-0.01</v>
+        <v>-25.23</v>
+      </c>
+      <c r="E29" s="8">
+        <v>1.17</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2096,149 +2096,149 @@
         <v>6</v>
       </c>
       <c r="C30" s="6">
-        <v>-8.539999999999999</v>
+        <v>-6.03</v>
       </c>
       <c r="D30" s="6">
-        <v>-6.03</v>
+        <v>-5.69</v>
       </c>
       <c r="E30" s="8">
-        <v>2.51</v>
+        <v>0.34</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="B31" s="5" t="s">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="C31" s="6">
-        <v>-21.27</v>
+        <v>169.35</v>
       </c>
       <c r="D31" s="6">
-        <v>-21.82</v>
+        <v>169</v>
       </c>
       <c r="E31" s="7">
-        <v>-0.55</v>
+        <v>-0.35</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C32" s="6">
-        <v>167.9</v>
+        <v>422.95</v>
       </c>
       <c r="D32" s="6">
-        <v>169.35</v>
+        <v>427.45</v>
       </c>
       <c r="E32" s="8">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C33" s="6">
-        <v>391.7</v>
+        <v>393</v>
       </c>
       <c r="D33" s="6">
-        <v>422.95</v>
+        <v>399.25</v>
       </c>
       <c r="E33" s="8">
-        <v>31.25</v>
+        <v>6.25</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="6">
-        <v>393.1</v>
+        <v>1004.8</v>
       </c>
       <c r="D34" s="6">
-        <v>393</v>
-      </c>
-      <c r="E34" s="7">
-        <v>-0.1</v>
+        <v>1008.5</v>
+      </c>
+      <c r="E34" s="8">
+        <v>3.7</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="5" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="B35" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C35" s="6">
-        <v>978</v>
+        <v>47.15</v>
       </c>
       <c r="D35" s="6">
-        <v>1004.8</v>
-      </c>
-      <c r="E35" s="8">
-        <v>26.8</v>
+        <v>46.6</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-0.55</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="5" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="B36" s="5" t="s">
-        <v>2</v>
+        <v>24</v>
       </c>
       <c r="C36" s="6">
-        <v>2.85</v>
+        <v>60.79</v>
       </c>
       <c r="D36" s="6">
-        <v>2.83</v>
-      </c>
-      <c r="E36" s="7">
-        <v>-0.02</v>
+        <v>62.54</v>
+      </c>
+      <c r="E36" s="8">
+        <v>1.75</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="5" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="B37" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C37" s="6">
-        <v>40</v>
+        <v>31.17</v>
       </c>
       <c r="D37" s="6">
-        <v>60</v>
+        <v>41</v>
       </c>
       <c r="E37" s="8">
-        <v>20</v>
+        <v>9.83</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B38" s="5" t="s">
-        <v>13</v>
+        <v>24</v>
       </c>
       <c r="C38" s="6">
-        <v>60</v>
+        <v>49.7</v>
       </c>
       <c r="D38" s="6">
-        <v>40</v>
-      </c>
-      <c r="E38" s="7">
-        <v>-20</v>
+        <v>50.89</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.19</v>
       </c>
     </row>
     <row r="39" spans="1:5">
@@ -2246,16 +2246,16 @@
         <v>37</v>
       </c>
       <c r="B39" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C39" s="6">
-        <v>44.6</v>
+        <v>-44.9</v>
       </c>
       <c r="D39" s="6">
-        <v>47.15</v>
+        <v>-13.28</v>
       </c>
       <c r="E39" s="8">
-        <v>2.55</v>
+        <v>31.62</v>
       </c>
     </row>
     <row r="40" spans="1:5">
@@ -2263,16 +2263,16 @@
         <v>38</v>
       </c>
       <c r="B40" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C40" s="6">
-        <v>43.82</v>
+        <v>4056.8</v>
       </c>
       <c r="D40" s="6">
-        <v>60.79</v>
-      </c>
-      <c r="E40" s="8">
-        <v>16.97</v>
+        <v>-29.42</v>
+      </c>
+      <c r="E40" s="7">
+        <v>-4086.22</v>
       </c>
     </row>
     <row r="41" spans="1:5">
@@ -2280,16 +2280,16 @@
         <v>39</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C41" s="6">
-        <v>31.25</v>
+        <v>247.59</v>
       </c>
       <c r="D41" s="6">
-        <v>31.17</v>
+        <v>-51.19</v>
       </c>
       <c r="E41" s="7">
-        <v>-0.08</v>
+        <v>-298.78</v>
       </c>
     </row>
     <row r="42" spans="1:5">
@@ -2297,16 +2297,16 @@
         <v>40</v>
       </c>
       <c r="B42" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C42" s="6">
-        <v>39.94</v>
+        <v>68.04000000000001</v>
       </c>
       <c r="D42" s="6">
-        <v>49.7</v>
-      </c>
-      <c r="E42" s="8">
-        <v>9.76</v>
+        <v>10.58</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-57.46</v>
       </c>
     </row>
     <row r="43" spans="1:5">
@@ -2314,101 +2314,16 @@
         <v>41</v>
       </c>
       <c r="B43" s="5" t="s">
-        <v>24</v>
+        <v>31</v>
       </c>
       <c r="C43" s="6">
-        <v>62.86</v>
+        <v>-67.61</v>
       </c>
       <c r="D43" s="6">
-        <v>61.47</v>
-      </c>
-      <c r="E43" s="7">
-        <v>-1.39</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C44" s="6">
-        <v>-0.5600000000000001</v>
-      </c>
-      <c r="D44" s="6">
-        <v>-44.9</v>
-      </c>
-      <c r="E44" s="7">
-        <v>-44.34</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="6">
-        <v>-84.59999999999999</v>
-      </c>
-      <c r="D45" s="6">
-        <v>4056.8</v>
-      </c>
-      <c r="E45" s="8">
-        <v>4141.4</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="6">
-        <v>-36.47</v>
-      </c>
-      <c r="D46" s="6">
-        <v>247.59</v>
-      </c>
-      <c r="E46" s="8">
-        <v>284.06</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="6">
-        <v>149.05</v>
-      </c>
-      <c r="D47" s="6">
-        <v>68.04000000000001</v>
-      </c>
-      <c r="E47" s="7">
-        <v>-81.01000000000001</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="6">
-        <v>-61.35</v>
-      </c>
-      <c r="D48" s="6">
-        <v>-67.61</v>
-      </c>
-      <c r="E48" s="7">
-        <v>-6.26</v>
+        <v>-49.62</v>
+      </c>
+      <c r="E43" s="8">
+        <v>17.99</v>
       </c>
     </row>
   </sheetData>
@@ -2467,22 +2382,22 @@
         <v>42</v>
       </c>
       <c r="B2" s="11">
-        <v>65.92</v>
+        <v>57.92</v>
       </c>
       <c r="C2" s="12">
         <v>5</v>
       </c>
       <c r="D2" s="11">
-        <v>50.1</v>
+        <v>52.5</v>
       </c>
       <c r="E2" s="11">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F2" s="11">
-        <v>1.8</v>
+        <v>3.1</v>
       </c>
       <c r="G2" s="11">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="H2" s="11">
         <v>59.8</v>
@@ -2607,19 +2522,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="14">
-        <v>0.2547</v>
+        <v>0.252</v>
       </c>
       <c r="B2" s="14">
-        <v>0.1079</v>
+        <v>0.115</v>
       </c>
       <c r="C2" s="14">
-        <v>0.0117</v>
+        <v>0.0156</v>
       </c>
       <c r="D2" s="14">
-        <v>0.0062</v>
+        <v>0.009399999999999999</v>
       </c>
       <c r="E2" s="14">
-        <v>-0.2048</v>
+        <v>-0.2043</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="212" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="76">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,19 +181,34 @@
     <t>Curr Value</t>
   </si>
   <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-4.0% → -1.9%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-4.0%</t>
+  </si>
+  <si>
+    <t>-1.9%</t>
+  </si>
+  <si>
     <t>RSI Momentum</t>
   </si>
   <si>
-    <t>49.7 → 50.9</t>
-  </si>
-  <si>
-    <t>🟢 BULLISH</t>
-  </si>
-  <si>
-    <t>49.7</t>
+    <t>50.9 → 47.5</t>
+  </si>
+  <si>
+    <t>🔴 BEARISH</t>
   </si>
   <si>
     <t>50.9</t>
+  </si>
+  <si>
+    <t>47.5</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -395,7 +410,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -403,10 +418,11 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -778,8 +794,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="17" width="8.7109375" customWidth="1"/>
-    <col min="18" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -918,10 +934,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="D2">
-        <v>-0.21</v>
+        <v>0.59</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -930,25 +946,25 @@
         <v>125.02</v>
       </c>
       <c r="G2">
-        <v>-18.89</v>
+        <v>-18.41</v>
       </c>
       <c r="H2">
-        <v>35.18</v>
+        <v>35.98</v>
       </c>
       <c r="I2">
-        <v>-3.85</v>
+        <v>-3.21</v>
       </c>
       <c r="J2">
-        <v>-4.79</v>
+        <v>-4.23</v>
       </c>
       <c r="K2">
-        <v>19.84</v>
+        <v>18.22</v>
       </c>
       <c r="L2">
-        <v>32.72</v>
+        <v>33.67</v>
       </c>
       <c r="M2">
-        <v>25.2</v>
+        <v>25.57</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -957,19 +973,19 @@
         <v>79</v>
       </c>
       <c r="P2">
-        <v>170.48</v>
+        <v>169.36</v>
       </c>
       <c r="Q2">
-        <v>173.97</v>
+        <v>173.77</v>
       </c>
       <c r="R2">
-        <v>166.05</v>
+        <v>166.3</v>
       </c>
       <c r="S2">
-        <v>169.2</v>
+        <v>169.34</v>
       </c>
       <c r="T2">
-        <v>-0.12</v>
+        <v>0.39</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -981,37 +997,37 @@
         <v>44</v>
       </c>
       <c r="X2">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Y2">
-        <v>46.6</v>
+        <v>48.47</v>
       </c>
       <c r="Z2">
-        <v>1.14</v>
+        <v>0.88</v>
       </c>
       <c r="AA2">
-        <v>2.58</v>
+        <v>2.24</v>
       </c>
       <c r="AB2">
-        <v>-1.44</v>
+        <v>-1.36</v>
       </c>
       <c r="AC2">
-        <v>7.57</v>
+        <v>14.01</v>
       </c>
       <c r="AD2">
-        <v>5</v>
+        <v>8.609999999999999</v>
       </c>
       <c r="AE2">
-        <v>4.45</v>
+        <v>4.4</v>
       </c>
       <c r="AF2">
-        <v>-13.28</v>
+        <v>-32.73</v>
       </c>
       <c r="AG2">
-        <v>180.04</v>
+        <v>180.1</v>
       </c>
       <c r="AH2">
-        <v>167.89</v>
+        <v>167.44</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -1020,7 +1036,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>22.67</v>
+        <v>20.29</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1031,10 +1047,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>427.45</v>
+        <v>436.95</v>
       </c>
       <c r="D3">
-        <v>1.06</v>
+        <v>2.22</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1043,25 +1059,25 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-4.01</v>
+        <v>-1.88</v>
       </c>
       <c r="H3">
-        <v>89.98</v>
+        <v>94.2</v>
       </c>
       <c r="I3">
-        <v>10.1</v>
+        <v>11.32</v>
       </c>
       <c r="J3">
-        <v>4.12</v>
+        <v>-0.3</v>
       </c>
       <c r="K3">
-        <v>7.85</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="L3">
-        <v>19.42</v>
+        <v>20.01</v>
       </c>
       <c r="M3">
-        <v>11.5</v>
+        <v>12.39</v>
       </c>
       <c r="N3">
         <v>60</v>
@@ -1070,19 +1086,19 @@
         <v>70</v>
       </c>
       <c r="P3">
-        <v>404.39</v>
+        <v>413.28</v>
       </c>
       <c r="Q3">
-        <v>406.18</v>
+        <v>406.62</v>
       </c>
       <c r="R3">
-        <v>404.09</v>
+        <v>404.76</v>
       </c>
       <c r="S3">
-        <v>328.23</v>
+        <v>328.78</v>
       </c>
       <c r="T3">
-        <v>30.23</v>
+        <v>32.9</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1097,43 +1113,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>62.54</v>
+        <v>66</v>
       </c>
       <c r="Z3">
-        <v>0.54</v>
+        <v>3.08</v>
       </c>
       <c r="AA3">
-        <v>-1.44</v>
+        <v>-0.54</v>
       </c>
       <c r="AB3">
-        <v>1.99</v>
+        <v>3.62</v>
       </c>
       <c r="AC3">
-        <v>79.88</v>
+        <v>100</v>
       </c>
       <c r="AD3">
-        <v>48.42</v>
+        <v>75.66</v>
       </c>
       <c r="AE3">
-        <v>15.23</v>
+        <v>15.08</v>
       </c>
       <c r="AF3">
-        <v>-29.42</v>
+        <v>-58.95</v>
       </c>
       <c r="AG3">
-        <v>437.6</v>
+        <v>439.54</v>
       </c>
       <c r="AH3">
-        <v>374.76</v>
+        <v>373.7</v>
       </c>
       <c r="AI3">
-        <v>383.11</v>
+        <v>387.65</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>38.5</v>
+        <v>41.73</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1144,10 +1160,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>399.25</v>
+        <v>395.55</v>
       </c>
       <c r="D4">
-        <v>1.59</v>
+        <v>-0.93</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1156,46 +1172,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-25.23</v>
+        <v>-25.93</v>
       </c>
       <c r="H4">
-        <v>15.83</v>
+        <v>14.75</v>
       </c>
       <c r="I4">
-        <v>-0.82</v>
+        <v>-1.25</v>
       </c>
       <c r="J4">
-        <v>-5.63</v>
+        <v>-7.67</v>
       </c>
       <c r="K4">
-        <v>-0.76</v>
+        <v>-1.17</v>
       </c>
       <c r="L4">
-        <v>-23.71</v>
+        <v>-24.45</v>
       </c>
       <c r="M4">
-        <v>-20.43</v>
+        <v>-20.6</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>395.92</v>
+        <v>394.92</v>
       </c>
       <c r="Q4">
-        <v>403.53</v>
+        <v>402.68</v>
       </c>
       <c r="R4">
-        <v>415.3</v>
+        <v>414.9</v>
       </c>
       <c r="S4">
-        <v>415.77</v>
+        <v>415.18</v>
       </c>
       <c r="T4">
-        <v>-3.97</v>
+        <v>-4.73</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1210,34 +1226,34 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>41</v>
+        <v>37.58</v>
       </c>
       <c r="Z4">
-        <v>-6.07</v>
+        <v>-5.99</v>
       </c>
       <c r="AA4">
-        <v>-5.61</v>
+        <v>-5.68</v>
       </c>
       <c r="AB4">
-        <v>-0.46</v>
+        <v>-0.3</v>
       </c>
       <c r="AC4">
-        <v>30.04</v>
+        <v>49.62</v>
       </c>
       <c r="AD4">
-        <v>10.01</v>
+        <v>26.55</v>
       </c>
       <c r="AE4">
-        <v>11.43</v>
+        <v>11.04</v>
       </c>
       <c r="AF4">
-        <v>-51.19</v>
+        <v>-66.09</v>
       </c>
       <c r="AG4">
-        <v>415.38</v>
+        <v>414.25</v>
       </c>
       <c r="AH4">
-        <v>391.69</v>
+        <v>391.12</v>
       </c>
       <c r="AI4">
         <v>426.99</v>
@@ -1246,7 +1262,7 @@
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>13.99</v>
+        <v>14.87</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1257,10 +1273,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1008.5</v>
+        <v>998</v>
       </c>
       <c r="D5">
-        <v>0.37</v>
+        <v>-1.04</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1269,46 +1285,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-5.69</v>
+        <v>-6.67</v>
       </c>
       <c r="H5">
-        <v>41.49</v>
+        <v>40.02</v>
       </c>
       <c r="I5">
-        <v>1.46</v>
+        <v>-1.83</v>
       </c>
       <c r="J5">
-        <v>-0.76</v>
+        <v>-2.35</v>
       </c>
       <c r="K5">
-        <v>12.68</v>
+        <v>8.15</v>
       </c>
       <c r="L5">
-        <v>34.25</v>
+        <v>29.93</v>
       </c>
       <c r="M5">
-        <v>0.9399999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="P5">
-        <v>1000.1</v>
+        <v>996.38</v>
       </c>
       <c r="Q5">
-        <v>1010</v>
+        <v>1008.54</v>
       </c>
       <c r="R5">
-        <v>1006.63</v>
+        <v>1008.28</v>
       </c>
       <c r="S5">
-        <v>914.8099999999999</v>
+        <v>915.61</v>
       </c>
       <c r="T5">
-        <v>10.24</v>
+        <v>9</v>
       </c>
       <c r="U5" t="s">
         <v>43</v>
@@ -1323,34 +1339,34 @@
         <v>3</v>
       </c>
       <c r="Y5">
-        <v>50.89</v>
+        <v>47.47</v>
       </c>
       <c r="Z5">
-        <v>-1.98</v>
+        <v>-2.32</v>
       </c>
       <c r="AA5">
-        <v>0.22</v>
+        <v>-0.29</v>
       </c>
       <c r="AB5">
-        <v>-2.2</v>
+        <v>-2.03</v>
       </c>
       <c r="AC5">
-        <v>49.4</v>
+        <v>67.92</v>
       </c>
       <c r="AD5">
-        <v>34.52</v>
+        <v>47.53</v>
       </c>
       <c r="AE5">
-        <v>20.64</v>
+        <v>20.8</v>
       </c>
       <c r="AF5">
-        <v>10.58</v>
+        <v>16.22</v>
       </c>
       <c r="AG5">
-        <v>1034.01</v>
+        <v>1031.66</v>
       </c>
       <c r="AH5">
-        <v>986</v>
+        <v>985.42</v>
       </c>
       <c r="AI5">
         <v>1038.34</v>
@@ -1359,7 +1375,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>13.89</v>
+        <v>14.59</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1370,10 +1386,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.83</v>
+        <v>2.98</v>
       </c>
       <c r="D6">
-        <v>0</v>
+        <v>5.3</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1382,46 +1398,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-21.82</v>
+        <v>-17.68</v>
       </c>
       <c r="H6">
-        <v>53.8</v>
+        <v>61.96</v>
       </c>
       <c r="I6">
-        <v>-6.29</v>
+        <v>5.3</v>
       </c>
       <c r="J6">
-        <v>22.51</v>
+        <v>28.45</v>
       </c>
       <c r="K6">
-        <v>12.75</v>
+        <v>16.41</v>
       </c>
       <c r="L6">
-        <v>-18.21</v>
+        <v>-13.62</v>
       </c>
       <c r="M6">
-        <v>1.56</v>
+        <v>3.17</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>55</v>
+        <v>64</v>
       </c>
       <c r="P6">
-        <v>2.84</v>
+        <v>2.87</v>
       </c>
       <c r="Q6">
-        <v>2.64</v>
+        <v>2.67</v>
       </c>
       <c r="R6">
-        <v>2.47</v>
+        <v>2.49</v>
       </c>
       <c r="S6">
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>5.48</v>
+        <v>11.1</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1436,34 +1452,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>61.47</v>
+        <v>67.7</v>
       </c>
       <c r="Z6">
+        <v>0.14</v>
+      </c>
+      <c r="AA6">
         <v>0.13</v>
-      </c>
-      <c r="AA6">
-        <v>0.12</v>
       </c>
       <c r="AB6">
         <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>55.85</v>
+        <v>59.12</v>
       </c>
       <c r="AD6">
-        <v>56.63</v>
+        <v>57.26</v>
       </c>
       <c r="AE6">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>-49.62</v>
+        <v>9.24</v>
       </c>
       <c r="AG6">
-        <v>3.28</v>
+        <v>3.31</v>
       </c>
       <c r="AH6">
-        <v>2</v>
+        <v>2.03</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1472,7 +1488,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>42.22</v>
+        <v>43.58</v>
       </c>
     </row>
   </sheetData>
@@ -1613,7 +1629,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F43"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1653,7 +1669,7 @@
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="4" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B3" s="4" t="s">
         <v>53</v>
@@ -1671,665 +1687,736 @@
         <v>57</v>
       </c>
     </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="2" t="s">
+    <row r="4" spans="1:6">
+      <c r="A4" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="2"/>
-      <c r="E5" s="2"/>
+      <c r="C4" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>60</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>61</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="3" t="s">
+      <c r="A6" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="3" t="s">
-        <v>59</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="E6" s="3" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="5" t="s">
+      <c r="B7" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="D7" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>67</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B8" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="6">
+      <c r="C8" s="7">
+        <v>-4.79</v>
+      </c>
+      <c r="D8" s="7">
+        <v>-4.23</v>
+      </c>
+      <c r="E8" s="8">
+        <v>0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="A9" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="7">
+        <v>4.12</v>
+      </c>
+      <c r="D9" s="7">
+        <v>-0.3</v>
+      </c>
+      <c r="E9" s="9">
+        <v>-4.42</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B10" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="7">
+        <v>-5.63</v>
+      </c>
+      <c r="D10" s="7">
+        <v>-7.67</v>
+      </c>
+      <c r="E10" s="9">
+        <v>-2.04</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B11" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="7">
+        <v>-0.76</v>
+      </c>
+      <c r="D11" s="7">
+        <v>-2.35</v>
+      </c>
+      <c r="E11" s="9">
+        <v>-1.59</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B12" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="C12" s="7">
+        <v>22.51</v>
+      </c>
+      <c r="D12" s="7">
+        <v>28.45</v>
+      </c>
+      <c r="E12" s="8">
+        <v>5.94</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B13" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="7">
+        <v>-3.85</v>
+      </c>
+      <c r="D13" s="7">
+        <v>-3.21</v>
+      </c>
+      <c r="E13" s="8">
+        <v>0.64</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B14" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="7">
+        <v>10.1</v>
+      </c>
+      <c r="D14" s="7">
+        <v>11.32</v>
+      </c>
+      <c r="E14" s="8">
+        <v>1.22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B15" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="7">
+        <v>-0.82</v>
+      </c>
+      <c r="D15" s="7">
+        <v>-1.25</v>
+      </c>
+      <c r="E15" s="9">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B16" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="7">
+        <v>1.46</v>
+      </c>
+      <c r="D16" s="7">
+        <v>-1.83</v>
+      </c>
+      <c r="E16" s="9">
+        <v>-3.29</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B17" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="C17" s="7">
+        <v>-6.29</v>
+      </c>
+      <c r="D17" s="7">
+        <v>5.3</v>
+      </c>
+      <c r="E17" s="8">
+        <v>11.59</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B18" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="7">
+        <v>32.72</v>
+      </c>
+      <c r="D18" s="7">
+        <v>33.67</v>
+      </c>
+      <c r="E18" s="8">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="7">
+        <v>19.42</v>
+      </c>
+      <c r="D19" s="7">
+        <v>20.01</v>
+      </c>
+      <c r="E19" s="8">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="6" t="s">
+        <v>39</v>
+      </c>
+      <c r="B20" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="7">
+        <v>-23.71</v>
+      </c>
+      <c r="D20" s="7">
+        <v>-24.45</v>
+      </c>
+      <c r="E20" s="9">
+        <v>-0.74</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="B21" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="7">
+        <v>34.25</v>
+      </c>
+      <c r="D21" s="7">
+        <v>29.93</v>
+      </c>
+      <c r="E21" s="9">
         <v>-4.32</v>
       </c>
-      <c r="D7" s="6">
-        <v>-4.79</v>
-      </c>
-      <c r="E7" s="7">
-        <v>-0.47</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="5" t="s">
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B22" s="6" t="s">
+        <v>11</v>
+      </c>
+      <c r="C22" s="7">
+        <v>-18.21</v>
+      </c>
+      <c r="D22" s="7">
+        <v>-13.62</v>
+      </c>
+      <c r="E22" s="8">
+        <v>4.59</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="B23" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="7">
+        <v>19.84</v>
+      </c>
+      <c r="D23" s="7">
+        <v>18.22</v>
+      </c>
+      <c r="E23" s="9">
+        <v>-1.62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="6">
-        <v>2.57</v>
-      </c>
-      <c r="D8" s="6">
-        <v>4.12</v>
-      </c>
-      <c r="E8" s="8">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9" s="5" t="s">
+      <c r="B24" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="7">
+        <v>7.85</v>
+      </c>
+      <c r="D24" s="7">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="E24" s="8">
+        <v>1.7</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="6">
-        <v>-7.2</v>
-      </c>
-      <c r="D9" s="6">
-        <v>-5.63</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.57</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="5" t="s">
+      <c r="B25" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="7">
+        <v>-0.76</v>
+      </c>
+      <c r="D25" s="7">
+        <v>-1.17</v>
+      </c>
+      <c r="E25" s="9">
+        <v>-0.41</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="6">
-        <v>-1.39</v>
-      </c>
-      <c r="D10" s="6">
-        <v>-0.76</v>
-      </c>
-      <c r="E10" s="8">
-        <v>0.63</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="5" t="s">
+      <c r="B26" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="7">
+        <v>12.68</v>
+      </c>
+      <c r="D26" s="7">
+        <v>8.15</v>
+      </c>
+      <c r="E26" s="9">
+        <v>-4.53</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="6">
-        <v>19.41</v>
-      </c>
-      <c r="D11" s="6">
-        <v>22.51</v>
-      </c>
-      <c r="E11" s="8">
-        <v>3.1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="5" t="s">
+      <c r="B27" s="6" t="s">
+        <v>10</v>
+      </c>
+      <c r="C27" s="7">
+        <v>12.75</v>
+      </c>
+      <c r="D27" s="7">
+        <v>16.41</v>
+      </c>
+      <c r="E27" s="8">
+        <v>3.66</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C12" s="6">
-        <v>-4.54</v>
-      </c>
-      <c r="D12" s="6">
-        <v>-3.85</v>
-      </c>
-      <c r="E12" s="8">
-        <v>0.6899999999999999</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="5" t="s">
+      <c r="B28" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="7">
+        <v>-18.89</v>
+      </c>
+      <c r="D28" s="7">
+        <v>-18.41</v>
+      </c>
+      <c r="E28" s="8">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C13" s="6">
-        <v>6.44</v>
-      </c>
-      <c r="D13" s="6">
-        <v>10.1</v>
-      </c>
-      <c r="E13" s="8">
-        <v>3.66</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="5" t="s">
+      <c r="B29" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="7">
+        <v>-4.01</v>
+      </c>
+      <c r="D29" s="7">
+        <v>-1.88</v>
+      </c>
+      <c r="E29" s="8">
+        <v>2.13</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="6">
-        <v>-2.37</v>
-      </c>
-      <c r="D14" s="6">
-        <v>-0.82</v>
-      </c>
-      <c r="E14" s="8">
-        <v>1.55</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="5" t="s">
+      <c r="B30" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="7">
+        <v>-25.23</v>
+      </c>
+      <c r="D30" s="7">
+        <v>-25.93</v>
+      </c>
+      <c r="E30" s="9">
+        <v>-0.7</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="6">
-        <v>0.19</v>
-      </c>
-      <c r="D15" s="6">
-        <v>1.46</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.27</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="5" t="s">
+      <c r="B31" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="7">
+        <v>-5.69</v>
+      </c>
+      <c r="D31" s="7">
+        <v>-6.67</v>
+      </c>
+      <c r="E31" s="9">
+        <v>-0.98</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="6">
-        <v>-4.39</v>
-      </c>
-      <c r="D16" s="6">
-        <v>-6.29</v>
-      </c>
-      <c r="E16" s="7">
-        <v>-1.9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
+      <c r="B32" s="6" t="s">
+        <v>6</v>
+      </c>
+      <c r="C32" s="7">
+        <v>-21.82</v>
+      </c>
+      <c r="D32" s="7">
+        <v>-17.68</v>
+      </c>
+      <c r="E32" s="8">
+        <v>4.14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C17" s="6">
-        <v>35.45</v>
-      </c>
-      <c r="D17" s="6">
-        <v>32.72</v>
-      </c>
-      <c r="E17" s="7">
-        <v>-2.73</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
+      <c r="B33" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="7">
+        <v>169</v>
+      </c>
+      <c r="D33" s="7">
+        <v>170</v>
+      </c>
+      <c r="E33" s="8">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C18" s="6">
-        <v>20.19</v>
-      </c>
-      <c r="D18" s="6">
-        <v>19.42</v>
-      </c>
-      <c r="E18" s="7">
-        <v>-0.77</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
+      <c r="B34" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="7">
+        <v>427.45</v>
+      </c>
+      <c r="D34" s="7">
+        <v>436.95</v>
+      </c>
+      <c r="E34" s="8">
+        <v>9.5</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="6">
-        <v>-23.81</v>
-      </c>
-      <c r="D19" s="6">
-        <v>-23.71</v>
-      </c>
-      <c r="E19" s="8">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="5" t="s">
+      <c r="B35" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="7">
+        <v>399.25</v>
+      </c>
+      <c r="D35" s="7">
+        <v>395.55</v>
+      </c>
+      <c r="E35" s="9">
+        <v>-3.7</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="6">
-        <v>33.47</v>
-      </c>
-      <c r="D20" s="6">
-        <v>34.25</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.78</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
+      <c r="B36" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="7">
+        <v>1008.5</v>
+      </c>
+      <c r="D36" s="7">
+        <v>998</v>
+      </c>
+      <c r="E36" s="9">
+        <v>-10.5</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="5" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="6">
-        <v>-15.02</v>
-      </c>
-      <c r="D21" s="6">
-        <v>-18.21</v>
-      </c>
-      <c r="E21" s="7">
-        <v>-3.19</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="5" t="s">
+      <c r="B37" s="6" t="s">
+        <v>2</v>
+      </c>
+      <c r="C37" s="7">
+        <v>2.83</v>
+      </c>
+      <c r="D37" s="7">
+        <v>2.98</v>
+      </c>
+      <c r="E37" s="8">
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C22" s="6">
-        <v>16.56</v>
-      </c>
-      <c r="D22" s="6">
-        <v>19.84</v>
-      </c>
-      <c r="E22" s="8">
-        <v>3.28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
+      <c r="B38" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="7">
+        <v>46.6</v>
+      </c>
+      <c r="D38" s="7">
+        <v>48.47</v>
+      </c>
+      <c r="E38" s="8">
+        <v>1.87</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C23" s="6">
-        <v>2.95</v>
-      </c>
-      <c r="D23" s="6">
-        <v>7.85</v>
-      </c>
-      <c r="E23" s="8">
-        <v>4.9</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="5" t="s">
+      <c r="B39" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="7">
+        <v>62.54</v>
+      </c>
+      <c r="D39" s="7">
+        <v>66</v>
+      </c>
+      <c r="E39" s="8">
+        <v>3.46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="6">
-        <v>-2.77</v>
-      </c>
-      <c r="D24" s="6">
-        <v>-0.76</v>
-      </c>
-      <c r="E24" s="8">
-        <v>2.01</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
+      <c r="B40" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="7">
+        <v>41</v>
+      </c>
+      <c r="D40" s="7">
+        <v>37.58</v>
+      </c>
+      <c r="E40" s="9">
+        <v>-3.42</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="6">
-        <v>11.05</v>
-      </c>
-      <c r="D25" s="6">
-        <v>12.68</v>
-      </c>
-      <c r="E25" s="8">
-        <v>1.63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="5" t="s">
+      <c r="B41" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="7">
+        <v>50.89</v>
+      </c>
+      <c r="D41" s="7">
+        <v>47.47</v>
+      </c>
+      <c r="E41" s="9">
+        <v>-3.42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="6">
-        <v>9.27</v>
-      </c>
-      <c r="D26" s="6">
-        <v>12.75</v>
-      </c>
-      <c r="E26" s="8">
-        <v>3.48</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="7">
+        <v>61.47</v>
+      </c>
+      <c r="D42" s="7">
+        <v>67.7</v>
+      </c>
+      <c r="E42" s="8">
+        <v>6.23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C27" s="6">
-        <v>-18.73</v>
-      </c>
-      <c r="D27" s="6">
-        <v>-18.89</v>
-      </c>
-      <c r="E27" s="7">
-        <v>-0.16</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="5" t="s">
+      <c r="B43" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="7">
+        <v>-13.28</v>
+      </c>
+      <c r="D43" s="7">
+        <v>-32.73</v>
+      </c>
+      <c r="E43" s="9">
+        <v>-19.45</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C28" s="6">
-        <v>-5.02</v>
-      </c>
-      <c r="D28" s="6">
-        <v>-4.01</v>
-      </c>
-      <c r="E28" s="8">
-        <v>1.01</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="5" t="s">
+      <c r="B44" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="7">
+        <v>-29.42</v>
+      </c>
+      <c r="D44" s="7">
+        <v>-58.95</v>
+      </c>
+      <c r="E44" s="9">
+        <v>-29.53</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="6" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="6">
-        <v>-26.4</v>
-      </c>
-      <c r="D29" s="6">
-        <v>-25.23</v>
-      </c>
-      <c r="E29" s="8">
-        <v>1.17</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="5" t="s">
+      <c r="B45" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="7">
+        <v>-51.19</v>
+      </c>
+      <c r="D45" s="7">
+        <v>-66.09</v>
+      </c>
+      <c r="E45" s="9">
+        <v>-14.9</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="6">
-        <v>-6.03</v>
-      </c>
-      <c r="D30" s="6">
-        <v>-5.69</v>
-      </c>
-      <c r="E30" s="8">
-        <v>0.34</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C31" s="6">
-        <v>169.35</v>
-      </c>
-      <c r="D31" s="6">
-        <v>169</v>
-      </c>
-      <c r="E31" s="7">
-        <v>-0.35</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B32" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C32" s="6">
-        <v>422.95</v>
-      </c>
-      <c r="D32" s="6">
-        <v>427.45</v>
-      </c>
-      <c r="E32" s="8">
-        <v>4.5</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B33" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C33" s="6">
-        <v>393</v>
-      </c>
-      <c r="D33" s="6">
-        <v>399.25</v>
-      </c>
-      <c r="E33" s="8">
-        <v>6.25</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B34" s="5" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="6">
-        <v>1004.8</v>
-      </c>
-      <c r="D34" s="6">
-        <v>1008.5</v>
-      </c>
-      <c r="E34" s="8">
-        <v>3.7</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B35" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C35" s="6">
-        <v>47.15</v>
-      </c>
-      <c r="D35" s="6">
-        <v>46.6</v>
-      </c>
-      <c r="E35" s="7">
-        <v>-0.55</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B36" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="6">
-        <v>60.79</v>
-      </c>
-      <c r="D36" s="6">
-        <v>62.54</v>
-      </c>
-      <c r="E36" s="8">
-        <v>1.75</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B37" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C37" s="6">
-        <v>31.17</v>
-      </c>
-      <c r="D37" s="6">
+      <c r="B46" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="7">
+        <v>10.58</v>
+      </c>
+      <c r="D46" s="7">
+        <v>16.22</v>
+      </c>
+      <c r="E46" s="8">
+        <v>5.64</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="E37" s="8">
-        <v>9.83</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B38" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C38" s="6">
-        <v>49.7</v>
-      </c>
-      <c r="D38" s="6">
-        <v>50.89</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.19</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="B39" s="5" t="s">
+      <c r="B47" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="C39" s="6">
-        <v>-44.9</v>
-      </c>
-      <c r="D39" s="6">
-        <v>-13.28</v>
-      </c>
-      <c r="E39" s="8">
-        <v>31.62</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="B40" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C40" s="6">
-        <v>4056.8</v>
-      </c>
-      <c r="D40" s="6">
-        <v>-29.42</v>
-      </c>
-      <c r="E40" s="7">
-        <v>-4086.22</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="B41" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C41" s="6">
-        <v>247.59</v>
-      </c>
-      <c r="D41" s="6">
-        <v>-51.19</v>
-      </c>
-      <c r="E41" s="7">
-        <v>-298.78</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B42" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C42" s="6">
-        <v>68.04000000000001</v>
-      </c>
-      <c r="D42" s="6">
-        <v>10.58</v>
-      </c>
-      <c r="E42" s="7">
-        <v>-57.46</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B43" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C43" s="6">
-        <v>-67.61</v>
-      </c>
-      <c r="D43" s="6">
+      <c r="C47" s="7">
         <v>-49.62</v>
       </c>
-      <c r="E43" s="8">
-        <v>17.99</v>
+      <c r="D47" s="7">
+        <v>9.24</v>
+      </c>
+      <c r="E47" s="8">
+        <v>58.86</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A5:E5"/>
+    <mergeCell ref="A6:E6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2349,60 +2436,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="9" t="s">
+      <c r="A1" s="10" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C1" s="9" t="s">
-        <v>64</v>
-      </c>
-      <c r="D1" s="9" t="s">
-        <v>65</v>
-      </c>
-      <c r="E1" s="9" t="s">
-        <v>66</v>
-      </c>
-      <c r="F1" s="9" t="s">
-        <v>67</v>
-      </c>
-      <c r="G1" s="9" t="s">
+      <c r="B1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="H1" s="9" t="s">
+      <c r="C1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="I1" s="9" t="s">
+      <c r="D1" s="10" t="s">
         <v>70</v>
       </c>
+      <c r="E1" s="10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F1" s="10" t="s">
+        <v>72</v>
+      </c>
+      <c r="G1" s="10" t="s">
+        <v>73</v>
+      </c>
+      <c r="H1" s="10" t="s">
+        <v>74</v>
+      </c>
+      <c r="I1" s="10" t="s">
+        <v>75</v>
+      </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="10" t="s">
+      <c r="A2" s="11" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="11">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="12">
+      <c r="B2" s="12">
+        <v>65.92</v>
+      </c>
+      <c r="C2" s="13">
         <v>5</v>
       </c>
-      <c r="D2" s="11">
-        <v>52.5</v>
-      </c>
-      <c r="E2" s="11">
-        <v>60</v>
-      </c>
-      <c r="F2" s="11">
-        <v>3.1</v>
-      </c>
-      <c r="G2" s="11">
-        <v>10.5</v>
-      </c>
-      <c r="H2" s="11">
+      <c r="D2" s="12">
+        <v>53.4</v>
+      </c>
+      <c r="E2" s="12">
+        <v>80</v>
+      </c>
+      <c r="F2" s="12">
+        <v>2.8</v>
+      </c>
+      <c r="G2" s="12">
+        <v>10.2</v>
+      </c>
+      <c r="H2" s="12">
         <v>59.8</v>
       </c>
-      <c r="I2" s="11">
+      <c r="I2" s="12">
         <v>40</v>
       </c>
     </row>
@@ -2504,37 +2591,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="13" t="s">
+      <c r="A1" s="14" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="13" t="s">
+      <c r="B1" s="14" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="13" t="s">
+      <c r="C1" s="14" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="13" t="s">
+      <c r="D1" s="14" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="13" t="s">
+      <c r="E1" s="14" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="14">
-        <v>0.252</v>
-      </c>
-      <c r="B2" s="14">
-        <v>0.115</v>
-      </c>
-      <c r="C2" s="14">
-        <v>0.0156</v>
-      </c>
-      <c r="D2" s="14">
-        <v>0.009399999999999999</v>
-      </c>
-      <c r="E2" s="14">
-        <v>-0.2043</v>
+      <c r="A2" s="15">
+        <v>0.2557</v>
+      </c>
+      <c r="B2" s="15">
+        <v>0.1239</v>
+      </c>
+      <c r="C2" s="15">
+        <v>0.0317</v>
+      </c>
+      <c r="D2" s="15">
+        <v>0.0054</v>
+      </c>
+      <c r="E2" s="15">
+        <v>-0.206</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="224" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="74">
   <si>
     <t>Symbol</t>
   </si>
@@ -181,34 +181,28 @@
     <t>Curr Value</t>
   </si>
   <si>
-    <t>Near 52W High</t>
-  </si>
-  <si>
-    <t>-4.0% → -1.9%</t>
-  </si>
-  <si>
-    <t>🟢 BREAKOUT WATCH</t>
-  </si>
-  <si>
-    <t>-4.0%</t>
+    <t>Left 52W High Zone</t>
+  </si>
+  <si>
+    <t>-1.9% → -2.2%</t>
+  </si>
+  <si>
+    <t>⚪ NEUTRAL</t>
   </si>
   <si>
     <t>-1.9%</t>
   </si>
   <si>
-    <t>RSI Momentum</t>
-  </si>
-  <si>
-    <t>50.9 → 47.5</t>
+    <t>-2.2%</t>
+  </si>
+  <si>
+    <t>Yes → No</t>
   </si>
   <si>
     <t>🔴 BEARISH</t>
   </si>
   <si>
-    <t>50.9</t>
-  </si>
-  <si>
-    <t>47.5</t>
+    <t>20 DMA &gt; 50 DMA</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -260,7 +254,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -294,7 +288,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF1F4E79"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -306,8 +300,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -334,13 +335,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -421,12 +428,12 @@
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -435,7 +442,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -934,37 +941,37 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="D2">
-        <v>0.59</v>
+        <v>-0.59</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>125.02</v>
+        <v>127.71</v>
       </c>
       <c r="G2">
-        <v>-18.41</v>
+        <v>-18.89</v>
       </c>
       <c r="H2">
-        <v>35.98</v>
+        <v>32.33</v>
       </c>
       <c r="I2">
-        <v>-3.21</v>
+        <v>-0.9</v>
       </c>
       <c r="J2">
-        <v>-4.23</v>
+        <v>-2.87</v>
       </c>
       <c r="K2">
-        <v>18.22</v>
+        <v>19.4</v>
       </c>
       <c r="L2">
-        <v>33.67</v>
+        <v>35.18</v>
       </c>
       <c r="M2">
-        <v>25.57</v>
+        <v>25.19</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -973,19 +980,19 @@
         <v>79</v>
       </c>
       <c r="P2">
-        <v>169.36</v>
+        <v>169.05</v>
       </c>
       <c r="Q2">
-        <v>173.77</v>
+        <v>173.48</v>
       </c>
       <c r="R2">
-        <v>166.3</v>
+        <v>166.53</v>
       </c>
       <c r="S2">
-        <v>169.34</v>
+        <v>169.47</v>
       </c>
       <c r="T2">
-        <v>0.39</v>
+        <v>-0.27</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -997,37 +1004,37 @@
         <v>44</v>
       </c>
       <c r="X2">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="Y2">
-        <v>48.47</v>
+        <v>46.71</v>
       </c>
       <c r="Z2">
-        <v>0.88</v>
+        <v>0.59</v>
       </c>
       <c r="AA2">
-        <v>2.24</v>
+        <v>1.91</v>
       </c>
       <c r="AB2">
-        <v>-1.36</v>
+        <v>-1.32</v>
       </c>
       <c r="AC2">
-        <v>14.01</v>
+        <v>13.27</v>
       </c>
       <c r="AD2">
-        <v>8.609999999999999</v>
+        <v>11.62</v>
       </c>
       <c r="AE2">
-        <v>4.4</v>
+        <v>4.26</v>
       </c>
       <c r="AF2">
-        <v>-32.73</v>
+        <v>-48.28</v>
       </c>
       <c r="AG2">
-        <v>180.1</v>
+        <v>180.13</v>
       </c>
       <c r="AH2">
-        <v>167.44</v>
+        <v>166.83</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -1036,7 +1043,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>20.29</v>
+        <v>18.82</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1047,10 +1054,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>436.95</v>
+        <v>435.6</v>
       </c>
       <c r="D3">
-        <v>2.22</v>
+        <v>-0.31</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1059,46 +1066,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-1.88</v>
+        <v>-2.18</v>
       </c>
       <c r="H3">
-        <v>94.2</v>
+        <v>93.59999999999999</v>
       </c>
       <c r="I3">
-        <v>11.32</v>
+        <v>12.46</v>
       </c>
       <c r="J3">
-        <v>-0.3</v>
+        <v>1.73</v>
       </c>
       <c r="K3">
-        <v>9.550000000000001</v>
+        <v>12.78</v>
       </c>
       <c r="L3">
-        <v>20.01</v>
+        <v>20.63</v>
       </c>
       <c r="M3">
-        <v>12.39</v>
+        <v>12.08</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="P3">
-        <v>413.28</v>
+        <v>422.93</v>
       </c>
       <c r="Q3">
-        <v>406.62</v>
+        <v>406.92</v>
       </c>
       <c r="R3">
-        <v>404.76</v>
+        <v>405.31</v>
       </c>
       <c r="S3">
-        <v>328.78</v>
+        <v>329.36</v>
       </c>
       <c r="T3">
-        <v>32.9</v>
+        <v>32.25</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1113,43 +1120,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>66</v>
+        <v>65.08</v>
       </c>
       <c r="Z3">
-        <v>3.08</v>
+        <v>4.93</v>
       </c>
       <c r="AA3">
-        <v>-0.54</v>
+        <v>0.55</v>
       </c>
       <c r="AB3">
-        <v>3.62</v>
+        <v>4.37</v>
       </c>
       <c r="AC3">
-        <v>100</v>
+        <v>98.81999999999999</v>
       </c>
       <c r="AD3">
-        <v>75.66</v>
+        <v>92.90000000000001</v>
       </c>
       <c r="AE3">
-        <v>15.08</v>
+        <v>14.64</v>
       </c>
       <c r="AF3">
-        <v>-58.95</v>
+        <v>-49.09</v>
       </c>
       <c r="AG3">
-        <v>439.54</v>
+        <v>440.82</v>
       </c>
       <c r="AH3">
-        <v>373.7</v>
+        <v>373.02</v>
       </c>
       <c r="AI3">
-        <v>387.65</v>
+        <v>393.52</v>
       </c>
       <c r="AJ3" t="s">
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>41.73</v>
+        <v>44.73</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1160,10 +1167,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>395.55</v>
+        <v>387.95</v>
       </c>
       <c r="D4">
-        <v>-0.93</v>
+        <v>-1.92</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1172,46 +1179,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-25.93</v>
+        <v>-27.35</v>
       </c>
       <c r="H4">
-        <v>14.75</v>
+        <v>12.55</v>
       </c>
       <c r="I4">
-        <v>-1.25</v>
+        <v>-1.46</v>
       </c>
       <c r="J4">
-        <v>-7.67</v>
+        <v>-5.95</v>
       </c>
       <c r="K4">
-        <v>-1.17</v>
+        <v>-13.86</v>
       </c>
       <c r="L4">
-        <v>-24.45</v>
+        <v>-25.68</v>
       </c>
       <c r="M4">
-        <v>-20.6</v>
+        <v>-20.89</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>394.92</v>
+        <v>393.77</v>
       </c>
       <c r="Q4">
-        <v>402.68</v>
+        <v>401.52</v>
       </c>
       <c r="R4">
-        <v>414.9</v>
+        <v>414.4</v>
       </c>
       <c r="S4">
-        <v>415.18</v>
+        <v>414.6</v>
       </c>
       <c r="T4">
-        <v>-4.73</v>
+        <v>-6.43</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1226,43 +1233,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>37.58</v>
+        <v>31.72</v>
       </c>
       <c r="Z4">
-        <v>-5.99</v>
+        <v>-6.46</v>
       </c>
       <c r="AA4">
-        <v>-5.68</v>
+        <v>-5.84</v>
       </c>
       <c r="AB4">
-        <v>-0.3</v>
+        <v>-0.62</v>
       </c>
       <c r="AC4">
-        <v>49.62</v>
+        <v>51.49</v>
       </c>
       <c r="AD4">
-        <v>26.55</v>
+        <v>43.72</v>
       </c>
       <c r="AE4">
-        <v>11.04</v>
+        <v>11.37</v>
       </c>
       <c r="AF4">
-        <v>-66.09</v>
+        <v>34.49</v>
       </c>
       <c r="AG4">
-        <v>414.25</v>
+        <v>414.09</v>
       </c>
       <c r="AH4">
-        <v>391.12</v>
+        <v>388.94</v>
       </c>
       <c r="AI4">
-        <v>426.99</v>
+        <v>424.7</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>14.87</v>
+        <v>16.46</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1273,10 +1280,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>998</v>
+        <v>997.7</v>
       </c>
       <c r="D5">
-        <v>-1.04</v>
+        <v>-0.03</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1285,88 +1292,88 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-6.67</v>
+        <v>-6.7</v>
       </c>
       <c r="H5">
-        <v>40.02</v>
+        <v>39.98</v>
       </c>
       <c r="I5">
-        <v>-1.83</v>
+        <v>0.51</v>
       </c>
       <c r="J5">
-        <v>-2.35</v>
+        <v>-2.88</v>
       </c>
       <c r="K5">
-        <v>8.15</v>
+        <v>12.87</v>
       </c>
       <c r="L5">
-        <v>29.93</v>
+        <v>32.17</v>
       </c>
       <c r="M5">
-        <v>0.54</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="P5">
-        <v>996.38</v>
+        <v>997.4</v>
       </c>
       <c r="Q5">
-        <v>1008.54</v>
+        <v>1007.98</v>
       </c>
       <c r="R5">
-        <v>1008.28</v>
+        <v>1009.75</v>
       </c>
       <c r="S5">
-        <v>915.61</v>
+        <v>916.45</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8.869999999999999</v>
       </c>
       <c r="U5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="V5" t="s">
         <v>43</v>
       </c>
       <c r="W5" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="X5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Y5">
-        <v>47.47</v>
+        <v>47.37</v>
       </c>
       <c r="Z5">
-        <v>-2.32</v>
+        <v>-2.59</v>
       </c>
       <c r="AA5">
-        <v>-0.29</v>
+        <v>-0.75</v>
       </c>
       <c r="AB5">
-        <v>-2.03</v>
+        <v>-1.84</v>
       </c>
       <c r="AC5">
-        <v>67.92</v>
+        <v>63.75</v>
       </c>
       <c r="AD5">
-        <v>47.53</v>
+        <v>60.36</v>
       </c>
       <c r="AE5">
-        <v>20.8</v>
+        <v>20.48</v>
       </c>
       <c r="AF5">
-        <v>16.22</v>
+        <v>-12.52</v>
       </c>
       <c r="AG5">
-        <v>1031.66</v>
+        <v>1031.6</v>
       </c>
       <c r="AH5">
-        <v>985.42</v>
+        <v>984.36</v>
       </c>
       <c r="AI5">
         <v>1038.34</v>
@@ -1375,7 +1382,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>14.59</v>
+        <v>13.52</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1386,10 +1393,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.98</v>
+        <v>2.92</v>
       </c>
       <c r="D6">
-        <v>5.3</v>
+        <v>-2.01</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1398,46 +1405,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-17.68</v>
+        <v>-19.34</v>
       </c>
       <c r="H6">
-        <v>61.96</v>
+        <v>58.7</v>
       </c>
       <c r="I6">
-        <v>5.3</v>
+        <v>2.46</v>
       </c>
       <c r="J6">
-        <v>28.45</v>
+        <v>25.86</v>
       </c>
       <c r="K6">
-        <v>16.41</v>
+        <v>14.96</v>
       </c>
       <c r="L6">
-        <v>-13.62</v>
+        <v>-14.62</v>
       </c>
       <c r="M6">
-        <v>3.17</v>
+        <v>2.04</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="P6">
-        <v>2.87</v>
+        <v>2.88</v>
       </c>
       <c r="Q6">
-        <v>2.67</v>
+        <v>2.7</v>
       </c>
       <c r="R6">
-        <v>2.49</v>
+        <v>2.5</v>
       </c>
       <c r="S6">
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>11.1</v>
+        <v>8.91</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1452,7 +1459,7 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>67.7</v>
+        <v>63.29</v>
       </c>
       <c r="Z6">
         <v>0.14</v>
@@ -1464,22 +1471,22 @@
         <v>0.01</v>
       </c>
       <c r="AC6">
-        <v>59.12</v>
+        <v>59.75</v>
       </c>
       <c r="AD6">
-        <v>57.26</v>
+        <v>58.24</v>
       </c>
       <c r="AE6">
         <v>0.14</v>
       </c>
       <c r="AF6">
-        <v>9.24</v>
+        <v>-55.66</v>
       </c>
       <c r="AG6">
-        <v>3.31</v>
+        <v>3.33</v>
       </c>
       <c r="AH6">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1488,7 +1495,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>43.58</v>
+        <v>44.75</v>
       </c>
     </row>
   </sheetData>
@@ -1629,7 +1636,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F47"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1692,731 +1699,751 @@
         <v>40</v>
       </c>
       <c r="B4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C4" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="D4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="E4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="C5" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>59</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="A7" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="B7" s="2"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B8" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6" s="2" t="s">
+      <c r="C8" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B7" s="3" t="s">
+      <c r="D8" s="3" t="s">
         <v>64</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="E8" s="3" t="s">
         <v>65</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B8" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C8" s="7">
-        <v>-4.79</v>
-      </c>
-      <c r="D8" s="7">
-        <v>-4.23</v>
-      </c>
-      <c r="E8" s="8">
-        <v>0.5600000000000001</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C9" s="7">
-        <v>4.12</v>
+        <v>-4.23</v>
       </c>
       <c r="D9" s="7">
-        <v>-0.3</v>
-      </c>
-      <c r="E9" s="9">
-        <v>-4.42</v>
+        <v>-2.87</v>
+      </c>
+      <c r="E9" s="8">
+        <v>1.36</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C10" s="7">
-        <v>-5.63</v>
+        <v>-0.3</v>
       </c>
       <c r="D10" s="7">
-        <v>-7.67</v>
-      </c>
-      <c r="E10" s="9">
-        <v>-2.04</v>
+        <v>1.73</v>
+      </c>
+      <c r="E10" s="8">
+        <v>2.03</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C11" s="7">
-        <v>-0.76</v>
+        <v>-7.67</v>
       </c>
       <c r="D11" s="7">
-        <v>-2.35</v>
-      </c>
-      <c r="E11" s="9">
-        <v>-1.59</v>
+        <v>-5.95</v>
+      </c>
+      <c r="E11" s="8">
+        <v>1.72</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>9</v>
       </c>
       <c r="C12" s="7">
-        <v>22.51</v>
+        <v>-2.35</v>
       </c>
       <c r="D12" s="7">
-        <v>28.45</v>
-      </c>
-      <c r="E12" s="8">
-        <v>5.94</v>
+        <v>-2.88</v>
+      </c>
+      <c r="E12" s="9">
+        <v>-0.53</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C13" s="7">
-        <v>-3.85</v>
+        <v>28.45</v>
       </c>
       <c r="D13" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="E13" s="8">
-        <v>0.64</v>
+        <v>25.86</v>
+      </c>
+      <c r="E13" s="9">
+        <v>-2.59</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C14" s="7">
-        <v>10.1</v>
+        <v>-3.21</v>
       </c>
       <c r="D14" s="7">
-        <v>11.32</v>
+        <v>-0.9</v>
       </c>
       <c r="E14" s="8">
-        <v>1.22</v>
+        <v>2.31</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C15" s="7">
-        <v>-0.82</v>
+        <v>11.32</v>
       </c>
       <c r="D15" s="7">
-        <v>-1.25</v>
-      </c>
-      <c r="E15" s="9">
-        <v>-0.43</v>
+        <v>12.46</v>
+      </c>
+      <c r="E15" s="8">
+        <v>1.14</v>
       </c>
     </row>
     <row r="16" spans="1:6">
       <c r="A16" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C16" s="7">
-        <v>1.46</v>
+        <v>-1.25</v>
       </c>
       <c r="D16" s="7">
-        <v>-1.83</v>
+        <v>-1.46</v>
       </c>
       <c r="E16" s="9">
-        <v>-3.29</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="17" spans="1:5">
       <c r="A17" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>8</v>
       </c>
       <c r="C17" s="7">
-        <v>-6.29</v>
+        <v>-1.83</v>
       </c>
       <c r="D17" s="7">
-        <v>5.3</v>
+        <v>0.51</v>
       </c>
       <c r="E17" s="8">
-        <v>11.59</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="18" spans="1:5">
       <c r="A18" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B18" s="6" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="C18" s="7">
-        <v>32.72</v>
+        <v>5.3</v>
       </c>
       <c r="D18" s="7">
-        <v>33.67</v>
-      </c>
-      <c r="E18" s="8">
-        <v>0.95</v>
+        <v>2.46</v>
+      </c>
+      <c r="E18" s="9">
+        <v>-2.84</v>
       </c>
     </row>
     <row r="19" spans="1:5">
       <c r="A19" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C19" s="7">
-        <v>19.42</v>
+        <v>33.67</v>
       </c>
       <c r="D19" s="7">
-        <v>20.01</v>
+        <v>35.18</v>
       </c>
       <c r="E19" s="8">
-        <v>0.59</v>
+        <v>1.51</v>
       </c>
     </row>
     <row r="20" spans="1:5">
       <c r="A20" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C20" s="7">
-        <v>-23.71</v>
+        <v>20.01</v>
       </c>
       <c r="D20" s="7">
-        <v>-24.45</v>
-      </c>
-      <c r="E20" s="9">
-        <v>-0.74</v>
+        <v>20.63</v>
+      </c>
+      <c r="E20" s="8">
+        <v>0.62</v>
       </c>
     </row>
     <row r="21" spans="1:5">
       <c r="A21" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C21" s="7">
-        <v>34.25</v>
+        <v>-24.45</v>
       </c>
       <c r="D21" s="7">
-        <v>29.93</v>
+        <v>-25.68</v>
       </c>
       <c r="E21" s="9">
-        <v>-4.32</v>
+        <v>-1.23</v>
       </c>
     </row>
     <row r="22" spans="1:5">
       <c r="A22" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>11</v>
       </c>
       <c r="C22" s="7">
-        <v>-18.21</v>
+        <v>29.93</v>
       </c>
       <c r="D22" s="7">
-        <v>-13.62</v>
+        <v>32.17</v>
       </c>
       <c r="E22" s="8">
-        <v>4.59</v>
+        <v>2.24</v>
       </c>
     </row>
     <row r="23" spans="1:5">
       <c r="A23" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B23" s="6" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C23" s="7">
-        <v>19.84</v>
+        <v>-13.62</v>
       </c>
       <c r="D23" s="7">
-        <v>18.22</v>
+        <v>-14.62</v>
       </c>
       <c r="E23" s="9">
-        <v>-1.62</v>
+        <v>-1</v>
       </c>
     </row>
     <row r="24" spans="1:5">
       <c r="A24" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C24" s="7">
-        <v>7.85</v>
+        <v>18.22</v>
       </c>
       <c r="D24" s="7">
-        <v>9.550000000000001</v>
+        <v>19.4</v>
       </c>
       <c r="E24" s="8">
-        <v>1.7</v>
+        <v>1.18</v>
       </c>
     </row>
     <row r="25" spans="1:5">
       <c r="A25" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C25" s="7">
-        <v>-0.76</v>
+        <v>9.550000000000001</v>
       </c>
       <c r="D25" s="7">
-        <v>-1.17</v>
-      </c>
-      <c r="E25" s="9">
-        <v>-0.41</v>
+        <v>12.78</v>
+      </c>
+      <c r="E25" s="8">
+        <v>3.23</v>
       </c>
     </row>
     <row r="26" spans="1:5">
       <c r="A26" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C26" s="7">
-        <v>12.68</v>
+        <v>-1.17</v>
       </c>
       <c r="D26" s="7">
-        <v>8.15</v>
+        <v>-13.86</v>
       </c>
       <c r="E26" s="9">
-        <v>-4.53</v>
+        <v>-12.69</v>
       </c>
     </row>
     <row r="27" spans="1:5">
       <c r="A27" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>10</v>
       </c>
       <c r="C27" s="7">
-        <v>12.75</v>
+        <v>8.15</v>
       </c>
       <c r="D27" s="7">
-        <v>16.41</v>
+        <v>12.87</v>
       </c>
       <c r="E27" s="8">
-        <v>3.66</v>
+        <v>4.72</v>
       </c>
     </row>
     <row r="28" spans="1:5">
       <c r="A28" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="C28" s="7">
-        <v>-18.89</v>
+        <v>16.41</v>
       </c>
       <c r="D28" s="7">
-        <v>-18.41</v>
-      </c>
-      <c r="E28" s="8">
-        <v>0.48</v>
+        <v>14.96</v>
+      </c>
+      <c r="E28" s="9">
+        <v>-1.45</v>
       </c>
     </row>
     <row r="29" spans="1:5">
       <c r="A29" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C29" s="7">
-        <v>-4.01</v>
+        <v>-18.41</v>
       </c>
       <c r="D29" s="7">
-        <v>-1.88</v>
-      </c>
-      <c r="E29" s="8">
-        <v>2.13</v>
+        <v>-18.89</v>
+      </c>
+      <c r="E29" s="9">
+        <v>-0.48</v>
       </c>
     </row>
     <row r="30" spans="1:5">
       <c r="A30" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C30" s="7">
-        <v>-25.23</v>
+        <v>-1.88</v>
       </c>
       <c r="D30" s="7">
-        <v>-25.93</v>
+        <v>-2.18</v>
       </c>
       <c r="E30" s="9">
-        <v>-0.7</v>
+        <v>-0.3</v>
       </c>
     </row>
     <row r="31" spans="1:5">
       <c r="A31" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C31" s="7">
-        <v>-5.69</v>
+        <v>-25.93</v>
       </c>
       <c r="D31" s="7">
-        <v>-6.67</v>
+        <v>-27.35</v>
       </c>
       <c r="E31" s="9">
-        <v>-0.98</v>
+        <v>-1.42</v>
       </c>
     </row>
     <row r="32" spans="1:5">
       <c r="A32" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>6</v>
       </c>
       <c r="C32" s="7">
-        <v>-21.82</v>
+        <v>-6.67</v>
       </c>
       <c r="D32" s="7">
-        <v>-17.68</v>
-      </c>
-      <c r="E32" s="8">
-        <v>4.14</v>
+        <v>-6.7</v>
+      </c>
+      <c r="E32" s="9">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="33" spans="1:5">
       <c r="A33" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B33" s="6" t="s">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="C33" s="7">
-        <v>169</v>
+        <v>-17.68</v>
       </c>
       <c r="D33" s="7">
-        <v>170</v>
-      </c>
-      <c r="E33" s="8">
-        <v>1</v>
+        <v>-19.34</v>
+      </c>
+      <c r="E33" s="9">
+        <v>-1.66</v>
       </c>
     </row>
     <row r="34" spans="1:5">
       <c r="A34" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B34" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C34" s="7">
-        <v>427.45</v>
+        <v>170</v>
       </c>
       <c r="D34" s="7">
-        <v>436.95</v>
-      </c>
-      <c r="E34" s="8">
-        <v>9.5</v>
+        <v>169</v>
+      </c>
+      <c r="E34" s="9">
+        <v>-1</v>
       </c>
     </row>
     <row r="35" spans="1:5">
       <c r="A35" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B35" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C35" s="7">
-        <v>399.25</v>
+        <v>436.95</v>
       </c>
       <c r="D35" s="7">
-        <v>395.55</v>
+        <v>435.6</v>
       </c>
       <c r="E35" s="9">
-        <v>-3.7</v>
+        <v>-1.35</v>
       </c>
     </row>
     <row r="36" spans="1:5">
       <c r="A36" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B36" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C36" s="7">
-        <v>1008.5</v>
+        <v>395.55</v>
       </c>
       <c r="D36" s="7">
-        <v>998</v>
+        <v>387.95</v>
       </c>
       <c r="E36" s="9">
-        <v>-10.5</v>
+        <v>-7.6</v>
       </c>
     </row>
     <row r="37" spans="1:5">
       <c r="A37" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B37" s="6" t="s">
         <v>2</v>
       </c>
       <c r="C37" s="7">
-        <v>2.83</v>
+        <v>998</v>
       </c>
       <c r="D37" s="7">
-        <v>2.98</v>
-      </c>
-      <c r="E37" s="8">
-        <v>0.15</v>
+        <v>997.7</v>
+      </c>
+      <c r="E37" s="9">
+        <v>-0.3</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B38" s="6" t="s">
-        <v>24</v>
+        <v>2</v>
       </c>
       <c r="C38" s="7">
-        <v>46.6</v>
+        <v>2.98</v>
       </c>
       <c r="D38" s="7">
-        <v>48.47</v>
-      </c>
-      <c r="E38" s="8">
-        <v>1.87</v>
+        <v>2.92</v>
+      </c>
+      <c r="E38" s="9">
+        <v>-0.06</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B39" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="7">
-        <v>62.54</v>
+        <v>48.47</v>
       </c>
       <c r="D39" s="7">
-        <v>66</v>
-      </c>
-      <c r="E39" s="8">
-        <v>3.46</v>
+        <v>46.71</v>
+      </c>
+      <c r="E39" s="9">
+        <v>-1.76</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B40" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="7">
-        <v>41</v>
+        <v>66</v>
       </c>
       <c r="D40" s="7">
-        <v>37.58</v>
+        <v>65.08</v>
       </c>
       <c r="E40" s="9">
-        <v>-3.42</v>
+        <v>-0.92</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B41" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="7">
-        <v>50.89</v>
+        <v>37.58</v>
       </c>
       <c r="D41" s="7">
-        <v>47.47</v>
+        <v>31.72</v>
       </c>
       <c r="E41" s="9">
-        <v>-3.42</v>
+        <v>-5.86</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B42" s="6" t="s">
         <v>24</v>
       </c>
       <c r="C42" s="7">
-        <v>61.47</v>
+        <v>47.47</v>
       </c>
       <c r="D42" s="7">
-        <v>67.7</v>
-      </c>
-      <c r="E42" s="8">
-        <v>6.23</v>
+        <v>47.37</v>
+      </c>
+      <c r="E42" s="9">
+        <v>-0.1</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="6" t="s">
-        <v>37</v>
+        <v>41</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="7">
-        <v>-13.28</v>
+        <v>67.7</v>
       </c>
       <c r="D43" s="7">
-        <v>-32.73</v>
+        <v>63.29</v>
       </c>
       <c r="E43" s="9">
-        <v>-19.45</v>
+        <v>-4.41</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="6" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="B44" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="7">
-        <v>-29.42</v>
+        <v>-32.73</v>
       </c>
       <c r="D44" s="7">
-        <v>-58.95</v>
+        <v>-48.28</v>
       </c>
       <c r="E44" s="9">
-        <v>-29.53</v>
+        <v>-15.55</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="6" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B45" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="7">
-        <v>-51.19</v>
+        <v>-58.95</v>
       </c>
       <c r="D45" s="7">
-        <v>-66.09</v>
-      </c>
-      <c r="E45" s="9">
-        <v>-14.9</v>
+        <v>-49.09</v>
+      </c>
+      <c r="E45" s="8">
+        <v>9.859999999999999</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="6" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="B46" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="7">
-        <v>10.58</v>
+        <v>-66.09</v>
       </c>
       <c r="D46" s="7">
-        <v>16.22</v>
+        <v>34.49</v>
       </c>
       <c r="E46" s="8">
-        <v>5.64</v>
+        <v>100.58</v>
       </c>
     </row>
     <row r="47" spans="1:5">
       <c r="A47" s="6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="B47" s="6" t="s">
         <v>31</v>
       </c>
       <c r="C47" s="7">
-        <v>-49.62</v>
+        <v>16.22</v>
       </c>
       <c r="D47" s="7">
+        <v>-12.52</v>
+      </c>
+      <c r="E47" s="9">
+        <v>-28.74</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="7">
         <v>9.24</v>
       </c>
-      <c r="E47" s="8">
-        <v>58.86</v>
+      <c r="D48" s="7">
+        <v>-55.66</v>
+      </c>
+      <c r="E48" s="9">
+        <v>-64.90000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A6:E6"/>
+    <mergeCell ref="A7:E7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2440,28 +2467,28 @@
         <v>1</v>
       </c>
       <c r="B1" s="10" t="s">
+        <v>66</v>
+      </c>
+      <c r="C1" s="10" t="s">
+        <v>67</v>
+      </c>
+      <c r="D1" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="10" t="s">
+      <c r="E1" s="10" t="s">
         <v>69</v>
       </c>
-      <c r="D1" s="10" t="s">
+      <c r="F1" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="E1" s="10" t="s">
+      <c r="G1" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="F1" s="10" t="s">
+      <c r="H1" s="10" t="s">
         <v>72</v>
       </c>
-      <c r="G1" s="10" t="s">
+      <c r="I1" s="10" t="s">
         <v>73</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>74</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>75</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -2469,28 +2496,28 @@
         <v>42</v>
       </c>
       <c r="B2" s="12">
-        <v>65.92</v>
+        <v>57.92</v>
       </c>
       <c r="C2" s="13">
         <v>5</v>
       </c>
       <c r="D2" s="12">
-        <v>53.4</v>
+        <v>50.8</v>
       </c>
       <c r="E2" s="12">
-        <v>80</v>
+        <v>60</v>
       </c>
       <c r="F2" s="12">
-        <v>2.8</v>
+        <v>3.2</v>
       </c>
       <c r="G2" s="12">
-        <v>10.2</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="H2" s="12">
         <v>59.8</v>
       </c>
       <c r="I2" s="12">
-        <v>40</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -2609,19 +2636,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="15">
-        <v>0.2557</v>
+        <v>0.2519</v>
       </c>
       <c r="B2" s="15">
-        <v>0.1239</v>
+        <v>0.1208</v>
       </c>
       <c r="C2" s="15">
-        <v>0.0317</v>
+        <v>0.0204</v>
       </c>
       <c r="D2" s="15">
-        <v>0.0054</v>
+        <v>0.005600000000000001</v>
       </c>
       <c r="E2" s="15">
-        <v>-0.206</v>
+        <v>-0.2089</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="230" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,43 +166,7 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>Signal</t>
-  </si>
-  <si>
-    <t>Change</t>
-  </si>
-  <si>
-    <t>Direction</t>
-  </si>
-  <si>
-    <t>Prev Value</t>
-  </si>
-  <si>
-    <t>Curr Value</t>
-  </si>
-  <si>
-    <t>Left 52W High Zone</t>
-  </si>
-  <si>
-    <t>-1.9% → -2.2%</t>
-  </si>
-  <si>
-    <t>⚪ NEUTRAL</t>
-  </si>
-  <si>
-    <t>-1.9%</t>
-  </si>
-  <si>
-    <t>-2.2%</t>
-  </si>
-  <si>
-    <t>Yes → No</t>
-  </si>
-  <si>
-    <t>🔴 BEARISH</t>
-  </si>
-  <si>
-    <t>20 DMA &gt; 50 DMA</t>
+    <t>No signal events detected since last run.</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -254,7 +218,7 @@
     <numFmt numFmtId="166" formatCode="0.0"/>
     <numFmt numFmtId="167" formatCode="0.00%"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -288,13 +252,6 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF1F4E79"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
@@ -308,7 +265,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -330,12 +287,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FF4A6FA5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -417,23 +368,21 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="6" fillId="7" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -442,7 +391,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="167" fontId="0" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
@@ -801,8 +750,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="18" width="8.7109375" customWidth="1"/>
+    <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -941,37 +890,37 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D2">
-        <v>-0.59</v>
+        <v>-1.18</v>
       </c>
       <c r="E2">
         <v>208.37</v>
       </c>
       <c r="F2">
-        <v>127.71</v>
+        <v>130.44</v>
       </c>
       <c r="G2">
-        <v>-18.89</v>
+        <v>-19.85</v>
       </c>
       <c r="H2">
-        <v>32.33</v>
+        <v>28.03</v>
       </c>
       <c r="I2">
-        <v>-0.9</v>
+        <v>-0.54</v>
       </c>
       <c r="J2">
-        <v>-2.87</v>
+        <v>-4.48</v>
       </c>
       <c r="K2">
-        <v>19.4</v>
+        <v>20.51</v>
       </c>
       <c r="L2">
-        <v>35.18</v>
+        <v>30.77</v>
       </c>
       <c r="M2">
-        <v>25.19</v>
+        <v>24.16</v>
       </c>
       <c r="N2">
         <v>99</v>
@@ -980,19 +929,19 @@
         <v>79</v>
       </c>
       <c r="P2">
-        <v>169.05</v>
+        <v>168.87</v>
       </c>
       <c r="Q2">
-        <v>173.48</v>
+        <v>172.99</v>
       </c>
       <c r="R2">
-        <v>166.53</v>
+        <v>166.62</v>
       </c>
       <c r="S2">
-        <v>169.47</v>
+        <v>169.59</v>
       </c>
       <c r="T2">
-        <v>-0.27</v>
+        <v>-1.53</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -1007,34 +956,34 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>46.71</v>
+        <v>43.31</v>
       </c>
       <c r="Z2">
-        <v>0.59</v>
+        <v>0.2</v>
       </c>
       <c r="AA2">
-        <v>1.91</v>
+        <v>1.57</v>
       </c>
       <c r="AB2">
-        <v>-1.32</v>
+        <v>-1.37</v>
       </c>
       <c r="AC2">
-        <v>13.27</v>
+        <v>9.949999999999999</v>
       </c>
       <c r="AD2">
-        <v>11.62</v>
+        <v>12.41</v>
       </c>
       <c r="AE2">
-        <v>4.26</v>
+        <v>4.17</v>
       </c>
       <c r="AF2">
-        <v>-48.28</v>
+        <v>-52.49</v>
       </c>
       <c r="AG2">
-        <v>180.13</v>
+        <v>180.05</v>
       </c>
       <c r="AH2">
-        <v>166.83</v>
+        <v>165.93</v>
       </c>
       <c r="AI2">
         <v>166.42</v>
@@ -1043,7 +992,7 @@
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>18.82</v>
+        <v>18.89</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1054,10 +1003,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>435.6</v>
+        <v>431.7</v>
       </c>
       <c r="D3">
-        <v>-0.31</v>
+        <v>-0.9</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1066,25 +1015,25 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-2.18</v>
+        <v>-3.05</v>
       </c>
       <c r="H3">
-        <v>93.59999999999999</v>
+        <v>91.87</v>
       </c>
       <c r="I3">
-        <v>12.46</v>
+        <v>10.21</v>
       </c>
       <c r="J3">
-        <v>1.73</v>
+        <v>0.5</v>
       </c>
       <c r="K3">
-        <v>12.78</v>
+        <v>13.03</v>
       </c>
       <c r="L3">
-        <v>20.63</v>
+        <v>20.07</v>
       </c>
       <c r="M3">
-        <v>12.08</v>
+        <v>11.21</v>
       </c>
       <c r="N3">
         <v>60</v>
@@ -1093,19 +1042,19 @@
         <v>72</v>
       </c>
       <c r="P3">
-        <v>422.93</v>
+        <v>430.93</v>
       </c>
       <c r="Q3">
         <v>406.92</v>
       </c>
       <c r="R3">
-        <v>405.31</v>
+        <v>405.9</v>
       </c>
       <c r="S3">
-        <v>329.36</v>
+        <v>329.94</v>
       </c>
       <c r="T3">
-        <v>32.25</v>
+        <v>30.84</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1120,34 +1069,34 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>65.08</v>
+        <v>62.38</v>
       </c>
       <c r="Z3">
-        <v>4.93</v>
+        <v>6.01</v>
       </c>
       <c r="AA3">
-        <v>0.55</v>
+        <v>1.64</v>
       </c>
       <c r="AB3">
-        <v>4.37</v>
+        <v>4.36</v>
       </c>
       <c r="AC3">
-        <v>98.81999999999999</v>
+        <v>94.15000000000001</v>
       </c>
       <c r="AD3">
-        <v>92.90000000000001</v>
+        <v>97.66</v>
       </c>
       <c r="AE3">
-        <v>14.64</v>
+        <v>14.3</v>
       </c>
       <c r="AF3">
-        <v>-49.09</v>
+        <v>-69.43000000000001</v>
       </c>
       <c r="AG3">
-        <v>440.82</v>
+        <v>440.8</v>
       </c>
       <c r="AH3">
-        <v>373.02</v>
+        <v>373.03</v>
       </c>
       <c r="AI3">
         <v>393.52</v>
@@ -1156,7 +1105,7 @@
         <v>45</v>
       </c>
       <c r="AK3">
-        <v>44.73</v>
+        <v>46.1</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1167,10 +1116,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>387.95</v>
+        <v>384.75</v>
       </c>
       <c r="D4">
-        <v>-1.92</v>
+        <v>-0.82</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1179,46 +1128,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-27.35</v>
+        <v>-27.95</v>
       </c>
       <c r="H4">
-        <v>12.55</v>
+        <v>11.62</v>
       </c>
       <c r="I4">
-        <v>-1.46</v>
+        <v>-2.12</v>
       </c>
       <c r="J4">
-        <v>-5.95</v>
+        <v>-6.46</v>
       </c>
       <c r="K4">
-        <v>-13.86</v>
+        <v>-9.94</v>
       </c>
       <c r="L4">
-        <v>-25.68</v>
+        <v>-26.05</v>
       </c>
       <c r="M4">
-        <v>-20.89</v>
+        <v>-21.29</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="P4">
-        <v>393.77</v>
+        <v>392.1</v>
       </c>
       <c r="Q4">
-        <v>401.52</v>
+        <v>400.42</v>
       </c>
       <c r="R4">
-        <v>414.4</v>
+        <v>413.81</v>
       </c>
       <c r="S4">
-        <v>414.6</v>
+        <v>414.02</v>
       </c>
       <c r="T4">
-        <v>-6.43</v>
+        <v>-7.07</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1233,43 +1182,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>31.72</v>
+        <v>29.63</v>
       </c>
       <c r="Z4">
-        <v>-6.46</v>
+        <v>-7.02</v>
       </c>
       <c r="AA4">
-        <v>-5.84</v>
+        <v>-6.07</v>
       </c>
       <c r="AB4">
-        <v>-0.62</v>
+        <v>-0.9399999999999999</v>
       </c>
       <c r="AC4">
-        <v>51.49</v>
+        <v>21.45</v>
       </c>
       <c r="AD4">
-        <v>43.72</v>
+        <v>40.85</v>
       </c>
       <c r="AE4">
-        <v>11.37</v>
+        <v>11.48</v>
       </c>
       <c r="AF4">
-        <v>34.49</v>
+        <v>-30.77</v>
       </c>
       <c r="AG4">
-        <v>414.09</v>
+        <v>414.79</v>
       </c>
       <c r="AH4">
-        <v>388.94</v>
+        <v>386.05</v>
       </c>
       <c r="AI4">
-        <v>424.7</v>
+        <v>421.88</v>
       </c>
       <c r="AJ4" t="s">
         <v>46</v>
       </c>
       <c r="AK4">
-        <v>16.46</v>
+        <v>18.46</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1280,10 +1229,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>997.7</v>
+        <v>1004</v>
       </c>
       <c r="D5">
-        <v>-0.03</v>
+        <v>0.63</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1292,46 +1241,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-6.7</v>
+        <v>-6.11</v>
       </c>
       <c r="H5">
-        <v>39.98</v>
+        <v>40.86</v>
       </c>
       <c r="I5">
-        <v>0.51</v>
+        <v>2.66</v>
       </c>
       <c r="J5">
-        <v>-2.88</v>
+        <v>-0.49</v>
       </c>
       <c r="K5">
-        <v>12.87</v>
+        <v>12.94</v>
       </c>
       <c r="L5">
-        <v>32.17</v>
+        <v>32.62</v>
       </c>
       <c r="M5">
-        <v>0.5600000000000001</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="N5">
         <v>79</v>
       </c>
       <c r="O5">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="P5">
-        <v>997.4</v>
+        <v>1002.6</v>
       </c>
       <c r="Q5">
-        <v>1007.98</v>
+        <v>1007.3</v>
       </c>
       <c r="R5">
-        <v>1009.75</v>
+        <v>1011</v>
       </c>
       <c r="S5">
-        <v>916.45</v>
+        <v>917.23</v>
       </c>
       <c r="T5">
-        <v>8.869999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1346,34 +1295,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>47.37</v>
+        <v>49.72</v>
       </c>
       <c r="Z5">
-        <v>-2.59</v>
+        <v>-2.26</v>
       </c>
       <c r="AA5">
-        <v>-0.75</v>
+        <v>-1.05</v>
       </c>
       <c r="AB5">
-        <v>-1.84</v>
+        <v>-1.21</v>
       </c>
       <c r="AC5">
-        <v>63.75</v>
+        <v>60.87</v>
       </c>
       <c r="AD5">
-        <v>60.36</v>
+        <v>64.18000000000001</v>
       </c>
       <c r="AE5">
-        <v>20.48</v>
+        <v>20.16</v>
       </c>
       <c r="AF5">
-        <v>-12.52</v>
+        <v>-17.5</v>
       </c>
       <c r="AG5">
-        <v>1031.6</v>
+        <v>1030.55</v>
       </c>
       <c r="AH5">
-        <v>984.36</v>
+        <v>984.0599999999999</v>
       </c>
       <c r="AI5">
         <v>1038.34</v>
@@ -1382,7 +1331,7 @@
         <v>46</v>
       </c>
       <c r="AK5">
-        <v>13.52</v>
+        <v>13.68</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1393,10 +1342,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="D6">
-        <v>-2.01</v>
+        <v>0.34</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1405,46 +1354,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-19.34</v>
+        <v>-19.06</v>
       </c>
       <c r="H6">
-        <v>58.7</v>
+        <v>59.24</v>
       </c>
       <c r="I6">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="J6">
-        <v>25.86</v>
+        <v>26.29</v>
       </c>
       <c r="K6">
-        <v>14.96</v>
+        <v>17.67</v>
       </c>
       <c r="L6">
-        <v>-14.62</v>
+        <v>-14.58</v>
       </c>
       <c r="M6">
-        <v>2.04</v>
+        <v>2.74</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="P6">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q6">
-        <v>2.7</v>
+        <v>2.73</v>
       </c>
       <c r="R6">
-        <v>2.5</v>
+        <v>2.51</v>
       </c>
       <c r="S6">
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>8.91</v>
+        <v>9.32</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1459,34 +1408,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>63.29</v>
+        <v>63.71</v>
       </c>
       <c r="Z6">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AA6">
         <v>0.13</v>
       </c>
       <c r="AB6">
-        <v>0.01</v>
+        <v>0</v>
       </c>
       <c r="AC6">
-        <v>59.75</v>
+        <v>44.82</v>
       </c>
       <c r="AD6">
-        <v>58.24</v>
+        <v>54.56</v>
       </c>
       <c r="AE6">
-        <v>0.14</v>
+        <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-55.66</v>
+        <v>-46.52</v>
       </c>
       <c r="AG6">
-        <v>3.33</v>
+        <v>3.34</v>
       </c>
       <c r="AH6">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1495,7 +1444,7 @@
         <v>45</v>
       </c>
       <c r="AK6">
-        <v>44.75</v>
+        <v>44.34</v>
       </c>
     </row>
   </sheetData>
@@ -1636,7 +1585,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F48"/>
+  <dimension ref="A1:F46"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1656,794 +1605,719 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="2"/>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="A6" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>48</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="3" t="s">
+      <c r="B6" s="4" t="s">
         <v>50</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="C6" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="D6" s="4" t="s">
         <v>52</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3" s="4" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="E6" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="C3" s="4" t="s">
-        <v>54</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>55</v>
-      </c>
-      <c r="E3" s="4" t="s">
-        <v>56</v>
-      </c>
-      <c r="F3" s="4" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C5" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="D5" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="E5" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="F5" s="5" t="s">
-        <v>44</v>
-      </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="B7" s="2"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="5">
+        <v>-2.87</v>
+      </c>
+      <c r="D7" s="5">
+        <v>-4.48</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-1.61</v>
+      </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8" s="3" t="s">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>62</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>63</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>65</v>
+        <v>9</v>
+      </c>
+      <c r="C8" s="5">
+        <v>1.73</v>
+      </c>
+      <c r="D8" s="5">
+        <v>0.5</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-1.23</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="6" t="s">
+      <c r="A9" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C9" s="5">
+        <v>-5.95</v>
+      </c>
+      <c r="D9" s="5">
+        <v>-6.46</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-0.51</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6">
+      <c r="A10" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C10" s="5">
+        <v>-2.88</v>
+      </c>
+      <c r="D10" s="5">
+        <v>-0.49</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2.39</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6">
+      <c r="A11" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="C11" s="5">
+        <v>25.86</v>
+      </c>
+      <c r="D11" s="5">
+        <v>26.29</v>
+      </c>
+      <c r="E11" s="7">
+        <v>0.43</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B9" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C9" s="7">
-        <v>-4.23</v>
-      </c>
-      <c r="D9" s="7">
-        <v>-2.87</v>
-      </c>
-      <c r="E9" s="8">
-        <v>1.36</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10" s="6" t="s">
+      <c r="B12" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C12" s="5">
+        <v>-0.9</v>
+      </c>
+      <c r="D12" s="5">
+        <v>-0.54</v>
+      </c>
+      <c r="E12" s="7">
+        <v>0.36</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6">
+      <c r="A13" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B10" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C10" s="7">
-        <v>-0.3</v>
-      </c>
-      <c r="D10" s="7">
-        <v>1.73</v>
-      </c>
-      <c r="E10" s="8">
-        <v>2.03</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11" s="6" t="s">
+      <c r="B13" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C13" s="5">
+        <v>12.46</v>
+      </c>
+      <c r="D13" s="5">
+        <v>10.21</v>
+      </c>
+      <c r="E13" s="6">
+        <v>-2.25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6">
+      <c r="A14" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B11" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C11" s="7">
-        <v>-7.67</v>
-      </c>
-      <c r="D11" s="7">
-        <v>-5.95</v>
-      </c>
-      <c r="E11" s="8">
-        <v>1.72</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12" s="6" t="s">
+      <c r="B14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C14" s="5">
+        <v>-1.46</v>
+      </c>
+      <c r="D14" s="5">
+        <v>-2.12</v>
+      </c>
+      <c r="E14" s="6">
+        <v>-0.66</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B12" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C12" s="7">
-        <v>-2.35</v>
-      </c>
-      <c r="D12" s="7">
-        <v>-2.88</v>
-      </c>
-      <c r="E12" s="9">
-        <v>-0.53</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13" s="6" t="s">
+      <c r="B15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C15" s="5">
+        <v>0.51</v>
+      </c>
+      <c r="D15" s="5">
+        <v>2.66</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6">
+      <c r="A16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B13" s="6" t="s">
-        <v>9</v>
-      </c>
-      <c r="C13" s="7">
-        <v>28.45</v>
-      </c>
-      <c r="D13" s="7">
-        <v>25.86</v>
-      </c>
-      <c r="E13" s="9">
-        <v>-2.59</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14" s="6" t="s">
+      <c r="B16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C16" s="5">
+        <v>2.46</v>
+      </c>
+      <c r="D16" s="5">
+        <v>2.81</v>
+      </c>
+      <c r="E16" s="7">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C14" s="7">
-        <v>-3.21</v>
-      </c>
-      <c r="D14" s="7">
-        <v>-0.9</v>
-      </c>
-      <c r="E14" s="8">
-        <v>2.31</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15" s="6" t="s">
+      <c r="B17" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C17" s="5">
+        <v>35.18</v>
+      </c>
+      <c r="D17" s="5">
+        <v>30.77</v>
+      </c>
+      <c r="E17" s="6">
+        <v>-4.41</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B15" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C15" s="7">
-        <v>11.32</v>
-      </c>
-      <c r="D15" s="7">
-        <v>12.46</v>
-      </c>
-      <c r="E15" s="8">
-        <v>1.14</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16" s="6" t="s">
+      <c r="B18" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C18" s="5">
+        <v>20.63</v>
+      </c>
+      <c r="D18" s="5">
+        <v>20.07</v>
+      </c>
+      <c r="E18" s="6">
+        <v>-0.5600000000000001</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B16" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C16" s="7">
-        <v>-1.25</v>
-      </c>
-      <c r="D16" s="7">
-        <v>-1.46</v>
-      </c>
-      <c r="E16" s="9">
-        <v>-0.21</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="6" t="s">
+      <c r="B19" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C19" s="5">
+        <v>-25.68</v>
+      </c>
+      <c r="D19" s="5">
+        <v>-26.05</v>
+      </c>
+      <c r="E19" s="6">
+        <v>-0.37</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="A20" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B17" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C17" s="7">
-        <v>-1.83</v>
-      </c>
-      <c r="D17" s="7">
-        <v>0.51</v>
-      </c>
-      <c r="E17" s="8">
-        <v>2.34</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="6" t="s">
+      <c r="B20" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="5">
+        <v>32.17</v>
+      </c>
+      <c r="D20" s="5">
+        <v>32.62</v>
+      </c>
+      <c r="E20" s="7">
+        <v>0.45</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="A21" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B18" s="6" t="s">
-        <v>8</v>
-      </c>
-      <c r="C18" s="7">
-        <v>5.3</v>
-      </c>
-      <c r="D18" s="7">
-        <v>2.46</v>
-      </c>
-      <c r="E18" s="9">
-        <v>-2.84</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="6" t="s">
+      <c r="B21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="C21" s="5">
+        <v>-14.62</v>
+      </c>
+      <c r="D21" s="5">
+        <v>-14.58</v>
+      </c>
+      <c r="E21" s="7">
+        <v>0.04</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5">
+      <c r="A22" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C19" s="7">
-        <v>33.67</v>
-      </c>
-      <c r="D19" s="7">
-        <v>35.18</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.51</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="6" t="s">
+      <c r="B22" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C22" s="5">
+        <v>19.4</v>
+      </c>
+      <c r="D22" s="5">
+        <v>20.51</v>
+      </c>
+      <c r="E22" s="7">
+        <v>1.11</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B20" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C20" s="7">
-        <v>20.01</v>
-      </c>
-      <c r="D20" s="7">
-        <v>20.63</v>
-      </c>
-      <c r="E20" s="8">
-        <v>0.62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="6" t="s">
+      <c r="B23" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C23" s="5">
+        <v>12.78</v>
+      </c>
+      <c r="D23" s="5">
+        <v>13.03</v>
+      </c>
+      <c r="E23" s="7">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="A24" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B21" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C21" s="7">
-        <v>-24.45</v>
-      </c>
-      <c r="D21" s="7">
-        <v>-25.68</v>
-      </c>
-      <c r="E21" s="9">
-        <v>-1.23</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="6" t="s">
+      <c r="B24" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C24" s="5">
+        <v>-13.86</v>
+      </c>
+      <c r="D24" s="5">
+        <v>-9.94</v>
+      </c>
+      <c r="E24" s="7">
+        <v>3.92</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="A25" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B22" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C22" s="7">
-        <v>29.93</v>
-      </c>
-      <c r="D22" s="7">
-        <v>32.17</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.24</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="6" t="s">
+      <c r="B25" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C25" s="5">
+        <v>12.87</v>
+      </c>
+      <c r="D25" s="5">
+        <v>12.94</v>
+      </c>
+      <c r="E25" s="7">
+        <v>0.07000000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="A26" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="6" t="s">
-        <v>11</v>
-      </c>
-      <c r="C23" s="7">
-        <v>-13.62</v>
-      </c>
-      <c r="D23" s="7">
-        <v>-14.62</v>
-      </c>
-      <c r="E23" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="6" t="s">
+      <c r="B26" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="C26" s="5">
+        <v>14.96</v>
+      </c>
+      <c r="D26" s="5">
+        <v>17.67</v>
+      </c>
+      <c r="E26" s="7">
+        <v>2.71</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5">
+      <c r="A27" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C24" s="7">
-        <v>18.22</v>
-      </c>
-      <c r="D24" s="7">
-        <v>19.4</v>
-      </c>
-      <c r="E24" s="8">
-        <v>1.18</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="6" t="s">
+      <c r="B27" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C27" s="5">
+        <v>-18.89</v>
+      </c>
+      <c r="D27" s="5">
+        <v>-19.85</v>
+      </c>
+      <c r="E27" s="6">
+        <v>-0.96</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C25" s="7">
-        <v>9.550000000000001</v>
-      </c>
-      <c r="D25" s="7">
-        <v>12.78</v>
-      </c>
-      <c r="E25" s="8">
-        <v>3.23</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="6" t="s">
+      <c r="B28" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C28" s="5">
+        <v>-2.18</v>
+      </c>
+      <c r="D28" s="5">
+        <v>-3.05</v>
+      </c>
+      <c r="E28" s="6">
+        <v>-0.87</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B26" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C26" s="7">
-        <v>-1.17</v>
-      </c>
-      <c r="D26" s="7">
-        <v>-13.86</v>
-      </c>
-      <c r="E26" s="9">
-        <v>-12.69</v>
-      </c>
-    </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="6" t="s">
+      <c r="B29" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C29" s="5">
+        <v>-27.35</v>
+      </c>
+      <c r="D29" s="5">
+        <v>-27.95</v>
+      </c>
+      <c r="E29" s="6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B27" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C27" s="7">
-        <v>8.15</v>
-      </c>
-      <c r="D27" s="7">
-        <v>12.87</v>
-      </c>
-      <c r="E27" s="8">
-        <v>4.72</v>
-      </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6" t="s">
+      <c r="B30" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C30" s="5">
+        <v>-6.7</v>
+      </c>
+      <c r="D30" s="5">
+        <v>-6.11</v>
+      </c>
+      <c r="E30" s="7">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B28" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="C28" s="7">
-        <v>16.41</v>
-      </c>
-      <c r="D28" s="7">
-        <v>14.96</v>
-      </c>
-      <c r="E28" s="9">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6" t="s">
+      <c r="B31" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="C31" s="5">
+        <v>-19.34</v>
+      </c>
+      <c r="D31" s="5">
+        <v>-19.06</v>
+      </c>
+      <c r="E31" s="7">
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B29" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C29" s="7">
-        <v>-18.41</v>
-      </c>
-      <c r="D29" s="7">
-        <v>-18.89</v>
-      </c>
-      <c r="E29" s="9">
-        <v>-0.48</v>
-      </c>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6" t="s">
+      <c r="B32" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C32" s="5">
+        <v>169</v>
+      </c>
+      <c r="D32" s="5">
+        <v>167</v>
+      </c>
+      <c r="E32" s="6">
+        <v>-2</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5">
+      <c r="A33" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B30" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C30" s="7">
-        <v>-1.88</v>
-      </c>
-      <c r="D30" s="7">
-        <v>-2.18</v>
-      </c>
-      <c r="E30" s="9">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6" t="s">
+      <c r="B33" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C33" s="5">
+        <v>435.6</v>
+      </c>
+      <c r="D33" s="5">
+        <v>431.7</v>
+      </c>
+      <c r="E33" s="6">
+        <v>-3.9</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5">
+      <c r="A34" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C31" s="7">
-        <v>-25.93</v>
-      </c>
-      <c r="D31" s="7">
-        <v>-27.35</v>
-      </c>
-      <c r="E31" s="9">
-        <v>-1.42</v>
-      </c>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6" t="s">
+      <c r="B34" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C34" s="5">
+        <v>387.95</v>
+      </c>
+      <c r="D34" s="5">
+        <v>384.75</v>
+      </c>
+      <c r="E34" s="6">
+        <v>-3.2</v>
+      </c>
+    </row>
+    <row r="35" spans="1:5">
+      <c r="A35" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B32" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C32" s="7">
-        <v>-6.67</v>
-      </c>
-      <c r="D32" s="7">
-        <v>-6.7</v>
-      </c>
-      <c r="E32" s="9">
-        <v>-0.03</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5">
-      <c r="A33" s="6" t="s">
+      <c r="B35" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C35" s="5">
+        <v>997.7</v>
+      </c>
+      <c r="D35" s="5">
+        <v>1004</v>
+      </c>
+      <c r="E35" s="7">
+        <v>6.3</v>
+      </c>
+    </row>
+    <row r="36" spans="1:5">
+      <c r="A36" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B33" s="6" t="s">
-        <v>6</v>
-      </c>
-      <c r="C33" s="7">
-        <v>-17.68</v>
-      </c>
-      <c r="D33" s="7">
-        <v>-19.34</v>
-      </c>
-      <c r="E33" s="9">
-        <v>-1.66</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5">
-      <c r="A34" s="6" t="s">
+      <c r="B36" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C36" s="5">
+        <v>2.92</v>
+      </c>
+      <c r="D36" s="5">
+        <v>2.93</v>
+      </c>
+      <c r="E36" s="7">
+        <v>0.01</v>
+      </c>
+    </row>
+    <row r="37" spans="1:5">
+      <c r="A37" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B34" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C34" s="7">
-        <v>170</v>
-      </c>
-      <c r="D34" s="7">
-        <v>169</v>
-      </c>
-      <c r="E34" s="9">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="35" spans="1:5">
-      <c r="A35" s="6" t="s">
+      <c r="B37" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C37" s="5">
+        <v>46.71</v>
+      </c>
+      <c r="D37" s="5">
+        <v>43.31</v>
+      </c>
+      <c r="E37" s="6">
+        <v>-3.4</v>
+      </c>
+    </row>
+    <row r="38" spans="1:5">
+      <c r="A38" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B35" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C35" s="7">
-        <v>436.95</v>
-      </c>
-      <c r="D35" s="7">
-        <v>435.6</v>
-      </c>
-      <c r="E35" s="9">
-        <v>-1.35</v>
-      </c>
-    </row>
-    <row r="36" spans="1:5">
-      <c r="A36" s="6" t="s">
+      <c r="B38" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C38" s="5">
+        <v>65.08</v>
+      </c>
+      <c r="D38" s="5">
+        <v>62.38</v>
+      </c>
+      <c r="E38" s="6">
+        <v>-2.7</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B36" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C36" s="7">
-        <v>395.55</v>
-      </c>
-      <c r="D36" s="7">
-        <v>387.95</v>
-      </c>
-      <c r="E36" s="9">
-        <v>-7.6</v>
-      </c>
-    </row>
-    <row r="37" spans="1:5">
-      <c r="A37" s="6" t="s">
+      <c r="B39" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="5">
+        <v>31.72</v>
+      </c>
+      <c r="D39" s="5">
+        <v>29.63</v>
+      </c>
+      <c r="E39" s="6">
+        <v>-2.09</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B37" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C37" s="7">
-        <v>998</v>
-      </c>
-      <c r="D37" s="7">
-        <v>997.7</v>
-      </c>
-      <c r="E37" s="9">
-        <v>-0.3</v>
-      </c>
-    </row>
-    <row r="38" spans="1:5">
-      <c r="A38" s="6" t="s">
+      <c r="B40" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="5">
+        <v>47.37</v>
+      </c>
+      <c r="D40" s="5">
+        <v>49.72</v>
+      </c>
+      <c r="E40" s="7">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>2</v>
-      </c>
-      <c r="C38" s="7">
-        <v>2.98</v>
-      </c>
-      <c r="D38" s="7">
-        <v>2.92</v>
-      </c>
-      <c r="E38" s="9">
-        <v>-0.06</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="6" t="s">
+      <c r="B41" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="5">
+        <v>63.29</v>
+      </c>
+      <c r="D41" s="5">
+        <v>63.71</v>
+      </c>
+      <c r="E41" s="7">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="7">
-        <v>48.47</v>
-      </c>
-      <c r="D39" s="7">
-        <v>46.71</v>
-      </c>
-      <c r="E39" s="9">
-        <v>-1.76</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="6" t="s">
+      <c r="B42" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C42" s="5">
+        <v>-48.28</v>
+      </c>
+      <c r="D42" s="5">
+        <v>-52.49</v>
+      </c>
+      <c r="E42" s="6">
+        <v>-4.21</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="3" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="7">
-        <v>66</v>
-      </c>
-      <c r="D40" s="7">
-        <v>65.08</v>
-      </c>
-      <c r="E40" s="9">
-        <v>-0.92</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="6" t="s">
+      <c r="B43" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C43" s="5">
+        <v>-49.09</v>
+      </c>
+      <c r="D43" s="5">
+        <v>-69.43000000000001</v>
+      </c>
+      <c r="E43" s="6">
+        <v>-20.34</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="7">
-        <v>37.58</v>
-      </c>
-      <c r="D41" s="7">
-        <v>31.72</v>
-      </c>
-      <c r="E41" s="9">
-        <v>-5.86</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="6" t="s">
+      <c r="B44" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="5">
+        <v>34.49</v>
+      </c>
+      <c r="D44" s="5">
+        <v>-30.77</v>
+      </c>
+      <c r="E44" s="6">
+        <v>-65.26000000000001</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="7">
-        <v>47.47</v>
-      </c>
-      <c r="D42" s="7">
-        <v>47.37</v>
-      </c>
-      <c r="E42" s="9">
-        <v>-0.1</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="6" t="s">
+      <c r="B45" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="5">
+        <v>-12.52</v>
+      </c>
+      <c r="D45" s="5">
+        <v>-17.5</v>
+      </c>
+      <c r="E45" s="6">
+        <v>-4.98</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="6" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="7">
-        <v>67.7</v>
-      </c>
-      <c r="D43" s="7">
-        <v>63.29</v>
-      </c>
-      <c r="E43" s="9">
-        <v>-4.41</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="6" t="s">
+      <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="7">
-        <v>-32.73</v>
-      </c>
-      <c r="D44" s="7">
-        <v>-48.28</v>
-      </c>
-      <c r="E44" s="9">
-        <v>-15.55</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="7">
-        <v>-58.95</v>
-      </c>
-      <c r="D45" s="7">
-        <v>-49.09</v>
-      </c>
-      <c r="E45" s="8">
-        <v>9.859999999999999</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="6" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="7">
-        <v>-66.09</v>
-      </c>
-      <c r="D46" s="7">
-        <v>34.49</v>
-      </c>
-      <c r="E46" s="8">
-        <v>100.58</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="6" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="7">
-        <v>16.22</v>
-      </c>
-      <c r="D47" s="7">
-        <v>-12.52</v>
-      </c>
-      <c r="E47" s="9">
-        <v>-28.74</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="6" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="7">
-        <v>9.24</v>
-      </c>
-      <c r="D48" s="7">
+      <c r="C46" s="5">
         <v>-55.66</v>
       </c>
-      <c r="E48" s="9">
-        <v>-64.90000000000001</v>
+      <c r="D46" s="5">
+        <v>-46.52</v>
+      </c>
+      <c r="E46" s="7">
+        <v>9.140000000000001</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A7:E7"/>
+    <mergeCell ref="A5:E5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2463,60 +2337,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="10" t="s">
+      <c r="A1" s="8" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C1" s="10" t="s">
-        <v>67</v>
-      </c>
-      <c r="D1" s="10" t="s">
-        <v>68</v>
-      </c>
-      <c r="E1" s="10" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="10" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="10" t="s">
-        <v>72</v>
-      </c>
-      <c r="I1" s="10" t="s">
-        <v>73</v>
+      <c r="B1" s="8" t="s">
+        <v>54</v>
+      </c>
+      <c r="C1" s="8" t="s">
+        <v>55</v>
+      </c>
+      <c r="D1" s="8" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="8" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="G1" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="H1" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="2" spans="1:9">
-      <c r="A2" s="11" t="s">
+      <c r="A2" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B2" s="12">
+      <c r="B2" s="10">
         <v>57.92</v>
       </c>
-      <c r="C2" s="13">
+      <c r="C2" s="11">
         <v>5</v>
       </c>
-      <c r="D2" s="12">
-        <v>50.8</v>
-      </c>
-      <c r="E2" s="12">
+      <c r="D2" s="10">
+        <v>49.8</v>
+      </c>
+      <c r="E2" s="10">
         <v>60</v>
       </c>
-      <c r="F2" s="12">
-        <v>3.2</v>
-      </c>
-      <c r="G2" s="12">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="H2" s="12">
+      <c r="F2" s="10">
+        <v>3.1</v>
+      </c>
+      <c r="G2" s="10">
+        <v>10.8</v>
+      </c>
+      <c r="H2" s="10">
         <v>59.8</v>
       </c>
-      <c r="I2" s="12">
+      <c r="I2" s="10">
         <v>20</v>
       </c>
     </row>
@@ -2618,37 +2492,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="14" t="s">
+      <c r="A1" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="14" t="s">
+      <c r="B1" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="14" t="s">
+      <c r="C1" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="14" t="s">
+      <c r="D1" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="14" t="s">
+      <c r="E1" s="12" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="15">
-        <v>0.2519</v>
-      </c>
-      <c r="B2" s="15">
-        <v>0.1208</v>
-      </c>
-      <c r="C2" s="15">
-        <v>0.0204</v>
-      </c>
-      <c r="D2" s="15">
-        <v>0.005600000000000001</v>
-      </c>
-      <c r="E2" s="15">
-        <v>-0.2089</v>
+      <c r="A2" s="13">
+        <v>0.2416</v>
+      </c>
+      <c r="B2" s="13">
+        <v>0.1121</v>
+      </c>
+      <c r="C2" s="13">
+        <v>0.0274</v>
+      </c>
+      <c r="D2" s="13">
+        <v>0.0069</v>
+      </c>
+      <c r="E2" s="13">
+        <v>-0.2129</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="207" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
   <si>
     <t>Symbol</t>
   </si>
@@ -157,10 +157,10 @@
     <t>No</t>
   </si>
   <si>
+    <t>DOWN</t>
+  </si>
+  <si>
     <t>UP</t>
-  </si>
-  <si>
-    <t>DOWN</t>
   </si>
   <si>
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
@@ -750,7 +750,9 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="18" width="8.7109375" customWidth="1"/>
+    <col min="16" max="16" width="8.7109375" customWidth="1"/>
+    <col min="17" max="17" width="9.7109375" customWidth="1"/>
+    <col min="18" max="18" width="8.7109375" customWidth="1"/>
     <col min="19" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
@@ -890,10 +892,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>167</v>
+        <v>166.12</v>
       </c>
       <c r="D2">
-        <v>-1.18</v>
+        <v>-0.53</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -902,46 +904,46 @@
         <v>130.44</v>
       </c>
       <c r="G2">
-        <v>-19.85</v>
+        <v>-20.28</v>
       </c>
       <c r="H2">
-        <v>28.03</v>
+        <v>27.35</v>
       </c>
       <c r="I2">
-        <v>-0.54</v>
+        <v>-1.91</v>
       </c>
       <c r="J2">
-        <v>-4.48</v>
+        <v>-5.99</v>
       </c>
       <c r="K2">
-        <v>20.51</v>
+        <v>8.970000000000001</v>
       </c>
       <c r="L2">
-        <v>30.77</v>
+        <v>23.9</v>
       </c>
       <c r="M2">
-        <v>24.16</v>
+        <v>24.48</v>
       </c>
       <c r="N2">
-        <v>99</v>
+        <v>79</v>
       </c>
       <c r="O2">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="P2">
-        <v>168.87</v>
+        <v>168.22</v>
       </c>
       <c r="Q2">
-        <v>172.99</v>
+        <v>172.49</v>
       </c>
       <c r="R2">
-        <v>166.62</v>
+        <v>166.65</v>
       </c>
       <c r="S2">
-        <v>169.59</v>
+        <v>169.71</v>
       </c>
       <c r="T2">
-        <v>-1.53</v>
+        <v>-2.11</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -956,43 +958,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>43.31</v>
+        <v>41.86</v>
       </c>
       <c r="Z2">
-        <v>0.2</v>
+        <v>-0.19</v>
       </c>
       <c r="AA2">
-        <v>1.57</v>
+        <v>1.22</v>
       </c>
       <c r="AB2">
-        <v>-1.37</v>
+        <v>-1.4</v>
       </c>
       <c r="AC2">
-        <v>9.949999999999999</v>
+        <v>3.5</v>
       </c>
       <c r="AD2">
-        <v>12.41</v>
+        <v>8.91</v>
       </c>
       <c r="AE2">
-        <v>4.17</v>
+        <v>4.04</v>
       </c>
       <c r="AF2">
-        <v>-52.49</v>
+        <v>10.25</v>
       </c>
       <c r="AG2">
-        <v>180.05</v>
+        <v>180.01</v>
       </c>
       <c r="AH2">
-        <v>165.93</v>
+        <v>164.97</v>
       </c>
       <c r="AI2">
-        <v>166.42</v>
+        <v>177.99</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>18.89</v>
+        <v>20.16</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1003,10 +1005,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>431.7</v>
+        <v>432.2</v>
       </c>
       <c r="D3">
-        <v>-0.9</v>
+        <v>0.12</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1015,46 +1017,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-3.05</v>
+        <v>-2.94</v>
       </c>
       <c r="H3">
-        <v>91.87</v>
+        <v>92.09</v>
       </c>
       <c r="I3">
-        <v>10.21</v>
+        <v>2.19</v>
       </c>
       <c r="J3">
-        <v>0.5</v>
+        <v>0.09</v>
       </c>
       <c r="K3">
-        <v>13.03</v>
+        <v>7.42</v>
       </c>
       <c r="L3">
-        <v>20.07</v>
+        <v>20.09</v>
       </c>
       <c r="M3">
-        <v>11.21</v>
+        <v>12.08</v>
       </c>
       <c r="N3">
         <v>60</v>
       </c>
       <c r="O3">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="P3">
-        <v>430.93</v>
+        <v>432.78</v>
       </c>
       <c r="Q3">
-        <v>406.92</v>
+        <v>406.98</v>
       </c>
       <c r="R3">
-        <v>405.9</v>
+        <v>406.54</v>
       </c>
       <c r="S3">
-        <v>329.94</v>
+        <v>330.59</v>
       </c>
       <c r="T3">
-        <v>30.84</v>
+        <v>30.73</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1069,43 +1071,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>62.38</v>
+        <v>62.59</v>
       </c>
       <c r="Z3">
-        <v>6.01</v>
+        <v>6.82</v>
       </c>
       <c r="AA3">
-        <v>1.64</v>
+        <v>2.68</v>
       </c>
       <c r="AB3">
-        <v>4.36</v>
+        <v>4.14</v>
       </c>
       <c r="AC3">
-        <v>94.15000000000001</v>
+        <v>89.76000000000001</v>
       </c>
       <c r="AD3">
-        <v>97.66</v>
+        <v>94.23999999999999</v>
       </c>
       <c r="AE3">
-        <v>14.3</v>
+        <v>13.83</v>
       </c>
       <c r="AF3">
-        <v>-69.43000000000001</v>
+        <v>-77.45</v>
       </c>
       <c r="AG3">
-        <v>440.8</v>
+        <v>441.07</v>
       </c>
       <c r="AH3">
-        <v>373.03</v>
+        <v>372.9</v>
       </c>
       <c r="AI3">
         <v>393.52</v>
       </c>
       <c r="AJ3" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK3">
-        <v>46.1</v>
+        <v>47.25</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1116,10 +1118,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>384.75</v>
+        <v>383.85</v>
       </c>
       <c r="D4">
-        <v>-0.82</v>
+        <v>-0.23</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1128,46 +1130,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-27.95</v>
+        <v>-28.12</v>
       </c>
       <c r="H4">
-        <v>11.62</v>
+        <v>11.36</v>
       </c>
       <c r="I4">
-        <v>-2.12</v>
+        <v>-2.33</v>
       </c>
       <c r="J4">
-        <v>-6.46</v>
+        <v>-5.63</v>
       </c>
       <c r="K4">
-        <v>-9.94</v>
+        <v>-10.23</v>
       </c>
       <c r="L4">
-        <v>-26.05</v>
+        <v>-26.73</v>
       </c>
       <c r="M4">
-        <v>-21.29</v>
+        <v>-22.13</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="P4">
-        <v>392.1</v>
+        <v>390.27</v>
       </c>
       <c r="Q4">
-        <v>400.42</v>
+        <v>399.37</v>
       </c>
       <c r="R4">
-        <v>413.81</v>
+        <v>413.1</v>
       </c>
       <c r="S4">
-        <v>414.02</v>
+        <v>413.54</v>
       </c>
       <c r="T4">
-        <v>-7.07</v>
+        <v>-7.18</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1182,43 +1184,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.63</v>
+        <v>29.05</v>
       </c>
       <c r="Z4">
-        <v>-7.02</v>
+        <v>-7.44</v>
       </c>
       <c r="AA4">
-        <v>-6.07</v>
+        <v>-6.35</v>
       </c>
       <c r="AB4">
-        <v>-0.9399999999999999</v>
+        <v>-1.09</v>
       </c>
       <c r="AC4">
-        <v>21.45</v>
+        <v>1.87</v>
       </c>
       <c r="AD4">
-        <v>40.85</v>
+        <v>24.94</v>
       </c>
       <c r="AE4">
-        <v>11.48</v>
+        <v>11.21</v>
       </c>
       <c r="AF4">
-        <v>-30.77</v>
+        <v>-63.08</v>
       </c>
       <c r="AG4">
-        <v>414.79</v>
+        <v>415.37</v>
       </c>
       <c r="AH4">
-        <v>386.05</v>
+        <v>383.38</v>
       </c>
       <c r="AI4">
-        <v>421.88</v>
+        <v>419.77</v>
       </c>
       <c r="AJ4" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK4">
-        <v>18.46</v>
+        <v>20.19</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1229,10 +1231,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>1004</v>
+        <v>993.3</v>
       </c>
       <c r="D5">
-        <v>0.63</v>
+        <v>-1.07</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1241,46 +1243,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-6.11</v>
+        <v>-7.11</v>
       </c>
       <c r="H5">
-        <v>40.86</v>
+        <v>39.36</v>
       </c>
       <c r="I5">
-        <v>2.66</v>
+        <v>-1.14</v>
       </c>
       <c r="J5">
-        <v>-0.49</v>
+        <v>-2.38</v>
       </c>
       <c r="K5">
-        <v>12.94</v>
+        <v>8.279999999999999</v>
       </c>
       <c r="L5">
-        <v>32.62</v>
+        <v>32.31</v>
       </c>
       <c r="M5">
-        <v>0.6899999999999999</v>
+        <v>0.54</v>
       </c>
       <c r="N5">
-        <v>79</v>
+        <v>99</v>
       </c>
       <c r="O5">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P5">
-        <v>1002.6</v>
+        <v>1000.3</v>
       </c>
       <c r="Q5">
-        <v>1007.3</v>
+        <v>1005.73</v>
       </c>
       <c r="R5">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="S5">
-        <v>917.23</v>
+        <v>918.02</v>
       </c>
       <c r="T5">
-        <v>9.460000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1295,43 +1297,43 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>49.72</v>
+        <v>45.97</v>
       </c>
       <c r="Z5">
-        <v>-2.26</v>
+        <v>-2.84</v>
       </c>
       <c r="AA5">
-        <v>-1.05</v>
+        <v>-1.41</v>
       </c>
       <c r="AB5">
-        <v>-1.21</v>
+        <v>-1.43</v>
       </c>
       <c r="AC5">
-        <v>60.87</v>
+        <v>57.17</v>
       </c>
       <c r="AD5">
-        <v>64.18000000000001</v>
+        <v>60.6</v>
       </c>
       <c r="AE5">
-        <v>20.16</v>
+        <v>19.96</v>
       </c>
       <c r="AF5">
-        <v>-17.5</v>
+        <v>-18.1</v>
       </c>
       <c r="AG5">
-        <v>1030.55</v>
+        <v>1028.26</v>
       </c>
       <c r="AH5">
-        <v>984.0599999999999</v>
+        <v>983.21</v>
       </c>
       <c r="AI5">
         <v>1038.34</v>
       </c>
       <c r="AJ5" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AK5">
-        <v>13.68</v>
+        <v>11.96</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1342,10 +1344,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.93</v>
+        <v>2.9</v>
       </c>
       <c r="D6">
-        <v>0.34</v>
+        <v>-1.02</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1354,46 +1356,46 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-19.06</v>
+        <v>-19.89</v>
       </c>
       <c r="H6">
-        <v>59.24</v>
+        <v>57.61</v>
       </c>
       <c r="I6">
-        <v>2.81</v>
+        <v>2.47</v>
       </c>
       <c r="J6">
-        <v>26.29</v>
+        <v>23.93</v>
       </c>
       <c r="K6">
-        <v>17.67</v>
+        <v>14.17</v>
       </c>
       <c r="L6">
-        <v>-14.58</v>
+        <v>-17.85</v>
       </c>
       <c r="M6">
-        <v>2.74</v>
+        <v>2.45</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="P6">
-        <v>2.9</v>
+        <v>2.91</v>
       </c>
       <c r="Q6">
-        <v>2.73</v>
+        <v>2.76</v>
       </c>
       <c r="R6">
-        <v>2.51</v>
+        <v>2.52</v>
       </c>
       <c r="S6">
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>9.32</v>
+        <v>8.24</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1408,7 +1410,7 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>63.71</v>
+        <v>61.42</v>
       </c>
       <c r="Z6">
         <v>0.13</v>
@@ -1417,34 +1419,34 @@
         <v>0.13</v>
       </c>
       <c r="AB6">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="AC6">
-        <v>44.82</v>
+        <v>22.3</v>
       </c>
       <c r="AD6">
-        <v>54.56</v>
+        <v>42.29</v>
       </c>
       <c r="AE6">
         <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-46.52</v>
+        <v>-65.18000000000001</v>
       </c>
       <c r="AG6">
-        <v>3.34</v>
+        <v>3.35</v>
       </c>
       <c r="AH6">
-        <v>2.12</v>
+        <v>2.17</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
       </c>
       <c r="AJ6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="AK6">
-        <v>44.34</v>
+        <v>43.98</v>
       </c>
     </row>
   </sheetData>
@@ -1585,7 +1587,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F46"/>
+  <dimension ref="A1:F48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="16.7109375" customWidth="1"/>
@@ -1642,13 +1644,13 @@
         <v>9</v>
       </c>
       <c r="C7" s="5">
-        <v>-2.87</v>
+        <v>-4.48</v>
       </c>
       <c r="D7" s="5">
-        <v>-4.48</v>
+        <v>-5.99</v>
       </c>
       <c r="E7" s="6">
-        <v>-1.61</v>
+        <v>-1.51</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -1659,13 +1661,13 @@
         <v>9</v>
       </c>
       <c r="C8" s="5">
-        <v>1.73</v>
+        <v>0.5</v>
       </c>
       <c r="D8" s="5">
-        <v>0.5</v>
+        <v>0.09</v>
       </c>
       <c r="E8" s="6">
-        <v>-1.23</v>
+        <v>-0.41</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -1676,13 +1678,13 @@
         <v>9</v>
       </c>
       <c r="C9" s="5">
-        <v>-5.95</v>
+        <v>-6.46</v>
       </c>
       <c r="D9" s="5">
-        <v>-6.46</v>
-      </c>
-      <c r="E9" s="6">
-        <v>-0.51</v>
+        <v>-5.63</v>
+      </c>
+      <c r="E9" s="7">
+        <v>0.83</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -1693,13 +1695,13 @@
         <v>9</v>
       </c>
       <c r="C10" s="5">
-        <v>-2.88</v>
+        <v>-0.49</v>
       </c>
       <c r="D10" s="5">
-        <v>-0.49</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2.39</v>
+        <v>-2.38</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-1.89</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -1710,13 +1712,13 @@
         <v>9</v>
       </c>
       <c r="C11" s="5">
-        <v>25.86</v>
+        <v>26.29</v>
       </c>
       <c r="D11" s="5">
-        <v>26.29</v>
-      </c>
-      <c r="E11" s="7">
-        <v>0.43</v>
+        <v>23.93</v>
+      </c>
+      <c r="E11" s="6">
+        <v>-2.36</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -1727,13 +1729,13 @@
         <v>8</v>
       </c>
       <c r="C12" s="5">
-        <v>-0.9</v>
+        <v>-0.54</v>
       </c>
       <c r="D12" s="5">
-        <v>-0.54</v>
-      </c>
-      <c r="E12" s="7">
-        <v>0.36</v>
+        <v>-1.91</v>
+      </c>
+      <c r="E12" s="6">
+        <v>-1.37</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -1744,13 +1746,13 @@
         <v>8</v>
       </c>
       <c r="C13" s="5">
-        <v>12.46</v>
+        <v>10.21</v>
       </c>
       <c r="D13" s="5">
-        <v>10.21</v>
+        <v>2.19</v>
       </c>
       <c r="E13" s="6">
-        <v>-2.25</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="14" spans="1:6">
@@ -1761,13 +1763,13 @@
         <v>8</v>
       </c>
       <c r="C14" s="5">
-        <v>-1.46</v>
+        <v>-2.12</v>
       </c>
       <c r="D14" s="5">
-        <v>-2.12</v>
+        <v>-2.33</v>
       </c>
       <c r="E14" s="6">
-        <v>-0.66</v>
+        <v>-0.21</v>
       </c>
     </row>
     <row r="15" spans="1:6">
@@ -1778,13 +1780,13 @@
         <v>8</v>
       </c>
       <c r="C15" s="5">
-        <v>0.51</v>
+        <v>2.66</v>
       </c>
       <c r="D15" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2.15</v>
+        <v>-1.14</v>
+      </c>
+      <c r="E15" s="6">
+        <v>-3.8</v>
       </c>
     </row>
     <row r="16" spans="1:6">
@@ -1795,13 +1797,13 @@
         <v>8</v>
       </c>
       <c r="C16" s="5">
-        <v>2.46</v>
+        <v>2.81</v>
       </c>
       <c r="D16" s="5">
-        <v>2.81</v>
-      </c>
-      <c r="E16" s="7">
-        <v>0.35</v>
+        <v>2.47</v>
+      </c>
+      <c r="E16" s="6">
+        <v>-0.34</v>
       </c>
     </row>
     <row r="17" spans="1:5">
@@ -1812,13 +1814,13 @@
         <v>11</v>
       </c>
       <c r="C17" s="5">
-        <v>35.18</v>
+        <v>30.77</v>
       </c>
       <c r="D17" s="5">
-        <v>30.77</v>
+        <v>23.9</v>
       </c>
       <c r="E17" s="6">
-        <v>-4.41</v>
+        <v>-6.87</v>
       </c>
     </row>
     <row r="18" spans="1:5">
@@ -1829,13 +1831,13 @@
         <v>11</v>
       </c>
       <c r="C18" s="5">
-        <v>20.63</v>
+        <v>20.07</v>
       </c>
       <c r="D18" s="5">
-        <v>20.07</v>
-      </c>
-      <c r="E18" s="6">
-        <v>-0.5600000000000001</v>
+        <v>20.09</v>
+      </c>
+      <c r="E18" s="7">
+        <v>0.02</v>
       </c>
     </row>
     <row r="19" spans="1:5">
@@ -1846,13 +1848,13 @@
         <v>11</v>
       </c>
       <c r="C19" s="5">
-        <v>-25.68</v>
+        <v>-26.05</v>
       </c>
       <c r="D19" s="5">
-        <v>-26.05</v>
+        <v>-26.73</v>
       </c>
       <c r="E19" s="6">
-        <v>-0.37</v>
+        <v>-0.68</v>
       </c>
     </row>
     <row r="20" spans="1:5">
@@ -1863,13 +1865,13 @@
         <v>11</v>
       </c>
       <c r="C20" s="5">
-        <v>32.17</v>
+        <v>32.62</v>
       </c>
       <c r="D20" s="5">
-        <v>32.62</v>
-      </c>
-      <c r="E20" s="7">
-        <v>0.45</v>
+        <v>32.31</v>
+      </c>
+      <c r="E20" s="6">
+        <v>-0.31</v>
       </c>
     </row>
     <row r="21" spans="1:5">
@@ -1880,13 +1882,13 @@
         <v>11</v>
       </c>
       <c r="C21" s="5">
-        <v>-14.62</v>
+        <v>-14.58</v>
       </c>
       <c r="D21" s="5">
-        <v>-14.58</v>
-      </c>
-      <c r="E21" s="7">
-        <v>0.04</v>
+        <v>-17.85</v>
+      </c>
+      <c r="E21" s="6">
+        <v>-3.27</v>
       </c>
     </row>
     <row r="22" spans="1:5">
@@ -1897,13 +1899,13 @@
         <v>10</v>
       </c>
       <c r="C22" s="5">
-        <v>19.4</v>
+        <v>20.51</v>
       </c>
       <c r="D22" s="5">
-        <v>20.51</v>
-      </c>
-      <c r="E22" s="7">
-        <v>1.11</v>
+        <v>8.970000000000001</v>
+      </c>
+      <c r="E22" s="6">
+        <v>-11.54</v>
       </c>
     </row>
     <row r="23" spans="1:5">
@@ -1914,13 +1916,13 @@
         <v>10</v>
       </c>
       <c r="C23" s="5">
-        <v>12.78</v>
+        <v>13.03</v>
       </c>
       <c r="D23" s="5">
-        <v>13.03</v>
-      </c>
-      <c r="E23" s="7">
-        <v>0.25</v>
+        <v>7.42</v>
+      </c>
+      <c r="E23" s="6">
+        <v>-5.61</v>
       </c>
     </row>
     <row r="24" spans="1:5">
@@ -1931,13 +1933,13 @@
         <v>10</v>
       </c>
       <c r="C24" s="5">
-        <v>-13.86</v>
+        <v>-9.94</v>
       </c>
       <c r="D24" s="5">
-        <v>-9.94</v>
-      </c>
-      <c r="E24" s="7">
-        <v>3.92</v>
+        <v>-10.23</v>
+      </c>
+      <c r="E24" s="6">
+        <v>-0.29</v>
       </c>
     </row>
     <row r="25" spans="1:5">
@@ -1948,13 +1950,13 @@
         <v>10</v>
       </c>
       <c r="C25" s="5">
-        <v>12.87</v>
+        <v>12.94</v>
       </c>
       <c r="D25" s="5">
-        <v>12.94</v>
-      </c>
-      <c r="E25" s="7">
-        <v>0.07000000000000001</v>
+        <v>8.279999999999999</v>
+      </c>
+      <c r="E25" s="6">
+        <v>-4.66</v>
       </c>
     </row>
     <row r="26" spans="1:5">
@@ -1965,13 +1967,13 @@
         <v>10</v>
       </c>
       <c r="C26" s="5">
-        <v>14.96</v>
+        <v>17.67</v>
       </c>
       <c r="D26" s="5">
-        <v>17.67</v>
-      </c>
-      <c r="E26" s="7">
-        <v>2.71</v>
+        <v>14.17</v>
+      </c>
+      <c r="E26" s="6">
+        <v>-3.5</v>
       </c>
     </row>
     <row r="27" spans="1:5">
@@ -1982,13 +1984,13 @@
         <v>6</v>
       </c>
       <c r="C27" s="5">
-        <v>-18.89</v>
+        <v>-19.85</v>
       </c>
       <c r="D27" s="5">
-        <v>-19.85</v>
+        <v>-20.28</v>
       </c>
       <c r="E27" s="6">
-        <v>-0.96</v>
+        <v>-0.43</v>
       </c>
     </row>
     <row r="28" spans="1:5">
@@ -1999,13 +2001,13 @@
         <v>6</v>
       </c>
       <c r="C28" s="5">
-        <v>-2.18</v>
+        <v>-3.05</v>
       </c>
       <c r="D28" s="5">
-        <v>-3.05</v>
-      </c>
-      <c r="E28" s="6">
-        <v>-0.87</v>
+        <v>-2.94</v>
+      </c>
+      <c r="E28" s="7">
+        <v>0.11</v>
       </c>
     </row>
     <row r="29" spans="1:5">
@@ -2016,13 +2018,13 @@
         <v>6</v>
       </c>
       <c r="C29" s="5">
-        <v>-27.35</v>
+        <v>-27.95</v>
       </c>
       <c r="D29" s="5">
-        <v>-27.95</v>
+        <v>-28.12</v>
       </c>
       <c r="E29" s="6">
-        <v>-0.6</v>
+        <v>-0.17</v>
       </c>
     </row>
     <row r="30" spans="1:5">
@@ -2033,13 +2035,13 @@
         <v>6</v>
       </c>
       <c r="C30" s="5">
-        <v>-6.7</v>
+        <v>-6.11</v>
       </c>
       <c r="D30" s="5">
-        <v>-6.11</v>
-      </c>
-      <c r="E30" s="7">
-        <v>0.59</v>
+        <v>-7.11</v>
+      </c>
+      <c r="E30" s="6">
+        <v>-1</v>
       </c>
     </row>
     <row r="31" spans="1:5">
@@ -2050,13 +2052,13 @@
         <v>6</v>
       </c>
       <c r="C31" s="5">
-        <v>-19.34</v>
+        <v>-19.06</v>
       </c>
       <c r="D31" s="5">
-        <v>-19.06</v>
-      </c>
-      <c r="E31" s="7">
-        <v>0.28</v>
+        <v>-19.89</v>
+      </c>
+      <c r="E31" s="6">
+        <v>-0.83</v>
       </c>
     </row>
     <row r="32" spans="1:5">
@@ -2067,13 +2069,13 @@
         <v>2</v>
       </c>
       <c r="C32" s="5">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="D32" s="5">
-        <v>167</v>
+        <v>166.12</v>
       </c>
       <c r="E32" s="6">
-        <v>-2</v>
+        <v>-0.88</v>
       </c>
     </row>
     <row r="33" spans="1:5">
@@ -2084,13 +2086,13 @@
         <v>2</v>
       </c>
       <c r="C33" s="5">
-        <v>435.6</v>
+        <v>431.7</v>
       </c>
       <c r="D33" s="5">
-        <v>431.7</v>
-      </c>
-      <c r="E33" s="6">
-        <v>-3.9</v>
+        <v>432.2</v>
+      </c>
+      <c r="E33" s="7">
+        <v>0.5</v>
       </c>
     </row>
     <row r="34" spans="1:5">
@@ -2101,13 +2103,13 @@
         <v>2</v>
       </c>
       <c r="C34" s="5">
-        <v>387.95</v>
+        <v>384.75</v>
       </c>
       <c r="D34" s="5">
-        <v>384.75</v>
+        <v>383.85</v>
       </c>
       <c r="E34" s="6">
-        <v>-3.2</v>
+        <v>-0.9</v>
       </c>
     </row>
     <row r="35" spans="1:5">
@@ -2118,13 +2120,13 @@
         <v>2</v>
       </c>
       <c r="C35" s="5">
-        <v>997.7</v>
+        <v>1004</v>
       </c>
       <c r="D35" s="5">
-        <v>1004</v>
-      </c>
-      <c r="E35" s="7">
-        <v>6.3</v>
+        <v>993.3</v>
+      </c>
+      <c r="E35" s="6">
+        <v>-10.7</v>
       </c>
     </row>
     <row r="36" spans="1:5">
@@ -2135,13 +2137,13 @@
         <v>2</v>
       </c>
       <c r="C36" s="5">
-        <v>2.92</v>
+        <v>2.93</v>
       </c>
       <c r="D36" s="5">
-        <v>2.93</v>
-      </c>
-      <c r="E36" s="7">
-        <v>0.01</v>
+        <v>2.9</v>
+      </c>
+      <c r="E36" s="6">
+        <v>-0.03</v>
       </c>
     </row>
     <row r="37" spans="1:5">
@@ -2149,169 +2151,203 @@
         <v>37</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C37" s="5">
-        <v>46.71</v>
+        <v>99</v>
       </c>
       <c r="D37" s="5">
-        <v>43.31</v>
+        <v>79</v>
       </c>
       <c r="E37" s="6">
-        <v>-3.4</v>
+        <v>-20</v>
       </c>
     </row>
     <row r="38" spans="1:5">
       <c r="A38" s="3" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="C38" s="5">
-        <v>65.08</v>
+        <v>79</v>
       </c>
       <c r="D38" s="5">
-        <v>62.38</v>
-      </c>
-      <c r="E38" s="6">
-        <v>-2.7</v>
+        <v>99</v>
+      </c>
+      <c r="E38" s="7">
+        <v>20</v>
       </c>
     </row>
     <row r="39" spans="1:5">
       <c r="A39" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C39" s="5">
-        <v>31.72</v>
+        <v>43.31</v>
       </c>
       <c r="D39" s="5">
-        <v>29.63</v>
+        <v>41.86</v>
       </c>
       <c r="E39" s="6">
-        <v>-2.09</v>
+        <v>-1.45</v>
       </c>
     </row>
     <row r="40" spans="1:5">
       <c r="A40" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C40" s="5">
-        <v>47.37</v>
+        <v>62.38</v>
       </c>
       <c r="D40" s="5">
-        <v>49.72</v>
+        <v>62.59</v>
       </c>
       <c r="E40" s="7">
-        <v>2.35</v>
+        <v>0.21</v>
       </c>
     </row>
     <row r="41" spans="1:5">
       <c r="A41" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>24</v>
       </c>
       <c r="C41" s="5">
-        <v>63.29</v>
+        <v>29.63</v>
       </c>
       <c r="D41" s="5">
-        <v>63.71</v>
-      </c>
-      <c r="E41" s="7">
-        <v>0.42</v>
+        <v>29.05</v>
+      </c>
+      <c r="E41" s="6">
+        <v>-0.58</v>
       </c>
     </row>
     <row r="42" spans="1:5">
       <c r="A42" s="3" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C42" s="5">
-        <v>-48.28</v>
+        <v>49.72</v>
       </c>
       <c r="D42" s="5">
-        <v>-52.49</v>
+        <v>45.97</v>
       </c>
       <c r="E42" s="6">
-        <v>-4.21</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="43" spans="1:5">
       <c r="A43" s="3" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="C43" s="5">
-        <v>-49.09</v>
+        <v>63.71</v>
       </c>
       <c r="D43" s="5">
-        <v>-69.43000000000001</v>
+        <v>61.42</v>
       </c>
       <c r="E43" s="6">
-        <v>-20.34</v>
+        <v>-2.29</v>
       </c>
     </row>
     <row r="44" spans="1:5">
       <c r="A44" s="3" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C44" s="5">
-        <v>34.49</v>
+        <v>-52.49</v>
       </c>
       <c r="D44" s="5">
-        <v>-30.77</v>
-      </c>
-      <c r="E44" s="6">
-        <v>-65.26000000000001</v>
+        <v>10.25</v>
+      </c>
+      <c r="E44" s="7">
+        <v>62.74</v>
       </c>
     </row>
     <row r="45" spans="1:5">
       <c r="A45" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C45" s="5">
-        <v>-12.52</v>
+        <v>-69.43000000000001</v>
       </c>
       <c r="D45" s="5">
-        <v>-17.5</v>
+        <v>-77.45</v>
       </c>
       <c r="E45" s="6">
-        <v>-4.98</v>
+        <v>-8.02</v>
       </c>
     </row>
     <row r="46" spans="1:5">
       <c r="A46" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>31</v>
       </c>
       <c r="C46" s="5">
-        <v>-55.66</v>
+        <v>-30.77</v>
       </c>
       <c r="D46" s="5">
+        <v>-63.08</v>
+      </c>
+      <c r="E46" s="6">
+        <v>-32.31</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="B47" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="5">
+        <v>-17.5</v>
+      </c>
+      <c r="D47" s="5">
+        <v>-18.1</v>
+      </c>
+      <c r="E47" s="6">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="B48" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="C48" s="5">
         <v>-46.52</v>
       </c>
-      <c r="E46" s="7">
-        <v>9.140000000000001</v>
+      <c r="D48" s="5">
+        <v>-65.18000000000001</v>
+      </c>
+      <c r="E48" s="6">
+        <v>-18.66</v>
       </c>
     </row>
   </sheetData>
@@ -2376,16 +2412,16 @@
         <v>5</v>
       </c>
       <c r="D2" s="10">
-        <v>49.8</v>
+        <v>48.2</v>
       </c>
       <c r="E2" s="10">
         <v>60</v>
       </c>
       <c r="F2" s="10">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="G2" s="10">
-        <v>10.8</v>
+        <v>5.7</v>
       </c>
       <c r="H2" s="10">
         <v>59.8</v>
@@ -2510,19 +2546,19 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="13">
-        <v>0.2416</v>
+        <v>0.2448</v>
       </c>
       <c r="B2" s="13">
-        <v>0.1121</v>
+        <v>0.1208</v>
       </c>
       <c r="C2" s="13">
-        <v>0.0274</v>
+        <v>0.0245</v>
       </c>
       <c r="D2" s="13">
-        <v>0.0069</v>
+        <v>0.0054</v>
       </c>
       <c r="E2" s="13">
-        <v>-0.2129</v>
+        <v>-0.2213</v>
       </c>
     </row>
   </sheetData>

--- a/HINDUJA_GROUP_Technical_Metrics.xlsx
+++ b/HINDUJA_GROUP_Technical_Metrics.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="211" uniqueCount="62">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="222" uniqueCount="71">
   <si>
     <t>Symbol</t>
   </si>
@@ -166,7 +166,34 @@
     <t>▶  SIGNAL EVENTS (vs Previous Run)</t>
   </si>
   <si>
-    <t>No signal events detected since last run.</t>
+    <t>Signal</t>
+  </si>
+  <si>
+    <t>Change</t>
+  </si>
+  <si>
+    <t>Direction</t>
+  </si>
+  <si>
+    <t>Prev Value</t>
+  </si>
+  <si>
+    <t>Curr Value</t>
+  </si>
+  <si>
+    <t>Near 52W High</t>
+  </si>
+  <si>
+    <t>-2.9% → -0.8%</t>
+  </si>
+  <si>
+    <t>🟢 BREAKOUT WATCH</t>
+  </si>
+  <si>
+    <t>-2.9%</t>
+  </si>
+  <si>
+    <t>-0.8%</t>
   </si>
   <si>
     <t>▶  NUMERIC METRIC CHANGES (vs Previous Run)</t>
@@ -252,14 +279,14 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C0006"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF006100"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -292,13 +319,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -368,17 +395,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="14">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="165" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -750,10 +778,8 @@
     <col min="13" max="13" width="10.7109375" customWidth="1"/>
     <col min="14" max="14" width="11.7109375" customWidth="1"/>
     <col min="15" max="15" width="10.7109375" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" customWidth="1"/>
-    <col min="17" max="17" width="9.7109375" customWidth="1"/>
-    <col min="18" max="18" width="8.7109375" customWidth="1"/>
-    <col min="19" max="19" width="9.7109375" customWidth="1"/>
+    <col min="16" max="17" width="8.7109375" customWidth="1"/>
+    <col min="18" max="19" width="9.7109375" customWidth="1"/>
     <col min="20" max="20" width="22.7109375" customWidth="1"/>
     <col min="21" max="21" width="9.7109375" customWidth="1"/>
     <col min="22" max="22" width="10.7109375" customWidth="1"/>
@@ -892,10 +918,10 @@
         <v>42</v>
       </c>
       <c r="C2">
-        <v>166.12</v>
+        <v>163.75</v>
       </c>
       <c r="D2">
-        <v>-0.53</v>
+        <v>-1.43</v>
       </c>
       <c r="E2">
         <v>208.37</v>
@@ -904,46 +930,46 @@
         <v>130.44</v>
       </c>
       <c r="G2">
-        <v>-20.28</v>
+        <v>-21.41</v>
       </c>
       <c r="H2">
-        <v>27.35</v>
+        <v>25.54</v>
       </c>
       <c r="I2">
-        <v>-1.91</v>
+        <v>-3.11</v>
       </c>
       <c r="J2">
-        <v>-5.99</v>
+        <v>-7.08</v>
       </c>
       <c r="K2">
-        <v>8.970000000000001</v>
+        <v>3.84</v>
       </c>
       <c r="L2">
-        <v>23.9</v>
+        <v>24.15</v>
       </c>
       <c r="M2">
-        <v>24.48</v>
+        <v>24.11</v>
       </c>
       <c r="N2">
-        <v>79</v>
+        <v>60</v>
       </c>
       <c r="O2">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="P2">
-        <v>168.22</v>
+        <v>167.17</v>
       </c>
       <c r="Q2">
-        <v>172.49</v>
+        <v>172.09</v>
       </c>
       <c r="R2">
-        <v>166.65</v>
+        <v>166.64</v>
       </c>
       <c r="S2">
-        <v>169.71</v>
+        <v>169.81</v>
       </c>
       <c r="T2">
-        <v>-2.11</v>
+        <v>-3.57</v>
       </c>
       <c r="U2" t="s">
         <v>43</v>
@@ -958,43 +984,43 @@
         <v>1</v>
       </c>
       <c r="Y2">
-        <v>41.86</v>
+        <v>38.17</v>
       </c>
       <c r="Z2">
-        <v>-0.19</v>
+        <v>-0.67</v>
       </c>
       <c r="AA2">
-        <v>1.22</v>
+        <v>0.84</v>
       </c>
       <c r="AB2">
-        <v>-1.4</v>
+        <v>-1.51</v>
       </c>
       <c r="AC2">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="AD2">
-        <v>8.91</v>
+        <v>4.48</v>
       </c>
       <c r="AE2">
-        <v>4.04</v>
+        <v>4.19</v>
       </c>
       <c r="AF2">
-        <v>10.25</v>
+        <v>27.15</v>
       </c>
       <c r="AG2">
-        <v>180.01</v>
+        <v>180.57</v>
       </c>
       <c r="AH2">
-        <v>164.97</v>
+        <v>163.62</v>
       </c>
       <c r="AI2">
-        <v>177.99</v>
+        <v>175.08</v>
       </c>
       <c r="AJ2" t="s">
         <v>45</v>
       </c>
       <c r="AK2">
-        <v>20.16</v>
+        <v>24.02</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -1005,10 +1031,10 @@
         <v>42</v>
       </c>
       <c r="C3">
-        <v>432.2</v>
+        <v>441.55</v>
       </c>
       <c r="D3">
-        <v>0.12</v>
+        <v>2.16</v>
       </c>
       <c r="E3">
         <v>445.3</v>
@@ -1017,46 +1043,46 @@
         <v>225</v>
       </c>
       <c r="G3">
-        <v>-2.94</v>
+        <v>-0.84</v>
       </c>
       <c r="H3">
-        <v>92.09</v>
+        <v>96.23999999999999</v>
       </c>
       <c r="I3">
-        <v>2.19</v>
+        <v>3.3</v>
       </c>
       <c r="J3">
-        <v>0.09</v>
+        <v>2.47</v>
       </c>
       <c r="K3">
-        <v>7.42</v>
+        <v>9.09</v>
       </c>
       <c r="L3">
-        <v>20.09</v>
+        <v>22.26</v>
       </c>
       <c r="M3">
-        <v>12.08</v>
+        <v>12.56</v>
       </c>
       <c r="N3">
-        <v>60</v>
+        <v>79</v>
       </c>
       <c r="O3">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="P3">
-        <v>432.78</v>
+        <v>435.6</v>
       </c>
       <c r="Q3">
-        <v>406.98</v>
+        <v>409.21</v>
       </c>
       <c r="R3">
-        <v>406.54</v>
+        <v>407.3</v>
       </c>
       <c r="S3">
-        <v>330.59</v>
+        <v>331.27</v>
       </c>
       <c r="T3">
-        <v>30.73</v>
+        <v>33.29</v>
       </c>
       <c r="U3" t="s">
         <v>43</v>
@@ -1071,43 +1097,43 @@
         <v>3</v>
       </c>
       <c r="Y3">
-        <v>62.59</v>
+        <v>66.45</v>
       </c>
       <c r="Z3">
-        <v>6.82</v>
+        <v>8.130000000000001</v>
       </c>
       <c r="AA3">
-        <v>2.68</v>
+        <v>3.77</v>
       </c>
       <c r="AB3">
-        <v>4.14</v>
+        <v>4.36</v>
       </c>
       <c r="AC3">
-        <v>89.76000000000001</v>
+        <v>90.95</v>
       </c>
       <c r="AD3">
-        <v>94.23999999999999</v>
+        <v>91.62</v>
       </c>
       <c r="AE3">
-        <v>13.83</v>
+        <v>14.25</v>
       </c>
       <c r="AF3">
-        <v>-77.45</v>
+        <v>-43.68</v>
       </c>
       <c r="AG3">
-        <v>441.07</v>
+        <v>446.24</v>
       </c>
       <c r="AH3">
-        <v>372.9</v>
+        <v>372.17</v>
       </c>
       <c r="AI3">
-        <v>393.52</v>
+        <v>393.69</v>
       </c>
       <c r="AJ3" t="s">
         <v>46</v>
       </c>
       <c r="AK3">
-        <v>47.25</v>
+        <v>49.32</v>
       </c>
     </row>
     <row r="4" spans="1:37">
@@ -1118,10 +1144,10 @@
         <v>42</v>
       </c>
       <c r="C4">
-        <v>383.85</v>
+        <v>381.45</v>
       </c>
       <c r="D4">
-        <v>-0.23</v>
+        <v>-0.63</v>
       </c>
       <c r="E4">
         <v>534</v>
@@ -1130,46 +1156,46 @@
         <v>344.7</v>
       </c>
       <c r="G4">
-        <v>-28.12</v>
+        <v>-28.57</v>
       </c>
       <c r="H4">
-        <v>11.36</v>
+        <v>10.66</v>
       </c>
       <c r="I4">
-        <v>-2.33</v>
+        <v>-4.46</v>
       </c>
       <c r="J4">
-        <v>-5.63</v>
+        <v>-5.74</v>
       </c>
       <c r="K4">
-        <v>-10.23</v>
+        <v>-11</v>
       </c>
       <c r="L4">
-        <v>-26.73</v>
+        <v>-27.33</v>
       </c>
       <c r="M4">
-        <v>-22.13</v>
+        <v>-22.21</v>
       </c>
       <c r="N4">
         <v>21</v>
       </c>
       <c r="O4">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="P4">
-        <v>390.27</v>
+        <v>386.71</v>
       </c>
       <c r="Q4">
-        <v>399.37</v>
+        <v>398.01</v>
       </c>
       <c r="R4">
-        <v>413.1</v>
+        <v>412.4</v>
       </c>
       <c r="S4">
-        <v>413.54</v>
+        <v>413.05</v>
       </c>
       <c r="T4">
-        <v>-7.18</v>
+        <v>-7.65</v>
       </c>
       <c r="U4" t="s">
         <v>44</v>
@@ -1184,43 +1210,43 @@
         <v>0</v>
       </c>
       <c r="Y4">
-        <v>29.05</v>
+        <v>27.5</v>
       </c>
       <c r="Z4">
-        <v>-7.44</v>
+        <v>-7.88</v>
       </c>
       <c r="AA4">
-        <v>-6.35</v>
+        <v>-6.65</v>
       </c>
       <c r="AB4">
-        <v>-1.09</v>
+        <v>-1.23</v>
       </c>
       <c r="AC4">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="AD4">
-        <v>24.94</v>
+        <v>7.77</v>
       </c>
       <c r="AE4">
-        <v>11.21</v>
+        <v>10.89</v>
       </c>
       <c r="AF4">
-        <v>-63.08</v>
+        <v>-40.08</v>
       </c>
       <c r="AG4">
-        <v>415.37</v>
+        <v>415.27</v>
       </c>
       <c r="AH4">
-        <v>383.38</v>
+        <v>380.76</v>
       </c>
       <c r="AI4">
-        <v>419.77</v>
+        <v>413.11</v>
       </c>
       <c r="AJ4" t="s">
         <v>45</v>
       </c>
       <c r="AK4">
-        <v>20.19</v>
+        <v>23.49</v>
       </c>
     </row>
     <row r="5" spans="1:37">
@@ -1231,10 +1257,10 @@
         <v>42</v>
       </c>
       <c r="C5">
-        <v>993.3</v>
+        <v>978.2</v>
       </c>
       <c r="D5">
-        <v>-1.07</v>
+        <v>-1.52</v>
       </c>
       <c r="E5">
         <v>1069.3</v>
@@ -1243,46 +1269,46 @@
         <v>712.75</v>
       </c>
       <c r="G5">
-        <v>-7.11</v>
+        <v>-8.52</v>
       </c>
       <c r="H5">
-        <v>39.36</v>
+        <v>37.24</v>
       </c>
       <c r="I5">
-        <v>-1.14</v>
+        <v>-3</v>
       </c>
       <c r="J5">
-        <v>-2.38</v>
+        <v>-4.54</v>
       </c>
       <c r="K5">
-        <v>8.279999999999999</v>
+        <v>4.82</v>
       </c>
       <c r="L5">
-        <v>32.31</v>
+        <v>31.1</v>
       </c>
       <c r="M5">
-        <v>0.54</v>
+        <v>0.23</v>
       </c>
       <c r="N5">
         <v>99</v>
       </c>
       <c r="O5">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="P5">
-        <v>1000.3</v>
+        <v>994.24</v>
       </c>
       <c r="Q5">
-        <v>1005.73</v>
+        <v>1003.6</v>
       </c>
       <c r="R5">
-        <v>1012</v>
+        <v>1012.07</v>
       </c>
       <c r="S5">
-        <v>918.02</v>
+        <v>918.71</v>
       </c>
       <c r="T5">
-        <v>8.199999999999999</v>
+        <v>6.48</v>
       </c>
       <c r="U5" t="s">
         <v>44</v>
@@ -1297,34 +1323,34 @@
         <v>2</v>
       </c>
       <c r="Y5">
-        <v>45.97</v>
+        <v>41.24</v>
       </c>
       <c r="Z5">
-        <v>-2.84</v>
+        <v>-4.46</v>
       </c>
       <c r="AA5">
-        <v>-1.41</v>
+        <v>-2.02</v>
       </c>
       <c r="AB5">
-        <v>-1.43</v>
+        <v>-2.44</v>
       </c>
       <c r="AC5">
-        <v>57.17</v>
+        <v>42.17</v>
       </c>
       <c r="AD5">
-        <v>60.6</v>
+        <v>53.4</v>
       </c>
       <c r="AE5">
-        <v>19.96</v>
+        <v>20.03</v>
       </c>
       <c r="AF5">
-        <v>-18.1</v>
+        <v>110.42</v>
       </c>
       <c r="AG5">
-        <v>1028.26</v>
+        <v>1028.1</v>
       </c>
       <c r="AH5">
-        <v>983.21</v>
+        <v>979.11</v>
       </c>
       <c r="AI5">
         <v>1038.34</v>
@@ -1333,7 +1359,7 @@
         <v>45</v>
       </c>
       <c r="AK5">
-        <v>11.96</v>
+        <v>13.19</v>
       </c>
     </row>
     <row r="6" spans="1:37">
@@ -1344,10 +1370,10 @@
         <v>42</v>
       </c>
       <c r="C6">
-        <v>2.9</v>
+        <v>2.86</v>
       </c>
       <c r="D6">
-        <v>-1.02</v>
+        <v>-1.38</v>
       </c>
       <c r="E6">
         <v>3.62</v>
@@ -1356,37 +1382,37 @@
         <v>1.84</v>
       </c>
       <c r="G6">
-        <v>-19.89</v>
+        <v>-20.99</v>
       </c>
       <c r="H6">
-        <v>57.61</v>
+        <v>55.43</v>
       </c>
       <c r="I6">
-        <v>2.47</v>
+        <v>1.06</v>
       </c>
       <c r="J6">
-        <v>23.93</v>
+        <v>21.19</v>
       </c>
       <c r="K6">
-        <v>14.17</v>
+        <v>9.58</v>
       </c>
       <c r="L6">
-        <v>-17.85</v>
+        <v>-18.52</v>
       </c>
       <c r="M6">
-        <v>2.45</v>
+        <v>2.16</v>
       </c>
       <c r="N6">
         <v>40</v>
       </c>
       <c r="O6">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="P6">
-        <v>2.91</v>
+        <v>2.92</v>
       </c>
       <c r="Q6">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="R6">
         <v>2.52</v>
@@ -1395,7 +1421,7 @@
         <v>2.68</v>
       </c>
       <c r="T6">
-        <v>8.24</v>
+        <v>6.78</v>
       </c>
       <c r="U6" t="s">
         <v>43</v>
@@ -1410,34 +1436,34 @@
         <v>2</v>
       </c>
       <c r="Y6">
-        <v>61.42</v>
+        <v>58.4</v>
       </c>
       <c r="Z6">
-        <v>0.13</v>
+        <v>0.12</v>
       </c>
       <c r="AA6">
         <v>0.13</v>
       </c>
       <c r="AB6">
-        <v>-0</v>
+        <v>-0.01</v>
       </c>
       <c r="AC6">
-        <v>22.3</v>
+        <v>3.37</v>
       </c>
       <c r="AD6">
-        <v>42.29</v>
+        <v>23.49</v>
       </c>
       <c r="AE6">
         <v>0.13</v>
       </c>
       <c r="AF6">
-        <v>-65.18000000000001</v>
+        <v>-71.44</v>
       </c>
       <c r="AG6">
-        <v>3.35</v>
+        <v>3.34</v>
       </c>
       <c r="AH6">
-        <v>2.17</v>
+        <v>2.23</v>
       </c>
       <c r="AI6">
         <v>2.65</v>
@@ -1446,7 +1472,7 @@
         <v>46</v>
       </c>
       <c r="AK6">
-        <v>43.98</v>
+        <v>40.28</v>
       </c>
     </row>
   </sheetData>
@@ -1607,12 +1633,47 @@
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="3" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>48</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>50</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="F2" s="3" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="4" t="s">
+        <v>38</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>53</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>54</v>
+      </c>
+      <c r="D3" s="4" t="s">
+        <v>55</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>49</v>
+        <v>58</v>
       </c>
       <c r="B5" s="2"/>
       <c r="C5" s="2"/>
@@ -1620,734 +1681,734 @@
       <c r="E5" s="2"/>
     </row>
     <row r="6" spans="1:6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>50</v>
-      </c>
-      <c r="C6" s="4" t="s">
-        <v>51</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>52</v>
-      </c>
-      <c r="E6" s="4" t="s">
-        <v>53</v>
+      <c r="B6" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>60</v>
+      </c>
+      <c r="D6" s="3" t="s">
+        <v>61</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:6">
-      <c r="A7" s="3" t="s">
+      <c r="A7" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="3" t="s">
+      <c r="B7" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="5">
-        <v>-4.48</v>
-      </c>
-      <c r="D7" s="5">
+      <c r="C7" s="6">
         <v>-5.99</v>
       </c>
-      <c r="E7" s="6">
-        <v>-1.51</v>
+      <c r="D7" s="6">
+        <v>-7.08</v>
+      </c>
+      <c r="E7" s="7">
+        <v>-1.09</v>
       </c>
     </row>
     <row r="8" spans="1:6">
-      <c r="A8" s="3" t="s">
+      <c r="A8" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B8" s="3" t="s">
+      <c r="B8" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C8" s="5">
-        <v>0.5</v>
-      </c>
-      <c r="D8" s="5">
+      <c r="C8" s="6">
         <v>0.09</v>
       </c>
-      <c r="E8" s="6">
-        <v>-0.41</v>
+      <c r="D8" s="6">
+        <v>2.47</v>
+      </c>
+      <c r="E8" s="8">
+        <v>2.38</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="A9" s="3" t="s">
+      <c r="A9" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B9" s="3" t="s">
+      <c r="B9" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="5">
-        <v>-6.46</v>
-      </c>
-      <c r="D9" s="5">
+      <c r="C9" s="6">
         <v>-5.63</v>
       </c>
+      <c r="D9" s="6">
+        <v>-5.74</v>
+      </c>
       <c r="E9" s="7">
-        <v>0.83</v>
+        <v>-0.11</v>
       </c>
     </row>
     <row r="10" spans="1:6">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C10" s="5">
-        <v>-0.49</v>
-      </c>
-      <c r="D10" s="5">
+      <c r="C10" s="6">
         <v>-2.38</v>
       </c>
-      <c r="E10" s="6">
-        <v>-1.89</v>
+      <c r="D10" s="6">
+        <v>-4.54</v>
+      </c>
+      <c r="E10" s="7">
+        <v>-2.16</v>
       </c>
     </row>
     <row r="11" spans="1:6">
-      <c r="A11" s="3" t="s">
+      <c r="A11" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B11" s="3" t="s">
+      <c r="B11" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C11" s="5">
-        <v>26.29</v>
-      </c>
-      <c r="D11" s="5">
+      <c r="C11" s="6">
         <v>23.93</v>
       </c>
-      <c r="E11" s="6">
-        <v>-2.36</v>
+      <c r="D11" s="6">
+        <v>21.19</v>
+      </c>
+      <c r="E11" s="7">
+        <v>-2.74</v>
       </c>
     </row>
     <row r="12" spans="1:6">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C12" s="5">
-        <v>-0.54</v>
-      </c>
-      <c r="D12" s="5">
+      <c r="C12" s="6">
         <v>-1.91</v>
       </c>
-      <c r="E12" s="6">
-        <v>-1.37</v>
+      <c r="D12" s="6">
+        <v>-3.11</v>
+      </c>
+      <c r="E12" s="7">
+        <v>-1.2</v>
       </c>
     </row>
     <row r="13" spans="1:6">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C13" s="5">
-        <v>10.21</v>
-      </c>
-      <c r="D13" s="5">
+      <c r="C13" s="6">
         <v>2.19</v>
       </c>
-      <c r="E13" s="6">
-        <v>-8.02</v>
+      <c r="D13" s="6">
+        <v>3.3</v>
+      </c>
+      <c r="E13" s="8">
+        <v>1.11</v>
       </c>
     </row>
     <row r="14" spans="1:6">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B14" s="3" t="s">
+      <c r="B14" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C14" s="5">
-        <v>-2.12</v>
-      </c>
-      <c r="D14" s="5">
+      <c r="C14" s="6">
         <v>-2.33</v>
       </c>
-      <c r="E14" s="6">
-        <v>-0.21</v>
+      <c r="D14" s="6">
+        <v>-4.46</v>
+      </c>
+      <c r="E14" s="7">
+        <v>-2.13</v>
       </c>
     </row>
     <row r="15" spans="1:6">
-      <c r="A15" s="3" t="s">
+      <c r="A15" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="3" t="s">
+      <c r="B15" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C15" s="5">
-        <v>2.66</v>
-      </c>
-      <c r="D15" s="5">
+      <c r="C15" s="6">
         <v>-1.14</v>
       </c>
-      <c r="E15" s="6">
-        <v>-3.8</v>
+      <c r="D15" s="6">
+        <v>-3</v>
+      </c>
+      <c r="E15" s="7">
+        <v>-1.86</v>
       </c>
     </row>
     <row r="16" spans="1:6">
-      <c r="A16" s="3" t="s">
+      <c r="A16" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B16" s="3" t="s">
+      <c r="B16" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="C16" s="5">
-        <v>2.81</v>
-      </c>
-      <c r="D16" s="5">
+      <c r="C16" s="6">
         <v>2.47</v>
       </c>
-      <c r="E16" s="6">
-        <v>-0.34</v>
+      <c r="D16" s="6">
+        <v>1.06</v>
+      </c>
+      <c r="E16" s="7">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="3" t="s">
+      <c r="A17" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="3" t="s">
+      <c r="B17" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C17" s="5">
-        <v>30.77</v>
-      </c>
-      <c r="D17" s="5">
+      <c r="C17" s="6">
         <v>23.9</v>
       </c>
-      <c r="E17" s="6">
-        <v>-6.87</v>
+      <c r="D17" s="6">
+        <v>24.15</v>
+      </c>
+      <c r="E17" s="8">
+        <v>0.25</v>
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="3" t="s">
+      <c r="A18" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B18" s="3" t="s">
+      <c r="B18" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C18" s="5">
-        <v>20.07</v>
-      </c>
-      <c r="D18" s="5">
+      <c r="C18" s="6">
         <v>20.09</v>
       </c>
-      <c r="E18" s="7">
-        <v>0.02</v>
+      <c r="D18" s="6">
+        <v>22.26</v>
+      </c>
+      <c r="E18" s="8">
+        <v>2.17</v>
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="3" t="s">
+      <c r="A19" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B19" s="3" t="s">
+      <c r="B19" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C19" s="5">
-        <v>-26.05</v>
-      </c>
-      <c r="D19" s="5">
+      <c r="C19" s="6">
         <v>-26.73</v>
       </c>
-      <c r="E19" s="6">
-        <v>-0.68</v>
+      <c r="D19" s="6">
+        <v>-27.33</v>
+      </c>
+      <c r="E19" s="7">
+        <v>-0.6</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="3" t="s">
+      <c r="A20" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B20" s="3" t="s">
+      <c r="B20" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C20" s="5">
-        <v>32.62</v>
-      </c>
-      <c r="D20" s="5">
+      <c r="C20" s="6">
         <v>32.31</v>
       </c>
-      <c r="E20" s="6">
-        <v>-0.31</v>
+      <c r="D20" s="6">
+        <v>31.1</v>
+      </c>
+      <c r="E20" s="7">
+        <v>-1.21</v>
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="3" t="s">
+      <c r="A21" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B21" s="3" t="s">
+      <c r="B21" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="C21" s="5">
-        <v>-14.58</v>
-      </c>
-      <c r="D21" s="5">
+      <c r="C21" s="6">
         <v>-17.85</v>
       </c>
-      <c r="E21" s="6">
-        <v>-3.27</v>
+      <c r="D21" s="6">
+        <v>-18.52</v>
+      </c>
+      <c r="E21" s="7">
+        <v>-0.67</v>
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="3" t="s">
+      <c r="A22" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B22" s="3" t="s">
+      <c r="B22" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C22" s="5">
-        <v>20.51</v>
-      </c>
-      <c r="D22" s="5">
+      <c r="C22" s="6">
         <v>8.970000000000001</v>
       </c>
-      <c r="E22" s="6">
-        <v>-11.54</v>
+      <c r="D22" s="6">
+        <v>3.84</v>
+      </c>
+      <c r="E22" s="7">
+        <v>-5.13</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="3" t="s">
+      <c r="A23" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B23" s="3" t="s">
+      <c r="B23" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C23" s="5">
-        <v>13.03</v>
-      </c>
-      <c r="D23" s="5">
+      <c r="C23" s="6">
         <v>7.42</v>
       </c>
-      <c r="E23" s="6">
-        <v>-5.61</v>
+      <c r="D23" s="6">
+        <v>9.09</v>
+      </c>
+      <c r="E23" s="8">
+        <v>1.67</v>
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="3" t="s">
+      <c r="A24" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B24" s="3" t="s">
+      <c r="B24" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C24" s="5">
-        <v>-9.94</v>
-      </c>
-      <c r="D24" s="5">
+      <c r="C24" s="6">
         <v>-10.23</v>
       </c>
-      <c r="E24" s="6">
-        <v>-0.29</v>
+      <c r="D24" s="6">
+        <v>-11</v>
+      </c>
+      <c r="E24" s="7">
+        <v>-0.77</v>
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="3" t="s">
+      <c r="A25" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B25" s="3" t="s">
+      <c r="B25" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C25" s="5">
-        <v>12.94</v>
-      </c>
-      <c r="D25" s="5">
+      <c r="C25" s="6">
         <v>8.279999999999999</v>
       </c>
-      <c r="E25" s="6">
-        <v>-4.66</v>
+      <c r="D25" s="6">
+        <v>4.82</v>
+      </c>
+      <c r="E25" s="7">
+        <v>-3.46</v>
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="3" t="s">
+      <c r="A26" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B26" s="3" t="s">
+      <c r="B26" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="C26" s="5">
-        <v>17.67</v>
-      </c>
-      <c r="D26" s="5">
+      <c r="C26" s="6">
         <v>14.17</v>
       </c>
-      <c r="E26" s="6">
-        <v>-3.5</v>
+      <c r="D26" s="6">
+        <v>9.58</v>
+      </c>
+      <c r="E26" s="7">
+        <v>-4.59</v>
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="3" t="s">
+      <c r="A27" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B27" s="3" t="s">
+      <c r="B27" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C27" s="5">
-        <v>-19.85</v>
-      </c>
-      <c r="D27" s="5">
+      <c r="C27" s="6">
         <v>-20.28</v>
       </c>
-      <c r="E27" s="6">
-        <v>-0.43</v>
+      <c r="D27" s="6">
+        <v>-21.41</v>
+      </c>
+      <c r="E27" s="7">
+        <v>-1.13</v>
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="3" t="s">
+      <c r="A28" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B28" s="3" t="s">
+      <c r="B28" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C28" s="5">
-        <v>-3.05</v>
-      </c>
-      <c r="D28" s="5">
+      <c r="C28" s="6">
         <v>-2.94</v>
       </c>
-      <c r="E28" s="7">
-        <v>0.11</v>
+      <c r="D28" s="6">
+        <v>-0.84</v>
+      </c>
+      <c r="E28" s="8">
+        <v>2.1</v>
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="3" t="s">
+      <c r="A29" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="3" t="s">
+      <c r="B29" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C29" s="5">
-        <v>-27.95</v>
-      </c>
-      <c r="D29" s="5">
+      <c r="C29" s="6">
         <v>-28.12</v>
       </c>
-      <c r="E29" s="6">
-        <v>-0.17</v>
+      <c r="D29" s="6">
+        <v>-28.57</v>
+      </c>
+      <c r="E29" s="7">
+        <v>-0.45</v>
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="3" t="s">
+      <c r="A30" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B30" s="3" t="s">
+      <c r="B30" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C30" s="5">
-        <v>-6.11</v>
-      </c>
-      <c r="D30" s="5">
+      <c r="C30" s="6">
         <v>-7.11</v>
       </c>
-      <c r="E30" s="6">
-        <v>-1</v>
+      <c r="D30" s="6">
+        <v>-8.52</v>
+      </c>
+      <c r="E30" s="7">
+        <v>-1.41</v>
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="3" t="s">
+      <c r="A31" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B31" s="3" t="s">
+      <c r="B31" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="C31" s="5">
-        <v>-19.06</v>
-      </c>
-      <c r="D31" s="5">
+      <c r="C31" s="6">
         <v>-19.89</v>
       </c>
-      <c r="E31" s="6">
-        <v>-0.83</v>
+      <c r="D31" s="6">
+        <v>-20.99</v>
+      </c>
+      <c r="E31" s="7">
+        <v>-1.1</v>
       </c>
     </row>
     <row r="32" spans="1:5">
-      <c r="A32" s="3" t="s">
+      <c r="A32" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B32" s="3" t="s">
+      <c r="B32" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C32" s="5">
-        <v>167</v>
-      </c>
-      <c r="D32" s="5">
+      <c r="C32" s="6">
         <v>166.12</v>
       </c>
-      <c r="E32" s="6">
-        <v>-0.88</v>
+      <c r="D32" s="6">
+        <v>163.75</v>
+      </c>
+      <c r="E32" s="7">
+        <v>-2.37</v>
       </c>
     </row>
     <row r="33" spans="1:5">
-      <c r="A33" s="3" t="s">
+      <c r="A33" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B33" s="3" t="s">
+      <c r="B33" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C33" s="5">
-        <v>431.7</v>
-      </c>
-      <c r="D33" s="5">
+      <c r="C33" s="6">
         <v>432.2</v>
       </c>
-      <c r="E33" s="7">
-        <v>0.5</v>
+      <c r="D33" s="6">
+        <v>441.55</v>
+      </c>
+      <c r="E33" s="8">
+        <v>9.35</v>
       </c>
     </row>
     <row r="34" spans="1:5">
-      <c r="A34" s="3" t="s">
+      <c r="A34" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B34" s="3" t="s">
+      <c r="B34" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C34" s="5">
-        <v>384.75</v>
-      </c>
-      <c r="D34" s="5">
+      <c r="C34" s="6">
         <v>383.85</v>
       </c>
-      <c r="E34" s="6">
-        <v>-0.9</v>
+      <c r="D34" s="6">
+        <v>381.45</v>
+      </c>
+      <c r="E34" s="7">
+        <v>-2.4</v>
       </c>
     </row>
     <row r="35" spans="1:5">
-      <c r="A35" s="3" t="s">
+      <c r="A35" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B35" s="3" t="s">
+      <c r="B35" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C35" s="5">
-        <v>1004</v>
-      </c>
-      <c r="D35" s="5">
+      <c r="C35" s="6">
         <v>993.3</v>
       </c>
-      <c r="E35" s="6">
-        <v>-10.7</v>
+      <c r="D35" s="6">
+        <v>978.2</v>
+      </c>
+      <c r="E35" s="7">
+        <v>-15.1</v>
       </c>
     </row>
     <row r="36" spans="1:5">
-      <c r="A36" s="3" t="s">
+      <c r="A36" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B36" s="3" t="s">
+      <c r="B36" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="C36" s="5">
-        <v>2.93</v>
-      </c>
-      <c r="D36" s="5">
+      <c r="C36" s="6">
         <v>2.9</v>
       </c>
-      <c r="E36" s="6">
-        <v>-0.03</v>
+      <c r="D36" s="6">
+        <v>2.86</v>
+      </c>
+      <c r="E36" s="7">
+        <v>-0.04</v>
       </c>
     </row>
     <row r="37" spans="1:5">
-      <c r="A37" s="3" t="s">
+      <c r="A37" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B37" s="3" t="s">
+      <c r="B37" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="C37" s="5">
-        <v>99</v>
-      </c>
-      <c r="D37" s="5">
+      <c r="C37" s="6">
         <v>79</v>
       </c>
-      <c r="E37" s="6">
-        <v>-20</v>
+      <c r="D37" s="6">
+        <v>60</v>
+      </c>
+      <c r="E37" s="7">
+        <v>-19</v>
       </c>
     </row>
     <row r="38" spans="1:5">
-      <c r="A38" s="3" t="s">
+      <c r="A38" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B38" s="5" t="s">
+        <v>13</v>
+      </c>
+      <c r="C38" s="6">
+        <v>60</v>
+      </c>
+      <c r="D38" s="6">
+        <v>79</v>
+      </c>
+      <c r="E38" s="8">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="39" spans="1:5">
+      <c r="A39" s="5" t="s">
+        <v>37</v>
+      </c>
+      <c r="B39" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C39" s="6">
+        <v>41.86</v>
+      </c>
+      <c r="D39" s="6">
+        <v>38.17</v>
+      </c>
+      <c r="E39" s="7">
+        <v>-3.69</v>
+      </c>
+    </row>
+    <row r="40" spans="1:5">
+      <c r="A40" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="B40" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C40" s="6">
+        <v>62.59</v>
+      </c>
+      <c r="D40" s="6">
+        <v>66.45</v>
+      </c>
+      <c r="E40" s="8">
+        <v>3.86</v>
+      </c>
+    </row>
+    <row r="41" spans="1:5">
+      <c r="A41" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="B41" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C41" s="6">
+        <v>29.05</v>
+      </c>
+      <c r="D41" s="6">
+        <v>27.5</v>
+      </c>
+      <c r="E41" s="7">
+        <v>-1.55</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5">
+      <c r="A42" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B38" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="C38" s="5">
-        <v>79</v>
-      </c>
-      <c r="D38" s="5">
-        <v>99</v>
-      </c>
-      <c r="E38" s="7">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="39" spans="1:5">
-      <c r="A39" s="3" t="s">
+      <c r="B42" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C42" s="6">
+        <v>45.97</v>
+      </c>
+      <c r="D42" s="6">
+        <v>41.24</v>
+      </c>
+      <c r="E42" s="7">
+        <v>-4.73</v>
+      </c>
+    </row>
+    <row r="43" spans="1:5">
+      <c r="A43" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B43" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C43" s="6">
+        <v>61.42</v>
+      </c>
+      <c r="D43" s="6">
+        <v>58.4</v>
+      </c>
+      <c r="E43" s="7">
+        <v>-3.02</v>
+      </c>
+    </row>
+    <row r="44" spans="1:5">
+      <c r="A44" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="B39" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C39" s="5">
-        <v>43.31</v>
-      </c>
-      <c r="D39" s="5">
-        <v>41.86</v>
-      </c>
-      <c r="E39" s="6">
-        <v>-1.45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:5">
-      <c r="A40" s="3" t="s">
+      <c r="B44" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C44" s="6">
+        <v>10.25</v>
+      </c>
+      <c r="D44" s="6">
+        <v>27.15</v>
+      </c>
+      <c r="E44" s="8">
+        <v>16.9</v>
+      </c>
+    </row>
+    <row r="45" spans="1:5">
+      <c r="A45" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="B40" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C40" s="5">
-        <v>62.38</v>
-      </c>
-      <c r="D40" s="5">
-        <v>62.59</v>
-      </c>
-      <c r="E40" s="7">
-        <v>0.21</v>
-      </c>
-    </row>
-    <row r="41" spans="1:5">
-      <c r="A41" s="3" t="s">
+      <c r="B45" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C45" s="6">
+        <v>-77.45</v>
+      </c>
+      <c r="D45" s="6">
+        <v>-43.68</v>
+      </c>
+      <c r="E45" s="8">
+        <v>33.77</v>
+      </c>
+    </row>
+    <row r="46" spans="1:5">
+      <c r="A46" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="B41" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C41" s="5">
-        <v>29.63</v>
-      </c>
-      <c r="D41" s="5">
-        <v>29.05</v>
-      </c>
-      <c r="E41" s="6">
-        <v>-0.58</v>
-      </c>
-    </row>
-    <row r="42" spans="1:5">
-      <c r="A42" s="3" t="s">
+      <c r="B46" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C46" s="6">
+        <v>-63.08</v>
+      </c>
+      <c r="D46" s="6">
+        <v>-40.08</v>
+      </c>
+      <c r="E46" s="8">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="47" spans="1:5">
+      <c r="A47" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C42" s="5">
-        <v>49.72</v>
-      </c>
-      <c r="D42" s="5">
-        <v>45.97</v>
-      </c>
-      <c r="E42" s="6">
-        <v>-3.75</v>
-      </c>
-    </row>
-    <row r="43" spans="1:5">
-      <c r="A43" s="3" t="s">
+      <c r="B47" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C47" s="6">
+        <v>-18.1</v>
+      </c>
+      <c r="D47" s="6">
+        <v>110.42</v>
+      </c>
+      <c r="E47" s="8">
+        <v>128.52</v>
+      </c>
+    </row>
+    <row r="48" spans="1:5">
+      <c r="A48" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="B43" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="C43" s="5">
-        <v>63.71</v>
-      </c>
-      <c r="D43" s="5">
-        <v>61.42</v>
-      </c>
-      <c r="E43" s="6">
-        <v>-2.29</v>
-      </c>
-    </row>
-    <row r="44" spans="1:5">
-      <c r="A44" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="B44" s="3" t="s">
+      <c r="B48" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="C44" s="5">
-        <v>-52.49</v>
-      </c>
-      <c r="D44" s="5">
-        <v>10.25</v>
-      </c>
-      <c r="E44" s="7">
-        <v>62.74</v>
-      </c>
-    </row>
-    <row r="45" spans="1:5">
-      <c r="A45" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B45" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C45" s="5">
-        <v>-69.43000000000001</v>
-      </c>
-      <c r="D45" s="5">
-        <v>-77.45</v>
-      </c>
-      <c r="E45" s="6">
-        <v>-8.02</v>
-      </c>
-    </row>
-    <row r="46" spans="1:5">
-      <c r="A46" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="B46" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C46" s="5">
-        <v>-30.77</v>
-      </c>
-      <c r="D46" s="5">
-        <v>-63.08</v>
-      </c>
-      <c r="E46" s="6">
-        <v>-32.31</v>
-      </c>
-    </row>
-    <row r="47" spans="1:5">
-      <c r="A47" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="B47" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C47" s="5">
-        <v>-17.5</v>
-      </c>
-      <c r="D47" s="5">
-        <v>-18.1</v>
-      </c>
-      <c r="E47" s="6">
-        <v>-0.6</v>
-      </c>
-    </row>
-    <row r="48" spans="1:5">
-      <c r="A48" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="B48" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="C48" s="5">
-        <v>-46.52</v>
-      </c>
-      <c r="D48" s="5">
+      <c r="C48" s="6">
         <v>-65.18000000000001</v>
       </c>
-      <c r="E48" s="6">
-        <v>-18.66</v>
+      <c r="D48" s="6">
+        <v>-71.44</v>
+      </c>
+      <c r="E48" s="7">
+        <v>-6.26</v>
       </c>
     </row>
   </sheetData>
@@ -2373,60 +2434,60 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="28" customHeight="1">
-      <c r="A1" s="8" t="s">
+      <c r="A1" s="9" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="8" t="s">
-        <v>54</v>
-      </c>
-      <c r="C1" s="8" t="s">
-        <v>55</v>
-      </c>
-      <c r="D1" s="8" t="s">
-        <v>56</v>
-      </c>
-      <c r="E1" s="8" t="s">
-        <v>57</v>
-      </c>
-      <c r="F1" s="8" t="s">
-        <v>58</v>
-      </c>
-      <c r="G1" s="8" t="s">
-        <v>59</v>
-      </c>
-      <c r="H1" s="8" t="s">
+      <c r="B1" s="9" t="s">
+        <v>63</v>
+      </c>
+      <c r="C1" s="9" t="s">
+        <v>64</v>
+      </c>
+      <c r="D1" s="9" t="s">
+        <v>65</v>
+      </c>
+      <c r="E1" s="9" t="s">
+        <v>66</v>
+      </c>
+      <c r="F1" s="9" t="s">
+        <v>67</v>
+      </c>
+      <c r="G1" s="9" t="s">
+        <v>68</v>
+      </c>
+      <c r="H1" s="9" t="s">
+        <v>69</v>
+      </c>
+      <c r="I1" s="9" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="B2" s="11">
+        <v>57.92</v>
+      </c>
+      <c r="C2" s="12">
+        <v>5</v>
+      </c>
+      <c r="D2" s="11">
+        <v>46.4</v>
+      </c>
+      <c r="E2" s="11">
         <v>60</v>
       </c>
-      <c r="I1" s="8" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
-      <c r="A2" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="B2" s="10">
-        <v>57.92</v>
-      </c>
-      <c r="C2" s="11">
-        <v>5</v>
-      </c>
-      <c r="D2" s="10">
-        <v>48.2</v>
-      </c>
-      <c r="E2" s="10">
-        <v>60</v>
-      </c>
-      <c r="F2" s="10">
-        <v>2</v>
-      </c>
-      <c r="G2" s="10">
-        <v>5.7</v>
-      </c>
-      <c r="H2" s="10">
+      <c r="F2" s="11">
+        <v>1.3</v>
+      </c>
+      <c r="G2" s="11">
+        <v>3.3</v>
+      </c>
+      <c r="H2" s="11">
         <v>59.8</v>
       </c>
-      <c r="I2" s="10">
+      <c r="I2" s="11">
         <v>20</v>
       </c>
     </row>
@@ -2528,37 +2589,37 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="12" t="s">
+      <c r="A1" s="13" t="s">
         <v>37</v>
       </c>
-      <c r="B1" s="12" t="s">
+      <c r="B1" s="13" t="s">
         <v>38</v>
       </c>
-      <c r="C1" s="12" t="s">
+      <c r="C1" s="13" t="s">
         <v>41</v>
       </c>
-      <c r="D1" s="12" t="s">
+      <c r="D1" s="13" t="s">
         <v>40</v>
       </c>
-      <c r="E1" s="12" t="s">
+      <c r="E1" s="13" t="s">
         <v>39</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="13">
-        <v>0.2448</v>
-      </c>
-      <c r="B2" s="13">
-        <v>0.1208</v>
-      </c>
-      <c r="C2" s="13">
-        <v>0.0245</v>
-      </c>
-      <c r="D2" s="13">
-        <v>0.0054</v>
-      </c>
-      <c r="E2" s="13">
-        <v>-0.2213</v>
+      <c r="A2" s="14">
+        <v>0.2411</v>
+      </c>
+      <c r="B2" s="14">
+        <v>0.1256</v>
+      </c>
+      <c r="C2" s="14">
+        <v>0.0216</v>
+      </c>
+      <c r="D2" s="14">
+        <v>0.0023</v>
+      </c>
+      <c r="E2" s="14">
+        <v>-0.2221</v>
       </c>
     </row>
   </sheetData>
